--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -575,45 +575,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>18.7</v>
+        <v>17</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.5149</v>
+        <v>0.4713</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3498</v>
+        <v>0.3487</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.165</v>
+        <v>0.1226</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0429</v>
+        <v>0.0455</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1.198</v>
+        <v>1.26</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1.071</v>
+        <v>1</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.263</v>
+        <v>0.222</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.907</v>
+        <v>0.8837</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.6824</v>
+        <v>0.6014</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>33 of 149</t>
+          <t>40 of 149</t>
         </is>
       </c>
     </row>
@@ -623,45 +623,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>17</v>
+        <v>15.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4944</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3487</v>
+        <v>0.3858</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1226</v>
+        <v>0.1086</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0455</v>
+        <v>0.0328</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.26</v>
+        <v>1.158</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1</v>
+        <v>1.239</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.222</v>
+        <v>0.323</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.8605</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.5743</v>
+        <v>0.5541</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>43 of 149</t>
+          <t>46 of 149</t>
         </is>
       </c>
     </row>
@@ -671,45 +671,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>19.7</v>
+        <v>11.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4636</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.3837</v>
+        <v>0.3576</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1163</v>
+        <v>0.106</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0253</v>
+        <v>0.0233</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.132</v>
+        <v>1.017</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1.169</v>
+        <v>0.706</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.293</v>
+        <v>0.172</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.6419</v>
+        <v>0.527</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37 of 149</t>
+          <t>50 of 149</t>
         </is>
       </c>
     </row>
@@ -719,45 +719,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Hunter Greene</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>17.3</v>
+        <v>18.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4749</v>
+        <v>0.4618</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3398</v>
+        <v>0.3282</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1351</v>
+        <v>0.1336</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0533</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.263</v>
+        <v>1.313</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.327</v>
+        <v>1.255</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.308</v>
+        <v>0.283</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.7442</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.5541</v>
+        <v>0.5068</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47 of 149</t>
+          <t>53 of 149</t>
         </is>
       </c>
     </row>
@@ -767,45 +767,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11.3</v>
+        <v>15.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4636</v>
+        <v>0.4773</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3576</v>
+        <v>0.3561</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.106</v>
+        <v>0.1212</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0233</v>
+        <v>0.0635</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.017</v>
+        <v>1.318</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.706</v>
+        <v>1.174</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.172</v>
+        <v>0.255</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7907</v>
+        <v>0.7209</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.5676</v>
+        <v>0.4865</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44 of 149</t>
+          <t>57 of 149</t>
         </is>
       </c>
     </row>
@@ -815,45 +815,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18.3</v>
+        <v>12.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4618</v>
+        <v>0.4717</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3282</v>
+        <v>0.3821</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1336</v>
+        <v>0.0896</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0533</v>
+        <v>0.0417</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.313</v>
+        <v>1.307</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.255</v>
+        <v>1.026</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.283</v>
+        <v>0.214</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.7209</v>
+        <v>0.6977</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.4797</v>
+        <v>0.4392</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55 of 149</t>
+          <t>65 of 149</t>
         </is>
       </c>
     </row>
@@ -863,45 +863,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Javier Assad</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15.3</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4773</v>
+        <v>0.4678</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3561</v>
+        <v>0.3684</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1212</v>
+        <v>0.0994</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0635</v>
+        <v>0.0244</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.318</v>
+        <v>1.327</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.174</v>
+        <v>1.4</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.255</v>
+        <v>0.333</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>0.6977</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.4527</v>
+        <v>0.473</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60 of 149</t>
+          <t>59 of 149</t>
         </is>
       </c>
     </row>
@@ -911,45 +911,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>20.3</v>
+        <v>22.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4377</v>
+        <v>0.4694</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3488</v>
+        <v>0.3806</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.089</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.038</v>
+        <v>0.023</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.32</v>
+        <v>1.096</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.131</v>
+        <v>1.015</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.263</v>
+        <v>0.264</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>0.6744</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.4392</v>
+        <v>0.4324</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>63 of 149</t>
+          <t>66 of 149</t>
         </is>
       </c>
     </row>
@@ -959,45 +959,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>22.7</v>
+        <v>13</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4694</v>
+        <v>0.4643</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3806</v>
+        <v>0.3661</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0982</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0833</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.096</v>
+        <v>1.345</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.015</v>
+        <v>1.615</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.264</v>
+        <v>0.333</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.6744</v>
+        <v>0.6512</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.4595</v>
+        <v>0.4257</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57 of 149</t>
+          <t>68 of 149</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Javier Assad</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1017,25 +1017,25 @@
         <v>10</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4545</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3706</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.0839</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.025</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.327</v>
+        <v>1.272</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>0.6512</v>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67 of 149</t>
+          <t>69 of 149</t>
         </is>
       </c>
     </row>
@@ -1055,45 +1055,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.5204</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.3234</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0839</v>
+        <v>0.197</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0625</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.272</v>
+        <v>1.352</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1</v>
+        <v>1.188</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6512</v>
+        <v>0.6279</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.4324</v>
+        <v>0.4189</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65 of 149</t>
+          <t>70 of 149</t>
         </is>
       </c>
     </row>
@@ -1103,45 +1103,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13</v>
+        <v>24.7</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4485</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3661</v>
+        <v>0.3536</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0982</v>
+        <v>0.095</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0297</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.345</v>
+        <v>1.379</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.615</v>
+        <v>1.257</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.333</v>
+        <v>0.274</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6047</v>
+        <v>0.5814</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.3986</v>
+        <v>0.3514</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>71 of 149</t>
+          <t>81 of 149</t>
         </is>
       </c>
     </row>
@@ -1185,11 +1185,11 @@
         <v>0.5814</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.3649</v>
+        <v>0.3919</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76 of 149</t>
+          <t>73 of 149</t>
         </is>
       </c>
     </row>
@@ -1199,45 +1199,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5204</v>
+        <v>0.4778</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3234</v>
+        <v>0.3481</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.197</v>
+        <v>0.1296</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.0417</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.352</v>
+        <v>1.384</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.188</v>
+        <v>1.56</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.25</v>
+        <v>0.347</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.5814</v>
+        <v>0.5349</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.3919</v>
+        <v>0.3176</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>73 of 149</t>
+          <t>85 of 149</t>
         </is>
       </c>
     </row>
@@ -1247,41 +1247,41 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>16.7</v>
+        <v>23.7</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4778</v>
+        <v>0.441</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3481</v>
+        <v>0.3792</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1296</v>
+        <v>0.0618</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.022</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.384</v>
+        <v>1.226</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.56</v>
+        <v>1.014</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.347</v>
+        <v>0.246</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.3041</v>
+        <v>0.2973</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1295,41 +1295,41 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Hunter Greene</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>23.7</v>
+        <v>11.3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.441</v>
+        <v>0.4386</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3792</v>
+        <v>0.3567</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.0618</v>
+        <v>0.0819</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.022</v>
+        <v>0.0192</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>1.226</v>
+        <v>1.404</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.014</v>
+        <v>1.676</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.246</v>
+        <v>0.35</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>0.5116000000000001</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.2838</v>
+        <v>0.2905</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>0.294</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4884</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>0.2838</v>
@@ -1425,11 +1425,11 @@
         <v>0.4419</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.2365</v>
+        <v>0.2432</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>99 of 149</t>
+          <t>96 of 149</t>
         </is>
       </c>
     </row>
@@ -1473,11 +1473,11 @@
         <v>0.4186</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.2297</v>
+        <v>0.2365</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>101 of 149</t>
+          <t>97 of 149</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Martin Perez</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1497,35 +1497,35 @@
         <v>19</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4626</v>
+        <v>0.4403</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3822</v>
+        <v>0.3881</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.0805</v>
+        <v>0.0522</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.0137</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.445</v>
+        <v>1.34</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.737</v>
+        <v>0.947</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.37</v>
+        <v>0.188</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>0.3953</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.2095</v>
+        <v>0.2365</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>104 of 149</t>
+          <t>98 of 149</t>
         </is>
       </c>
     </row>
@@ -1535,45 +1535,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Martin Perez</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4403</v>
+        <v>0.4726</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3881</v>
+        <v>0.3562</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.0522</v>
+        <v>0.1164</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0137</v>
+        <v>0.025</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.34</v>
+        <v>1.493</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.947</v>
+        <v>2.125</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.188</v>
+        <v>0.423</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.3953</v>
+        <v>0.3488</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.2162</v>
+        <v>0.1622</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>103 of 149</t>
+          <t>110 of 149</t>
         </is>
       </c>
     </row>
@@ -1614,14 +1614,14 @@
         <v>0.267</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.3488</v>
+        <v>0.3256</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.1824</v>
+        <v>0.1892</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>110 of 149</t>
+          <t>105 of 149</t>
         </is>
       </c>
     </row>
@@ -1631,45 +1631,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>German Marquez</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.4208</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3889</v>
+        <v>0.3756</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0452</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.414</v>
+        <v>1.461</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.875</v>
+        <v>1.188</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.3256</v>
+        <v>0.3023</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.1757</v>
+        <v>0.1824</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>111 of 149</t>
+          <t>106 of 149</t>
         </is>
       </c>
     </row>
@@ -1679,45 +1679,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Luinder Avila</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>13.3</v>
+        <v>20.3</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4642</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.4126</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0516</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.033</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.535</v>
+        <v>1.509</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.575</v>
+        <v>1.82</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.3</v>
+        <v>0.409</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.3256</v>
+        <v>0.2791</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.1486</v>
+        <v>0.1351</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>113 of 149</t>
+          <t>114 of 149</t>
         </is>
       </c>
     </row>
@@ -1727,41 +1727,41 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Luinder Avila</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.44</v>
+        <v>0.443</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3908</v>
+        <v>0.3904</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.0526</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0238</v>
+        <v>0.0167</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.536</v>
+        <v>1.535</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.552</v>
+        <v>1.575</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.3023</v>
+        <v>0.2558</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.1419</v>
+        <v>0.1284</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1775,45 +1775,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>15</v>
+        <v>19.3</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4251</v>
+        <v>0.44</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3846</v>
+        <v>0.3908</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.0492</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.0238</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.496</v>
+        <v>1.536</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.667</v>
+        <v>1.552</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.356</v>
+        <v>0.31</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.2558</v>
+        <v>0.2326</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.1351</v>
+        <v>0.1216</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>116 of 149</t>
+          <t>117 of 149</t>
         </is>
       </c>
     </row>
@@ -1823,45 +1823,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Reynaldo Lopez</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.4436</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.4023</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.0414</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0435</v>
+        <v>0.0299</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.261</v>
+        <v>1.368</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.8</v>
+        <v>1.312</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.429</v>
+        <v>0.279</v>
       </c>
       <c r="L28" s="8" t="n">
         <v>0.2326</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1284</v>
+        <v>0.1486</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>117 of 149</t>
+          <t>111 of 149</t>
         </is>
       </c>
     </row>
@@ -1902,14 +1902,14 @@
         <v>0.325</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.2326</v>
+        <v>0.2093</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1081</v>
+        <v>0.0878</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>121 of 149</t>
+          <t>126 of 149</t>
         </is>
       </c>
     </row>
@@ -1919,45 +1919,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>15</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4437</v>
+        <v>0.4251</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.404</v>
+        <v>0.3846</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0397</v>
+        <v>0.0405</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.0462</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.295</v>
+        <v>1.496</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.393</v>
+        <v>1.667</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.286</v>
+        <v>0.356</v>
       </c>
       <c r="L30" s="8" t="n">
         <v>0.2093</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1216</v>
+        <v>0.1419</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>118 of 149</t>
+          <t>112 of 149</t>
         </is>
       </c>
     </row>
@@ -1967,45 +1967,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Reynaldo Lopez</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4335</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3931</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.1131</v>
+        <v>0.0405</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.0435</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.596</v>
+        <v>1.261</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.367</v>
+        <v>0.429</v>
       </c>
       <c r="L31" s="8" t="n">
         <v>0.186</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.0743</v>
+        <v>0.1351</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>129 of 149</t>
+          <t>113 of 149</t>
         </is>
       </c>
     </row>
@@ -2015,45 +2015,45 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4327</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3926</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.0401</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0106</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>1.59</v>
+        <v>1.446</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.867</v>
+        <v>1.208</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.351</v>
+        <v>0.265</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.186</v>
+        <v>0.1628</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.0743</v>
+        <v>0.1284</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>130 of 149</t>
+          <t>116 of 149</t>
         </is>
       </c>
     </row>
@@ -2063,45 +2063,45 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>10.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4094</v>
+        <v>0.4643</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.4027</v>
+        <v>0.3512</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.0067</v>
+        <v>0.1131</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0</v>
+        <v>0.0682</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>1.539</v>
+        <v>1.596</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.406</v>
+        <v>2.16</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.29</v>
+        <v>0.367</v>
       </c>
       <c r="L33" s="8" t="n">
         <v>0.1628</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0608</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>131 of 149</t>
+          <t>132 of 149</t>
         </is>
       </c>
     </row>
@@ -2142,14 +2142,14 @@
         <v>0.463</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.1628</v>
+        <v>0.1395</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0541</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>132 of 149</t>
+          <t>134 of 149</t>
         </is>
       </c>
     </row>
@@ -2159,45 +2159,45 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Mason Barnett</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>21.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4474</v>
+        <v>0.4437</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3934</v>
+        <v>0.404</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.0541</v>
+        <v>0.0397</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0337</v>
+        <v>0.0732</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>1.613</v>
+        <v>1.295</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.477</v>
+        <v>1.393</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.291</v>
+        <v>0.286</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>0.1395</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.0608</v>
+        <v>0.1216</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>134 of 149</t>
+          <t>118 of 149</t>
         </is>
       </c>
     </row>
@@ -2207,45 +2207,45 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>18</v>
+        <v>21.7</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.416</v>
+        <v>0.4474</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.4122</v>
+        <v>0.3934</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.0038</v>
+        <v>0.0541</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0</v>
+        <v>0.0337</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>1.541</v>
+        <v>1.613</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.278</v>
+        <v>1.477</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.275</v>
+        <v>0.291</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.1395</v>
+        <v>0.1163</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.0541</v>
+        <v>0.0473</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>135 of 149</t>
+          <t>136 of 149</t>
         </is>
       </c>
     </row>
@@ -2255,32 +2255,32 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Miles Mikolas</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>12.3</v>
+        <v>15</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.3827</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.3704</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0123</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>1.494</v>
+        <v>1.59</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.784</v>
+        <v>1.867</v>
       </c>
       <c r="K37" s="7" t="n">
         <v>0.351</v>
@@ -2289,11 +2289,11 @@
         <v>0.1163</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.0541</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>139 of 149</t>
+          <t>135 of 149</t>
         </is>
       </c>
     </row>
@@ -2303,45 +2303,45 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Carson Whisenhunt</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4579</v>
+        <v>0.4091</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.4182</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.0607</v>
+        <v>-0.0091</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.0345</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>1.635</v>
+        <v>1.494</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>2.229</v>
+        <v>1.784</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.438</v>
+        <v>0.351</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.1163</v>
+        <v>0.093</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.0541</v>
+        <v>0.0338</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>136 of 149</t>
+          <t>141 of 149</t>
         </is>
       </c>
     </row>
@@ -2351,45 +2351,45 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Carson Whisenhunt</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>16.7</v>
+        <v>11.7</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4579</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.3972</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0607</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0517</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1.413</v>
+        <v>1.635</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.56</v>
+        <v>2.229</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.333</v>
+        <v>0.438</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>0.093</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0405</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>142 of 149</t>
+          <t>139 of 149</t>
         </is>
       </c>
     </row>
@@ -2399,45 +2399,45 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Randy Vasquez</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4336</v>
+        <v>0.4167</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3628</v>
+        <v>0.4263</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.0708</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1.669</v>
+        <v>1.413</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.12</v>
+        <v>0.333</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.093</v>
+        <v>0.0698</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.027</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>140 of 149</t>
+          <t>142 of 149</t>
         </is>
       </c>
     </row>
@@ -2447,45 +2447,45 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Randy Vasquez</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>10.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4155</v>
+        <v>0.4336</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3732</v>
+        <v>0.3628</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.0423</v>
+        <v>0.0708</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.805</v>
+        <v>1.669</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>0.968</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.107</v>
+        <v>0.12</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.0465</v>
+        <v>0.0698</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.0135</v>
+        <v>0.027</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>145 of 149</t>
+          <t>143 of 149</t>
         </is>
       </c>
     </row>
@@ -2495,41 +2495,41 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4275</v>
+        <v>0.4155</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.4431</v>
+        <v>0.3732</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>-0.0157</v>
+        <v>0.0423</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0455</v>
+        <v>0.0769</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.826</v>
+        <v>1.805</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>2.023</v>
+        <v>0.968</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.375</v>
+        <v>0.107</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.0233</v>
+        <v>0.0465</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.0068</v>
+        <v>0.0135</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>144 of 149</t>
+          <t>145 of 149</t>
         </is>
       </c>
     </row>
@@ -2591,35 +2591,35 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>17.3</v>
+        <v>10.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.3917</v>
+        <v>0.401</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.4459</v>
+        <v>0.4213</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>-0.0541</v>
+        <v>-0.0203</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0408</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.78</v>
+        <v>1.892</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.788</v>
+        <v>2.032</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.294</v>
+        <v>0.333</v>
       </c>
       <c r="L44" s="8" t="n">
         <v>0</v>
@@ -2639,35 +2639,35 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.401</v>
+        <v>0.3822</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.4213</v>
+        <v>0.4444</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>-0.0203</v>
+        <v>-0.0622</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0408</v>
+        <v>0.05</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.892</v>
+        <v>1.844</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>2.032</v>
+        <v>2.108</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>0</v>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -575,47 +575,41 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Cade Povich</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.5172</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3487</v>
+        <v>0.3218</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1226</v>
+        <v>0.1954</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0455</v>
+        <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1.26</v>
+        <v>0.788</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.222</v>
+        <v>0.5</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.8837</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>0.6014</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>40 of 149</t>
-        </is>
-      </c>
+        <v>0.9787</v>
+      </c>
+      <c r="M2" s="8" t="n"/>
+      <c r="N2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -623,45 +617,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>15.3</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.4944</v>
+        <v>0.4805</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3858</v>
+        <v>0.3514</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1086</v>
+        <v>0.1291</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0328</v>
+        <v>0.0345</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.158</v>
+        <v>1.216</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.239</v>
+        <v>1.7</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.323</v>
+        <v>0.436</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.8723</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.5541</v>
+        <v>0.6419</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>46 of 149</t>
+          <t>37 of 149</t>
         </is>
       </c>
     </row>
@@ -671,45 +665,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11.3</v>
+        <v>17</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.4636</v>
+        <v>0.4713</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.3576</v>
+        <v>0.3487</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.106</v>
+        <v>0.1226</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0233</v>
+        <v>0.0455</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.017</v>
+        <v>1.26</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>0.706</v>
+        <v>1</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.172</v>
+        <v>0.222</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8298</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.527</v>
+        <v>0.6014</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50 of 149</t>
+          <t>40 of 149</t>
         </is>
       </c>
     </row>
@@ -719,45 +713,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4618</v>
+        <v>0.4944</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3282</v>
+        <v>0.3858</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1336</v>
+        <v>0.1086</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0533</v>
+        <v>0.0328</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.313</v>
+        <v>1.158</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.255</v>
+        <v>1.239</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.283</v>
+        <v>0.323</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.7442</v>
+        <v>0.7872</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.5068</v>
+        <v>0.5541</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53 of 149</t>
+          <t>46 of 149</t>
         </is>
       </c>
     </row>
@@ -767,45 +761,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>15.3</v>
+        <v>11.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4773</v>
+        <v>0.4636</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3561</v>
+        <v>0.3576</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1212</v>
+        <v>0.106</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0635</v>
+        <v>0.0233</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.318</v>
+        <v>1.017</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.174</v>
+        <v>0.706</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.255</v>
+        <v>0.172</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7209</v>
+        <v>0.766</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.4865</v>
+        <v>0.527</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57 of 149</t>
+          <t>50 of 149</t>
         </is>
       </c>
     </row>
@@ -815,45 +809,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12.7</v>
+        <v>18.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4717</v>
+        <v>0.4618</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3821</v>
+        <v>0.3282</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0896</v>
+        <v>0.1336</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0533</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.307</v>
+        <v>1.313</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.026</v>
+        <v>1.255</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.214</v>
+        <v>0.283</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.6977</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.4392</v>
+        <v>0.5068</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>65 of 149</t>
+          <t>53 of 149</t>
         </is>
       </c>
     </row>
@@ -863,45 +857,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Javier Assad</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10</v>
+        <v>15.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4773</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3561</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1212</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0635</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.327</v>
+        <v>1.318</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.4</v>
+        <v>1.174</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.333</v>
+        <v>0.255</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.6977</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.473</v>
+        <v>0.4865</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59 of 149</t>
+          <t>57 of 149</t>
         </is>
       </c>
     </row>
@@ -911,45 +905,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>22.7</v>
+        <v>12.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4694</v>
+        <v>0.4717</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3806</v>
+        <v>0.3821</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0896</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0417</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.096</v>
+        <v>1.307</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.015</v>
+        <v>1.026</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.264</v>
+        <v>0.214</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.6744</v>
+        <v>0.6596</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.4324</v>
+        <v>0.4392</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66 of 149</t>
+          <t>65 of 149</t>
         </is>
       </c>
     </row>
@@ -959,45 +953,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Javier Assad</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4678</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3661</v>
+        <v>0.3684</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0982</v>
+        <v>0.0994</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0244</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.345</v>
+        <v>1.327</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.615</v>
+        <v>1.4</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>0.333</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.6512</v>
+        <v>0.6596</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.4257</v>
+        <v>0.473</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68 of 149</t>
+          <t>59 of 149</t>
         </is>
       </c>
     </row>
@@ -1007,45 +1001,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10</v>
+        <v>22.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.4694</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.3806</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0839</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.272</v>
+        <v>1.096</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1</v>
+        <v>1.015</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.2</v>
+        <v>0.264</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6512</v>
+        <v>0.6383</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.4257</v>
+        <v>0.4324</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69 of 149</t>
+          <t>66 of 149</t>
         </is>
       </c>
     </row>
@@ -1055,45 +1049,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.5204</v>
+        <v>0.4643</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3234</v>
+        <v>0.3661</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.197</v>
+        <v>0.0982</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.0833</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.352</v>
+        <v>1.345</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.188</v>
+        <v>1.615</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6279</v>
+        <v>0.617</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.4189</v>
+        <v>0.4257</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70 of 149</t>
+          <t>68 of 149</t>
         </is>
       </c>
     </row>
@@ -1103,45 +1097,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24.7</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4485</v>
+        <v>0.4545</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3536</v>
+        <v>0.3706</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.095</v>
+        <v>0.0839</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.025</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.379</v>
+        <v>1.272</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.257</v>
+        <v>1</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.274</v>
+        <v>0.2</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.5814</v>
+        <v>0.617</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.3514</v>
+        <v>0.4257</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81 of 149</t>
+          <t>69 of 149</t>
         </is>
       </c>
     </row>
@@ -1151,45 +1145,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12.3</v>
+        <v>16</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4412</v>
+        <v>0.5204</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3647</v>
+        <v>0.3234</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0765</v>
+        <v>0.197</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0625</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.308</v>
+        <v>1.352</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.054</v>
+        <v>1.188</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.235</v>
+        <v>0.25</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.5814</v>
+        <v>0.5957</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.3919</v>
+        <v>0.4189</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73 of 149</t>
+          <t>70 of 149</t>
         </is>
       </c>
     </row>
@@ -1199,47 +1193,41 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16.7</v>
+        <v>5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4778</v>
+        <v>0.4583</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3481</v>
+        <v>0.375</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1296</v>
+        <v>0.0833</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.384</v>
+        <v>1.184</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.347</v>
+        <v>0.353</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.5349</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>0.3176</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>85 of 149</t>
-        </is>
-      </c>
+        <v>0.5957</v>
+      </c>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1247,45 +1235,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>23.7</v>
+        <v>24.7</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.441</v>
+        <v>0.4485</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3792</v>
+        <v>0.3536</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0618</v>
+        <v>0.095</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.022</v>
+        <v>0.0297</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.226</v>
+        <v>1.379</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.014</v>
+        <v>1.257</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.246</v>
+        <v>0.274</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5532</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.2973</v>
+        <v>0.3514</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88 of 149</t>
+          <t>81 of 149</t>
         </is>
       </c>
     </row>
@@ -1293,47 +1281,47 @@
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Hunter Greene</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4386</v>
+        <v>0.4412</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3567</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>0.0819</v>
+        <v>0.3647</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.0765</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0192</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>1.404</v>
+        <v>0.0417</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>1.308</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.676</v>
+        <v>1.054</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.35</v>
+        <v>0.235</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5319</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.2905</v>
+        <v>0.3919</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91 of 149</t>
+          <t>73 of 149</t>
         </is>
       </c>
     </row>
@@ -1343,45 +1331,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Jack Perkins</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>19</v>
+        <v>16.7</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4473</v>
+        <v>0.4778</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3738</v>
+        <v>0.3481</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>0.0735</v>
+        <v>0.1296</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0595</v>
+        <v>0.0417</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>1.408</v>
+        <v>1.384</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.474</v>
+        <v>1.56</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.294</v>
+        <v>0.347</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.4884</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.2838</v>
+        <v>0.3176</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92 of 149</t>
+          <t>85 of 149</t>
         </is>
       </c>
     </row>
@@ -1391,45 +1379,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Hunter Greene</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>14.7</v>
+        <v>11.3</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4567</v>
+        <v>0.4386</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3976</v>
+        <v>0.3567</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.0819</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0303</v>
+        <v>0.0192</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>1.436</v>
+        <v>1.404</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.636</v>
+        <v>1.676</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.341</v>
+        <v>0.35</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.4419</v>
+        <v>0.4894</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.2432</v>
+        <v>0.2905</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>96 of 149</t>
+          <t>91 of 149</t>
         </is>
       </c>
     </row>
@@ -1439,45 +1427,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>22</v>
+        <v>23.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4419</v>
+        <v>0.441</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3613</v>
+        <v>0.3792</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>0.0806</v>
+        <v>0.0618</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>1.438</v>
+        <v>1.226</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.182</v>
+        <v>1.014</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.288</v>
+        <v>0.246</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.4186</v>
+        <v>0.4681</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.2365</v>
+        <v>0.2973</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97 of 149</t>
+          <t>88 of 149</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1475,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Martin Perez</t>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1497,35 +1485,35 @@
         <v>19</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4403</v>
+        <v>0.4473</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3881</v>
+        <v>0.3738</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.0522</v>
+        <v>0.0735</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0137</v>
+        <v>0.0595</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.34</v>
+        <v>1.408</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.947</v>
+        <v>1.474</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.188</v>
+        <v>0.294</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.3953</v>
+        <v>0.4681</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.2365</v>
+        <v>0.2838</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>98 of 149</t>
+          <t>92 of 149</t>
         </is>
       </c>
     </row>
@@ -1535,45 +1523,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8</v>
+        <v>14.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4726</v>
+        <v>0.4567</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3562</v>
+        <v>0.3976</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.1164</v>
+        <v>0.0591</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0303</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.493</v>
+        <v>1.436</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>2.125</v>
+        <v>1.636</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.423</v>
+        <v>0.341</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.3488</v>
+        <v>0.4255</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.1622</v>
+        <v>0.2432</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>110 of 149</t>
+          <t>96 of 149</t>
         </is>
       </c>
     </row>
@@ -1583,45 +1571,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>13.3</v>
+        <v>22</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4419</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3613</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0806</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.1</v>
+        <v>0.025</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.136</v>
+        <v>1.438</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.05</v>
+        <v>1.182</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.267</v>
+        <v>0.288</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.3256</v>
+        <v>0.4043</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.1892</v>
+        <v>0.2365</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>105 of 149</t>
+          <t>97 of 149</t>
         </is>
       </c>
     </row>
@@ -1631,45 +1619,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Martin Perez</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.4403</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3756</v>
+        <v>0.3881</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0522</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.461</v>
+        <v>1.34</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.188</v>
+        <v>0.947</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.25</v>
+        <v>0.188</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.3023</v>
+        <v>0.3617</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.1824</v>
+        <v>0.2365</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>106 of 149</t>
+          <t>98 of 149</t>
         </is>
       </c>
     </row>
@@ -1679,45 +1667,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>20.3</v>
+        <v>8</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4642</v>
+        <v>0.4726</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4126</v>
+        <v>0.3562</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.0516</v>
+        <v>0.1164</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.033</v>
+        <v>0.025</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.509</v>
+        <v>1.493</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.82</v>
+        <v>2.125</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.409</v>
+        <v>0.423</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.2791</v>
+        <v>0.3404</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.1351</v>
+        <v>0.1622</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>114 of 149</t>
+          <t>110 of 149</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1715,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Luinder Avila</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -1737,35 +1725,35 @@
         <v>13.3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4444</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.3981</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0463</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.1</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.535</v>
+        <v>1.136</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.575</v>
+        <v>1.05</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.2558</v>
+        <v>0.2979</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.1284</v>
+        <v>0.1892</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>115 of 149</t>
+          <t>105 of 149</t>
         </is>
       </c>
     </row>
@@ -1775,45 +1763,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>19.3</v>
+        <v>16</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.44</v>
+        <v>0.4208</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3908</v>
+        <v>0.3756</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.0452</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0238</v>
+        <v>0</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.536</v>
+        <v>1.461</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.552</v>
+        <v>1.188</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.2326</v>
+        <v>0.2766</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.1216</v>
+        <v>0.1824</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>117 of 149</t>
+          <t>106 of 149</t>
         </is>
       </c>
     </row>
@@ -1823,45 +1811,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>16</v>
+        <v>20.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4436</v>
+        <v>0.4626</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4023</v>
+        <v>0.4138</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0414</v>
+        <v>0.0489</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0299</v>
+        <v>0.0333</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.368</v>
+        <v>1.511</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.312</v>
+        <v>1.82</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.279</v>
+        <v>0.419</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.2326</v>
+        <v>0.2766</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1486</v>
+        <v>0.1351</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>111 of 149</t>
+          <t>114 of 149</t>
         </is>
       </c>
     </row>
@@ -1871,45 +1859,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Luinder Avila</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.451</v>
+        <v>0.443</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3904</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.0526</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0167</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.578</v>
+        <v>1.535</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.756</v>
+        <v>1.575</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.325</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.2093</v>
+        <v>0.2553</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.0878</v>
+        <v>0.1284</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>126 of 149</t>
+          <t>115 of 149</t>
         </is>
       </c>
     </row>
@@ -1919,45 +1907,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>15</v>
+        <v>19.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4251</v>
+        <v>0.44</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3846</v>
+        <v>0.3908</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.0492</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.0238</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.496</v>
+        <v>1.536</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.667</v>
+        <v>1.552</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.356</v>
+        <v>0.31</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.2093</v>
+        <v>0.234</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1419</v>
+        <v>0.1216</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>112 of 149</t>
+          <t>117 of 149</t>
         </is>
       </c>
     </row>
@@ -1967,45 +1955,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Reynaldo Lopez</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>10</v>
+        <v>13.7</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.451</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.4078</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.0431</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0435</v>
+        <v>0.0312</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.261</v>
+        <v>1.578</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.8</v>
+        <v>1.756</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.429</v>
+        <v>0.325</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.186</v>
+        <v>0.2128</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.1351</v>
+        <v>0.0878</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>113 of 149</t>
+          <t>126 of 149</t>
         </is>
       </c>
     </row>
@@ -2013,47 +2001,47 @@
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>Seth Lugo</t>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4327</v>
+        <v>0.4436</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3926</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>0.0401</v>
+        <v>0.4023</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>0.0414</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0106</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>1.446</v>
+        <v>0.0299</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>1.368</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.208</v>
+        <v>1.312</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.265</v>
+        <v>0.279</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.1628</v>
+        <v>0.2128</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.1284</v>
+        <v>0.1486</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>116 of 149</t>
+          <t>111 of 149</t>
         </is>
       </c>
     </row>
@@ -2061,47 +2049,47 @@
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Slade Cecconi</t>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>15</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4251</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3512</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.3846</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>0.0405</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0682</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>1.596</v>
+        <v>0.0462</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>1.496</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>2.16</v>
+        <v>1.667</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.367</v>
+        <v>0.356</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.1628</v>
+        <v>0.1915</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.0608</v>
+        <v>0.1419</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>132 of 149</t>
+          <t>112 of 149</t>
         </is>
       </c>
     </row>
@@ -2111,47 +2099,41 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>10.7</v>
+        <v>5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.465</v>
+        <v>0.4891</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3663</v>
+        <v>0.3696</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.0988</v>
+        <v>0.1196</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0536</v>
+        <v>0</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>1.609</v>
+        <v>1.589</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>2.531</v>
+        <v>1.8</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.463</v>
+        <v>0.375</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.1395</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>0.0541</v>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>134 of 149</t>
-        </is>
-      </c>
+        <v>0.1915</v>
+      </c>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2159,45 +2141,45 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>Reynaldo Lopez</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4437</v>
+        <v>0.4335</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.404</v>
+        <v>0.3931</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.0397</v>
+        <v>0.0405</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.0435</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>1.295</v>
+        <v>1.261</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.393</v>
+        <v>1.8</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.286</v>
+        <v>0.429</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.1395</v>
+        <v>0.1702</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.1216</v>
+        <v>0.1351</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>118 of 149</t>
+          <t>113 of 149</t>
         </is>
       </c>
     </row>
@@ -2207,45 +2189,45 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>21.7</v>
+        <v>24</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.4474</v>
+        <v>0.4327</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3934</v>
+        <v>0.3926</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.0541</v>
+        <v>0.0401</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0337</v>
+        <v>0.0106</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>1.613</v>
+        <v>1.446</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.477</v>
+        <v>1.208</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.291</v>
+        <v>0.265</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.1163</v>
+        <v>0.1489</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.0473</v>
+        <v>0.1284</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>136 of 149</t>
+          <t>116 of 149</t>
         </is>
       </c>
     </row>
@@ -2255,45 +2237,45 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4643</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3512</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.1131</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0682</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>1.59</v>
+        <v>1.596</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.867</v>
+        <v>2.16</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.351</v>
+        <v>0.367</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.1163</v>
+        <v>0.1489</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.0541</v>
+        <v>0.0608</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>135 of 149</t>
+          <t>132 of 149</t>
         </is>
       </c>
     </row>
@@ -2303,45 +2285,45 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>12.3</v>
+        <v>10.7</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.465</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.3663</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0988</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0536</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>1.494</v>
+        <v>1.609</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.784</v>
+        <v>2.531</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.351</v>
+        <v>0.463</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.093</v>
+        <v>0.1277</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0541</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>141 of 149</t>
+          <t>134 of 149</t>
         </is>
       </c>
     </row>
@@ -2351,45 +2333,45 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Carson Whisenhunt</t>
+          <t>Mason Barnett</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>11.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4579</v>
+        <v>0.4437</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.404</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.0607</v>
+        <v>0.0397</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.0732</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1.635</v>
+        <v>1.295</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>2.229</v>
+        <v>1.393</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.438</v>
+        <v>0.286</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.093</v>
+        <v>0.1277</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.1216</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>139 of 149</t>
+          <t>118 of 149</t>
         </is>
       </c>
     </row>
@@ -2399,45 +2381,45 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>16.7</v>
+        <v>21.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4474</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.3934</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0541</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0337</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1.413</v>
+        <v>1.613</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.56</v>
+        <v>1.477</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.333</v>
+        <v>0.291</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.0698</v>
+        <v>0.1064</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0473</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>142 of 149</t>
+          <t>136 of 149</t>
         </is>
       </c>
     </row>
@@ -2447,45 +2429,45 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Randy Vasquez</t>
+          <t>Miles Mikolas</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>15</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4336</v>
+        <v>0.3827</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3628</v>
+        <v>0.3704</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.0708</v>
+        <v>0.0123</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.669</v>
+        <v>1.59</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.867</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.12</v>
+        <v>0.351</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.0698</v>
+        <v>0.1064</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0541</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>143 of 149</t>
+          <t>135 of 149</t>
         </is>
       </c>
     </row>
@@ -2495,45 +2477,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4155</v>
+        <v>0.4091</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3732</v>
+        <v>0.4182</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.0423</v>
+        <v>-0.0091</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0769</v>
+        <v>0.0345</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.805</v>
+        <v>1.494</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>0.968</v>
+        <v>1.784</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.107</v>
+        <v>0.351</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.0465</v>
+        <v>0.0851</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.0135</v>
+        <v>0.0338</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>146 of 149</t>
+          <t>141 of 149</t>
         </is>
       </c>
     </row>
@@ -2543,45 +2525,45 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Carson Whisenhunt</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>17</v>
+        <v>11.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.3874</v>
+        <v>0.4579</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.4111</v>
+        <v>0.3972</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>-0.0237</v>
+        <v>0.0607</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.0588</v>
+        <v>0.0517</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.381</v>
+        <v>1.635</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1.118</v>
+        <v>2.229</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.235</v>
+        <v>0.438</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.0233</v>
+        <v>0.0851</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.0135</v>
+        <v>0.0405</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>145 of 149</t>
+          <t>139 of 149</t>
         </is>
       </c>
     </row>
@@ -2591,45 +2573,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.401</v>
+        <v>0.4167</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.4213</v>
+        <v>0.4263</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>-0.0203</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0408</v>
+        <v>0.0411</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.892</v>
+        <v>1.413</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>2.032</v>
+        <v>1.56</v>
       </c>
       <c r="K44" s="7" t="n">
         <v>0.333</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0</v>
+        <v>0.0638</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>148 of 149</t>
+          <t>142 of 149</t>
         </is>
       </c>
     </row>
@@ -2639,101 +2621,300 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
+          <t>Randy Vasquez</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>1.669</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>143 of 149</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Jake Irvin</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>146 of 149</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Tomoyuki Sugano</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>-0.0237</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>1.381</v>
+      </c>
+      <c r="J47" s="7" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="M47" s="8" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>145 of 149</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Jeffrey Springs</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>2.032</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>148 of 149</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
           <t>Ryan Johnson</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D49" s="2" t="n">
         <v>12.3</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E49" s="4" t="n">
         <v>0.3822</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F49" s="4" t="n">
         <v>0.4444</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="G49" s="13" t="n">
         <v>-0.0622</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="I45" s="14" t="n">
+      <c r="I49" s="14" t="n">
         <v>1.844</v>
       </c>
-      <c r="J45" s="7" t="n">
+      <c r="J49" s="7" t="n">
         <v>2.108</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="K49" s="7" t="n">
         <v>0.35</v>
       </c>
-      <c r="L45" s="8" t="n">
+      <c r="L49" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="8" t="n">
+      <c r="M49" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>149 of 149</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>Stoplight shading (Pitcher, CMD%, Model WHIP) reflects Score (Relative): MIN of each pitcher's percentile rank on CMD% (higher=better) and Model WHIP (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by Score (Relative) rank position.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>Score (Absolute) uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 20-day window). Rank (Absolute) shows literal rank position within that league-wide pool.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (Model WHIP inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>Stoplight shading (Pitcher, CMD%, Model WHIP) reflects Score (Relative): MIN of each pitcher's percentile rank on CMD% (higher=better) and Model WHIP (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by Score (Relative) rank position.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>Score (Absolute) uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 20-day window). Rank (Absolute) shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Model WHIP = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. Actual WHIP is real (H+BB)/IP over the same window.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="15" t="inlineStr">
         <is>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>K%, BB%, HR% (Model WHIP inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Model WHIP = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. Actual WHIP is real (H+BB)/IP over the same window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="15" t="inlineStr">
+        <is>
           <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 20-day window -- single-start genuine starters are included here. The league-wide absolute pool behind Score (Absolute)/Rank (Absolute) still requires 2+ starts, so a 1-start pitcher can appear here with a Score (Relative) but a blank Score (Absolute)/Rank (Absolute).</t>
         </is>
       </c>
     </row>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -606,7 +606,7 @@
         <v>0.5</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9787</v>
+        <v>0.9792</v>
       </c>
       <c r="M2" s="8" t="n"/>
       <c r="N2" s="2" t="n"/>
@@ -648,7 +648,7 @@
         <v>0.436</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.8723</v>
+        <v>0.8542</v>
       </c>
       <c r="M3" s="8" t="n">
         <v>0.6419</v>
@@ -696,7 +696,7 @@
         <v>0.222</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8298</v>
+        <v>0.8125</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>0.6014</v>
@@ -744,7 +744,7 @@
         <v>0.323</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.7872</v>
+        <v>0.7917</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>0.5541</v>
@@ -792,7 +792,7 @@
         <v>0.172</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.766</v>
+        <v>0.7708</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>0.527</v>
@@ -809,45 +809,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18.3</v>
+        <v>15.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4618</v>
+        <v>0.4619</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3282</v>
+        <v>0.3559</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1336</v>
+        <v>0.1059</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0533</v>
+        <v>0</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.313</v>
+        <v>1.114</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.255</v>
+        <v>1.277</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.283</v>
+        <v>0.348</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5068</v>
+        <v>0.5203</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53 of 149</t>
+          <t>51 of 149</t>
         </is>
       </c>
     </row>
@@ -857,45 +857,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4773</v>
+        <v>0.4618</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3561</v>
+        <v>0.3282</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1212</v>
+        <v>0.1336</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0635</v>
+        <v>0.0533</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.318</v>
+        <v>1.313</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.174</v>
+        <v>1.255</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.255</v>
+        <v>0.283</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6875</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.4865</v>
+        <v>0.5068</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57 of 149</t>
+          <t>53 of 149</t>
         </is>
       </c>
     </row>
@@ -905,45 +905,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4717</v>
+        <v>0.4773</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3821</v>
+        <v>0.3561</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0896</v>
+        <v>0.1212</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0635</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.307</v>
+        <v>1.318</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.026</v>
+        <v>1.174</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.214</v>
+        <v>0.255</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.6596</v>
+        <v>0.6667</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.4392</v>
+        <v>0.4865</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65 of 149</t>
+          <t>57 of 149</t>
         </is>
       </c>
     </row>
@@ -953,45 +953,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Javier Assad</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4717</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3821</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.0896</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0417</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.327</v>
+        <v>1.307</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.4</v>
+        <v>1.026</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.333</v>
+        <v>0.214</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.6596</v>
+        <v>0.6458</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.473</v>
+        <v>0.4392</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59 of 149</t>
+          <t>65 of 149</t>
         </is>
       </c>
     </row>
@@ -1001,45 +1001,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Javier Assad</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>22.7</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4694</v>
+        <v>0.4678</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3806</v>
+        <v>0.3684</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0994</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0244</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.096</v>
+        <v>1.327</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.015</v>
+        <v>1.4</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.264</v>
+        <v>0.333</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6383</v>
+        <v>0.6458</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.4324</v>
+        <v>0.473</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66 of 149</t>
+          <t>59 of 149</t>
         </is>
       </c>
     </row>
@@ -1049,45 +1049,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>13</v>
+        <v>22.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4694</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3661</v>
+        <v>0.3806</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0982</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.023</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.345</v>
+        <v>1.096</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.615</v>
+        <v>1.015</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.333</v>
+        <v>0.264</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.617</v>
+        <v>0.625</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.4257</v>
+        <v>0.4324</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68 of 149</t>
+          <t>66 of 149</t>
         </is>
       </c>
     </row>
@@ -1097,45 +1097,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.4643</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.3661</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0839</v>
+        <v>0.0982</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0833</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.272</v>
+        <v>1.345</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1</v>
+        <v>1.615</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.617</v>
+        <v>0.6042</v>
       </c>
       <c r="M13" s="8" t="n">
         <v>0.4257</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69 of 149</t>
+          <t>68 of 149</t>
         </is>
       </c>
     </row>
@@ -1145,45 +1145,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.5204</v>
+        <v>0.4545</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3234</v>
+        <v>0.3706</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.197</v>
+        <v>0.0839</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.025</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.352</v>
+        <v>1.272</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.188</v>
+        <v>1</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.5957</v>
+        <v>0.6042</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.4189</v>
+        <v>0.4257</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70 of 149</t>
+          <t>69 of 149</t>
         </is>
       </c>
     </row>
@@ -1193,41 +1193,47 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4583</v>
+        <v>0.5204</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.375</v>
+        <v>0.3234</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0833</v>
+        <v>0.197</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.184</v>
+        <v>1.352</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.4</v>
+        <v>1.188</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.353</v>
+        <v>0.25</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.5957</v>
-      </c>
-      <c r="M15" s="8" t="n"/>
-      <c r="N15" s="2" t="n"/>
+        <v>0.5833</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>70 of 149</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1235,47 +1241,41 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24.7</v>
+        <v>5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4485</v>
+        <v>0.4583</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3536</v>
+        <v>0.375</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.095</v>
+        <v>0.0833</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0297</v>
+        <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.379</v>
+        <v>1.184</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.257</v>
+        <v>1.4</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.274</v>
+        <v>0.353</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5532</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>0.3514</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>81 of 149</t>
-        </is>
-      </c>
+        <v>0.5833</v>
+      </c>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1283,45 +1283,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>12.3</v>
+        <v>24.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4412</v>
+        <v>0.4485</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3647</v>
+        <v>0.3536</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0765</v>
+        <v>0.095</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0297</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.308</v>
+        <v>1.379</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.054</v>
+        <v>1.257</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.235</v>
+        <v>0.274</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5319</v>
+        <v>0.5417</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3919</v>
+        <v>0.3514</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73 of 149</t>
+          <t>81 of 149</t>
         </is>
       </c>
     </row>
@@ -1329,47 +1329,47 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Janson Junk</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>16.7</v>
+        <v>12.3</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4778</v>
+        <v>0.4412</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3481</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>0.1296</v>
+        <v>0.3647</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.0765</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0.0417</v>
       </c>
-      <c r="I18" s="11" t="n">
-        <v>1.384</v>
+      <c r="I18" s="6" t="n">
+        <v>1.308</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.56</v>
+        <v>1.054</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.347</v>
+        <v>0.235</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5208</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3176</v>
+        <v>0.3919</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85 of 149</t>
+          <t>73 of 149</t>
         </is>
       </c>
     </row>
@@ -1379,45 +1379,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Hunter Greene</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11.3</v>
+        <v>16.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4386</v>
+        <v>0.4778</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3567</v>
+        <v>0.3481</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0.0819</v>
+        <v>0.1296</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.0417</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>1.404</v>
+        <v>1.384</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.676</v>
+        <v>1.56</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.4894</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.2905</v>
+        <v>0.3176</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>91 of 149</t>
+          <t>85 of 149</t>
         </is>
       </c>
     </row>
@@ -1427,45 +1427,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Hunter Greene</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>23.7</v>
+        <v>11.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.441</v>
+        <v>0.4386</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3792</v>
+        <v>0.3567</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>0.0618</v>
+        <v>0.0819</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.022</v>
+        <v>0.0192</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>1.226</v>
+        <v>1.404</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.014</v>
+        <v>1.676</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.246</v>
+        <v>0.35</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.4681</v>
+        <v>0.4792</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.2973</v>
+        <v>0.2905</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88 of 149</t>
+          <t>91 of 149</t>
         </is>
       </c>
     </row>
@@ -1475,45 +1475,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Jack Perkins</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>19</v>
+        <v>23.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4473</v>
+        <v>0.441</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3738</v>
+        <v>0.3792</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.0735</v>
+        <v>0.0618</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0595</v>
+        <v>0.022</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.408</v>
+        <v>1.226</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.474</v>
+        <v>1.014</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.294</v>
+        <v>0.246</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.4681</v>
+        <v>0.4583</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.2838</v>
+        <v>0.2973</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>92 of 149</t>
+          <t>88 of 149</t>
         </is>
       </c>
     </row>
@@ -1523,45 +1523,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>14.7</v>
+        <v>19</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4567</v>
+        <v>0.4473</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3976</v>
+        <v>0.3738</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.0735</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0303</v>
+        <v>0.0595</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.436</v>
+        <v>1.408</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.636</v>
+        <v>1.474</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.341</v>
+        <v>0.294</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4255</v>
+        <v>0.4583</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.2432</v>
+        <v>0.2838</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>96 of 149</t>
+          <t>92 of 149</t>
         </is>
       </c>
     </row>
@@ -1571,45 +1571,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>22</v>
+        <v>14.7</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4419</v>
+        <v>0.4567</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3613</v>
+        <v>0.3976</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0806</v>
+        <v>0.0591</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0303</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.438</v>
+        <v>1.436</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.182</v>
+        <v>1.636</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.288</v>
+        <v>0.341</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4043</v>
+        <v>0.4167</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.2365</v>
+        <v>0.2432</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97 of 149</t>
+          <t>96 of 149</t>
         </is>
       </c>
     </row>
@@ -1619,45 +1619,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Martin Perez</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4403</v>
+        <v>0.4419</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3881</v>
+        <v>0.3613</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0522</v>
+        <v>0.0806</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0137</v>
+        <v>0.025</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.34</v>
+        <v>1.438</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.947</v>
+        <v>1.182</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.188</v>
+        <v>0.288</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.3617</v>
+        <v>0.3958</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>0.2365</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>98 of 149</t>
+          <t>97 of 149</t>
         </is>
       </c>
     </row>
@@ -1667,45 +1667,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Martin Perez</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4726</v>
+        <v>0.4403</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3562</v>
+        <v>0.3881</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.1164</v>
+        <v>0.0522</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0137</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.493</v>
+        <v>1.34</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>2.125</v>
+        <v>0.947</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.423</v>
+        <v>0.188</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.3404</v>
+        <v>0.3542</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.1622</v>
+        <v>0.2365</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>110 of 149</t>
+          <t>98 of 149</t>
         </is>
       </c>
     </row>
@@ -1715,45 +1715,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>13.3</v>
+        <v>8</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4726</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3562</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.1164</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1</v>
+        <v>0.025</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.136</v>
+        <v>1.493</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.05</v>
+        <v>2.125</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.267</v>
+        <v>0.423</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.2979</v>
+        <v>0.3333</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.1892</v>
+        <v>0.1622</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>105 of 149</t>
+          <t>110 of 149</t>
         </is>
       </c>
     </row>
@@ -1763,45 +1763,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>16</v>
+        <v>13.3</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.4444</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3756</v>
+        <v>0.3981</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0463</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.461</v>
+        <v>1.136</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.188</v>
+        <v>1.05</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.2766</v>
+        <v>0.2917</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.1824</v>
+        <v>0.1892</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>106 of 149</t>
+          <t>105 of 149</t>
         </is>
       </c>
     </row>
@@ -1811,45 +1811,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>20.3</v>
+        <v>16</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4626</v>
+        <v>0.4208</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4138</v>
+        <v>0.3756</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0489</v>
+        <v>0.0452</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.511</v>
+        <v>1.461</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.82</v>
+        <v>1.188</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.419</v>
+        <v>0.25</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.2766</v>
+        <v>0.2708</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1351</v>
+        <v>0.1824</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>114 of 149</t>
+          <t>106 of 149</t>
         </is>
       </c>
     </row>
@@ -1859,45 +1859,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Luinder Avila</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13.3</v>
+        <v>20.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4626</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.4138</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0489</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0333</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.535</v>
+        <v>1.511</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.575</v>
+        <v>1.82</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.3</v>
+        <v>0.419</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.2553</v>
+        <v>0.2708</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1284</v>
+        <v>0.1351</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>115 of 149</t>
+          <t>114 of 149</t>
         </is>
       </c>
     </row>
@@ -1907,45 +1907,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Luinder Avila</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.44</v>
+        <v>0.443</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3908</v>
+        <v>0.3904</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.0526</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0238</v>
+        <v>0.0167</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.536</v>
+        <v>1.535</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.552</v>
+        <v>1.575</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.234</v>
+        <v>0.25</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1216</v>
+        <v>0.1284</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>117 of 149</t>
+          <t>115 of 149</t>
         </is>
       </c>
     </row>
@@ -1955,45 +1955,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>13.7</v>
+        <v>19.3</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.451</v>
+        <v>0.44</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3908</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.0492</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0238</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.578</v>
+        <v>1.536</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.756</v>
+        <v>1.552</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.325</v>
+        <v>0.31</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.2128</v>
+        <v>0.2292</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.0878</v>
+        <v>0.1216</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>126 of 149</t>
+          <t>117 of 149</t>
         </is>
       </c>
     </row>
@@ -2003,45 +2003,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>16</v>
+        <v>13.7</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4436</v>
+        <v>0.451</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4023</v>
+        <v>0.4078</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0414</v>
+        <v>0.0431</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0299</v>
+        <v>0.0312</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.368</v>
+        <v>1.578</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.312</v>
+        <v>1.756</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.279</v>
+        <v>0.325</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2128</v>
+        <v>0.2083</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.1486</v>
+        <v>0.0878</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>111 of 149</t>
+          <t>126 of 149</t>
         </is>
       </c>
     </row>
@@ -2051,45 +2051,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4251</v>
+        <v>0.4436</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3846</v>
+        <v>0.4023</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.0414</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.0299</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.496</v>
+        <v>1.368</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.667</v>
+        <v>1.312</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.356</v>
+        <v>0.279</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.1915</v>
+        <v>0.2083</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1419</v>
+        <v>0.1486</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>112 of 149</t>
+          <t>111 of 149</t>
         </is>
       </c>
     </row>
@@ -2097,43 +2097,49 @@
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Quinn Mathews</t>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.4251</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3696</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>0.1196</v>
+        <v>0.3846</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>0.0405</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>1.589</v>
+        <v>0.0462</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>1.496</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.375</v>
+        <v>0.356</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.1915</v>
-      </c>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="2" t="n"/>
+        <v>0.1875</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>112 of 149</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2141,47 +2147,41 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Reynaldo Lopez</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.4891</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.3696</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.0405</v>
+        <v>0.1196</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0435</v>
+        <v>0</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>1.261</v>
+        <v>1.589</v>
       </c>
       <c r="J35" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.1702</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>0.1351</v>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>113 of 149</t>
-        </is>
-      </c>
+        <v>0.1875</v>
+      </c>
+      <c r="M35" s="8" t="n"/>
+      <c r="N35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2189,45 +2189,45 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Reynaldo Lopez</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.4327</v>
+        <v>0.4335</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3926</v>
+        <v>0.3931</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.0401</v>
+        <v>0.0405</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0106</v>
+        <v>0.0435</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>1.446</v>
+        <v>1.261</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.208</v>
+        <v>1.8</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.265</v>
+        <v>0.429</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.1489</v>
+        <v>0.1667</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.1284</v>
+        <v>0.1351</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>116 of 149</t>
+          <t>113 of 149</t>
         </is>
       </c>
     </row>
@@ -2237,45 +2237,45 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>24</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4327</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3926</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.0401</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.0106</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>1.596</v>
+        <v>1.446</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>2.16</v>
+        <v>1.208</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.367</v>
+        <v>0.265</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.1489</v>
+        <v>0.1458</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.0608</v>
+        <v>0.1284</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>132 of 149</t>
+          <t>116 of 149</t>
         </is>
       </c>
     </row>
@@ -2285,45 +2285,45 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>10.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.465</v>
+        <v>0.4643</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3663</v>
+        <v>0.3512</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.0988</v>
+        <v>0.1131</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0536</v>
+        <v>0.0682</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>1.609</v>
+        <v>1.596</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>2.531</v>
+        <v>2.16</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.463</v>
+        <v>0.367</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.1277</v>
+        <v>0.1458</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.0541</v>
+        <v>0.0608</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>134 of 149</t>
+          <t>132 of 149</t>
         </is>
       </c>
     </row>
@@ -2333,45 +2333,45 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4437</v>
+        <v>0.465</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.404</v>
+        <v>0.3663</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.0397</v>
+        <v>0.0988</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.0536</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1.295</v>
+        <v>1.609</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.393</v>
+        <v>2.531</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.286</v>
+        <v>0.463</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.1277</v>
+        <v>0.125</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.1216</v>
+        <v>0.0541</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>118 of 149</t>
+          <t>134 of 149</t>
         </is>
       </c>
     </row>
@@ -2381,45 +2381,45 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Mason Barnett</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>21.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4474</v>
+        <v>0.4437</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3934</v>
+        <v>0.404</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.0541</v>
+        <v>0.0397</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0337</v>
+        <v>0.0732</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1.613</v>
+        <v>1.295</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.477</v>
+        <v>1.393</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.291</v>
+        <v>0.286</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.1064</v>
+        <v>0.125</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.0473</v>
+        <v>0.1216</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>136 of 149</t>
+          <t>118 of 149</t>
         </is>
       </c>
     </row>
@@ -2429,45 +2429,45 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>15</v>
+        <v>21.7</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4474</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3934</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.0541</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0337</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.59</v>
+        <v>1.613</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>1.867</v>
+        <v>1.477</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.351</v>
+        <v>0.291</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.1064</v>
+        <v>0.1042</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.0541</v>
+        <v>0.0473</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>135 of 149</t>
+          <t>136 of 149</t>
         </is>
       </c>
     </row>
@@ -2477,45 +2477,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Miles Mikolas</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>12.3</v>
+        <v>15</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.3827</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.3704</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0123</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.494</v>
+        <v>1.59</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.784</v>
+        <v>1.867</v>
       </c>
       <c r="K42" s="7" t="n">
         <v>0.351</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.0851</v>
+        <v>0.1042</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0541</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>141 of 149</t>
+          <t>135 of 149</t>
         </is>
       </c>
     </row>
@@ -2525,45 +2525,45 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Carson Whisenhunt</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.4579</v>
+        <v>0.4091</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.4182</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.0607</v>
+        <v>-0.0091</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.0345</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.635</v>
+        <v>1.494</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>2.229</v>
+        <v>1.784</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.438</v>
+        <v>0.351</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.0851</v>
+        <v>0.0833</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.0338</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>139 of 149</t>
+          <t>141 of 149</t>
         </is>
       </c>
     </row>
@@ -2573,45 +2573,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Carson Whisenhunt</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>16.7</v>
+        <v>11.7</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4579</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.3972</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0607</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0517</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.413</v>
+        <v>1.635</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.56</v>
+        <v>2.229</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.333</v>
+        <v>0.438</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.0638</v>
+        <v>0.0833</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0405</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>142 of 149</t>
+          <t>139 of 149</t>
         </is>
       </c>
     </row>
@@ -2621,45 +2621,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Randy Vasquez</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4336</v>
+        <v>0.4167</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3628</v>
+        <v>0.4263</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.0708</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.669</v>
+        <v>1.413</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.12</v>
+        <v>0.333</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.0638</v>
+        <v>0.0625</v>
       </c>
       <c r="M45" s="8" t="n">
         <v>0.027</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>143 of 149</t>
+          <t>142 of 149</t>
         </is>
       </c>
     </row>
@@ -2669,45 +2669,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Randy Vasquez</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>10.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4155</v>
+        <v>0.4336</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.3732</v>
+        <v>0.3628</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.0423</v>
+        <v>0.0708</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.805</v>
+        <v>1.669</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>0.968</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.107</v>
+        <v>0.12</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.0426</v>
+        <v>0.0625</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.0135</v>
+        <v>0.027</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>146 of 149</t>
+          <t>143 of 149</t>
         </is>
       </c>
     </row>
@@ -2717,45 +2717,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>17</v>
+        <v>10.3</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.3874</v>
+        <v>0.4155</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.4111</v>
+        <v>0.3732</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>-0.0237</v>
+        <v>0.0423</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0588</v>
+        <v>0.0769</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.381</v>
+        <v>1.805</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.118</v>
+        <v>0.968</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.235</v>
+        <v>0.107</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.0213</v>
+        <v>0.0417</v>
       </c>
       <c r="M47" s="8" t="n">
         <v>0.0135</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>145 of 149</t>
+          <t>146 of 149</t>
         </is>
       </c>
     </row>
@@ -2765,45 +2765,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>10.3</v>
+        <v>17</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.401</v>
+        <v>0.3874</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.4213</v>
+        <v>0.4111</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>-0.0203</v>
+        <v>-0.0237</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0408</v>
+        <v>0.0588</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.892</v>
+        <v>1.381</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>2.032</v>
+        <v>1.118</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.333</v>
+        <v>0.235</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>148 of 149</t>
+          <t>145 of 149</t>
         </is>
       </c>
     </row>
@@ -2813,35 +2813,35 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>12.3</v>
+        <v>10.3</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.3822</v>
+        <v>0.401</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4213</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>-0.0622</v>
+        <v>-0.0203</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0408</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.844</v>
+        <v>1.892</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>2.108</v>
+        <v>2.032</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="L49" s="8" t="n">
         <v>0</v>
@@ -2851,68 +2851,116 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
+          <t>148 of 149</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Ryan Johnson</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>-0.0622</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>1.844</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
           <t>149 of 149</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>Stoplight shading (Pitcher, CMD%, Model WHIP) reflects Score (Relative): MIN of each pitcher's percentile rank on CMD% (higher=better) and Model WHIP (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by Score (Relative) rank position.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Score (Absolute) uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 20-day window). Rank (Absolute) shows literal rank position within that league-wide pool.</t>
+          <t>Stoplight shading (Pitcher, CMD%, Model WHIP) reflects Score (Relative): MIN of each pitcher's percentile rank on CMD% (higher=better) and Model WHIP (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by Score (Relative) rank position.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+          <t>Score (Absolute) uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 20-day window). Rank (Absolute) shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (Model WHIP inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>K%, BB%, HR% (Model WHIP inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Model WHIP = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. Actual WHIP is real (H+BB)/IP over the same window.</t>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+          <t>Model WHIP = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. Actual WHIP is real (H+BB)/IP over the same window.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 20-day window -- single-start genuine starters are included here. The league-wide absolute pool behind Score (Absolute)/Rank (Absolute) still requires 2+ starts, so a 1-start pitcher can appear here with a Score (Relative) but a blank Score (Absolute)/Rank (Absolute).</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -575,41 +575,47 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Cade Povich</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>12.7</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.5172</v>
+        <v>0.4767</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3218</v>
+        <v>0.3368</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1954</v>
+        <v>0.1399</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0</v>
+        <v>0.0189</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.788</v>
+        <v>1.152</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1.333</v>
+        <v>1.421</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.5</v>
+        <v>0.368</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9792</v>
-      </c>
-      <c r="M2" s="8" t="n"/>
-      <c r="N2" s="2" t="n"/>
+        <v>0.9375</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>26 of 151</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -651,11 +657,11 @@
         <v>0.8542</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.6419</v>
+        <v>0.6267</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>37 of 149</t>
+          <t>41 of 151</t>
         </is>
       </c>
     </row>
@@ -699,11 +705,11 @@
         <v>0.8125</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.6014</v>
+        <v>0.5733</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40 of 149</t>
+          <t>46 of 151</t>
         </is>
       </c>
     </row>
@@ -744,14 +750,14 @@
         <v>0.323</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.7917</v>
+        <v>0.8125</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.5541</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46 of 149</t>
+          <t>47 of 151</t>
         </is>
       </c>
     </row>
@@ -792,14 +798,14 @@
         <v>0.172</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7708</v>
+        <v>0.7917</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.527</v>
+        <v>0.5467</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50 of 149</t>
+          <t>51 of 151</t>
         </is>
       </c>
     </row>
@@ -840,14 +846,14 @@
         <v>0.348</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.75</v>
+        <v>0.7708</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5203</v>
+        <v>0.54</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51 of 149</t>
+          <t>52 of 151</t>
         </is>
       </c>
     </row>
@@ -857,45 +863,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>18.3</v>
+        <v>12.7</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4618</v>
+        <v>0.4717</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3282</v>
+        <v>0.3821</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1336</v>
+        <v>0.0896</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0533</v>
+        <v>0.0417</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.313</v>
+        <v>1.307</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.255</v>
+        <v>1.026</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.283</v>
+        <v>0.214</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.6875</v>
+        <v>0.7083</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.5068</v>
+        <v>0.4667</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53 of 149</t>
+          <t>66 of 151</t>
         </is>
       </c>
     </row>
@@ -905,45 +911,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>15.3</v>
+        <v>22.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4773</v>
+        <v>0.4694</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3561</v>
+        <v>0.3806</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1212</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0635</v>
+        <v>0.023</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.318</v>
+        <v>1.096</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.174</v>
+        <v>1.015</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.255</v>
+        <v>0.264</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.6667</v>
+        <v>0.6875</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.4865</v>
+        <v>0.46</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57 of 149</t>
+          <t>67 of 151</t>
         </is>
       </c>
     </row>
@@ -953,45 +959,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12.7</v>
+        <v>18.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4717</v>
+        <v>0.457</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3821</v>
+        <v>0.354</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0896</v>
+        <v>0.1031</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.013</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.307</v>
+        <v>1.309</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.026</v>
+        <v>1.179</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.214</v>
+        <v>0.263</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.6458</v>
+        <v>0.6875</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.4392</v>
+        <v>0.4733</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65 of 149</t>
+          <t>64 of 151</t>
         </is>
       </c>
     </row>
@@ -1001,45 +1007,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Javier Assad</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10</v>
+        <v>18.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4618</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3282</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1336</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0533</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.327</v>
+        <v>1.313</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.4</v>
+        <v>1.255</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.333</v>
+        <v>0.283</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6458</v>
+        <v>0.6667</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.473</v>
+        <v>0.4667</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59 of 149</t>
+          <t>65 of 151</t>
         </is>
       </c>
     </row>
@@ -1049,45 +1055,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>22.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4694</v>
+        <v>0.4773</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3806</v>
+        <v>0.3561</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1212</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0635</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.096</v>
+        <v>1.318</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.015</v>
+        <v>1.174</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.264</v>
+        <v>0.255</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.625</v>
+        <v>0.6458</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.4324</v>
+        <v>0.46</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66 of 149</t>
+          <t>68 of 151</t>
         </is>
       </c>
     </row>
@@ -1097,45 +1103,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4545</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3661</v>
+        <v>0.3706</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0982</v>
+        <v>0.0839</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.025</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.345</v>
+        <v>1.272</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.615</v>
+        <v>1</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6042</v>
+        <v>0.6458</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.4257</v>
+        <v>0.44</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68 of 149</t>
+          <t>71 of 151</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1151,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Javier Assad</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1155,35 +1161,35 @@
         <v>10</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.4678</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.3684</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0839</v>
+        <v>0.0994</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0244</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.272</v>
+        <v>1.327</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6042</v>
+        <v>0.625</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.4257</v>
+        <v>0.4533</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69 of 149</t>
+          <t>69 of 151</t>
         </is>
       </c>
     </row>
@@ -1193,47 +1199,41 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5204</v>
+        <v>0.4583</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3234</v>
+        <v>0.375</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.197</v>
+        <v>0.0833</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.352</v>
+        <v>1.184</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.188</v>
+        <v>1.4</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.25</v>
+        <v>0.353</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.5833</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>0.4189</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>70 of 149</t>
-        </is>
-      </c>
+        <v>0.625</v>
+      </c>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1241,41 +1241,47 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4583</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.375</v>
+        <v>0.3486</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0833</v>
+        <v>0.16</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0</v>
+        <v>0.0482</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.184</v>
+        <v>1.337</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.353</v>
+        <v>0.298</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5833</v>
-      </c>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="2" t="n"/>
+        <v>0.6042</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>72 of 151</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1283,45 +1289,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24.7</v>
+        <v>12.3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4485</v>
+        <v>0.4412</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3536</v>
+        <v>0.3647</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.095</v>
+        <v>0.0765</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.0417</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.379</v>
+        <v>1.308</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.257</v>
+        <v>1.054</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.274</v>
+        <v>0.235</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5417</v>
+        <v>0.5625</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3514</v>
+        <v>0.4</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81 of 149</t>
+          <t>73 of 151</t>
         </is>
       </c>
     </row>
@@ -1331,45 +1337,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Cade Povich</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12.3</v>
+        <v>9</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4412</v>
+        <v>0.4558</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3647</v>
+        <v>0.381</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0765</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0278</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.308</v>
+        <v>1.209</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.054</v>
+        <v>1.556</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.235</v>
+        <v>0.435</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5208</v>
+        <v>0.5417</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3919</v>
+        <v>0.3867</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>73 of 149</t>
+          <t>77 of 151</t>
         </is>
       </c>
     </row>
@@ -1379,45 +1385,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>16.7</v>
+        <v>11.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4778</v>
+        <v>0.4305</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3481</v>
+        <v>0.3642</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0.1296</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>1.384</v>
+        <v>1.339</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.56</v>
+        <v>0.857</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.347</v>
+        <v>0.182</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3176</v>
+        <v>0.34</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>85 of 149</t>
+          <t>84 of 151</t>
         </is>
       </c>
     </row>
@@ -1461,11 +1467,11 @@
         <v>0.4792</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.2905</v>
+        <v>0.3067</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91 of 149</t>
+          <t>88 of 151</t>
         </is>
       </c>
     </row>
@@ -1509,11 +1515,11 @@
         <v>0.4583</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.2973</v>
+        <v>0.3067</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>88 of 149</t>
+          <t>87 of 151</t>
         </is>
       </c>
     </row>
@@ -1557,11 +1563,11 @@
         <v>0.4583</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.2838</v>
+        <v>0.3</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92 of 149</t>
+          <t>89 of 151</t>
         </is>
       </c>
     </row>
@@ -1571,45 +1577,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>14.7</v>
+        <v>7.7</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4567</v>
+        <v>0.4643</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3976</v>
+        <v>0.3786</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.0857</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0303</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.436</v>
+        <v>1.415</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.636</v>
+        <v>1.565</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.341</v>
+        <v>0.273</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>0.4167</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.2432</v>
+        <v>0.28</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96 of 149</t>
+          <t>93 of 151</t>
         </is>
       </c>
     </row>
@@ -1619,45 +1625,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>22</v>
+        <v>14.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4419</v>
+        <v>0.4567</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3613</v>
+        <v>0.3976</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0806</v>
+        <v>0.0591</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0303</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.438</v>
+        <v>1.436</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.182</v>
+        <v>1.636</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.288</v>
+        <v>0.341</v>
       </c>
       <c r="L24" s="8" t="n">
         <v>0.3958</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.2365</v>
+        <v>0.2533</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>97 of 149</t>
+          <t>95 of 151</t>
         </is>
       </c>
     </row>
@@ -1667,45 +1673,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Martin Perez</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4403</v>
+        <v>0.4419</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3881</v>
+        <v>0.3613</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.0522</v>
+        <v>0.0806</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0137</v>
+        <v>0.025</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.34</v>
+        <v>1.438</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.947</v>
+        <v>1.182</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.188</v>
+        <v>0.288</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.3542</v>
+        <v>0.375</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.2365</v>
+        <v>0.24</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>98 of 149</t>
+          <t>98 of 151</t>
         </is>
       </c>
     </row>
@@ -1715,45 +1721,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Martin Perez</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4726</v>
+        <v>0.4403</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3562</v>
+        <v>0.3881</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.1164</v>
+        <v>0.0522</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0137</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.493</v>
+        <v>1.34</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>2.125</v>
+        <v>0.947</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.423</v>
+        <v>0.188</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.3542</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.1622</v>
+        <v>0.2467</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>110 of 149</t>
+          <t>96 of 151</t>
         </is>
       </c>
     </row>
@@ -1763,45 +1769,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>13.3</v>
+        <v>8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4726</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3562</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.1164</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1</v>
+        <v>0.025</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.136</v>
+        <v>1.493</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.05</v>
+        <v>2.125</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.267</v>
+        <v>0.423</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.2917</v>
+        <v>0.3333</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.1892</v>
+        <v>0.1733</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>105 of 149</t>
+          <t>109 of 151</t>
         </is>
       </c>
     </row>
@@ -1811,45 +1817,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>16</v>
+        <v>20.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.4626</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3756</v>
+        <v>0.4138</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0489</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.461</v>
+        <v>1.511</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.188</v>
+        <v>1.82</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.25</v>
+        <v>0.419</v>
       </c>
       <c r="L28" s="8" t="n">
         <v>0.2708</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1824</v>
+        <v>0.1467</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>106 of 149</t>
+          <t>115 of 151</t>
         </is>
       </c>
     </row>
@@ -1859,45 +1865,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Luinder Avila</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>20.3</v>
+        <v>13.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4626</v>
+        <v>0.443</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4138</v>
+        <v>0.3904</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0489</v>
+        <v>0.0526</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.0167</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.511</v>
+        <v>1.535</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.82</v>
+        <v>1.575</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.419</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.2708</v>
+        <v>0.25</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1351</v>
+        <v>0.1267</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>114 of 149</t>
+          <t>119 of 151</t>
         </is>
       </c>
     </row>
@@ -1907,45 +1913,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Luinder Avila</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13.3</v>
+        <v>16</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4436</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.4023</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0414</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0299</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.535</v>
+        <v>1.368</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.575</v>
+        <v>1.312</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.3</v>
+        <v>0.279</v>
       </c>
       <c r="L30" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1284</v>
+        <v>0.1667</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>115 of 149</t>
+          <t>110 of 151</t>
         </is>
       </c>
     </row>
@@ -1989,11 +1995,11 @@
         <v>0.2292</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.1216</v>
+        <v>0.12</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>117 of 149</t>
+          <t>121 of 151</t>
         </is>
       </c>
     </row>
@@ -2003,45 +2009,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.451</v>
+        <v>0.4251</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3846</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.0405</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0462</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.578</v>
+        <v>1.496</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.756</v>
+        <v>1.667</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.325</v>
+        <v>0.356</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2083</v>
+        <v>0.2292</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.0878</v>
+        <v>0.16</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>126 of 149</t>
+          <t>111 of 151</t>
         </is>
       </c>
     </row>
@@ -2051,45 +2057,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Reynaldo Lopez</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4436</v>
+        <v>0.4335</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.4023</v>
+        <v>0.3931</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0414</v>
+        <v>0.0405</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0299</v>
+        <v>0.0435</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.368</v>
+        <v>1.261</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.312</v>
+        <v>1.8</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.279</v>
+        <v>0.429</v>
       </c>
       <c r="L33" s="8" t="n">
         <v>0.2083</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1486</v>
+        <v>0.1533</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>111 of 149</t>
+          <t>112 of 151</t>
         </is>
       </c>
     </row>
@@ -2099,45 +2105,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Randy Vasquez</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>15</v>
+        <v>13.7</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4251</v>
+        <v>0.4162</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3846</v>
+        <v>0.3584</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.0578</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.0217</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.496</v>
+        <v>1.563</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.667</v>
+        <v>0.585</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.356</v>
+        <v>0.1</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.1875</v>
+        <v>0.2083</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1419</v>
+        <v>0.1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>112 of 149</t>
+          <t>127 of 151</t>
         </is>
       </c>
     </row>
@@ -2147,41 +2153,47 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5</v>
+        <v>13.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.451</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3696</v>
+        <v>0.4078</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.1196</v>
+        <v>0.0431</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>1.589</v>
+        <v>1.578</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.8</v>
+        <v>1.756</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.375</v>
+        <v>0.325</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>0.1875</v>
       </c>
-      <c r="M35" s="8" t="n"/>
-      <c r="N35" s="2" t="n"/>
+      <c r="M35" s="8" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>131 of 151</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2189,45 +2201,45 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Reynaldo Lopez</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.4327</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.3926</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.0405</v>
+        <v>0.0401</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0435</v>
+        <v>0.0106</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>1.261</v>
+        <v>1.446</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.8</v>
+        <v>1.208</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.429</v>
+        <v>0.265</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.1667</v>
+        <v>0.1875</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.1351</v>
+        <v>0.1467</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>113 of 149</t>
+          <t>114 of 151</t>
         </is>
       </c>
     </row>
@@ -2237,45 +2249,45 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Mason Barnett</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>24</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4327</v>
+        <v>0.4437</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3926</v>
+        <v>0.404</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.0401</v>
+        <v>0.0397</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0106</v>
+        <v>0.0732</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>1.446</v>
+        <v>1.295</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.208</v>
+        <v>1.393</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.265</v>
+        <v>0.286</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.1458</v>
+        <v>0.1667</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.1284</v>
+        <v>0.14</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>116 of 149</t>
+          <t>117 of 151</t>
         </is>
       </c>
     </row>
@@ -2285,47 +2297,41 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4891</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3696</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.1196</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>1.596</v>
+        <v>1.589</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.1458</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>0.0608</v>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>132 of 149</t>
-        </is>
-      </c>
+        <v>0.1667</v>
+      </c>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2333,45 +2339,45 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Miles Mikolas</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>10.7</v>
+        <v>15</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.465</v>
+        <v>0.3827</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3663</v>
+        <v>0.3704</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.0988</v>
+        <v>0.0123</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0536</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1.609</v>
+        <v>1.59</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>2.531</v>
+        <v>1.867</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.463</v>
+        <v>0.351</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.125</v>
+        <v>0.1458</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.0541</v>
+        <v>0.08</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>134 of 149</t>
+          <t>132 of 151</t>
         </is>
       </c>
     </row>
@@ -2381,45 +2387,45 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4437</v>
+        <v>0.4643</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.404</v>
+        <v>0.3512</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.0397</v>
+        <v>0.1131</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.0682</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1.295</v>
+        <v>1.596</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.393</v>
+        <v>2.16</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.286</v>
+        <v>0.367</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>0.125</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.1216</v>
+        <v>0.0667</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>118 of 149</t>
+          <t>135 of 151</t>
         </is>
       </c>
     </row>
@@ -2429,45 +2435,45 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>21.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4474</v>
+        <v>0.4091</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3934</v>
+        <v>0.4156</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.0541</v>
+        <v>-0.0065</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0337</v>
+        <v>0.1111</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.613</v>
+        <v>1.34</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>1.477</v>
+        <v>1.071</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.291</v>
+        <v>0.217</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>0.1042</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.0473</v>
+        <v>0.0533</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>136 of 149</t>
+          <t>136 of 151</t>
         </is>
       </c>
     </row>
@@ -2477,45 +2483,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Carson Whisenhunt</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>15</v>
+        <v>11.7</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4579</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3972</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.0607</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0517</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.59</v>
+        <v>1.635</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.867</v>
+        <v>2.229</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.351</v>
+        <v>0.438</v>
       </c>
       <c r="L42" s="8" t="n">
         <v>0.1042</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.0541</v>
+        <v>0.0533</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>135 of 149</t>
+          <t>137 of 151</t>
         </is>
       </c>
     </row>
@@ -2559,11 +2565,11 @@
         <v>0.0833</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.0338</v>
+        <v>0.0467</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>141 of 149</t>
+          <t>138 of 151</t>
         </is>
       </c>
     </row>
@@ -2573,45 +2579,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Carson Whisenhunt</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>11.7</v>
+        <v>17</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4579</v>
+        <v>0.4286</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.4206</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.0607</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.0149</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.635</v>
+        <v>1.673</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>2.229</v>
+        <v>1.353</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.438</v>
+        <v>0.25</v>
       </c>
       <c r="L44" s="8" t="n">
         <v>0.0833</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.0467</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>139 of 149</t>
+          <t>139 of 151</t>
         </is>
       </c>
     </row>
@@ -2621,45 +2627,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4491</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.3862</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0629</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0513</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.413</v>
+        <v>1.708</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>1.56</v>
+        <v>2.533</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.333</v>
+        <v>0.448</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>0.0625</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.027</v>
+        <v>0.04</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>142 of 149</t>
+          <t>140 of 151</t>
         </is>
       </c>
     </row>
@@ -2669,45 +2675,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Randy Vasquez</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4336</v>
+        <v>0.4167</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.3628</v>
+        <v>0.4263</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.0708</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.669</v>
+        <v>1.413</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>0.6919999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.12</v>
+        <v>0.333</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>0.0625</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.027</v>
+        <v>0.04</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>143 of 149</t>
+          <t>141 of 151</t>
         </is>
       </c>
     </row>
@@ -2717,45 +2723,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>10.3</v>
+        <v>17</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4155</v>
+        <v>0.3874</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.3732</v>
+        <v>0.4111</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.0423</v>
+        <v>-0.0237</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0769</v>
+        <v>0.0588</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.805</v>
+        <v>1.381</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>0.968</v>
+        <v>1.118</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.107</v>
+        <v>0.235</v>
       </c>
       <c r="L47" s="8" t="n">
         <v>0.0417</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0135</v>
+        <v>0.0267</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>146 of 149</t>
+          <t>144 of 151</t>
         </is>
       </c>
     </row>
@@ -2765,45 +2771,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>17</v>
+        <v>10.3</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.3874</v>
+        <v>0.4155</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.4111</v>
+        <v>0.3732</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>-0.0237</v>
+        <v>0.0423</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0588</v>
+        <v>0.0769</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.381</v>
+        <v>1.805</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.118</v>
+        <v>0.968</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.235</v>
+        <v>0.107</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0417</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0135</v>
+        <v>0.02</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>145 of 149</t>
+          <t>146 of 151</t>
         </is>
       </c>
     </row>
@@ -2813,45 +2819,45 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.401</v>
+        <v>0.3822</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.4213</v>
+        <v>0.4444</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>-0.0203</v>
+        <v>-0.0622</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.0408</v>
+        <v>0.05</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.892</v>
+        <v>1.844</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>2.032</v>
+        <v>2.108</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>148 of 149</t>
+          <t>149 of 151</t>
         </is>
       </c>
     </row>
@@ -2861,35 +2867,35 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>12.3</v>
+        <v>5.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.3822</v>
+        <v>0.3833</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4583</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>-0.0622</v>
+        <v>-0.075</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0333</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.844</v>
+        <v>2.149</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>2.108</v>
+        <v>2.625</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="L50" s="8" t="n">
         <v>0</v>
@@ -2899,7 +2905,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>149 of 149</t>
+          <t>151 of 151</t>
         </is>
       </c>
     </row>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -575,45 +575,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12.7</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.4767</v>
+        <v>0.4805</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3368</v>
+        <v>0.3514</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1399</v>
+        <v>0.1291</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0189</v>
+        <v>0.0345</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1.152</v>
+        <v>1.216</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1.421</v>
+        <v>1.7</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.368</v>
+        <v>0.436</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9375</v>
+        <v>0.913</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.74</v>
+        <v>0.6267</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>26 of 151</t>
+          <t>41 of 151</t>
         </is>
       </c>
     </row>
@@ -623,45 +623,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.4805</v>
+        <v>0.4713</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3514</v>
+        <v>0.3487</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1291</v>
+        <v>0.1226</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0455</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.216</v>
+        <v>1.26</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.436</v>
+        <v>0.222</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.8542</v>
+        <v>0.8696</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.6267</v>
+        <v>0.5733</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>41 of 151</t>
+          <t>46 of 151</t>
         </is>
       </c>
     </row>
@@ -671,45 +671,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>17</v>
+        <v>11.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4636</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.3487</v>
+        <v>0.3576</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1226</v>
+        <v>0.106</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0455</v>
+        <v>0.0233</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.26</v>
+        <v>1.017</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1</v>
+        <v>0.706</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.222</v>
+        <v>0.172</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8125</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.5733</v>
+        <v>0.5467</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46 of 151</t>
+          <t>51 of 151</t>
         </is>
       </c>
     </row>
@@ -719,45 +719,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>15.3</v>
+        <v>15.7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4944</v>
+        <v>0.4619</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3858</v>
+        <v>0.3559</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1086</v>
+        <v>0.1059</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0328</v>
+        <v>0</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.158</v>
+        <v>1.114</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.239</v>
+        <v>1.277</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.323</v>
+        <v>0.348</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8125</v>
+        <v>0.8043</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47 of 151</t>
+          <t>52 of 151</t>
         </is>
       </c>
     </row>
@@ -767,45 +767,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11.3</v>
+        <v>18.7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4636</v>
+        <v>0.457</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3576</v>
+        <v>0.354</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.106</v>
+        <v>0.1031</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0233</v>
+        <v>0.013</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.017</v>
+        <v>1.309</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.706</v>
+        <v>1.179</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.172</v>
+        <v>0.263</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7917</v>
+        <v>0.7826</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.5467</v>
+        <v>0.4733</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51 of 151</t>
+          <t>64 of 151</t>
         </is>
       </c>
     </row>
@@ -815,45 +815,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15.7</v>
+        <v>18.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4619</v>
+        <v>0.4618</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3559</v>
+        <v>0.3282</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1059</v>
+        <v>0.1336</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
+        <v>0.0533</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.114</v>
+        <v>1.313</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.277</v>
+        <v>1.255</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.348</v>
+        <v>0.283</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.7708</v>
+        <v>0.7609</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.54</v>
+        <v>0.4667</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52 of 151</t>
+          <t>65 of 151</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
         <v>0.214</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.7083</v>
+        <v>0.7391</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>0.4667</v>
@@ -911,45 +911,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Javier Assad</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>22.7</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4694</v>
+        <v>0.4678</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3806</v>
+        <v>0.3684</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0994</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0244</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.096</v>
+        <v>1.327</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.015</v>
+        <v>1.4</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.264</v>
+        <v>0.333</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.6875</v>
+        <v>0.7391</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.46</v>
+        <v>0.4533</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67 of 151</t>
+          <t>69 of 151</t>
         </is>
       </c>
     </row>
@@ -959,45 +959,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>18.7</v>
+        <v>20</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.457</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.354</v>
+        <v>0.3486</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1031</v>
+        <v>0.16</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.013</v>
+        <v>0.0482</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.309</v>
+        <v>1.337</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.179</v>
+        <v>1.35</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.263</v>
+        <v>0.298</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.6875</v>
+        <v>0.6957</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.4733</v>
+        <v>0.42</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64 of 151</t>
+          <t>72 of 151</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,41 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>18.3</v>
+        <v>5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4618</v>
+        <v>0.4583</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3282</v>
+        <v>0.375</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1336</v>
+        <v>0.0833</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0533</v>
+        <v>0</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.313</v>
+        <v>1.184</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.255</v>
+        <v>1.4</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.283</v>
+        <v>0.353</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>0.4667</v>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>65 of 151</t>
-        </is>
-      </c>
+        <v>0.6957</v>
+      </c>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1055,45 +1049,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Cade Povich</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4773</v>
+        <v>0.4558</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3561</v>
+        <v>0.381</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1212</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0635</v>
+        <v>0.0278</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.318</v>
+        <v>1.209</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.174</v>
+        <v>1.556</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.255</v>
+        <v>0.435</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6458</v>
+        <v>0.6304</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.46</v>
+        <v>0.3867</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68 of 151</t>
+          <t>77 of 151</t>
         </is>
       </c>
     </row>
@@ -1103,45 +1097,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4545</v>
+        <v>0.4513</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3706</v>
+        <v>0.3769</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0839</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0101</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.272</v>
+        <v>1.327</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1</v>
+        <v>1.522</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.2</v>
+        <v>0.352</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6458</v>
+        <v>0.6087</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.44</v>
+        <v>0.3733</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>71 of 151</t>
+          <t>79 of 151</t>
         </is>
       </c>
     </row>
@@ -1151,45 +1145,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Javier Assad</t>
+          <t>Connor Prielipp</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4902</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3608</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1294</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0492</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.327</v>
+        <v>1.365</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.4</v>
+        <v>1.125</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.333</v>
+        <v>0.235</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.625</v>
+        <v>0.6087</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.4533</v>
+        <v>0.3533</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69 of 151</t>
+          <t>83 of 151</t>
         </is>
       </c>
     </row>
@@ -1199,41 +1193,47 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>11.7</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4583</v>
+        <v>0.4305</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.375</v>
+        <v>0.3642</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0833</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.184</v>
+        <v>1.339</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.4</v>
+        <v>0.857</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.353</v>
+        <v>0.182</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="M15" s="8" t="n"/>
-      <c r="N15" s="2" t="n"/>
+        <v>0.5652</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>84 of 151</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1241,45 +1241,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>20</v>
+        <v>23.7</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.441</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3486</v>
+        <v>0.3792</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.16</v>
+        <v>0.0618</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.022</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.337</v>
+        <v>1.226</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.35</v>
+        <v>1.014</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.298</v>
+        <v>0.246</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.6042</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.42</v>
+        <v>0.3067</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72 of 151</t>
+          <t>87 of 151</t>
         </is>
       </c>
     </row>
@@ -1289,45 +1289,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Hunter Greene</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>12.3</v>
+        <v>11.3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4412</v>
+        <v>0.4386</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3647</v>
+        <v>0.3567</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0765</v>
+        <v>0.0819</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0192</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.308</v>
+        <v>1.404</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.054</v>
+        <v>1.676</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.235</v>
+        <v>0.35</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5625</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3067</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73 of 151</t>
+          <t>88 of 151</t>
         </is>
       </c>
     </row>
@@ -1335,47 +1335,47 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Cade Povich</t>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.4473</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.3738</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>0.0735</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0278</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>1.209</v>
+        <v>0.0595</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>1.408</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.556</v>
+        <v>1.474</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.435</v>
+        <v>0.294</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5417</v>
+        <v>0.5</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3867</v>
+        <v>0.3</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>77 of 151</t>
+          <t>89 of 151</t>
         </is>
       </c>
     </row>
@@ -1385,45 +1385,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Grant Holmes</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11.7</v>
+        <v>21.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4305</v>
+        <v>0.4319</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3642</v>
+        <v>0.3721</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0598</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0</v>
+        <v>0.0361</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>1.339</v>
+        <v>1.372</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.857</v>
+        <v>1.2</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.182</v>
+        <v>0.281</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.5</v>
+        <v>0.4783</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.34</v>
+        <v>0.2867</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>84 of 151</t>
+          <t>91 of 151</t>
         </is>
       </c>
     </row>
@@ -1433,45 +1433,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Hunter Greene</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>11.3</v>
+        <v>7.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4386</v>
+        <v>0.4643</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3567</v>
+        <v>0.3786</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>0.0819</v>
+        <v>0.0857</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>1.404</v>
+        <v>1.415</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.676</v>
+        <v>1.565</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.35</v>
+        <v>0.273</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.4792</v>
+        <v>0.4348</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.3067</v>
+        <v>0.28</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88 of 151</t>
+          <t>93 of 151</t>
         </is>
       </c>
     </row>
@@ -1481,45 +1481,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>23.7</v>
+        <v>8</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.441</v>
+        <v>0.4726</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3792</v>
+        <v>0.3562</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.0618</v>
+        <v>0.1164</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.226</v>
+        <v>1.493</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.014</v>
+        <v>2.125</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.246</v>
+        <v>0.423</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.4583</v>
+        <v>0.3913</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.3067</v>
+        <v>0.1733</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>87 of 151</t>
+          <t>109 of 151</t>
         </is>
       </c>
     </row>
@@ -1529,45 +1529,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Jack Perkins</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>19</v>
+        <v>20.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4473</v>
+        <v>0.4626</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3738</v>
+        <v>0.4138</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.0735</v>
+        <v>0.0489</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0595</v>
+        <v>0.0333</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.408</v>
+        <v>1.511</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.474</v>
+        <v>1.82</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.294</v>
+        <v>0.419</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4583</v>
+        <v>0.3261</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.3</v>
+        <v>0.1467</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>89 of 151</t>
+          <t>115 of 151</t>
         </is>
       </c>
     </row>
@@ -1577,45 +1577,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Zebby Matthews</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7.7</v>
+        <v>16</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4436</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3786</v>
+        <v>0.4023</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.0414</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0299</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.415</v>
+        <v>1.368</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.565</v>
+        <v>1.312</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.273</v>
+        <v>0.279</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4167</v>
+        <v>0.3261</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.28</v>
+        <v>0.1667</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93 of 151</t>
+          <t>110 of 151</t>
         </is>
       </c>
     </row>
@@ -1625,45 +1625,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Luinder Avila</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>14.7</v>
+        <v>13.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4567</v>
+        <v>0.443</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3976</v>
+        <v>0.3904</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0591</v>
+        <v>0.0526</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0303</v>
+        <v>0.0167</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.436</v>
+        <v>1.535</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.636</v>
+        <v>1.575</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.341</v>
+        <v>0.3</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.3958</v>
+        <v>0.3043</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.2533</v>
+        <v>0.1267</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>95 of 151</t>
+          <t>119 of 151</t>
         </is>
       </c>
     </row>
@@ -1673,45 +1673,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4419</v>
+        <v>0.4251</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3613</v>
+        <v>0.3846</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.0806</v>
+        <v>0.0405</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0462</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.438</v>
+        <v>1.496</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.182</v>
+        <v>1.667</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.288</v>
+        <v>0.356</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.375</v>
+        <v>0.3043</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>98 of 151</t>
+          <t>111 of 151</t>
         </is>
       </c>
     </row>
@@ -1721,45 +1721,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Martin Perez</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4403</v>
+        <v>0.44</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3881</v>
+        <v>0.3908</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0522</v>
+        <v>0.0492</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0137</v>
+        <v>0.0238</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.34</v>
+        <v>1.536</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.947</v>
+        <v>1.552</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.188</v>
+        <v>0.31</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.3542</v>
+        <v>0.2826</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.2467</v>
+        <v>0.12</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96 of 151</t>
+          <t>121 of 151</t>
         </is>
       </c>
     </row>
@@ -1769,45 +1769,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Reynaldo Lopez</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4726</v>
+        <v>0.4335</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3562</v>
+        <v>0.3931</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.1164</v>
+        <v>0.0405</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0435</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.493</v>
+        <v>1.261</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>2.125</v>
+        <v>1.8</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.423</v>
+        <v>0.429</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.2826</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.1733</v>
+        <v>0.1533</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>109 of 151</t>
+          <t>112 of 151</t>
         </is>
       </c>
     </row>
@@ -1817,45 +1817,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>20.3</v>
+        <v>24</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4626</v>
+        <v>0.4327</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4138</v>
+        <v>0.3926</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0489</v>
+        <v>0.0401</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.0106</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.511</v>
+        <v>1.446</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.82</v>
+        <v>1.208</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.419</v>
+        <v>0.265</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.2708</v>
+        <v>0.2609</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>0.1467</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>115 of 151</t>
+          <t>114 of 151</t>
         </is>
       </c>
     </row>
@@ -1865,45 +1865,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Luinder Avila</t>
+          <t>Randy Vasquez</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4162</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.3584</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0578</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0217</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.535</v>
+        <v>1.563</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.575</v>
+        <v>0.585</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2609</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1267</v>
+        <v>0.1</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>119 of 151</t>
+          <t>127 of 151</t>
         </is>
       </c>
     </row>
@@ -1913,45 +1913,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>16</v>
+        <v>13.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4436</v>
+        <v>0.451</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4023</v>
+        <v>0.4078</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0414</v>
+        <v>0.0431</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0299</v>
+        <v>0.0312</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.368</v>
+        <v>1.578</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.312</v>
+        <v>1.756</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.279</v>
+        <v>0.325</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2391</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1667</v>
+        <v>0.0867</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>110 of 151</t>
+          <t>131 of 151</t>
         </is>
       </c>
     </row>
@@ -1961,45 +1961,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Mason Barnett</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.44</v>
+        <v>0.4437</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3908</v>
+        <v>0.404</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.0397</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0238</v>
+        <v>0.0732</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.536</v>
+        <v>1.295</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.552</v>
+        <v>1.393</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.31</v>
+        <v>0.286</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.2292</v>
+        <v>0.2391</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>121 of 151</t>
+          <t>117 of 151</t>
         </is>
       </c>
     </row>
@@ -2009,45 +2009,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4251</v>
+        <v>0.433</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3846</v>
+        <v>0.3985</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.0345</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.0435</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.496</v>
+        <v>1.356</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.667</v>
+        <v>1.529</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.356</v>
+        <v>0.381</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2292</v>
+        <v>0.2174</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>111 of 151</t>
+          <t>122 of 151</t>
         </is>
       </c>
     </row>
@@ -2057,93 +2057,87 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Reynaldo Lopez</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.4891</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.3696</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.1196</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0435</v>
+        <v>0</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.261</v>
+        <v>1.589</v>
       </c>
       <c r="J33" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.2083</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>0.1533</v>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>112 of 151</t>
-        </is>
-      </c>
+        <v>0.2174</v>
+      </c>
+      <c r="M33" s="8" t="n"/>
+      <c r="N33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Randy Vasquez</t>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>13.7</v>
+        <v>22</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.4313</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3584</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.4066</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0.0247</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0217</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>1.563</v>
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>1.414</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.585</v>
+        <v>1.455</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.1</v>
+        <v>0.316</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.2083</v>
+        <v>0.1957</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1</v>
+        <v>0.1067</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>127 of 151</t>
+          <t>126 of 151</t>
         </is>
       </c>
     </row>
@@ -2153,45 +2147,45 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>13.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.451</v>
+        <v>0.4643</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3512</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.0431</v>
+        <v>0.1131</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0682</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>1.578</v>
+        <v>1.596</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.756</v>
+        <v>2.16</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.325</v>
+        <v>0.367</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.1875</v>
+        <v>0.1739</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.0867</v>
+        <v>0.0667</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>131 of 151</t>
+          <t>135 of 151</t>
         </is>
       </c>
     </row>
@@ -2201,45 +2195,45 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Miles Mikolas</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.4327</v>
+        <v>0.3827</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3926</v>
+        <v>0.3704</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.0401</v>
+        <v>0.0123</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0106</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>1.446</v>
+        <v>1.59</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.208</v>
+        <v>1.867</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.265</v>
+        <v>0.351</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.1875</v>
+        <v>0.1739</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.1467</v>
+        <v>0.08</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>114 of 151</t>
+          <t>132 of 151</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2243,7 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2259,35 +2253,35 @@
         <v>9.300000000000001</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4437</v>
+        <v>0.4091</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.404</v>
+        <v>0.4156</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.0397</v>
+        <v>-0.0065</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.1111</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>1.295</v>
+        <v>1.34</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.393</v>
+        <v>1.071</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.286</v>
+        <v>0.217</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.1667</v>
+        <v>0.1304</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.14</v>
+        <v>0.0533</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>117 of 151</t>
+          <t>136 of 151</t>
         </is>
       </c>
     </row>
@@ -2297,41 +2291,47 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Carson Whisenhunt</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5</v>
+        <v>11.7</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.4579</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3696</v>
+        <v>0.3972</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.1196</v>
+        <v>0.0607</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0</v>
+        <v>0.0517</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>1.589</v>
+        <v>1.635</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.8</v>
+        <v>2.229</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.375</v>
+        <v>0.438</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="2" t="n"/>
+        <v>0.1304</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>137 of 151</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2339,45 +2339,45 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4091</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.4182</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.0123</v>
+        <v>-0.0091</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0345</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1.59</v>
+        <v>1.494</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.867</v>
+        <v>1.784</v>
       </c>
       <c r="K39" s="7" t="n">
         <v>0.351</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.1458</v>
+        <v>0.1087</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.08</v>
+        <v>0.0467</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>132 of 151</t>
+          <t>138 of 151</t>
         </is>
       </c>
     </row>
@@ -2387,45 +2387,45 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>17</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4286</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.4206</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.0149</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1.596</v>
+        <v>1.673</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>2.16</v>
+        <v>1.353</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.367</v>
+        <v>0.25</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.125</v>
+        <v>0.1087</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.0667</v>
+        <v>0.0467</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>135 of 151</t>
+          <t>139 of 151</t>
         </is>
       </c>
     </row>
@@ -2435,45 +2435,45 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>15</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4491</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.4156</v>
+        <v>0.3862</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>-0.0065</v>
+        <v>0.0629</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.0513</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.34</v>
+        <v>1.708</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>1.071</v>
+        <v>2.533</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.217</v>
+        <v>0.448</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.1042</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.0533</v>
+        <v>0.04</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>136 of 151</t>
+          <t>140 of 151</t>
         </is>
       </c>
     </row>
@@ -2483,45 +2483,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Carson Whisenhunt</t>
+          <t>Kohl Drake</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>11.7</v>
+        <v>16.7</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4579</v>
+        <v>0.4167</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.4263</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.0607</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.0411</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.635</v>
+        <v>1.413</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>2.229</v>
+        <v>1.56</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.438</v>
+        <v>0.333</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.1042</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.0533</v>
+        <v>0.04</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>137 of 151</t>
+          <t>141 of 151</t>
         </is>
       </c>
     </row>
@@ -2531,45 +2531,45 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>12.3</v>
+        <v>17</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.3874</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.4111</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>-0.0091</v>
+        <v>-0.0237</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0588</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.494</v>
+        <v>1.381</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1.784</v>
+        <v>1.118</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.351</v>
+        <v>0.235</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.0833</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.0467</v>
+        <v>0.0267</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>138 of 151</t>
+          <t>144 of 151</t>
         </is>
       </c>
     </row>
@@ -2579,45 +2579,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>17</v>
+        <v>10.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4286</v>
+        <v>0.4155</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.4206</v>
+        <v>0.3732</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0423</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0149</v>
+        <v>0.0769</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.673</v>
+        <v>1.805</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.353</v>
+        <v>0.968</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.25</v>
+        <v>0.107</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.0833</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.0467</v>
+        <v>0.02</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>139 of 151</t>
+          <t>146 of 151</t>
         </is>
       </c>
     </row>
@@ -2627,45 +2627,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Ronel Blanco</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4491</v>
+        <v>0.4538</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3862</v>
+        <v>0.3739</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.0629</v>
+        <v>0.0798</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0513</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.708</v>
+        <v>1.814</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>2.533</v>
+        <v>1.432</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.448</v>
+        <v>0.243</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.0435</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0133</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>140 of 151</t>
+          <t>148 of 151</t>
         </is>
       </c>
     </row>
@@ -2675,45 +2675,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>16.7</v>
+        <v>12.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.3822</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.4444</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0622</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.05</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.413</v>
+        <v>1.844</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>1.56</v>
+        <v>2.108</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.0625</v>
+        <v>0.0217</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0067</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>141 of 151</t>
+          <t>149 of 151</t>
         </is>
       </c>
     </row>
@@ -2723,45 +2723,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.3874</v>
+        <v>0.3591</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.4111</v>
+        <v>0.443</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>-0.0237</v>
+        <v>-0.0839</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0588</v>
+        <v>0.0241</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.381</v>
+        <v>1.618</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.118</v>
+        <v>1.579</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.235</v>
+        <v>0.298</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0267</v>
+        <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>144 of 151</t>
+          <t>150 of 151</t>
         </is>
       </c>
     </row>
@@ -2771,202 +2771,106 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4155</v>
+        <v>0.3833</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.3732</v>
+        <v>0.4583</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.0423</v>
+        <v>-0.075</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0769</v>
+        <v>0.0333</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.805</v>
+        <v>2.149</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>0.968</v>
+        <v>2.625</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.107</v>
+        <v>0.333</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>146 of 151</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>Ryan Johnson</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>0.3822</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="G49" s="13" t="n">
-        <v>-0.0622</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>1.844</v>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L49" s="8" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="M49" s="8" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>149 of 151</t>
+          <t>151 of 151</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>Jeffrey Springs</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>0.3833</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>0.4583</v>
-      </c>
-      <c r="G50" s="13" t="n">
-        <v>-0.075</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>0.0333</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <v>2.149</v>
-      </c>
-      <c r="J50" s="7" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="L50" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>151 of 151</t>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Stoplight shading (Pitcher, CMD%, Model WHIP) reflects Score (Relative): MIN of each pitcher's percentile rank on CMD% (higher=better) and Model WHIP (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by Score (Relative) rank position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Score (Absolute) uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 20-day window). Rank (Absolute) shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Stoplight shading (Pitcher, CMD%, Model WHIP) reflects Score (Relative): MIN of each pitcher's percentile rank on CMD% (higher=better) and Model WHIP (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by Score (Relative) rank position.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Score (Absolute) uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 20-day window). Rank (Absolute) shows literal rank position within that league-wide pool.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+          <t>K%, BB%, HR% (Model WHIP inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (Model WHIP inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>Model WHIP = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. Actual WHIP is real (H+BB)/IP over the same window.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>Model WHIP = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. Actual WHIP is real (H+BB)/IP over the same window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 20-day window -- single-start genuine starters are included here. The league-wide absolute pool behind Score (Absolute)/Rank (Absolute) still requires 2+ starts, so a 1-start pitcher can appear here with a Score (Relative) but a blank Score (Absolute)/Rank (Absolute).</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,23 +478,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,12 +540,12 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Model WHIP</t>
+          <t>m_whip</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Actual WHIP</t>
+          <t>rl_whip</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -555,17 +555,17 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Score (Relative)</t>
+          <t>rel_score</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Score (Absolute)</t>
+          <t>abs_score</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Rank (Absolute)</t>
+          <t>abs_rank</t>
         </is>
       </c>
     </row>
@@ -575,45 +575,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>M. Liberatore</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.4805</v>
+        <v>0.4839</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3514</v>
+        <v>0.3424</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1291</v>
+        <v>0.1414</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0278</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1.216</v>
+        <v>1.148</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.436</v>
+        <v>0.406</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.913</v>
+        <v>0.9412</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.6267</v>
+        <v>0.7613</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>41 of 151</t>
+          <t>25 of 156</t>
         </is>
       </c>
     </row>
@@ -623,45 +623,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>R. Gasser</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>17</v>
+        <v>23.7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4745</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3487</v>
+        <v>0.3378</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1226</v>
+        <v>0.1367</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0455</v>
+        <v>0.0312</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.26</v>
+        <v>1.108</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.222</v>
+        <v>0.353</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.8696</v>
+        <v>0.902</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.5733</v>
+        <v>0.7419</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>46 of 151</t>
+          <t>27 of 156</t>
         </is>
       </c>
     </row>
@@ -671,45 +671,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>E. Sheehan</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.4636</v>
+        <v>0.4953</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.3576</v>
+        <v>0.3551</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.106</v>
+        <v>0.1402</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0233</v>
+        <v>0.0625</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.017</v>
+        <v>1.193</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>0.706</v>
+        <v>1.364</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.172</v>
+        <v>0.312</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8824</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.5467</v>
+        <v>0.6839</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51 of 151</t>
+          <t>34 of 156</t>
         </is>
       </c>
     </row>
@@ -719,45 +719,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>15.7</v>
+        <v>30.7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4619</v>
+        <v>0.4723</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3559</v>
+        <v>0.3362</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1059</v>
+        <v>0.1362</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.114</v>
+        <v>1.232</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.277</v>
+        <v>1.207</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.348</v>
+        <v>0.294</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8043</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.54</v>
+        <v>0.6065</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52 of 151</t>
+          <t>43 of 156</t>
         </is>
       </c>
     </row>
@@ -767,45 +767,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>C. Quantrill</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18.7</v>
+        <v>15.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.457</v>
+        <v>0.4619</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.354</v>
+        <v>0.3432</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1031</v>
+        <v>0.1186</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.013</v>
+        <v>0.0455</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.309</v>
+        <v>1.193</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.179</v>
+        <v>1.304</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.263</v>
+        <v>0.304</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7826</v>
+        <v>0.7647</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.4733</v>
+        <v>0.6323</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>64 of 151</t>
+          <t>39 of 156</t>
         </is>
       </c>
     </row>
@@ -815,45 +815,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>H. Greene</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4618</v>
+        <v>0.4749</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3282</v>
+        <v>0.3398</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1336</v>
+        <v>0.1351</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0533</v>
+        <v>0.0411</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.313</v>
+        <v>1.263</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.255</v>
+        <v>1.327</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.283</v>
+        <v>0.308</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.7609</v>
+        <v>0.7647</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.4667</v>
+        <v>0.5355</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>65 of 151</t>
+          <t>54 of 156</t>
         </is>
       </c>
     </row>
@@ -863,45 +863,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>C. Rea</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12.7</v>
+        <v>23</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4717</v>
+        <v>0.4713</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3821</v>
+        <v>0.3534</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0896</v>
+        <v>0.1178</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0444</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.307</v>
+        <v>1.211</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.026</v>
+        <v>1</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.214</v>
+        <v>0.23</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.7391</v>
+        <v>0.7451</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.4667</v>
+        <v>0.6194</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66 of 151</t>
+          <t>41 of 156</t>
         </is>
       </c>
     </row>
@@ -911,45 +911,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Javier Assad</t>
+          <t>G. Jump</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10</v>
+        <v>29.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4923</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3865</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1058</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0231</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.327</v>
+        <v>1.324</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.4</v>
+        <v>1.685</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.333</v>
+        <v>0.422</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7391</v>
+        <v>0.6863</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.4533</v>
+        <v>0.4323</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69 of 151</t>
+          <t>66 of 156</t>
         </is>
       </c>
     </row>
@@ -959,45 +959,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>J. Assad</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.4643</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3486</v>
+        <v>0.3611</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.16</v>
+        <v>0.1032</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.05</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.337</v>
+        <v>1.293</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.298</v>
+        <v>0.35</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.6957</v>
+        <v>0.6667</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.42</v>
+        <v>0.4774</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72 of 151</t>
+          <t>59 of 156</t>
         </is>
       </c>
     </row>
@@ -1007,41 +1007,47 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5</v>
+        <v>19.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4583</v>
+        <v>0.4669</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.375</v>
+        <v>0.331</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0833</v>
+        <v>0.1359</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0</v>
+        <v>0.0494</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.184</v>
+        <v>1.339</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.4</v>
+        <v>1.345</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.353</v>
+        <v>0.298</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6957</v>
-      </c>
-      <c r="M11" s="8" t="n"/>
-      <c r="N11" s="2" t="n"/>
+        <v>0.6667</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>68 of 156</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1049,45 +1055,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cade Povich</t>
+          <t>S. Drohan</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9</v>
+        <v>29.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.4643</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.381</v>
+        <v>0.3643</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.0351</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.209</v>
+        <v>1.111</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.556</v>
+        <v>1.261</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.435</v>
+        <v>0.357</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6304</v>
+        <v>0.6471</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.3867</v>
+        <v>0.4968</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77 of 151</t>
+          <t>55 of 156</t>
         </is>
       </c>
     </row>
@@ -1097,45 +1103,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>G. Rodriguez</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4513</v>
+        <v>0.4988</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3769</v>
+        <v>0.355</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.1439</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0101</v>
+        <v>0.0481</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.327</v>
+        <v>1.342</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.522</v>
+        <v>1.458</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.352</v>
+        <v>0.317</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6087</v>
+        <v>0.6471</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.3733</v>
+        <v>0.4129</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79 of 151</t>
+          <t>70 of 156</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1151,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Connor Prielipp</t>
+          <t>C. Prielipp</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1176,14 +1182,14 @@
         <v>0.235</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6087</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.3533</v>
+        <v>0.3484</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83 of 151</t>
+          <t>83 of 156</t>
         </is>
       </c>
     </row>
@@ -1193,47 +1199,41 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>B. Tidwell</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11.7</v>
+        <v>5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4305</v>
+        <v>0.4583</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3642</v>
+        <v>0.375</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.339</v>
+        <v>1.184</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.857</v>
+        <v>1.4</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.182</v>
+        <v>0.353</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>84 of 151</t>
-        </is>
-      </c>
+        <v>0.6078</v>
+      </c>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1241,45 +1241,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>B. Singer</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>23.7</v>
+        <v>30</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.441</v>
+        <v>0.4509</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3792</v>
+        <v>0.3758</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0618</v>
+        <v>0.0752</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.022</v>
+        <v>0.0161</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.226</v>
+        <v>1.243</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.014</v>
+        <v>1.3</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.246</v>
+        <v>0.315</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5686</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.3067</v>
+        <v>0.329</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87 of 151</t>
+          <t>88 of 156</t>
         </is>
       </c>
     </row>
@@ -1289,45 +1289,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Hunter Greene</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11.3</v>
+        <v>9</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4386</v>
+        <v>0.4558</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3567</v>
+        <v>0.381</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0819</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.0278</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.404</v>
+        <v>1.209</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.676</v>
+        <v>1.556</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.35</v>
+        <v>0.435</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3067</v>
+        <v>0.3161</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88 of 151</t>
+          <t>92 of 156</t>
         </is>
       </c>
     </row>
@@ -1335,9 +1335,9 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Jack Perkins</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1352,13 +1352,13 @@
       <c r="F18" s="4" t="n">
         <v>0.3738</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="5" t="n">
         <v>0.0735</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0.0595</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="6" t="n">
         <v>1.408</v>
       </c>
       <c r="J18" s="7" t="n">
@@ -1368,14 +1368,14 @@
         <v>0.294</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5294</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3</v>
+        <v>0.2645</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89 of 151</t>
+          <t>101 of 156</t>
         </is>
       </c>
     </row>
@@ -1383,47 +1383,47 @@
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Grant Holmes</t>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>T. McDonald</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>21.7</v>
+        <v>11</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4319</v>
+        <v>0.4733</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3721</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>0.0598</v>
+        <v>0.3053</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.1679</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0361</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>1.372</v>
+        <v>0.0488</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1.419</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.2</v>
+        <v>0.909</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.281</v>
+        <v>0.172</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.4783</v>
+        <v>0.5098</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.2867</v>
+        <v>0.2387</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>91 of 151</t>
+          <t>104 of 156</t>
         </is>
       </c>
     </row>
@@ -1433,45 +1433,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7.7</v>
+        <v>19</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4626</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3786</v>
+        <v>0.3822</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.0805</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0349</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>1.415</v>
+        <v>1.445</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.565</v>
+        <v>1.737</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.273</v>
+        <v>0.37</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.4348</v>
+        <v>0.4902</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.28</v>
+        <v>0.2194</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93 of 151</t>
+          <t>108 of 156</t>
         </is>
       </c>
     </row>
@@ -1481,45 +1481,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>R. Lopez</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4726</v>
+        <v>0.4392</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3562</v>
+        <v>0.3765</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.1164</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0462</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.493</v>
+        <v>1.293</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>2.125</v>
+        <v>1.6</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.423</v>
+        <v>0.381</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.3913</v>
+        <v>0.4706</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.1733</v>
+        <v>0.271</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>109 of 151</t>
+          <t>99 of 156</t>
         </is>
       </c>
     </row>
@@ -1529,45 +1529,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>G. Holmes</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>20.3</v>
+        <v>26.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4626</v>
+        <v>0.4274</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.4138</v>
+        <v>0.3656</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.0489</v>
+        <v>0.0618</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.0283</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.511</v>
+        <v>1.395</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.82</v>
+        <v>1.312</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.419</v>
+        <v>0.303</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.3261</v>
+        <v>0.451</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.1467</v>
+        <v>0.2645</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>115 of 151</t>
+          <t>100 of 156</t>
         </is>
       </c>
     </row>
@@ -1577,45 +1577,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Zebby Matthews</t>
+          <t>D. Peterson</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>16</v>
+        <v>23.7</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4436</v>
+        <v>0.441</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.4023</v>
+        <v>0.3792</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0414</v>
+        <v>0.0618</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0299</v>
+        <v>0.022</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.368</v>
+        <v>1.226</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.312</v>
+        <v>1.014</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.279</v>
+        <v>0.246</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.3261</v>
+        <v>0.4314</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.1667</v>
+        <v>0.2581</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>110 of 151</t>
+          <t>102 of 156</t>
         </is>
       </c>
     </row>
@@ -1625,45 +1625,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Luinder Avila</t>
+          <t>R. Stock</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>13.3</v>
+        <v>8</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4726</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.3562</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.1164</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.025</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.535</v>
+        <v>1.493</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.575</v>
+        <v>2.125</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.3</v>
+        <v>0.423</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.3043</v>
+        <v>0.4314</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.1267</v>
+        <v>0.1806</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>119 of 151</t>
+          <t>116 of 156</t>
         </is>
       </c>
     </row>
@@ -1673,45 +1673,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4251</v>
+        <v>0.4468</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3846</v>
+        <v>0.386</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.0608</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.0366</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.496</v>
+        <v>1.48</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.667</v>
+        <v>1.684</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.356</v>
+        <v>0.37</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.3043</v>
+        <v>0.4118</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.16</v>
+        <v>0.1935</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>111 of 151</t>
+          <t>112 of 156</t>
         </is>
       </c>
     </row>
@@ -1721,45 +1721,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>G. Marquez</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.44</v>
+        <v>0.4624</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3908</v>
+        <v>0.3757</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.0867</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0238</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.536</v>
+        <v>1.525</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.552</v>
+        <v>1.929</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.2826</v>
+        <v>0.3529</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.12</v>
+        <v>0.1484</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>121 of 151</t>
+          <t>119 of 156</t>
         </is>
       </c>
     </row>
@@ -1769,45 +1769,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Reynaldo Lopez</t>
+          <t>S. Lugo</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.4417</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.3939</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.0478</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0435</v>
+        <v>0.0148</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.261</v>
+        <v>1.41</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.8</v>
+        <v>1.206</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.429</v>
+        <v>0.263</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.2826</v>
+        <v>0.3333</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.1533</v>
+        <v>0.1871</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>112 of 151</t>
+          <t>113 of 156</t>
         </is>
       </c>
     </row>
@@ -1817,45 +1817,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>24</v>
+        <v>13.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4327</v>
+        <v>0.443</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3926</v>
+        <v>0.3904</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.0526</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0106</v>
+        <v>0.0167</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.446</v>
+        <v>1.535</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.208</v>
+        <v>1.575</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.265</v>
+        <v>0.3</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.2609</v>
+        <v>0.3333</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1467</v>
+        <v>0.1419</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>114 of 151</t>
+          <t>121 of 156</t>
         </is>
       </c>
     </row>
@@ -1865,45 +1865,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Randy Vasquez</t>
+          <t>T. Yesavage</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13.7</v>
+        <v>20.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.475</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3584</v>
+        <v>0.4028</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0722</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.0361</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.563</v>
+        <v>1.557</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.585</v>
+        <v>1.377</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.1</v>
+        <v>0.256</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.2609</v>
+        <v>0.3137</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1</v>
+        <v>0.1355</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>127 of 151</t>
+          <t>122 of 156</t>
         </is>
       </c>
     </row>
@@ -1913,45 +1913,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.451</v>
+        <v>0.4444</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3981</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.0463</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.1</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.578</v>
+        <v>1.136</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.756</v>
+        <v>1.05</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.325</v>
+        <v>0.267</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.2391</v>
+        <v>0.2941</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.0867</v>
+        <v>0.1613</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>131 of 151</t>
+          <t>118 of 156</t>
         </is>
       </c>
     </row>
@@ -1961,45 +1961,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4437</v>
+        <v>0.4162</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.404</v>
+        <v>0.3584</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0397</v>
+        <v>0.0578</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.0217</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.295</v>
+        <v>1.563</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.393</v>
+        <v>0.585</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.286</v>
+        <v>0.1</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.2391</v>
+        <v>0.2941</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.14</v>
+        <v>0.1226</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>117 of 151</t>
+          <t>126 of 156</t>
         </is>
       </c>
     </row>
@@ -2009,47 +2009,41 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>M. Englert</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.433</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3985</v>
+        <v>0.3059</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.2118</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0435</v>
+        <v>0.1304</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.356</v>
+        <v>1.589</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.529</v>
+        <v>1.8</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.381</v>
+        <v>0.333</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2174</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>122 of 151</t>
-        </is>
-      </c>
+        <v>0.2745</v>
+      </c>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2057,87 +2051,93 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>A. Alvarez</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.4208</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3696</v>
+        <v>0.3756</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.1196</v>
+        <v>0.0452</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.589</v>
+        <v>1.461</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.8</v>
+        <v>1.188</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.2174</v>
-      </c>
-      <c r="M33" s="8" t="n"/>
-      <c r="N33" s="2" t="n"/>
+        <v>0.2745</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>120 of 156</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Aaron Nola</t>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>A. Nola</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4313</v>
+        <v>0.4401</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.4066</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>0.0247</v>
+        <v>0.3965</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>0.0436</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.06519999999999999</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>1.414</v>
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>1.52</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.455</v>
+        <v>1.5</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.316</v>
+        <v>0.3</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.1957</v>
+        <v>0.2549</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1067</v>
+        <v>0.1355</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>126 of 151</t>
+          <t>123 of 156</t>
         </is>
       </c>
     </row>
@@ -2145,95 +2145,89 @@
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Slade Cecconi</t>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4891</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3512</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.3696</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>0.1196</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0682</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>1.596</v>
+        <v>0</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>1.589</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.1739</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>0.0667</v>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>135 of 151</t>
-        </is>
-      </c>
+        <v>0.2549</v>
+      </c>
+      <c r="M35" s="8" t="n"/>
+      <c r="N35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>Miles Mikolas</t>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>S. Cecconi</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4643</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3704</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.3512</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>0.1131</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>1.59</v>
+        <v>0.0682</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>1.596</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.867</v>
+        <v>2.16</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.351</v>
+        <v>0.367</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.1739</v>
+        <v>0.2157</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.08</v>
+        <v>0.0839</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>132 of 151</t>
+          <t>135 of 156</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2237,7 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>M. Barnett</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2253,35 +2247,35 @@
         <v>9.300000000000001</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4437</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.4156</v>
+        <v>0.404</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>-0.0065</v>
+        <v>0.0397</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.0732</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>1.34</v>
+        <v>1.295</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.071</v>
+        <v>1.393</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.217</v>
+        <v>0.286</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.1304</v>
+        <v>0.2157</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.0533</v>
+        <v>0.1161</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>136 of 151</t>
+          <t>128 of 156</t>
         </is>
       </c>
     </row>
@@ -2291,45 +2285,45 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Carson Whisenhunt</t>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>11.7</v>
+        <v>16.7</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4579</v>
+        <v>0.4713</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.4018</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.0607</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.0385</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>1.635</v>
+        <v>1.603</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>2.229</v>
+        <v>1.68</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.438</v>
+        <v>0.292</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.1304</v>
+        <v>0.1961</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.0533</v>
+        <v>0.0774</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>137 of 151</t>
+          <t>136 of 156</t>
         </is>
       </c>
     </row>
@@ -2339,45 +2333,45 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>12.3</v>
+        <v>11.7</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4579</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.3972</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0607</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0517</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1.494</v>
+        <v>1.635</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.784</v>
+        <v>2.229</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.351</v>
+        <v>0.438</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.1087</v>
+        <v>0.1765</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.0467</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>138 of 151</t>
+          <t>138 of 156</t>
         </is>
       </c>
     </row>
@@ -2387,45 +2381,45 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>M. Mikolas</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4286</v>
+        <v>0.3827</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.4206</v>
+        <v>0.3704</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0123</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0149</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1.673</v>
+        <v>1.59</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.353</v>
+        <v>1.867</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.25</v>
+        <v>0.351</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.1087</v>
+        <v>0.1569</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.0467</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>139 of 151</t>
+          <t>137 of 156</t>
         </is>
       </c>
     </row>
@@ -2435,45 +2429,45 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>W. Buehler</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>15</v>
+        <v>21.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4491</v>
+        <v>0.4227</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3862</v>
+        <v>0.4149</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.0629</v>
+        <v>0.0077</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0513</v>
+        <v>0.0309</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.708</v>
+        <v>1.7</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>2.533</v>
+        <v>1.734</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.448</v>
+        <v>0.308</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1373</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0581</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>140 of 151</t>
+          <t>140 of 156</t>
         </is>
       </c>
     </row>
@@ -2483,45 +2477,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Kohl Drake</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>16.7</v>
+        <v>19.3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4861</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.3622</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.1238</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0779</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.413</v>
+        <v>1.725</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.56</v>
+        <v>1.345</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.333</v>
+        <v>0.209</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1373</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0516</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>141 of 151</t>
+          <t>143 of 156</t>
         </is>
       </c>
     </row>
@@ -2531,45 +2525,45 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>17</v>
+        <v>24.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.3874</v>
+        <v>0.4246</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.4111</v>
+        <v>0.4092</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>-0.0237</v>
+        <v>0.0153</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.0588</v>
+        <v>0.0385</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.381</v>
+        <v>1.73</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1.118</v>
+        <v>1.541</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.235</v>
+        <v>0.273</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.1176</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.0267</v>
+        <v>0.0452</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>144 of 151</t>
+          <t>144 of 156</t>
         </is>
       </c>
     </row>
@@ -2579,45 +2573,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Jake Irvin</t>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>10.3</v>
+        <v>23.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4155</v>
+        <v>0.3879</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3732</v>
+        <v>0.3939</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.0423</v>
+        <v>-0.0061</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0769</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.805</v>
+        <v>1.367</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>0.968</v>
+        <v>1.071</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.107</v>
+        <v>0.229</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.1176</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.02</v>
+        <v>0.0387</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>146 of 151</t>
+          <t>147 of 156</t>
         </is>
       </c>
     </row>
@@ -2627,45 +2621,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Ronel Blanco</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>14.7</v>
+        <v>20</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4538</v>
+        <v>0.4296</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3739</v>
+        <v>0.3932</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.0798</v>
+        <v>0.0364</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0404</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.814</v>
+        <v>1.731</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>1.432</v>
+        <v>2.3</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.243</v>
+        <v>0.413</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.098</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.0387</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>148 of 151</t>
+          <t>146 of 156</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2669,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -2685,35 +2679,35 @@
         <v>12.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.3822</v>
+        <v>0.4091</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4182</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>-0.0622</v>
+        <v>-0.0091</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0345</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.844</v>
+        <v>1.494</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>2.108</v>
+        <v>1.784</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.0217</v>
+        <v>0.098</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.0067</v>
+        <v>0.0323</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>149 of 151</t>
+          <t>149 of 156</t>
         </is>
       </c>
     </row>
@@ -2723,45 +2717,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>K. Drake</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>19</v>
+        <v>16.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.3591</v>
+        <v>0.4167</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4263</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>-0.0839</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0241</v>
+        <v>0.0411</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.618</v>
+        <v>1.413</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.579</v>
+        <v>1.56</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.298</v>
+        <v>0.333</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0</v>
+        <v>0.0258</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>150 of 151</t>
+          <t>150 of 156</t>
         </is>
       </c>
     </row>
@@ -2771,108 +2765,355 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Z. Littell</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5.3</v>
+        <v>10.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.3833</v>
+        <v>0.4294</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.4583</v>
+        <v>0.3824</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>-0.075</v>
+        <v>0.0471</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.04</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>2.149</v>
+        <v>1.792</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>2.625</v>
+        <v>1.781</v>
       </c>
       <c r="K48" s="7" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>151 of 156</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>S. Bieber</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>-0.0479</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="J49" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>152 of 156</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>J. Irvin</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>153 of 156</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>S. Arrighetti</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>-0.0541</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>154 of 156</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>R. Johnson</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>1.835</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>1.657</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="L52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>155 of 156</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>J. Springs</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>2.032</v>
+      </c>
+      <c r="K53" s="7" t="n">
         <v>0.333</v>
       </c>
-      <c r="L48" s="8" t="n">
+      <c r="L53" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="8" t="n">
+      <c r="M53" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>151 of 151</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Stoplight shading (Pitcher, CMD%, Model WHIP) reflects Score (Relative): MIN of each pitcher's percentile rank on CMD% (higher=better) and Model WHIP (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by Score (Relative) rank position.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>Score (Absolute) uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 20-day window). Rank (Absolute) shows literal rank position within that league-wide pool.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>K%, BB%, HR% (Model WHIP inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>156 of 156</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Model WHIP = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. Actual WHIP is real (H+BB)/IP over the same window.</t>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 20-day window -- single-start genuine starters are included here. The league-wide absolute pool behind Score (Absolute)/Rank (Absolute) still requires 2+ starts, so a 1-start pitcher can appear here with a Score (Relative) but a blank Score (Absolute)/Rank (Absolute).</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>
       </c>
     </row>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -575,45 +575,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>M. Liberatore</t>
+          <t>R. Gasser</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>26</v>
+        <v>23.7</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.4839</v>
+        <v>0.4745</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3424</v>
+        <v>0.3378</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1414</v>
+        <v>0.1367</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.0312</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1.148</v>
+        <v>1.108</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.406</v>
+        <v>0.353</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9412</v>
+        <v>0.9038</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.7613</v>
+        <v>0.7372</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>25 of 156</t>
+          <t>29 of 157</t>
         </is>
       </c>
     </row>
@@ -623,45 +623,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>R. Gasser</t>
+          <t>E. Sheehan</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>23.7</v>
+        <v>18.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.4745</v>
+        <v>0.4953</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3378</v>
+        <v>0.3551</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1367</v>
+        <v>0.1402</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0625</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.108</v>
+        <v>1.193</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.31</v>
+        <v>1.364</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.353</v>
+        <v>0.312</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.902</v>
+        <v>0.9038</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.7419</v>
+        <v>0.6859</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>27 of 156</t>
+          <t>33 of 157</t>
         </is>
       </c>
     </row>
@@ -671,45 +671,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>E. Sheehan</t>
+          <t>T. Yesavage</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.4953</v>
+        <v>0.5149</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.3551</v>
+        <v>0.3498</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1402</v>
+        <v>0.165</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.0429</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.193</v>
+        <v>1.198</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1.364</v>
+        <v>1.071</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.312</v>
+        <v>0.263</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8824</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.6839</v>
+        <v>0.6795</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34 of 156</t>
+          <t>34 of 157</t>
         </is>
       </c>
     </row>
@@ -719,45 +719,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>K. Freeland</t>
+          <t>M. Liberatore</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>30.7</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4723</v>
+        <v>0.4805</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3362</v>
+        <v>0.3514</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1362</v>
+        <v>0.1291</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0325</v>
+        <v>0.0345</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.232</v>
+        <v>1.216</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.207</v>
+        <v>1.7</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.294</v>
+        <v>0.436</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.8269</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.6065</v>
+        <v>0.6474</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43 of 156</t>
+          <t>38 of 157</t>
         </is>
       </c>
     </row>
@@ -798,14 +798,14 @@
         <v>0.304</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7647</v>
+        <v>0.7692</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.6323</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39 of 156</t>
+          <t>40 of 157</t>
         </is>
       </c>
     </row>
@@ -815,45 +815,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>H. Greene</t>
+          <t>C. Rea</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>17.3</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4749</v>
+        <v>0.4713</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3398</v>
+        <v>0.3534</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1351</v>
+        <v>0.1178</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0444</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.263</v>
+        <v>1.211</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.327</v>
+        <v>1</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.308</v>
+        <v>0.23</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.7647</v>
+        <v>0.75</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5355</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54 of 156</t>
+          <t>42 of 157</t>
         </is>
       </c>
     </row>
@@ -863,45 +863,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>C. Rea</t>
+          <t>H. Greene</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>23</v>
+        <v>17.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4749</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3534</v>
+        <v>0.3398</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1178</v>
+        <v>0.1351</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0444</v>
+        <v>0.0411</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.211</v>
+        <v>1.263</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1</v>
+        <v>1.327</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.23</v>
+        <v>0.308</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.7451</v>
+        <v>0.7308</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.6194</v>
+        <v>0.5256</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41 of 156</t>
+          <t>53 of 157</t>
         </is>
       </c>
     </row>
@@ -911,45 +911,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>G. Jump</t>
+          <t>B. Tidwell</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>29.7</v>
+        <v>10.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4923</v>
+        <v>0.4762</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3865</v>
+        <v>0.3651</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1058</v>
+        <v>0.1111</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0231</v>
+        <v>0</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.324</v>
+        <v>1.026</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.685</v>
+        <v>1.125</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.422</v>
+        <v>0.323</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.6863</v>
+        <v>0.6923</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.4323</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66 of 156</t>
+          <t>51 of 157</t>
         </is>
       </c>
     </row>
@@ -963,41 +963,41 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4678</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3611</v>
+        <v>0.3684</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1032</v>
+        <v>0.0994</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0244</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.293</v>
+        <v>1.327</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>1.4</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.6667</v>
+        <v>0.6731</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.4774</v>
+        <v>0.4359</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59 of 156</t>
+          <t>65 of 157</t>
         </is>
       </c>
     </row>
@@ -1038,14 +1038,14 @@
         <v>0.298</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6667</v>
+        <v>0.6538</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.4258</v>
+        <v>0.4167</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68 of 156</t>
+          <t>69 of 157</t>
         </is>
       </c>
     </row>
@@ -1055,45 +1055,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>S. Drohan</t>
+          <t>G. Hughes</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>29.3</v>
+        <v>24.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4672</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3643</v>
+        <v>0.3712</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1</v>
+        <v>0.096</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0351</v>
+        <v>0.0196</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.111</v>
+        <v>1.254</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.261</v>
+        <v>1.378</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.357</v>
+        <v>0.338</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6471</v>
+        <v>0.6538</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.4968</v>
+        <v>0.4872</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55 of 156</t>
+          <t>57 of 157</t>
         </is>
       </c>
     </row>
@@ -1134,14 +1134,14 @@
         <v>0.317</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6471</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.4129</v>
+        <v>0.4038</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70 of 156</t>
+          <t>72 of 157</t>
         </is>
       </c>
     </row>
@@ -1151,45 +1151,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>C. Prielipp</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4902</v>
+        <v>0.4627</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3608</v>
+        <v>0.3735</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.1294</v>
+        <v>0.0892</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0288</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.365</v>
+        <v>1.334</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.125</v>
+        <v>1.308</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.235</v>
+        <v>0.309</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.3484</v>
+        <v>0.4231</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83 of 156</t>
+          <t>68 of 157</t>
         </is>
       </c>
     </row>
@@ -1199,41 +1199,47 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>B. Tidwell</t>
+          <t>C. Prielipp</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4583</v>
+        <v>0.4902</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.375</v>
+        <v>0.3608</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0833</v>
+        <v>0.1294</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.184</v>
+        <v>1.365</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.4</v>
+        <v>1.125</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.353</v>
+        <v>0.235</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.6078</v>
-      </c>
-      <c r="M15" s="8" t="n"/>
-      <c r="N15" s="2" t="n"/>
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>80 of 157</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1241,45 +1247,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>B. Singer</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>30</v>
+        <v>24.7</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4509</v>
+        <v>0.4485</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3758</v>
+        <v>0.3536</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0752</v>
+        <v>0.095</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.0297</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.243</v>
+        <v>1.379</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.3</v>
+        <v>1.257</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.315</v>
+        <v>0.274</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5686</v>
+        <v>0.5769</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.329</v>
+        <v>0.3077</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88 of 156</t>
+          <t>92 of 157</t>
         </is>
       </c>
     </row>
@@ -1289,45 +1295,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>C. Povich</t>
+          <t>G. Jump</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.4862</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.381</v>
+        <v>0.4009</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0853</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.028</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.209</v>
+        <v>1.393</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.556</v>
+        <v>1.792</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.435</v>
+        <v>0.44</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.549</v>
+        <v>0.5577</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3161</v>
+        <v>0.2756</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92 of 156</t>
+          <t>98 of 157</t>
         </is>
       </c>
     </row>
@@ -1337,45 +1343,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>J. Perkins</t>
+          <t>B. Singer</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4473</v>
+        <v>0.4509</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3738</v>
+        <v>0.3758</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0735</v>
+        <v>0.0752</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0595</v>
+        <v>0.0161</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.408</v>
+        <v>1.243</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.474</v>
+        <v>1.3</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.294</v>
+        <v>0.315</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5294</v>
+        <v>0.5385</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.2645</v>
+        <v>0.3397</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>101 of 156</t>
+          <t>83 of 157</t>
         </is>
       </c>
     </row>
@@ -1385,45 +1391,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>T. McDonald</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4733</v>
+        <v>0.4558</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3053</v>
+        <v>0.381</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.1679</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0488</v>
+        <v>0.0278</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.419</v>
+        <v>1.209</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.909</v>
+        <v>1.556</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.172</v>
+        <v>0.435</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.5098</v>
+        <v>0.5192</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.2387</v>
+        <v>0.3269</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>104 of 156</t>
+          <t>87 of 157</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1439,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Z. Matthews</t>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1443,35 +1449,35 @@
         <v>19</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4626</v>
+        <v>0.4473</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3822</v>
+        <v>0.3738</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>0.0805</v>
+        <v>0.0735</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.0595</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>1.445</v>
+        <v>1.408</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.737</v>
+        <v>1.474</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.37</v>
+        <v>0.294</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.4902</v>
+        <v>0.5</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.2194</v>
+        <v>0.25</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>108 of 156</t>
+          <t>104 of 157</t>
         </is>
       </c>
     </row>
@@ -1481,45 +1487,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>R. Lopez</t>
+          <t>S. Drohan</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4392</v>
+        <v>0.4529</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3765</v>
+        <v>0.3882</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.0337</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.293</v>
+        <v>1.168</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.6</v>
+        <v>1.391</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.381</v>
+        <v>0.404</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.4706</v>
+        <v>0.4808</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.271</v>
+        <v>0.2756</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>99 of 156</t>
+          <t>99 of 157</t>
         </is>
       </c>
     </row>
@@ -1529,45 +1535,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>G. Holmes</t>
+          <t>T. McDonald</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>26.7</v>
+        <v>11</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4274</v>
+        <v>0.4733</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3656</v>
+        <v>0.3053</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.0618</v>
+        <v>0.1679</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0283</v>
+        <v>0.0488</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.395</v>
+        <v>1.419</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.312</v>
+        <v>0.909</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.303</v>
+        <v>0.172</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.451</v>
+        <v>0.4615</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.2645</v>
+        <v>0.2244</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>100 of 156</t>
+          <t>107 of 157</t>
         </is>
       </c>
     </row>
@@ -1577,45 +1583,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>D. Peterson</t>
+          <t>G. Holmes</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>23.7</v>
+        <v>26.7</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.441</v>
+        <v>0.4274</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3792</v>
+        <v>0.3656</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>0.0618</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.022</v>
+        <v>0.0283</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.226</v>
+        <v>1.395</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.014</v>
+        <v>1.312</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.246</v>
+        <v>0.303</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4314</v>
+        <v>0.4615</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.2581</v>
+        <v>0.2692</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>102 of 156</t>
+          <t>100 of 157</t>
         </is>
       </c>
     </row>
@@ -1625,45 +1631,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>R. Stock</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4726</v>
+        <v>0.4626</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3562</v>
+        <v>0.3822</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.1164</v>
+        <v>0.0805</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0349</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.493</v>
+        <v>1.445</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>2.125</v>
+        <v>1.737</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.423</v>
+        <v>0.37</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4314</v>
+        <v>0.4423</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.1806</v>
+        <v>0.2051</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>116 of 156</t>
+          <t>111 of 157</t>
         </is>
       </c>
     </row>
@@ -1673,45 +1679,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>D. Kremer</t>
+          <t>D. Peterson</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>19</v>
+        <v>23.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4468</v>
+        <v>0.441</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.386</v>
+        <v>0.3792</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.0608</v>
+        <v>0.0618</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0366</v>
+        <v>0.022</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.48</v>
+        <v>1.226</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.684</v>
+        <v>1.014</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.37</v>
+        <v>0.246</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.4118</v>
+        <v>0.4423</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.1935</v>
+        <v>0.2628</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>112 of 156</t>
+          <t>102 of 157</t>
         </is>
       </c>
     </row>
@@ -1721,45 +1727,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>G. Marquez</t>
+          <t>R. Stock</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4624</v>
+        <v>0.4726</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3757</v>
+        <v>0.3562</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0867</v>
+        <v>0.1164</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.025</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.525</v>
+        <v>1.493</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.929</v>
+        <v>2.125</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.37</v>
+        <v>0.423</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.3529</v>
+        <v>0.4038</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.1484</v>
+        <v>0.1667</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>119 of 156</t>
+          <t>120 of 157</t>
         </is>
       </c>
     </row>
@@ -1800,14 +1806,14 @@
         <v>0.263</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.3462</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.1871</v>
+        <v>0.1859</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>113 of 156</t>
+          <t>115 of 157</t>
         </is>
       </c>
     </row>
@@ -1817,45 +1823,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>L. Avila</t>
+          <t>G. Marquez</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4624</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.3757</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0867</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.535</v>
+        <v>1.525</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.575</v>
+        <v>1.929</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.3269</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1419</v>
+        <v>0.141</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>121 of 156</t>
+          <t>123 of 157</t>
         </is>
       </c>
     </row>
@@ -1865,45 +1871,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>T. Yesavage</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>20.3</v>
+        <v>13.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.475</v>
+        <v>0.4444</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4028</v>
+        <v>0.3981</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0722</v>
+        <v>0.0463</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0361</v>
+        <v>0.1</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.557</v>
+        <v>1.136</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.377</v>
+        <v>1.05</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.256</v>
+        <v>0.267</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.3137</v>
+        <v>0.3077</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1355</v>
+        <v>0.1603</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>122 of 156</t>
+          <t>121 of 157</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1919,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>E. Fedde</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1923,35 +1929,35 @@
         <v>13.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.443</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3904</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0526</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0167</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.136</v>
+        <v>1.535</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.05</v>
+        <v>1.575</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.2941</v>
+        <v>0.3077</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1613</v>
+        <v>0.1346</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>118 of 156</t>
+          <t>125 of 157</t>
         </is>
       </c>
     </row>
@@ -1961,45 +1967,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>R. Vasquez</t>
+          <t>A. Alvarez</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>13.7</v>
+        <v>16</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.4208</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3584</v>
+        <v>0.3756</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0452</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.563</v>
+        <v>1.461</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.585</v>
+        <v>1.188</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.2941</v>
+        <v>0.2885</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.1226</v>
+        <v>0.1474</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>126 of 156</t>
+          <t>122 of 157</t>
         </is>
       </c>
     </row>
@@ -2009,41 +2015,47 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>M. Englert</t>
+          <t>W. Buehler</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>19.3</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3059</v>
+        <v>0.3908</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.2118</v>
+        <v>0.0492</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1304</v>
+        <v>0.0238</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.589</v>
+        <v>1.536</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.8</v>
+        <v>1.552</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2745</v>
-      </c>
-      <c r="M32" s="8" t="n"/>
-      <c r="N32" s="2" t="n"/>
+        <v>0.2885</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>126 of 157</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2051,45 +2063,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>A. Alvarez</t>
+          <t>A. Nola</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.4401</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3756</v>
+        <v>0.3965</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0436</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.461</v>
+        <v>1.52</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.188</v>
+        <v>1.5</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.2745</v>
+        <v>0.2692</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1484</v>
+        <v>0.1346</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>120 of 156</t>
+          <t>124 of 157</t>
         </is>
       </c>
     </row>
@@ -2099,45 +2111,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>A. Nola</t>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>28</v>
+        <v>13.7</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4401</v>
+        <v>0.4162</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3965</v>
+        <v>0.3584</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.0436</v>
+        <v>0.0578</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0217</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.52</v>
+        <v>1.563</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.5</v>
+        <v>0.585</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.2549</v>
+        <v>0.2692</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1355</v>
+        <v>0.109</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>123 of 156</t>
+          <t>129 of 157</t>
         </is>
       </c>
     </row>
@@ -2147,41 +2159,47 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Q. Mathews</t>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5</v>
+        <v>13.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.451</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3696</v>
+        <v>0.4078</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.1196</v>
+        <v>0.0431</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.589</v>
+        <v>1.578</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.8</v>
+        <v>1.756</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.375</v>
+        <v>0.325</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.2549</v>
-      </c>
-      <c r="M35" s="8" t="n"/>
-      <c r="N35" s="2" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>131 of 157</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2189,93 +2207,87 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>S. Cecconi</t>
+          <t>M. Englert</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3059</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.1131</v>
+        <v>0.2118</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.1304</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.596</v>
+        <v>1.589</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.367</v>
+        <v>0.333</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.2157</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0.0839</v>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>135 of 156</t>
-        </is>
-      </c>
+        <v>0.2308</v>
+      </c>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>M. Barnett</t>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>R. Lopez</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4437</v>
+        <v>0.4335</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>0.0397</v>
+        <v>0.3931</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>0.0405</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0732</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>1.295</v>
+        <v>0.0435</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>1.261</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.393</v>
+        <v>1.8</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.286</v>
+        <v>0.429</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.2157</v>
+        <v>0.2115</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.1161</v>
+        <v>0.1154</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>128 of 156</t>
+          <t>127 of 157</t>
         </is>
       </c>
     </row>
@@ -2285,47 +2297,41 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>B. Sproat</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>16.7</v>
+        <v>5</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4891</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.4018</v>
+        <v>0.3696</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.1196</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0385</v>
+        <v>0</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>1.603</v>
+        <v>1.589</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.292</v>
+        <v>0.375</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.1961</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>0.0774</v>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>136 of 156</t>
-        </is>
-      </c>
+        <v>0.2115</v>
+      </c>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2333,45 +2339,45 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>M. Barnett</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>11.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4579</v>
+        <v>0.4437</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.404</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.0607</v>
+        <v>0.0397</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.0732</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1.635</v>
+        <v>1.295</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>2.229</v>
+        <v>1.393</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.438</v>
+        <v>0.286</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.1765</v>
+        <v>0.1923</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>138 of 156</t>
+          <t>130 of 157</t>
         </is>
       </c>
     </row>
@@ -2381,45 +2387,45 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>M. Mikolas</t>
+          <t>S. Cecconi</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4643</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3512</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.1131</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0682</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1.59</v>
+        <v>1.596</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.867</v>
+        <v>2.16</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.351</v>
+        <v>0.367</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.1569</v>
+        <v>0.1731</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>137 of 156</t>
+          <t>138 of 157</t>
         </is>
       </c>
     </row>
@@ -2429,45 +2435,45 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>W. Buehler</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>21.3</v>
+        <v>11.7</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4227</v>
+        <v>0.4579</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.4149</v>
+        <v>0.3972</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.0077</v>
+        <v>0.0607</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0309</v>
+        <v>0.0517</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.7</v>
+        <v>1.635</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>1.734</v>
+        <v>2.229</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.308</v>
+        <v>0.438</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.1373</v>
+        <v>0.1538</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.0581</v>
+        <v>0.0641</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>140 of 156</t>
+          <t>140 of 157</t>
         </is>
       </c>
     </row>
@@ -2508,14 +2514,14 @@
         <v>0.209</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.1373</v>
+        <v>0.1346</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.0516</v>
+        <v>0.0513</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>143 of 156</t>
+          <t>144 of 157</t>
         </is>
       </c>
     </row>
@@ -2525,45 +2531,45 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>M. Mikolas</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>24.7</v>
+        <v>15</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.4246</v>
+        <v>0.3827</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.4092</v>
+        <v>0.3704</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.0153</v>
+        <v>0.0123</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.0385</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1.541</v>
+        <v>1.867</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.273</v>
+        <v>0.351</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.1176</v>
+        <v>0.1346</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.0452</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>144 of 156</t>
+          <t>139 of 157</t>
         </is>
       </c>
     </row>
@@ -2573,45 +2579,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>T. Sugano</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>23.3</v>
+        <v>24.7</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.3879</v>
+        <v>0.4246</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3939</v>
+        <v>0.4092</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>-0.0061</v>
+        <v>0.0153</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0385</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.367</v>
+        <v>1.73</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.071</v>
+        <v>1.541</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.229</v>
+        <v>0.273</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.1176</v>
+        <v>0.1154</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0449</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>147 of 156</t>
+          <t>145 of 157</t>
         </is>
       </c>
     </row>
@@ -2621,45 +2627,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>M. Lorenzen</t>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4296</v>
+        <v>0.3879</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3932</v>
+        <v>0.3939</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.0364</v>
+        <v>-0.0061</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0404</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.731</v>
+        <v>1.367</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>2.3</v>
+        <v>1.071</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.413</v>
+        <v>0.229</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.098</v>
+        <v>0.1154</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.0387</v>
+        <v>0.0385</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>146 of 156</t>
+          <t>148 of 157</t>
         </is>
       </c>
     </row>
@@ -2669,45 +2675,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>M. Keller</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>12.3</v>
+        <v>20</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4296</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.3932</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0364</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0404</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.494</v>
+        <v>1.731</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>1.784</v>
+        <v>2.3</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.351</v>
+        <v>0.413</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.098</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.0323</v>
+        <v>0.0385</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>149 of 156</t>
+          <t>147 of 157</t>
         </is>
       </c>
     </row>
@@ -2717,45 +2723,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>K. Drake</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>16.7</v>
+        <v>12.3</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4091</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.4182</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0345</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.413</v>
+        <v>1.494</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.56</v>
+        <v>1.784</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.333</v>
+        <v>0.351</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.0784</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0258</v>
+        <v>0.0321</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>150 of 156</t>
+          <t>150 of 157</t>
         </is>
       </c>
     </row>
@@ -2765,45 +2771,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Z. Littell</t>
+          <t>K. Drake</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>10.7</v>
+        <v>16.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4294</v>
+        <v>0.4167</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.3824</v>
+        <v>0.4263</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.0471</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.04</v>
+        <v>0.0411</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.792</v>
+        <v>1.413</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.781</v>
+        <v>1.56</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.0588</v>
+        <v>0.0769</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0194</v>
+        <v>0.0256</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>151 of 156</t>
+          <t>151 of 157</t>
         </is>
       </c>
     </row>
@@ -2844,14 +2850,14 @@
         <v>0.282</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.0385</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.0129</v>
+        <v>0.0128</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>152 of 156</t>
+          <t>152 of 157</t>
         </is>
       </c>
     </row>
@@ -2861,45 +2867,45 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>Z. Littell</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.4155</v>
+        <v>0.4294</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.3732</v>
+        <v>0.3824</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.0423</v>
+        <v>0.0471</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.0769</v>
+        <v>0.04</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.805</v>
+        <v>1.792</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>0.968</v>
+        <v>1.781</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.107</v>
+        <v>0.286</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>0.0392</v>
+        <v>0.0385</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.0129</v>
+        <v>0.0128</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>153 of 156</t>
+          <t>153 of 157</t>
         </is>
       </c>
     </row>
@@ -2940,14 +2946,14 @@
         <v>0.2</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.0196</v>
+        <v>0.0192</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.0065</v>
+        <v>0.0064</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>154 of 156</t>
+          <t>154 of 157</t>
         </is>
       </c>
     </row>
@@ -2957,45 +2963,45 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>R. Johnson</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>22.3</v>
+        <v>10.3</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.384</v>
+        <v>0.4155</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.451</v>
+        <v>0.3732</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>-0.067</v>
+        <v>0.0423</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0769</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1.835</v>
+        <v>1.805</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>1.657</v>
+        <v>0.968</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>0.262</v>
+        <v>0.107</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>0</v>
+        <v>0.0192</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0</v>
+        <v>0.0064</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>155 of 156</t>
+          <t>155 of 157</t>
         </is>
       </c>
     </row>
@@ -3005,35 +3011,35 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>J. Springs</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>10.3</v>
+        <v>17.3</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.401</v>
+        <v>0.3917</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.4213</v>
+        <v>0.4459</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>-0.0203</v>
+        <v>-0.0541</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.0408</v>
+        <v>0.05</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>1.892</v>
+        <v>1.78</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>2.032</v>
+        <v>1.788</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.333</v>
+        <v>0.294</v>
       </c>
       <c r="L53" s="8" t="n">
         <v>0</v>
@@ -3043,75 +3049,123 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>156 of 156</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
+          <t>156 of 157</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>J. Springs</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>2.032</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>157 of 157</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -575,45 +575,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>R. Gasser</t>
+          <t>T. Yesavage</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>23.7</v>
+        <v>18.7</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.4745</v>
+        <v>0.5149</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3378</v>
+        <v>0.3498</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1367</v>
+        <v>0.165</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0429</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1.108</v>
+        <v>1.198</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1.31</v>
+        <v>1.071</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.353</v>
+        <v>0.263</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9038</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.7372</v>
+        <v>0.6943</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>29 of 157</t>
+          <t>34 of 158</t>
         </is>
       </c>
     </row>
@@ -623,45 +623,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>E. Sheehan</t>
+          <t>N. Schultz</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>18.3</v>
+        <v>7.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.4953</v>
+        <v>0.4767</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3551</v>
+        <v>0.3488</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1402</v>
+        <v>0.1279</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.0244</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.193</v>
+        <v>1.166</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.364</v>
+        <v>2.455</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.312</v>
+        <v>0.5</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.9038</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.6859</v>
+        <v>0.7006</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>33 of 157</t>
+          <t>33 of 158</t>
         </is>
       </c>
     </row>
@@ -671,45 +671,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>T. Yesavage</t>
+          <t>M. Liberatore</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>18.7</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.5149</v>
+        <v>0.4805</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.3498</v>
+        <v>0.3514</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.165</v>
+        <v>0.1291</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0429</v>
+        <v>0.0345</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.198</v>
+        <v>1.216</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1.071</v>
+        <v>1.7</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.263</v>
+        <v>0.436</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8269</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.6795</v>
+        <v>0.6561</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34 of 157</t>
+          <t>38 of 158</t>
         </is>
       </c>
     </row>
@@ -719,45 +719,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>M. Liberatore</t>
+          <t>C. Quantrill</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>20</v>
+        <v>15.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4805</v>
+        <v>0.4619</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3514</v>
+        <v>0.3432</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1291</v>
+        <v>0.1186</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0455</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.216</v>
+        <v>1.193</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.7</v>
+        <v>1.304</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.436</v>
+        <v>0.304</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8269</v>
+        <v>0.8077</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.6474</v>
+        <v>0.6306</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38 of 157</t>
+          <t>41 of 158</t>
         </is>
       </c>
     </row>
@@ -767,45 +767,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>C. Quantrill</t>
+          <t>C. Rea</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>15.3</v>
+        <v>23</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4619</v>
+        <v>0.4713</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3432</v>
+        <v>0.3534</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1186</v>
+        <v>0.1178</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0455</v>
+        <v>0.0444</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.193</v>
+        <v>1.211</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.304</v>
+        <v>1</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.304</v>
+        <v>0.23</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7692</v>
+        <v>0.7885</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6115</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40 of 157</t>
+          <t>43 of 158</t>
         </is>
       </c>
     </row>
@@ -815,45 +815,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>C. Rea</t>
+          <t>R. Gasser</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23</v>
+        <v>20.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4704</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3534</v>
+        <v>0.3551</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1178</v>
+        <v>0.1153</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0444</v>
+        <v>0.0125</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.211</v>
+        <v>1.06</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1</v>
+        <v>1.113</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.23</v>
+        <v>0.316</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>0.75</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.5924</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42 of 157</t>
+          <t>45 of 158</t>
         </is>
       </c>
     </row>
@@ -897,11 +897,11 @@
         <v>0.7308</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.5256</v>
+        <v>0.5414</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53 of 157</t>
+          <t>51 of 158</t>
         </is>
       </c>
     </row>
@@ -911,45 +911,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>B. Tidwell</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10.7</v>
+        <v>18.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4762</v>
+        <v>0.4618</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3651</v>
+        <v>0.3282</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1111</v>
+        <v>0.1336</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
+        <v>0.0533</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.026</v>
+        <v>1.313</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.125</v>
+        <v>1.255</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.323</v>
+        <v>0.283</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.6923</v>
+        <v>0.7115</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.4459</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51 of 157</t>
+          <t>66 of 158</t>
         </is>
       </c>
     </row>
@@ -959,45 +959,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>J. Assad</t>
+          <t>B. Tidwell</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4762</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3651</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1111</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0244</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.327</v>
+        <v>1.026</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.4</v>
+        <v>1.125</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.6731</v>
+        <v>0.7115</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.4359</v>
+        <v>0.5414</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65 of 157</t>
+          <t>52 of 158</t>
         </is>
       </c>
     </row>
@@ -1007,45 +1007,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>T. Phillips</t>
+          <t>J. Assad</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>19.3</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4669</v>
+        <v>0.4678</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.331</v>
+        <v>0.3684</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1359</v>
+        <v>0.0994</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0494</v>
+        <v>0.0244</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.339</v>
+        <v>1.327</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.345</v>
+        <v>1.4</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.298</v>
+        <v>0.333</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6538</v>
+        <v>0.6731</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.4167</v>
+        <v>0.4204</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69 of 157</t>
+          <t>70 of 158</t>
         </is>
       </c>
     </row>
@@ -1089,11 +1089,11 @@
         <v>0.6538</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.4872</v>
+        <v>0.4841</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57 of 157</t>
+          <t>59 of 158</t>
         </is>
       </c>
     </row>
@@ -1137,11 +1137,11 @@
         <v>0.6346000000000001</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.4038</v>
+        <v>0.3949</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72 of 157</t>
+          <t>75 of 158</t>
         </is>
       </c>
     </row>
@@ -1151,45 +1151,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>D. Kremer</t>
+          <t>E. Sheehan</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4627</v>
+        <v>0.4643</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3735</v>
+        <v>0.3661</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0892</v>
+        <v>0.0982</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.0833</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.334</v>
+        <v>1.345</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.308</v>
+        <v>1.615</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.309</v>
+        <v>0.333</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>0.6153999999999999</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.4231</v>
+        <v>0.3822</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68 of 157</t>
+          <t>76 of 158</t>
         </is>
       </c>
     </row>
@@ -1199,45 +1199,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>C. Prielipp</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4902</v>
+        <v>0.4627</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3608</v>
+        <v>0.3735</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1294</v>
+        <v>0.0892</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0288</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.365</v>
+        <v>1.334</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.125</v>
+        <v>1.308</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.235</v>
+        <v>0.309</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.5962</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.3526</v>
+        <v>0.4013</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80 of 157</t>
+          <t>74 of 158</t>
         </is>
       </c>
     </row>
@@ -1247,45 +1247,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>K. Freeland</t>
+          <t>C. Prielipp</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>24.7</v>
+        <v>16</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4485</v>
+        <v>0.4902</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3536</v>
+        <v>0.3608</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.095</v>
+        <v>0.1294</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.0492</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.379</v>
+        <v>1.365</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.257</v>
+        <v>1.125</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.274</v>
+        <v>0.235</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5769</v>
+        <v>0.5962</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.3077</v>
+        <v>0.3439</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92 of 157</t>
+          <t>84 of 158</t>
         </is>
       </c>
     </row>
@@ -1295,45 +1295,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>G. Jump</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24</v>
+        <v>24.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4862</v>
+        <v>0.4485</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.4009</v>
+        <v>0.3536</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0853</v>
+        <v>0.095</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.028</v>
+        <v>0.0297</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.393</v>
+        <v>1.379</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.792</v>
+        <v>1.257</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.44</v>
+        <v>0.274</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5577</v>
+        <v>0.5769</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.2756</v>
+        <v>0.3185</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98 of 157</t>
+          <t>91 of 158</t>
         </is>
       </c>
     </row>
@@ -1343,45 +1343,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>B. Singer</t>
+          <t>G. Jump</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4509</v>
+        <v>0.4862</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3758</v>
+        <v>0.4009</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0752</v>
+        <v>0.0853</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.028</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.243</v>
+        <v>1.393</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.3</v>
+        <v>1.792</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.315</v>
+        <v>0.44</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5385</v>
+        <v>0.5577</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3397</v>
+        <v>0.2866</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>83 of 157</t>
+          <t>97 of 158</t>
         </is>
       </c>
     </row>
@@ -1391,45 +1391,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>C. Povich</t>
+          <t>B. Singer</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.4509</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.381</v>
+        <v>0.3758</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0752</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.0161</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.209</v>
+        <v>1.243</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.556</v>
+        <v>1.3</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.435</v>
+        <v>0.315</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>0.5192</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3269</v>
+        <v>0.3439</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>87 of 157</t>
+          <t>83 of 158</t>
         </is>
       </c>
     </row>
@@ -1439,45 +1439,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>J. Perkins</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4473</v>
+        <v>0.4558</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3738</v>
+        <v>0.381</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>0.0735</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0595</v>
+        <v>0.0278</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>1.408</v>
+        <v>1.209</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.474</v>
+        <v>1.556</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.294</v>
+        <v>0.435</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.25</v>
+        <v>0.3376</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>104 of 157</t>
+          <t>86 of 158</t>
         </is>
       </c>
     </row>
@@ -1487,45 +1487,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>S. Drohan</t>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4529</v>
+        <v>0.4473</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.3738</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0735</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0337</v>
+        <v>0.0595</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.168</v>
+        <v>1.408</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.391</v>
+        <v>1.474</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.404</v>
+        <v>0.294</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>0.4808</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.2756</v>
+        <v>0.2611</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>99 of 157</t>
+          <t>101 of 158</t>
         </is>
       </c>
     </row>
@@ -1535,45 +1535,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>T. McDonald</t>
+          <t>S. Drohan</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4733</v>
+        <v>0.4529</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3053</v>
+        <v>0.3882</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.1679</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0488</v>
+        <v>0.0337</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.419</v>
+        <v>1.168</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.909</v>
+        <v>1.391</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.172</v>
+        <v>0.404</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4615</v>
+        <v>0.4423</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.2244</v>
+        <v>0.2675</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>107 of 157</t>
+          <t>100 of 158</t>
         </is>
       </c>
     </row>
@@ -1583,45 +1583,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>G. Holmes</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>26.7</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4274</v>
+        <v>0.4626</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3656</v>
+        <v>0.3822</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0618</v>
+        <v>0.0805</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0283</v>
+        <v>0.0349</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.395</v>
+        <v>1.445</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.312</v>
+        <v>1.737</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.303</v>
+        <v>0.37</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4615</v>
+        <v>0.4423</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.2692</v>
+        <v>0.2038</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>100 of 157</t>
+          <t>112 of 158</t>
         </is>
       </c>
     </row>
@@ -1631,45 +1631,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Z. Matthews</t>
+          <t>G. Holmes</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>19</v>
+        <v>26.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4626</v>
+        <v>0.4274</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3822</v>
+        <v>0.3656</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0805</v>
+        <v>0.0618</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.0283</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.445</v>
+        <v>1.395</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.737</v>
+        <v>1.312</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.37</v>
+        <v>0.303</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4423</v>
+        <v>0.4038</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.2051</v>
+        <v>0.2484</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>111 of 157</t>
+          <t>103 of 158</t>
         </is>
       </c>
     </row>
@@ -1710,14 +1710,14 @@
         <v>0.246</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.4423</v>
+        <v>0.3846</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.2628</v>
+        <v>0.242</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>102 of 157</t>
+          <t>104 of 158</t>
         </is>
       </c>
     </row>
@@ -1758,14 +1758,14 @@
         <v>0.423</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.4038</v>
+        <v>0.3846</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.1667</v>
+        <v>0.1592</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>120 of 157</t>
+          <t>121 of 158</t>
         </is>
       </c>
     </row>
@@ -1779,41 +1779,41 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4417</v>
+        <v>0.4381</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3939</v>
+        <v>0.3876</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0478</v>
+        <v>0.0505</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0148</v>
+        <v>0.0086</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.41</v>
+        <v>1.435</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.206</v>
+        <v>1.167</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.263</v>
+        <v>0.259</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.3462</v>
+        <v>0.3269</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.1859</v>
+        <v>0.1847</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>115 of 157</t>
+          <t>115 of 158</t>
         </is>
       </c>
     </row>
@@ -1823,45 +1823,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>G. Marquez</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4624</v>
+        <v>0.443</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3757</v>
+        <v>0.3904</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0867</v>
+        <v>0.0526</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0167</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.525</v>
+        <v>1.535</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.929</v>
+        <v>1.575</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.3269</v>
+        <v>0.3077</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.141</v>
+        <v>0.1338</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>123 of 157</t>
+          <t>124 of 158</t>
         </is>
       </c>
     </row>
@@ -1902,14 +1902,14 @@
         <v>0.267</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.3077</v>
+        <v>0.2885</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1603</v>
+        <v>0.1592</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>121 of 157</t>
+          <t>120 of 158</t>
         </is>
       </c>
     </row>
@@ -1919,45 +1919,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>L. Avila</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13.3</v>
+        <v>27.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4632</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.3725</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0907</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0367</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.535</v>
+        <v>1.548</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.575</v>
+        <v>1.337</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.3</v>
+        <v>0.275</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.3077</v>
+        <v>0.2885</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1346</v>
+        <v>0.1274</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>125 of 157</t>
+          <t>126 of 158</t>
         </is>
       </c>
     </row>
@@ -1998,14 +1998,14 @@
         <v>0.25</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.2885</v>
+        <v>0.2692</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.1474</v>
+        <v>0.1465</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>122 of 157</t>
+          <t>122 of 158</t>
         </is>
       </c>
     </row>
@@ -2015,45 +2015,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>W. Buehler</t>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>19.3</v>
+        <v>13.7</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.44</v>
+        <v>0.4162</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3908</v>
+        <v>0.3584</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.0578</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0238</v>
+        <v>0.0217</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.536</v>
+        <v>1.563</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.552</v>
+        <v>0.585</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2885</v>
+        <v>0.2692</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.1282</v>
+        <v>0.1083</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>126 of 157</t>
+          <t>130 of 158</t>
         </is>
       </c>
     </row>
@@ -2063,45 +2063,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>A. Nola</t>
+          <t>G. Marquez</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>28</v>
+        <v>5.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4401</v>
+        <v>0.4333</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3965</v>
+        <v>0.3889</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0436</v>
+        <v>0.0444</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.52</v>
+        <v>1.414</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.5</v>
+        <v>1.875</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.2692</v>
+        <v>0.25</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1346</v>
+        <v>0.1401</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>124 of 157</t>
+          <t>123 of 158</t>
         </is>
       </c>
     </row>
@@ -2111,45 +2111,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>R. Vasquez</t>
+          <t>A. Nola</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>13.7</v>
+        <v>28</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.4401</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3584</v>
+        <v>0.3965</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0436</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.563</v>
+        <v>1.52</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.585</v>
+        <v>1.5</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.2692</v>
+        <v>0.2308</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.109</v>
+        <v>0.1274</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>129 of 157</t>
+          <t>125 of 158</t>
         </is>
       </c>
     </row>
@@ -2159,47 +2159,41 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>B. Sproat</t>
+          <t>M. Englert</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>13.7</v>
+        <v>5</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.451</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3059</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.2118</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.1304</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.578</v>
+        <v>1.589</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.756</v>
+        <v>1.8</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.325</v>
+        <v>0.333</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>0.1026</v>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>131 of 157</t>
-        </is>
-      </c>
+        <v>0.2308</v>
+      </c>
+      <c r="M35" s="8" t="n"/>
+      <c r="N35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2207,41 +2201,47 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>M. Englert</t>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5</v>
+        <v>13.7</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.451</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3059</v>
+        <v>0.4078</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.2118</v>
+        <v>0.0431</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.1304</v>
+        <v>0.0312</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.589</v>
+        <v>1.578</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.8</v>
+        <v>1.756</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.333</v>
+        <v>0.325</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="M36" s="8" t="n"/>
-      <c r="N36" s="2" t="n"/>
+        <v>0.2115</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>132 of 158</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2249,47 +2249,41 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>R. Lopez</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.4891</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.3696</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.1196</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0435</v>
+        <v>0</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>1.261</v>
+        <v>1.589</v>
       </c>
       <c r="J37" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>0.2115</v>
       </c>
-      <c r="M37" s="8" t="n">
-        <v>0.1154</v>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>127 of 157</t>
-        </is>
-      </c>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2297,41 +2291,47 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Q. Mathews</t>
+          <t>W. Buehler</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5</v>
+        <v>25.3</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.4371</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3696</v>
+        <v>0.3943</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.1196</v>
+        <v>0.0428</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0</v>
+        <v>0.0187</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>1.589</v>
+        <v>1.462</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.8</v>
+        <v>1.382</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.375</v>
+        <v>0.284</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.2115</v>
-      </c>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="2" t="n"/>
+        <v>0.1923</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>127 of 158</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2339,45 +2339,45 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>M. Barnett</t>
+          <t>R. Lopez</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4437</v>
+        <v>0.4335</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.404</v>
+        <v>0.3931</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.0397</v>
+        <v>0.0405</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.0435</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>1.295</v>
+        <v>1.261</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.393</v>
+        <v>1.8</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.286</v>
+        <v>0.429</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.1923</v>
+        <v>0.1731</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.109</v>
+        <v>0.1083</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>130 of 157</t>
+          <t>129 of 158</t>
         </is>
       </c>
     </row>
@@ -2421,11 +2421,11 @@
         <v>0.1731</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>138 of 157</t>
+          <t>140 of 158</t>
         </is>
       </c>
     </row>
@@ -2435,45 +2435,45 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>11.7</v>
+        <v>29.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4579</v>
+        <v>0.4086</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.3777</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.0607</v>
+        <v>0.0309</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.0696</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.635</v>
+        <v>1.321</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>2.229</v>
+        <v>1.057</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.438</v>
+        <v>0.233</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>0.1538</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.0641</v>
+        <v>0.0828</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>140 of 157</t>
+          <t>138 of 158</t>
         </is>
       </c>
     </row>
@@ -2483,45 +2483,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>R. Blanco</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>19.3</v>
+        <v>17.3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4861</v>
+        <v>0.4572</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3622</v>
+        <v>0.3882</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.1238</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0779</v>
+        <v>0.0361</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.725</v>
+        <v>1.637</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.345</v>
+        <v>1.904</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.209</v>
+        <v>0.346</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.1346</v>
+        <v>0.1538</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.0513</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>144 of 157</t>
+          <t>142 of 158</t>
         </is>
       </c>
     </row>
@@ -2565,11 +2565,11 @@
         <v>0.1346</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>139 of 157</t>
+          <t>141 of 158</t>
         </is>
       </c>
     </row>
@@ -2579,45 +2579,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>24.7</v>
+        <v>21.7</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4246</v>
+        <v>0.4181</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.4092</v>
+        <v>0.4257</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.0153</v>
+        <v>-0.0076</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0385</v>
+        <v>0.051</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.73</v>
+        <v>1.705</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.541</v>
+        <v>1.662</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.273</v>
+        <v>0.279</v>
       </c>
       <c r="L44" s="8" t="n">
         <v>0.1154</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.0449</v>
+        <v>0.0382</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>145 of 157</t>
+          <t>147 of 158</t>
         </is>
       </c>
     </row>
@@ -2627,45 +2627,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>T. Sugano</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>23.3</v>
+        <v>15</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.3879</v>
+        <v>0.4491</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3939</v>
+        <v>0.3862</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>-0.0061</v>
+        <v>0.0629</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0513</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.367</v>
+        <v>1.708</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>1.071</v>
+        <v>2.533</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.229</v>
+        <v>0.448</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.1154</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0382</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>148 of 157</t>
+          <t>148 of 158</t>
         </is>
       </c>
     </row>
@@ -2675,45 +2675,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>M. Lorenzen</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>20</v>
+        <v>12.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4296</v>
+        <v>0.4091</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.3932</v>
+        <v>0.4182</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.0364</v>
+        <v>-0.0091</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0404</v>
+        <v>0.0345</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.731</v>
+        <v>1.494</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>2.3</v>
+        <v>1.784</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.413</v>
+        <v>0.351</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>0.09619999999999999</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0318</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>147 of 157</t>
+          <t>149 of 158</t>
         </is>
       </c>
     </row>
@@ -2723,45 +2723,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>M. Keller</t>
+          <t>K. Drake</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>12.3</v>
+        <v>16.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4167</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.4263</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>-0.0091</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0411</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.494</v>
+        <v>1.413</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.784</v>
+        <v>1.56</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.351</v>
+        <v>0.333</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0769</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0321</v>
+        <v>0.0255</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>150 of 157</t>
+          <t>152 of 158</t>
         </is>
       </c>
     </row>
@@ -2771,45 +2771,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>K. Drake</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>16.7</v>
+        <v>13.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4598</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.375</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0848</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.413</v>
+        <v>1.715</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.56</v>
+        <v>1.171</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.333</v>
+        <v>0.158</v>
       </c>
       <c r="L48" s="8" t="n">
         <v>0.0769</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0256</v>
+        <v>0.0318</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>151 of 157</t>
+          <t>150 of 158</t>
         </is>
       </c>
     </row>
@@ -2819,45 +2819,45 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>S. Bieber</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>25</v>
+        <v>19.3</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.3803</v>
+        <v>0.4861</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.4282</v>
+        <v>0.3622</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>-0.0479</v>
+        <v>0.1238</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.019</v>
+        <v>0.0779</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.507</v>
+        <v>1.725</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>1.4</v>
+        <v>1.345</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.282</v>
+        <v>0.209</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0577</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.0128</v>
+        <v>0.0255</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>152 of 157</t>
+          <t>151 of 158</t>
         </is>
       </c>
     </row>
@@ -2867,45 +2867,45 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Z. Littell</t>
+          <t>M. Barnett</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>10.7</v>
+        <v>13.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.4294</v>
+        <v>0.3972</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.3824</v>
+        <v>0.4299</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.0471</v>
+        <v>-0.0327</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.04</v>
+        <v>0.0984</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.792</v>
+        <v>1.695</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1.781</v>
+        <v>1.575</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.286</v>
+        <v>0.229</v>
       </c>
       <c r="L50" s="8" t="n">
         <v>0.0385</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.0128</v>
+        <v>0.0127</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>153 of 157</t>
+          <t>154 of 158</t>
         </is>
       </c>
     </row>
@@ -2915,35 +2915,35 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>S. Arrighetti</t>
+          <t>S. Bieber</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.4144</v>
+        <v>0.3803</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.4685</v>
+        <v>0.4282</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>-0.0541</v>
+        <v>-0.0479</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.778</v>
+        <v>1.507</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.2</v>
+        <v>0.282</v>
       </c>
       <c r="L51" s="8" t="n">
         <v>0.0192</v>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>154 of 157</t>
+          <t>155 of 158</t>
         </is>
       </c>
     </row>
@@ -2963,35 +2963,35 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>Z. Littell</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.4155</v>
+        <v>0.4294</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.3732</v>
+        <v>0.3824</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.0423</v>
+        <v>0.0471</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.0769</v>
+        <v>0.04</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1.805</v>
+        <v>1.792</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>0.968</v>
+        <v>1.781</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>0.107</v>
+        <v>0.286</v>
       </c>
       <c r="L52" s="8" t="n">
         <v>0.0192</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>155 of 157</t>
+          <t>156 of 158</t>
         </is>
       </c>
     </row>
@@ -3011,35 +3011,35 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>R. Johnson</t>
+          <t>S. Arrighetti</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>17.3</v>
+        <v>6</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.3917</v>
+        <v>0.4144</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.4459</v>
+        <v>0.4685</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>-0.0541</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>1.78</v>
+        <v>1.778</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>1.788</v>
+        <v>1.5</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.294</v>
+        <v>0.2</v>
       </c>
       <c r="L53" s="8" t="n">
         <v>0</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>156 of 157</t>
+          <t>157 of 158</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>157 of 157</t>
+          <t>158 of 158</t>
         </is>
       </c>
     </row>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -575,47 +575,41 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>T. Yesavage</t>
+          <t>A. Houser</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>18.7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.5149</v>
+        <v>0.5143</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3498</v>
+        <v>0.3143</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.165</v>
+        <v>0.2</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0429</v>
+        <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1.198</v>
+        <v>0.9</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1.071</v>
+        <v>0.5</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.263</v>
+        <v>0.182</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.8846000000000001</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>0.6943</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>34 of 158</t>
-        </is>
-      </c>
+        <v>0.9821</v>
+      </c>
+      <c r="M2" s="8" t="n"/>
+      <c r="N2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -623,45 +617,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>N. Schultz</t>
+          <t>T. Yesavage</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7.3</v>
+        <v>18.7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.4767</v>
+        <v>0.5149</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3488</v>
+        <v>0.3498</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1279</v>
+        <v>0.165</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0429</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.166</v>
+        <v>1.198</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>2.455</v>
+        <v>1.071</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.5</v>
+        <v>0.263</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8929</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.7006</v>
+        <v>0.7089</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>33 of 158</t>
+          <t>31 of 159</t>
         </is>
       </c>
     </row>
@@ -671,45 +665,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>M. Liberatore</t>
+          <t>N. Schultz</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>20</v>
+        <v>7.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.4805</v>
+        <v>0.4767</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.3514</v>
+        <v>0.3488</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1291</v>
+        <v>0.1279</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0244</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.216</v>
+        <v>1.166</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1.7</v>
+        <v>2.455</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.436</v>
+        <v>0.5</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8269</v>
+        <v>0.8393</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.6561</v>
+        <v>0.6962</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38 of 158</t>
+          <t>33 of 159</t>
         </is>
       </c>
     </row>
@@ -719,45 +713,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>C. Quantrill</t>
+          <t>M. Liberatore</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>15.3</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4619</v>
+        <v>0.4805</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3432</v>
+        <v>0.3514</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1186</v>
+        <v>0.1291</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0455</v>
+        <v>0.0345</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.193</v>
+        <v>1.216</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.304</v>
+        <v>1.7</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.304</v>
+        <v>0.436</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8077</v>
+        <v>0.8393</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.6306</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41 of 158</t>
+          <t>36 of 159</t>
         </is>
       </c>
     </row>
@@ -798,14 +792,14 @@
         <v>0.23</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7885</v>
+        <v>0.7857</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.6115</v>
+        <v>0.6076</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43 of 158</t>
+          <t>42 of 159</t>
         </is>
       </c>
     </row>
@@ -849,11 +843,11 @@
         <v>0.75</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5924</v>
+        <v>0.5949</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45 of 158</t>
+          <t>44 of 159</t>
         </is>
       </c>
     </row>
@@ -863,45 +857,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>H. Greene</t>
+          <t>E. Lauer</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>17.3</v>
+        <v>21.7</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4749</v>
+        <v>0.4866</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3398</v>
+        <v>0.3548</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1351</v>
+        <v>0.1317</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0444</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.263</v>
+        <v>1.26</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.327</v>
+        <v>1.108</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.308</v>
+        <v>0.242</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.7308</v>
+        <v>0.75</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.5414</v>
+        <v>0.5633</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51 of 158</t>
+          <t>49 of 159</t>
         </is>
       </c>
     </row>
@@ -911,45 +905,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>T. Phillips</t>
+          <t>H. Greene</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4618</v>
+        <v>0.4749</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3282</v>
+        <v>0.3398</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1336</v>
+        <v>0.1351</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0533</v>
+        <v>0.0411</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.313</v>
+        <v>1.263</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.255</v>
+        <v>1.327</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.283</v>
+        <v>0.308</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7115</v>
+        <v>0.7143</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.4459</v>
+        <v>0.5506</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66 of 158</t>
+          <t>50 of 159</t>
         </is>
       </c>
     </row>
@@ -990,14 +984,14 @@
         <v>0.323</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.7115</v>
+        <v>0.7143</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.5414</v>
+        <v>0.5506</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52 of 158</t>
+          <t>51 of 159</t>
         </is>
       </c>
     </row>
@@ -1007,45 +1001,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>J. Assad</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10</v>
+        <v>18.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4618</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3282</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1336</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0533</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.327</v>
+        <v>1.313</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.4</v>
+        <v>1.255</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.333</v>
+        <v>0.283</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6731</v>
+        <v>0.6964</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.4204</v>
+        <v>0.443</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70 of 158</t>
+          <t>68 of 159</t>
         </is>
       </c>
     </row>
@@ -1055,45 +1049,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>G. Hughes</t>
+          <t>C. Quantrill</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>24.7</v>
+        <v>20.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4672</v>
+        <v>0.4574</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3712</v>
+        <v>0.3596</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.096</v>
+        <v>0.0978</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0196</v>
+        <v>0.0345</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.254</v>
+        <v>1.216</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.378</v>
+        <v>1.328</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.338</v>
+        <v>0.31</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6538</v>
+        <v>0.6607</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.4841</v>
+        <v>0.5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59 of 158</t>
+          <t>58 of 159</t>
         </is>
       </c>
     </row>
@@ -1103,45 +1097,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>G. Rodriguez</t>
+          <t>J. Assad</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4988</v>
+        <v>0.4678</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.355</v>
+        <v>0.3684</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1439</v>
+        <v>0.0994</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0481</v>
+        <v>0.0244</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.342</v>
+        <v>1.327</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.458</v>
+        <v>1.4</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.317</v>
+        <v>0.333</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6607</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.3949</v>
+        <v>0.4241</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75 of 158</t>
+          <t>71 of 159</t>
         </is>
       </c>
     </row>
@@ -1151,45 +1145,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>E. Sheehan</t>
+          <t>G. Hughes</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13</v>
+        <v>24.7</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4672</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3661</v>
+        <v>0.3712</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0982</v>
+        <v>0.096</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0196</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.345</v>
+        <v>1.254</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.615</v>
+        <v>1.378</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6429</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.3822</v>
+        <v>0.481</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76 of 158</t>
+          <t>61 of 159</t>
         </is>
       </c>
     </row>
@@ -1199,45 +1193,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>D. Kremer</t>
+          <t>G. Rodriguez</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4627</v>
+        <v>0.4988</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3735</v>
+        <v>0.355</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0892</v>
+        <v>0.1439</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.0481</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.334</v>
+        <v>1.342</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.308</v>
+        <v>1.458</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.309</v>
+        <v>0.317</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.5962</v>
+        <v>0.625</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.4013</v>
+        <v>0.3987</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>74 of 158</t>
+          <t>76 of 159</t>
         </is>
       </c>
     </row>
@@ -1247,45 +1241,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>C. Prielipp</t>
+          <t>E. Sheehan</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4902</v>
+        <v>0.4643</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3608</v>
+        <v>0.3661</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1294</v>
+        <v>0.0982</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0833</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.365</v>
+        <v>1.345</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.125</v>
+        <v>1.615</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.235</v>
+        <v>0.333</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5962</v>
+        <v>0.6071</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.3439</v>
+        <v>0.3861</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>84 of 158</t>
+          <t>78 of 159</t>
         </is>
       </c>
     </row>
@@ -1295,45 +1289,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>K. Freeland</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24.7</v>
+        <v>26</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4485</v>
+        <v>0.4627</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3536</v>
+        <v>0.3735</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.095</v>
+        <v>0.0892</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.0288</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.379</v>
+        <v>1.334</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.257</v>
+        <v>1.308</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.274</v>
+        <v>0.309</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5769</v>
+        <v>0.5893</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3185</v>
+        <v>0.4051</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91 of 158</t>
+          <t>75 of 159</t>
         </is>
       </c>
     </row>
@@ -1343,45 +1337,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>G. Jump</t>
+          <t>C. Prielipp</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4862</v>
+        <v>0.4902</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.4009</v>
+        <v>0.3608</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0853</v>
+        <v>0.1294</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.028</v>
+        <v>0.0492</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.393</v>
+        <v>1.365</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.792</v>
+        <v>1.125</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.44</v>
+        <v>0.235</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5577</v>
+        <v>0.5893</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.2866</v>
+        <v>0.3418</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>97 of 158</t>
+          <t>87 of 159</t>
         </is>
       </c>
     </row>
@@ -1391,45 +1385,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>B. Singer</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>30</v>
+        <v>24.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4509</v>
+        <v>0.4485</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3758</v>
+        <v>0.3536</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0752</v>
+        <v>0.095</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.0297</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.243</v>
+        <v>1.379</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.3</v>
+        <v>1.257</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.315</v>
+        <v>0.274</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5714</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3439</v>
+        <v>0.3165</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>83 of 158</t>
+          <t>95 of 159</t>
         </is>
       </c>
     </row>
@@ -1437,47 +1431,47 @@
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>C. Povich</t>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>G. Jump</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.4862</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.4009</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.0853</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0278</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>1.209</v>
+        <v>0.028</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1.393</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.556</v>
+        <v>1.792</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.435</v>
+        <v>0.44</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5536</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.3376</v>
+        <v>0.2911</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86 of 158</t>
+          <t>99 of 159</t>
         </is>
       </c>
     </row>
@@ -1487,45 +1481,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>J. Perkins</t>
+          <t>B. Singer</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4473</v>
+        <v>0.4509</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3738</v>
+        <v>0.3758</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.0735</v>
+        <v>0.0752</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0595</v>
+        <v>0.0161</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.408</v>
+        <v>1.243</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.474</v>
+        <v>1.3</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.294</v>
+        <v>0.315</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.4808</v>
+        <v>0.5</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.2611</v>
+        <v>0.3481</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>101 of 158</t>
+          <t>85 of 159</t>
         </is>
       </c>
     </row>
@@ -1535,45 +1529,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>S. Drohan</t>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4529</v>
+        <v>0.4455</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.3688</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0767</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0337</v>
+        <v>0.0556</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.168</v>
+        <v>1.416</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.391</v>
+        <v>1.708</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.404</v>
+        <v>0.366</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4423</v>
+        <v>0.4821</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.2675</v>
+        <v>0.2468</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>100 of 158</t>
+          <t>107 of 159</t>
         </is>
       </c>
     </row>
@@ -1583,45 +1577,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Z. Matthews</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4626</v>
+        <v>0.4558</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3822</v>
+        <v>0.381</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0805</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.0278</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.445</v>
+        <v>1.209</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.737</v>
+        <v>1.556</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.37</v>
+        <v>0.435</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4423</v>
+        <v>0.4821</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.2038</v>
+        <v>0.3418</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>112 of 158</t>
+          <t>88 of 159</t>
         </is>
       </c>
     </row>
@@ -1631,45 +1625,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>G. Holmes</t>
+          <t>D. Peterson</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>26.7</v>
+        <v>28.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4274</v>
+        <v>0.4459</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3656</v>
+        <v>0.3739</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0618</v>
+        <v>0.0721</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0283</v>
+        <v>0.0171</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.395</v>
+        <v>1.24</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.312</v>
+        <v>1.256</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.303</v>
+        <v>0.305</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4038</v>
+        <v>0.4643</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.2484</v>
+        <v>0.3291</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>103 of 158</t>
+          <t>92 of 159</t>
         </is>
       </c>
     </row>
@@ -1679,45 +1673,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>D. Peterson</t>
+          <t>S. Drohan</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>23.7</v>
+        <v>23</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.441</v>
+        <v>0.4529</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3792</v>
+        <v>0.3882</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.0618</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.022</v>
+        <v>0.0337</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.226</v>
+        <v>1.168</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.014</v>
+        <v>1.391</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.246</v>
+        <v>0.404</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.3846</v>
+        <v>0.4286</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.242</v>
+        <v>0.2722</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>104 of 158</t>
+          <t>103 of 159</t>
         </is>
       </c>
     </row>
@@ -1727,45 +1721,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>R. Stock</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4726</v>
+        <v>0.4633</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3562</v>
+        <v>0.3807</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.1164</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0377</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.493</v>
+        <v>1.451</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>2.125</v>
+        <v>1.708</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.423</v>
+        <v>0.373</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.3846</v>
+        <v>0.4286</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.1592</v>
+        <v>0.2025</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>121 of 158</t>
+          <t>114 of 159</t>
         </is>
       </c>
     </row>
@@ -1775,45 +1769,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>S. Lugo</t>
+          <t>G. Holmes</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>30</v>
+        <v>26.7</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4381</v>
+        <v>0.4274</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3876</v>
+        <v>0.3656</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0618</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0086</v>
+        <v>0.0283</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.435</v>
+        <v>1.395</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.167</v>
+        <v>1.312</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.259</v>
+        <v>0.303</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.3269</v>
+        <v>0.3929</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.1847</v>
+        <v>0.2532</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>115 of 158</t>
+          <t>105 of 159</t>
         </is>
       </c>
     </row>
@@ -1823,45 +1817,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>L. Avila</t>
+          <t>R. Stock</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13.3</v>
+        <v>8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4726</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.3562</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.1164</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.025</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.535</v>
+        <v>1.493</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.575</v>
+        <v>2.125</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.3</v>
+        <v>0.423</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.3077</v>
+        <v>0.375</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1338</v>
+        <v>0.1709</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>124 of 158</t>
+          <t>120 of 159</t>
         </is>
       </c>
     </row>
@@ -1871,45 +1865,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>E. Fedde</t>
+          <t>S. Lugo</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13.3</v>
+        <v>30</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4381</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3876</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0505</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0086</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.136</v>
+        <v>1.435</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.05</v>
+        <v>1.167</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.267</v>
+        <v>0.259</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.2885</v>
+        <v>0.3393</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1592</v>
+        <v>0.1772</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>120 of 158</t>
+          <t>117 of 159</t>
         </is>
       </c>
     </row>
@@ -1919,45 +1913,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>27.7</v>
+        <v>13.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4632</v>
+        <v>0.4444</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3725</v>
+        <v>0.3981</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0907</v>
+        <v>0.0463</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0367</v>
+        <v>0.1</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.548</v>
+        <v>1.136</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.337</v>
+        <v>1.05</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.275</v>
+        <v>0.267</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.2885</v>
+        <v>0.3036</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1274</v>
+        <v>0.1456</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>126 of 158</t>
+          <t>122 of 159</t>
         </is>
       </c>
     </row>
@@ -1967,45 +1961,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>A. Alvarez</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>16</v>
+        <v>13.3</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.443</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3756</v>
+        <v>0.3904</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0526</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.461</v>
+        <v>1.535</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.188</v>
+        <v>1.575</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.2692</v>
+        <v>0.3036</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.1465</v>
+        <v>0.1392</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>122 of 158</t>
+          <t>124 of 159</t>
         </is>
       </c>
     </row>
@@ -2015,45 +2009,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>R. Vasquez</t>
+          <t>A. Alvarez</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>13.7</v>
+        <v>16</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.4208</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3584</v>
+        <v>0.3756</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0452</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.563</v>
+        <v>1.461</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.585</v>
+        <v>1.188</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2692</v>
+        <v>0.2857</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.1083</v>
+        <v>0.1329</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>130 of 158</t>
+          <t>125 of 159</t>
         </is>
       </c>
     </row>
@@ -2063,45 +2057,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>G. Marquez</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5.3</v>
+        <v>27.7</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.4632</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3889</v>
+        <v>0.3725</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0907</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.08</v>
+        <v>0.0367</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.414</v>
+        <v>1.548</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.875</v>
+        <v>1.337</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.4</v>
+        <v>0.275</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2857</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1401</v>
+        <v>0.1329</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>123 of 158</t>
+          <t>126 of 159</t>
         </is>
       </c>
     </row>
@@ -2111,45 +2105,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>A. Nola</t>
+          <t>G. Marquez</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>28</v>
+        <v>5.3</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4401</v>
+        <v>0.4333</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3965</v>
+        <v>0.3889</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.0436</v>
+        <v>0.0444</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.52</v>
+        <v>1.414</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.5</v>
+        <v>1.875</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.2308</v>
+        <v>0.2679</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1274</v>
+        <v>0.1266</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>125 of 158</t>
+          <t>128 of 159</t>
         </is>
       </c>
     </row>
@@ -2159,41 +2153,47 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>M. Englert</t>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5</v>
+        <v>13.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4162</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3059</v>
+        <v>0.3584</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.2118</v>
+        <v>0.0578</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1304</v>
+        <v>0.0217</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.589</v>
+        <v>1.563</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.8</v>
+        <v>0.585</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.333</v>
+        <v>0.1</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="M35" s="8" t="n"/>
-      <c r="N35" s="2" t="n"/>
+        <v>0.2679</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>130 of 159</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2201,45 +2201,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>B. Sproat</t>
+          <t>A. Nola</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>13.7</v>
+        <v>28</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.451</v>
+        <v>0.4401</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3965</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.0436</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.578</v>
+        <v>1.52</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.756</v>
+        <v>1.5</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.325</v>
+        <v>0.3</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.2115</v>
+        <v>0.25</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.1019</v>
+        <v>0.1203</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>132 of 158</t>
+          <t>129 of 159</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Q. Mathews</t>
+          <t>M. Englert</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2259,16 +2259,16 @@
         <v>5</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3696</v>
+        <v>0.3059</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.1196</v>
+        <v>0.2118</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0</v>
+        <v>0.1304</v>
       </c>
       <c r="I37" s="11" t="n">
         <v>1.589</v>
@@ -2277,10 +2277,10 @@
         <v>1.8</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.2115</v>
+        <v>0.2321</v>
       </c>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="2" t="n"/>
@@ -2289,47 +2289,47 @@
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>W. Buehler</t>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>25.3</v>
+        <v>13.7</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4371</v>
+        <v>0.451</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3943</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>0.0428</v>
+        <v>0.4078</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>0.0431</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0187</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>1.462</v>
+        <v>0.0312</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>1.578</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.382</v>
+        <v>1.756</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.284</v>
+        <v>0.325</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.1923</v>
+        <v>0.2321</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.1146</v>
+        <v>0.1076</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>127 of 158</t>
+          <t>132 of 159</t>
         </is>
       </c>
     </row>
@@ -2337,47 +2337,47 @@
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>R. Lopez</t>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>W. Buehler</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>10</v>
+        <v>25.3</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.4371</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3931</v>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>0.0405</v>
+        <v>0.3943</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>0.0428</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0435</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>1.261</v>
+        <v>0.0187</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>1.462</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.8</v>
+        <v>1.382</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.429</v>
+        <v>0.284</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.1731</v>
+        <v>0.2143</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.1083</v>
+        <v>0.1076</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>129 of 158</t>
+          <t>131 of 159</t>
         </is>
       </c>
     </row>
@@ -2387,47 +2387,41 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>S. Cecconi</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4891</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3696</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.1196</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1.596</v>
+        <v>1.589</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.1731</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>0.0701</v>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>140 of 158</t>
-        </is>
-      </c>
+        <v>0.2143</v>
+      </c>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2435,45 +2429,45 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>T. Sugano</t>
+          <t>R. Lopez</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>29.3</v>
+        <v>10</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4086</v>
+        <v>0.4335</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3777</v>
+        <v>0.3931</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.0309</v>
+        <v>0.0405</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0696</v>
+        <v>0.0435</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>1.321</v>
+        <v>1.261</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>1.057</v>
+        <v>1.8</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.233</v>
+        <v>0.429</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.1538</v>
+        <v>0.1964</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.0828</v>
+        <v>0.1013</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>138 of 158</t>
+          <t>134 of 159</t>
         </is>
       </c>
     </row>
@@ -2483,45 +2477,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>S. Cecconi</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>17.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4572</v>
+        <v>0.4643</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.3512</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.1131</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0361</v>
+        <v>0.0682</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.637</v>
+        <v>1.596</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.904</v>
+        <v>2.16</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.346</v>
+        <v>0.367</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.1538</v>
+        <v>0.1786</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>142 of 158</t>
+          <t>140 of 159</t>
         </is>
       </c>
     </row>
@@ -2531,45 +2525,45 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>M. Mikolas</t>
+          <t>M. Perez</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4269</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3926</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.0344</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0104</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1.867</v>
+        <v>1</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.351</v>
+        <v>0.197</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.1346</v>
+        <v>0.1786</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.0701</v>
+        <v>0.0886</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>141 of 158</t>
+          <t>138 of 159</t>
         </is>
       </c>
     </row>
@@ -2579,45 +2573,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>R. Johnson</t>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>21.7</v>
+        <v>29.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4181</v>
+        <v>0.4086</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.4257</v>
+        <v>0.3777</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>-0.0076</v>
+        <v>0.0309</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0696</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.705</v>
+        <v>1.321</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.662</v>
+        <v>1.057</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.279</v>
+        <v>0.233</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.1154</v>
+        <v>0.1607</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0823</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>147 of 158</t>
+          <t>139 of 159</t>
         </is>
       </c>
     </row>
@@ -2627,45 +2621,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>M. Lorenzen</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4491</v>
+        <v>0.4572</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3862</v>
+        <v>0.3882</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.0629</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0513</v>
+        <v>0.0361</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.708</v>
+        <v>1.637</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>2.533</v>
+        <v>1.904</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.448</v>
+        <v>0.346</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1607</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0696</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>148 of 158</t>
+          <t>142 of 159</t>
         </is>
       </c>
     </row>
@@ -2675,45 +2669,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>M. Keller</t>
+          <t>M. Mikolas</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>12.3</v>
+        <v>15</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.3827</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.3704</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0123</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.494</v>
+        <v>1.59</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>1.784</v>
+        <v>1.867</v>
       </c>
       <c r="K46" s="7" t="n">
         <v>0.351</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1429</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.0318</v>
+        <v>0.0759</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>149 of 158</t>
+          <t>141 of 159</t>
         </is>
       </c>
     </row>
@@ -2723,45 +2717,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>K. Drake</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>16.7</v>
+        <v>21.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4181</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.4257</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0076</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.051</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.413</v>
+        <v>1.705</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.56</v>
+        <v>1.662</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.333</v>
+        <v>0.279</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.0769</v>
+        <v>0.1071</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0255</v>
+        <v>0.038</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>152 of 158</t>
+          <t>148 of 159</t>
         </is>
       </c>
     </row>
@@ -2771,45 +2765,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4598</v>
+        <v>0.4491</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.375</v>
+        <v>0.3862</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.0848</v>
+        <v>0.0629</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0513</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.715</v>
+        <v>1.708</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.171</v>
+        <v>2.533</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.158</v>
+        <v>0.448</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.0769</v>
+        <v>0.1071</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0318</v>
+        <v>0.0443</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>150 of 158</t>
+          <t>147 of 159</t>
         </is>
       </c>
     </row>
@@ -2819,45 +2813,45 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>R. Blanco</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.4861</v>
+        <v>0.4091</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.3622</v>
+        <v>0.4182</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.1238</v>
+        <v>-0.0091</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.0779</v>
+        <v>0.0345</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.725</v>
+        <v>1.494</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>1.345</v>
+        <v>1.784</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.209</v>
+        <v>0.351</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.0577</v>
+        <v>0.0893</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.0255</v>
+        <v>0.0316</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>151 of 158</t>
+          <t>151 of 159</t>
         </is>
       </c>
     </row>
@@ -2867,45 +2861,45 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>M. Barnett</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.4598</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.4299</v>
+        <v>0.375</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>-0.0327</v>
+        <v>0.0848</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.0984</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.695</v>
+        <v>1.715</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1.575</v>
+        <v>1.171</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.229</v>
+        <v>0.158</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.0893</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.0127</v>
+        <v>0.038</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>154 of 158</t>
+          <t>149 of 159</t>
         </is>
       </c>
     </row>
@@ -2915,45 +2909,45 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>S. Bieber</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>25</v>
+        <v>19.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.3803</v>
+        <v>0.4861</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.4282</v>
+        <v>0.3622</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>-0.0479</v>
+        <v>0.1238</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.019</v>
+        <v>0.0779</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.507</v>
+        <v>1.725</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>1.4</v>
+        <v>1.345</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.282</v>
+        <v>0.209</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.0192</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.0064</v>
+        <v>0.0316</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>155 of 158</t>
+          <t>150 of 159</t>
         </is>
       </c>
     </row>
@@ -2963,45 +2957,45 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Z. Littell</t>
+          <t>K. Drake</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10.7</v>
+        <v>16.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.4294</v>
+        <v>0.4167</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.3824</v>
+        <v>0.4263</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.0471</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.04</v>
+        <v>0.0411</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1.792</v>
+        <v>1.413</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>1.781</v>
+        <v>1.56</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>0.0192</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0.0064</v>
+        <v>0.0253</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>156 of 158</t>
+          <t>153 of 159</t>
         </is>
       </c>
     </row>
@@ -3011,45 +3005,45 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>S. Arrighetti</t>
+          <t>Z. Littell</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.4144</v>
+        <v>0.4294</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.4685</v>
+        <v>0.3824</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>-0.0541</v>
+        <v>0.0471</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>1.778</v>
+        <v>1.792</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>1.5</v>
+        <v>1.781</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>0</v>
+        <v>0.0357</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>0</v>
+        <v>0.0127</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>157 of 158</t>
+          <t>154 of 159</t>
         </is>
       </c>
     </row>
@@ -3059,113 +3053,305 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>J. Springs</t>
+          <t>M. Barnett</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D54" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>-0.0327</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="L54" s="8" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="M54" s="8" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>155 of 159</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>S. Bieber</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>-0.0479</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="J55" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="M55" s="8" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>156 of 159</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>C. Mlodzinski</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="L56" s="8" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="M56" s="8" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>157 of 159</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>S. Arrighetti</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>-0.0541</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>158 of 159</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>J. Springs</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="2" t="n">
         <v>10.3</v>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E58" s="4" t="n">
         <v>0.401</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F58" s="4" t="n">
         <v>0.4213</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="G58" s="13" t="n">
         <v>-0.0203</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>0.0408</v>
       </c>
-      <c r="I54" s="14" t="n">
+      <c r="I58" s="14" t="n">
         <v>1.892</v>
       </c>
-      <c r="J54" s="7" t="n">
+      <c r="J58" s="7" t="n">
         <v>2.032</v>
       </c>
-      <c r="K54" s="7" t="n">
+      <c r="K58" s="7" t="n">
         <v>0.333</v>
       </c>
-      <c r="L54" s="8" t="n">
+      <c r="L58" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="8" t="n">
+      <c r="M58" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>158 of 158</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>159 of 159</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -606,7 +606,7 @@
         <v>0.182</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9821</v>
+        <v>0.9818</v>
       </c>
       <c r="M2" s="8" t="n"/>
       <c r="N2" s="2" t="n"/>
@@ -648,14 +648,14 @@
         <v>0.263</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.8929</v>
+        <v>0.9273</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.7089</v>
+        <v>0.7025</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>31 of 159</t>
+          <t>33 of 159</t>
         </is>
       </c>
     </row>
@@ -696,14 +696,14 @@
         <v>0.5</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8393</v>
+        <v>0.8545</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.6962</v>
+        <v>0.7089</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33 of 159</t>
+          <t>32 of 159</t>
         </is>
       </c>
     </row>
@@ -713,45 +713,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>M. Liberatore</t>
+          <t>C. Rea</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4805</v>
+        <v>0.4713</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3514</v>
+        <v>0.3534</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1291</v>
+        <v>0.1178</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0444</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.216</v>
+        <v>1.211</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.436</v>
+        <v>0.23</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8393</v>
+        <v>0.8</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.6139</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36 of 159</t>
+          <t>42 of 159</t>
         </is>
       </c>
     </row>
@@ -761,45 +761,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>C. Rea</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>23</v>
+        <v>23.7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4759</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3534</v>
+        <v>0.3229</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1178</v>
+        <v>0.153</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0444</v>
+        <v>0.051</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.211</v>
+        <v>1.256</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1</v>
+        <v>1.268</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.23</v>
+        <v>0.294</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7857</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.6076</v>
+        <v>0.5696</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42 of 159</t>
+          <t>48 of 159</t>
         </is>
       </c>
     </row>
@@ -809,45 +809,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>R. Gasser</t>
+          <t>E. Lauer</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4704</v>
+        <v>0.4866</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3551</v>
+        <v>0.3548</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1153</v>
+        <v>0.1317</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0125</v>
+        <v>0.0444</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.113</v>
+        <v>1.108</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.316</v>
+        <v>0.242</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.75</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5949</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44 of 159</t>
+          <t>52 of 159</t>
         </is>
       </c>
     </row>
@@ -857,41 +857,41 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>E. Lauer</t>
+          <t>B. Tidwell</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>21.7</v>
+        <v>10.7</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4866</v>
+        <v>0.4762</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3548</v>
+        <v>0.3651</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1317</v>
+        <v>0.1111</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0444</v>
+        <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.26</v>
+        <v>1.026</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.108</v>
+        <v>1.125</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.242</v>
+        <v>0.323</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.75</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.5633</v>
+        <v>0.5696</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -936,14 +936,14 @@
         <v>0.308</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7143</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.5506</v>
+        <v>0.5443</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50 of 159</t>
+          <t>54 of 159</t>
         </is>
       </c>
     </row>
@@ -953,45 +953,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>B. Tidwell</t>
+          <t>C. Quantrill</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10.7</v>
+        <v>20.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4762</v>
+        <v>0.4574</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3651</v>
+        <v>0.3596</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1111</v>
+        <v>0.0978</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0</v>
+        <v>0.0345</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.026</v>
+        <v>1.216</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.125</v>
+        <v>1.328</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.323</v>
+        <v>0.31</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.7143</v>
+        <v>0.6909</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.5506</v>
+        <v>0.519</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51 of 159</t>
+          <t>56 of 159</t>
         </is>
       </c>
     </row>
@@ -1001,45 +1001,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>T. Phillips</t>
+          <t>J. Assad</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>18.3</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4618</v>
+        <v>0.4678</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3282</v>
+        <v>0.3684</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1336</v>
+        <v>0.0994</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0533</v>
+        <v>0.0244</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.313</v>
+        <v>1.327</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.255</v>
+        <v>1.4</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.283</v>
+        <v>0.333</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6964</v>
+        <v>0.6727</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.443</v>
+        <v>0.4177</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68 of 159</t>
+          <t>73 of 159</t>
         </is>
       </c>
     </row>
@@ -1049,45 +1049,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>C. Quantrill</t>
+          <t>G. Hughes</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4574</v>
+        <v>0.4672</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3596</v>
+        <v>0.3712</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0978</v>
+        <v>0.096</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0196</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.216</v>
+        <v>1.254</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.328</v>
+        <v>1.378</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.31</v>
+        <v>0.338</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6607</v>
+        <v>0.6545</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58 of 159</t>
+          <t>59 of 159</t>
         </is>
       </c>
     </row>
@@ -1097,45 +1097,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>J. Assad</t>
+          <t>G. Rodriguez</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4988</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.355</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1439</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0481</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.327</v>
+        <v>1.342</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.4</v>
+        <v>1.458</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.333</v>
+        <v>0.317</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6607</v>
+        <v>0.6364</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.4241</v>
+        <v>0.3987</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>71 of 159</t>
+          <t>77 of 159</t>
         </is>
       </c>
     </row>
@@ -1145,45 +1145,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>G. Hughes</t>
+          <t>E. Sheehan</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>24.7</v>
+        <v>13</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4672</v>
+        <v>0.4643</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3712</v>
+        <v>0.3661</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.096</v>
+        <v>0.0982</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0196</v>
+        <v>0.0833</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.254</v>
+        <v>1.345</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.378</v>
+        <v>1.615</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6429</v>
+        <v>0.6182</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.481</v>
+        <v>0.3861</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61 of 159</t>
+          <t>78 of 159</t>
         </is>
       </c>
     </row>
@@ -1193,45 +1193,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>G. Rodriguez</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4988</v>
+        <v>0.4627</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.355</v>
+        <v>0.3735</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1439</v>
+        <v>0.0892</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0481</v>
+        <v>0.0288</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.342</v>
+        <v>1.334</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.458</v>
+        <v>1.308</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.317</v>
+        <v>0.309</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.3987</v>
+        <v>0.4051</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>76 of 159</t>
+          <t>75 of 159</t>
         </is>
       </c>
     </row>
@@ -1241,45 +1241,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>E. Sheehan</t>
+          <t>C. Prielipp</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4902</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3661</v>
+        <v>0.3608</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0982</v>
+        <v>0.1294</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0492</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.345</v>
+        <v>1.365</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.615</v>
+        <v>1.125</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.333</v>
+        <v>0.235</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.6071</v>
+        <v>0.6</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.3861</v>
+        <v>0.3544</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78 of 159</t>
+          <t>85 of 159</t>
         </is>
       </c>
     </row>
@@ -1289,45 +1289,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>D. Kremer</t>
+          <t>N. Eovaldi</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>26</v>
+        <v>21.3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4627</v>
+        <v>0.4561</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3735</v>
+        <v>0.3596</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0892</v>
+        <v>0.0965</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.0556</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.334</v>
+        <v>1.376</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.308</v>
+        <v>1.359</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.309</v>
+        <v>0.29</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5893</v>
+        <v>0.5818</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.4051</v>
+        <v>0.3418</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75 of 159</t>
+          <t>88 of 159</t>
         </is>
       </c>
     </row>
@@ -1337,45 +1337,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>C. Prielipp</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>16</v>
+        <v>24.7</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4902</v>
+        <v>0.4485</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3608</v>
+        <v>0.3536</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.1294</v>
+        <v>0.095</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0297</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.365</v>
+        <v>1.379</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.125</v>
+        <v>1.257</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.235</v>
+        <v>0.274</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5893</v>
+        <v>0.5636</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3418</v>
+        <v>0.3291</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>87 of 159</t>
+          <t>92 of 159</t>
         </is>
       </c>
     </row>
@@ -1385,45 +1385,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>K. Freeland</t>
+          <t>B. Singer</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>24.7</v>
+        <v>30</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4485</v>
+        <v>0.4509</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3536</v>
+        <v>0.3758</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.095</v>
+        <v>0.0752</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.0161</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.379</v>
+        <v>1.243</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.257</v>
+        <v>1.3</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.274</v>
+        <v>0.315</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.5714</v>
+        <v>0.5273</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3165</v>
+        <v>0.3481</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>95 of 159</t>
+          <t>87 of 159</t>
         </is>
       </c>
     </row>
@@ -1433,45 +1433,45 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>G. Jump</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4862</v>
+        <v>0.4558</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4009</v>
+        <v>0.381</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0853</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.028</v>
+        <v>0.0278</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1.393</v>
+        <v>1.209</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.792</v>
+        <v>1.556</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.44</v>
+        <v>0.435</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.5536</v>
+        <v>0.5091</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.2911</v>
+        <v>0.3418</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99 of 159</t>
+          <t>89 of 159</t>
         </is>
       </c>
     </row>
@@ -1481,45 +1481,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>B. Singer</t>
+          <t>D. Peterson</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>30</v>
+        <v>28.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4509</v>
+        <v>0.4459</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3758</v>
+        <v>0.3739</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.0752</v>
+        <v>0.0721</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.0171</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1.243</v>
+        <v>1.24</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.3</v>
+        <v>1.256</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.315</v>
+        <v>0.305</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.5</v>
+        <v>0.4909</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.3481</v>
+        <v>0.3291</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>85 of 159</t>
+          <t>93 of 159</t>
         </is>
       </c>
     </row>
@@ -1529,45 +1529,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>J. Perkins</t>
+          <t>S. Drohan</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>24</v>
+        <v>28.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4455</v>
+        <v>0.4563</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.3853</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.0767</v>
+        <v>0.0709</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.027</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.416</v>
+        <v>1.211</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.708</v>
+        <v>1.341</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4821</v>
+        <v>0.4727</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.2468</v>
+        <v>0.3228</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>107 of 159</t>
+          <t>94 of 159</t>
         </is>
       </c>
     </row>
@@ -1577,45 +1577,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>C. Povich</t>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.4455</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.381</v>
+        <v>0.3688</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0767</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.0556</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.209</v>
+        <v>1.416</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.556</v>
+        <v>1.708</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.435</v>
+        <v>0.366</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4821</v>
+        <v>0.4727</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.3418</v>
+        <v>0.2595</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88 of 159</t>
+          <t>103 of 159</t>
         </is>
       </c>
     </row>
@@ -1625,45 +1625,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>D. Peterson</t>
+          <t>H. Dobbins</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.7</v>
+        <v>17.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4459</v>
+        <v>0.4508</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3739</v>
+        <v>0.3826</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0721</v>
+        <v>0.0682</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0171</v>
+        <v>0.029</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.24</v>
+        <v>1.302</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.256</v>
+        <v>1.154</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.305</v>
+        <v>0.261</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4643</v>
+        <v>0.4364</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.3291</v>
+        <v>0.3038</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>92 of 159</t>
+          <t>97 of 159</t>
         </is>
       </c>
     </row>
@@ -1673,45 +1673,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>S. Drohan</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4529</v>
+        <v>0.4633</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.3807</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0337</v>
+        <v>0.0377</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.168</v>
+        <v>1.451</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.391</v>
+        <v>1.708</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.404</v>
+        <v>0.373</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.4286</v>
+        <v>0.4182</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.2722</v>
+        <v>0.2089</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>103 of 159</t>
+          <t>113 of 159</t>
         </is>
       </c>
     </row>
@@ -1721,45 +1721,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Z. Matthews</t>
+          <t>G. Holmes</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24</v>
+        <v>26.7</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4633</v>
+        <v>0.4274</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3807</v>
+        <v>0.3656</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0618</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0377</v>
+        <v>0.0283</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.451</v>
+        <v>1.395</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.708</v>
+        <v>1.312</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.373</v>
+        <v>0.303</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.4286</v>
+        <v>0.4</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.2025</v>
+        <v>0.2532</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>114 of 159</t>
+          <t>104 of 159</t>
         </is>
       </c>
     </row>
@@ -1769,41 +1769,41 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>G. Holmes</t>
+          <t>P. Sandoval</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>26.7</v>
+        <v>25.7</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4274</v>
+        <v>0.445</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3656</v>
+        <v>0.3839</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0618</v>
+        <v>0.0611</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0283</v>
+        <v>0.0261</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.395</v>
+        <v>1.387</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.312</v>
+        <v>1.753</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.303</v>
+        <v>0.395</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.3929</v>
+        <v>0.3818</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.2532</v>
+        <v>0.2468</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1848,14 +1848,14 @@
         <v>0.423</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.375</v>
+        <v>0.3455</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1709</v>
+        <v>0.1646</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>120 of 159</t>
+          <t>122 of 159</t>
         </is>
       </c>
     </row>
@@ -1865,45 +1865,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>S. Lugo</t>
+          <t>A. Nola</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4381</v>
+        <v>0.4495</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3876</v>
+        <v>0.3989</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>0.0505</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0086</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.435</v>
+        <v>1.463</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.167</v>
+        <v>1.515</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.259</v>
+        <v>0.316</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.3393</v>
+        <v>0.3273</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1772</v>
+        <v>0.1835</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>117 of 159</t>
+          <t>115 of 159</t>
         </is>
       </c>
     </row>
@@ -1913,45 +1913,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>E. Fedde</t>
+          <t>Z. Thornton</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13.3</v>
+        <v>28</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4197</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3705</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0492</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0288</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.136</v>
+        <v>1.44</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.05</v>
+        <v>1.214</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.267</v>
+        <v>0.291</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.3036</v>
+        <v>0.3091</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1456</v>
+        <v>0.1709</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>122 of 159</t>
+          <t>120 of 159</t>
         </is>
       </c>
     </row>
@@ -1992,14 +1992,14 @@
         <v>0.3</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.3036</v>
+        <v>0.3091</v>
       </c>
       <c r="M31" s="8" t="n">
         <v>0.1392</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>124 of 159</t>
+          <t>125 of 159</t>
         </is>
       </c>
     </row>
@@ -2009,45 +2009,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>A. Alvarez</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>16</v>
+        <v>27.7</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.4632</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3756</v>
+        <v>0.3725</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0907</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.461</v>
+        <v>1.548</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.188</v>
+        <v>1.337</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.25</v>
+        <v>0.275</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2857</v>
+        <v>0.2909</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>0.1329</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>125 of 159</t>
+          <t>126 of 159</t>
         </is>
       </c>
     </row>
@@ -2057,45 +2057,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>27.7</v>
+        <v>13.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4632</v>
+        <v>0.4444</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3725</v>
+        <v>0.3981</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0907</v>
+        <v>0.0463</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0367</v>
+        <v>0.1</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.548</v>
+        <v>1.136</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.337</v>
+        <v>1.05</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.275</v>
+        <v>0.267</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.2857</v>
+        <v>0.2727</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1329</v>
+        <v>0.1456</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>126 of 159</t>
+          <t>123 of 159</t>
         </is>
       </c>
     </row>
@@ -2105,45 +2105,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>G. Marquez</t>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5.3</v>
+        <v>13.7</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.4162</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3889</v>
+        <v>0.3584</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0578</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.08</v>
+        <v>0.0217</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.414</v>
+        <v>1.563</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.875</v>
+        <v>0.585</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.2679</v>
+        <v>0.2727</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1266</v>
+        <v>0.1139</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>128 of 159</t>
+          <t>130 of 159</t>
         </is>
       </c>
     </row>
@@ -2153,45 +2153,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>R. Vasquez</t>
+          <t>A. Alvarez</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>13.7</v>
+        <v>16</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.4208</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3584</v>
+        <v>0.3756</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0452</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.563</v>
+        <v>1.461</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.585</v>
+        <v>1.188</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.2679</v>
+        <v>0.2545</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.1139</v>
+        <v>0.1266</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>130 of 159</t>
+          <t>128 of 159</t>
         </is>
       </c>
     </row>
@@ -2201,47 +2201,41 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>A. Nola</t>
+          <t>M. Englert</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="2" t="n">
-        <v>28</v>
-      </c>
       <c r="E36" s="4" t="n">
-        <v>0.4401</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3965</v>
+        <v>0.3059</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.0436</v>
+        <v>0.2118</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.1304</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.52</v>
+        <v>1.589</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0.1203</v>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>129 of 159</t>
-        </is>
-      </c>
+        <v>0.2364</v>
+      </c>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2249,41 +2243,47 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>M. Englert</t>
+          <t>G. Marquez</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4333</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3059</v>
+        <v>0.3889</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.2118</v>
+        <v>0.0444</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.1304</v>
+        <v>0.08</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>1.589</v>
+        <v>1.414</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.8</v>
+        <v>1.875</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.2321</v>
-      </c>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="2" t="n"/>
+        <v>0.2364</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>129 of 159</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2322,7 +2322,7 @@
         <v>0.325</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.2321</v>
+        <v>0.2182</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>0.1076</v>
@@ -2339,47 +2339,41 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>W. Buehler</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="2" t="n">
-        <v>25.3</v>
-      </c>
       <c r="E39" s="4" t="n">
-        <v>0.4371</v>
+        <v>0.4891</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3943</v>
+        <v>0.3696</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0.0428</v>
+        <v>0.1196</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0187</v>
+        <v>0</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>1.462</v>
+        <v>1.589</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.382</v>
+        <v>1.8</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.284</v>
+        <v>0.375</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.2143</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>0.1076</v>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>131 of 159</t>
-        </is>
-      </c>
+        <v>0.2182</v>
+      </c>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2387,41 +2381,47 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Q. Mathews</t>
+          <t>W. Buehler</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>5</v>
+        <v>25.3</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.4371</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3696</v>
+        <v>0.3943</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.1196</v>
+        <v>0.0428</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0</v>
+        <v>0.0187</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>1.589</v>
+        <v>1.462</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.8</v>
+        <v>1.382</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.375</v>
+        <v>0.284</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.2143</v>
-      </c>
-      <c r="M40" s="8" t="n"/>
-      <c r="N40" s="2" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>131 of 159</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2460,7 +2460,7 @@
         <v>0.429</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.1964</v>
+        <v>0.1818</v>
       </c>
       <c r="M41" s="8" t="n">
         <v>0.1013</v>
@@ -2508,7 +2508,7 @@
         <v>0.367</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.1786</v>
+        <v>0.1818</v>
       </c>
       <c r="M42" s="8" t="n">
         <v>0.0759</v>
@@ -2556,7 +2556,7 @@
         <v>0.197</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.1786</v>
+        <v>0.1636</v>
       </c>
       <c r="M43" s="8" t="n">
         <v>0.0886</v>
@@ -2573,45 +2573,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>T. Sugano</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>29.3</v>
+        <v>17.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4086</v>
+        <v>0.4572</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3777</v>
+        <v>0.3882</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.0309</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H44" s="4" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>1.637</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="L44" s="8" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="M44" s="8" t="n">
         <v>0.0696</v>
       </c>
-      <c r="I44" s="14" t="n">
-        <v>1.321</v>
-      </c>
-      <c r="J44" s="7" t="n">
-        <v>1.057</v>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="L44" s="8" t="n">
-        <v>0.1607</v>
-      </c>
-      <c r="M44" s="8" t="n">
-        <v>0.0823</v>
-      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>139 of 159</t>
+          <t>142 of 159</t>
         </is>
       </c>
     </row>
@@ -2621,45 +2621,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>17.3</v>
+        <v>29.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4572</v>
+        <v>0.4086</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.3777</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0309</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0361</v>
+        <v>0.0696</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.637</v>
+        <v>1.321</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>1.904</v>
+        <v>1.057</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.346</v>
+        <v>0.233</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.1607</v>
+        <v>0.1455</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.0696</v>
+        <v>0.0823</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>142 of 159</t>
+          <t>139 of 159</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>0.351</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.1429</v>
+        <v>0.1273</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>0.0759</v>
@@ -2717,45 +2717,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>R. Johnson</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>21.7</v>
+        <v>15</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4181</v>
+        <v>0.4491</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.4257</v>
+        <v>0.3862</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>-0.0076</v>
+        <v>0.0629</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0513</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.705</v>
+        <v>1.708</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.662</v>
+        <v>2.533</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.279</v>
+        <v>0.448</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.1071</v>
+        <v>0.1091</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0443</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>148 of 159</t>
+          <t>147 of 159</t>
         </is>
       </c>
     </row>
@@ -2765,45 +2765,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>M. Lorenzen</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>15</v>
+        <v>21.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4491</v>
+        <v>0.4181</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.3862</v>
+        <v>0.4257</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.0629</v>
+        <v>-0.0076</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0513</v>
+        <v>0.051</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.708</v>
+        <v>1.705</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>2.533</v>
+        <v>1.662</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.448</v>
+        <v>0.279</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.1071</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.038</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>147 of 159</t>
+          <t>148 of 159</t>
         </is>
       </c>
     </row>
@@ -2813,45 +2813,45 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>M. Keller</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>12.3</v>
+        <v>13.7</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4598</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.375</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0848</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.494</v>
+        <v>1.715</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>1.784</v>
+        <v>1.171</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.351</v>
+        <v>0.158</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.0893</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.0316</v>
+        <v>0.038</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>151 of 159</t>
+          <t>149 of 159</t>
         </is>
       </c>
     </row>
@@ -2861,45 +2861,45 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>13.7</v>
+        <v>19.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.4598</v>
+        <v>0.4861</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.375</v>
+        <v>0.3622</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.0848</v>
+        <v>0.1238</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0779</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.715</v>
+        <v>1.725</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1.171</v>
+        <v>1.345</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.158</v>
+        <v>0.209</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>0.0893</v>
+        <v>0.0727</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0316</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>149 of 159</t>
+          <t>150 of 159</t>
         </is>
       </c>
     </row>
@@ -2909,45 +2909,45 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>R. Blanco</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.4861</v>
+        <v>0.4091</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.3622</v>
+        <v>0.4182</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.1238</v>
+        <v>-0.0091</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.0779</v>
+        <v>0.0345</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.725</v>
+        <v>1.494</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>1.345</v>
+        <v>1.784</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.209</v>
+        <v>0.351</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="M51" s="8" t="n">
         <v>0.0316</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>150 of 159</t>
+          <t>151 of 159</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
         <v>0.333</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0545</v>
       </c>
       <c r="M52" s="8" t="n">
         <v>0.0253</v>
@@ -3036,7 +3036,7 @@
         <v>0.286</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>0.0357</v>
+        <v>0.0364</v>
       </c>
       <c r="M53" s="8" t="n">
         <v>0.0127</v>
@@ -3084,7 +3084,7 @@
         <v>0.229</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>0.0357</v>
+        <v>0.0182</v>
       </c>
       <c r="M54" s="8" t="n">
         <v>0.0127</v>
@@ -3101,45 +3101,45 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>S. Bieber</t>
+          <t>C. Mlodzinski</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>25</v>
+        <v>5.3</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.3803</v>
+        <v>0.4</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.4282</v>
+        <v>0.4</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>-0.0479</v>
+        <v>0</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>0.019</v>
+        <v>0.0333</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>1.507</v>
+        <v>1.855</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.282</v>
+        <v>0.478</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0.0179</v>
+        <v>0.0182</v>
       </c>
       <c r="M55" s="8" t="n">
         <v>0.0063</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>156 of 159</t>
+          <t>157 of 159</t>
         </is>
       </c>
     </row>
@@ -3149,45 +3149,45 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>C. Mlodzinski</t>
+          <t>S. Arrighetti</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.4</v>
+        <v>0.4144</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.4</v>
+        <v>0.4685</v>
       </c>
       <c r="G56" s="13" t="n">
+        <v>-0.0541</v>
+      </c>
+      <c r="H56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="4" t="n">
-        <v>0.0333</v>
-      </c>
       <c r="I56" s="14" t="n">
-        <v>1.855</v>
+        <v>1.778</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>0.478</v>
+        <v>0.2</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>0.0179</v>
+        <v>0</v>
       </c>
       <c r="M56" s="8" t="n">
-        <v>0.0063</v>
+        <v>0</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>157 of 159</t>
+          <t>158 of 159</t>
         </is>
       </c>
     </row>
@@ -3197,35 +3197,35 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>S. Arrighetti</t>
+          <t>J. Springs</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>6</v>
+        <v>10.3</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.4144</v>
+        <v>0.401</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.4685</v>
+        <v>0.4213</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>-0.0541</v>
+        <v>-0.0203</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>1.778</v>
+        <v>1.892</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>1.5</v>
+        <v>2.032</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="L57" s="8" t="n">
         <v>0</v>
@@ -3235,123 +3235,75 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>158 of 159</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>J. Springs</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>0.4213</v>
-      </c>
-      <c r="G58" s="13" t="n">
-        <v>-0.0203</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>1.892</v>
-      </c>
-      <c r="J58" s="7" t="n">
-        <v>2.032</v>
-      </c>
-      <c r="K58" s="7" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="L58" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
           <t>159 of 159</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -606,7 +606,7 @@
         <v>0.182</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9818</v>
+        <v>0.9831</v>
       </c>
       <c r="M2" s="8" t="n"/>
       <c r="N2" s="2" t="n"/>
@@ -648,14 +648,14 @@
         <v>0.263</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.9273</v>
+        <v>0.9153</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.7025</v>
+        <v>0.6875</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>33 of 159</t>
+          <t>34 of 161</t>
         </is>
       </c>
     </row>
@@ -665,45 +665,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>N. Schultz</t>
+          <t>R. Gasser</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7.3</v>
+        <v>27</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.4767</v>
+        <v>0.4763</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.3488</v>
+        <v>0.346</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1279</v>
+        <v>0.1303</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0278</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.166</v>
+        <v>1.087</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.455</v>
+        <v>1.185</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8545</v>
+        <v>0.8814</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.7089</v>
+        <v>0.7375</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32 of 159</t>
+          <t>28 of 161</t>
         </is>
       </c>
     </row>
@@ -713,45 +713,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>C. Rea</t>
+          <t>N. Schultz</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>23</v>
+        <v>7.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4767</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3534</v>
+        <v>0.3488</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1178</v>
+        <v>0.1279</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0444</v>
+        <v>0.0244</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.211</v>
+        <v>1.166</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1</v>
+        <v>2.455</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.6139</v>
+        <v>0.7125</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42 of 159</t>
+          <t>30 of 161</t>
         </is>
       </c>
     </row>
@@ -761,45 +761,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>T. Phillips</t>
+          <t>M. Liberatore</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>23.7</v>
+        <v>25.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4759</v>
+        <v>0.4824</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3229</v>
+        <v>0.3607</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1218</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0283</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.256</v>
+        <v>1.146</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.268</v>
+        <v>1.461</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.294</v>
+        <v>0.388</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.8305</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.5696</v>
+        <v>0.6562</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48 of 159</t>
+          <t>39 of 161</t>
         </is>
       </c>
     </row>
@@ -809,45 +809,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>E. Lauer</t>
+          <t>C. Rea</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>21.7</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4866</v>
+        <v>0.4713</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3548</v>
+        <v>0.3534</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1317</v>
+        <v>0.1178</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>0.0444</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.26</v>
+        <v>1.211</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.108</v>
+        <v>1</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.242</v>
+        <v>0.23</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7966</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.6062</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52 of 159</t>
+          <t>45 of 161</t>
         </is>
       </c>
     </row>
@@ -857,45 +857,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>B. Tidwell</t>
+          <t>A. Kay</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10.7</v>
+        <v>26.7</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4762</v>
+        <v>0.4686</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3651</v>
+        <v>0.3551</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1111</v>
+        <v>0.1135</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.026</v>
+        <v>1.252</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.125</v>
+        <v>1.238</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.323</v>
+        <v>0.286</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.5696</v>
+        <v>0.5875</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49 of 159</t>
+          <t>47 of 161</t>
         </is>
       </c>
     </row>
@@ -905,45 +905,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>H. Greene</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>17.3</v>
+        <v>23.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4749</v>
+        <v>0.4759</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3398</v>
+        <v>0.3229</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1351</v>
+        <v>0.153</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.051</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.263</v>
+        <v>1.256</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.327</v>
+        <v>1.268</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.308</v>
+        <v>0.294</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.5443</v>
+        <v>0.5625</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54 of 159</t>
+          <t>51 of 161</t>
         </is>
       </c>
     </row>
@@ -953,45 +953,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>C. Quantrill</t>
+          <t>E. Lauer</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>20.3</v>
+        <v>21.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4574</v>
+        <v>0.4866</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3596</v>
+        <v>0.3548</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0978</v>
+        <v>0.1317</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0444</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.216</v>
+        <v>1.26</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.328</v>
+        <v>1.108</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.31</v>
+        <v>0.242</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.6909</v>
+        <v>0.7627</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.519</v>
+        <v>0.55</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56 of 159</t>
+          <t>54 of 161</t>
         </is>
       </c>
     </row>
@@ -1001,45 +1001,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>J. Assad</t>
+          <t>J. Bennett</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4511</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3489</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1021</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0224</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.327</v>
+        <v>1.242</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.4</v>
+        <v>1.242</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.333</v>
+        <v>0.302</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6727</v>
+        <v>0.7288</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.4177</v>
+        <v>0.5563</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73 of 159</t>
+          <t>52 of 161</t>
         </is>
       </c>
     </row>
@@ -1049,45 +1049,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>G. Hughes</t>
+          <t>H. Greene</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>24.7</v>
+        <v>17.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4672</v>
+        <v>0.4749</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3712</v>
+        <v>0.3398</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.096</v>
+        <v>0.1351</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0196</v>
+        <v>0.0411</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.254</v>
+        <v>1.263</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.378</v>
+        <v>1.327</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.338</v>
+        <v>0.308</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6545</v>
+        <v>0.7288</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5375</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59 of 159</t>
+          <t>56 of 161</t>
         </is>
       </c>
     </row>
@@ -1097,45 +1097,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>G. Rodriguez</t>
+          <t>J. Assad</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4988</v>
+        <v>0.4678</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.355</v>
+        <v>0.3684</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1439</v>
+        <v>0.0994</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0481</v>
+        <v>0.0244</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.342</v>
+        <v>1.327</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.458</v>
+        <v>1.4</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.317</v>
+        <v>0.333</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6364</v>
+        <v>0.678</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.3987</v>
+        <v>0.4313</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>77 of 159</t>
+          <t>73 of 161</t>
         </is>
       </c>
     </row>
@@ -1145,45 +1145,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>E. Sheehan</t>
+          <t>C. Quantrill</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13</v>
+        <v>20.3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4574</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3661</v>
+        <v>0.3596</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0982</v>
+        <v>0.0978</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0345</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.345</v>
+        <v>1.216</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.615</v>
+        <v>1.328</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6182</v>
+        <v>0.661</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.3861</v>
+        <v>0.5125</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78 of 159</t>
+          <t>59 of 161</t>
         </is>
       </c>
     </row>
@@ -1193,45 +1193,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>D. Kremer</t>
+          <t>E. Sheehan</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4627</v>
+        <v>0.4643</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3735</v>
+        <v>0.3661</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0892</v>
+        <v>0.0982</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.0833</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.334</v>
+        <v>1.345</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.308</v>
+        <v>1.615</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.309</v>
+        <v>0.333</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.6</v>
+        <v>0.6441</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.4051</v>
+        <v>0.4</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>75 of 159</t>
+          <t>78 of 161</t>
         </is>
       </c>
     </row>
@@ -1241,45 +1241,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>C. Prielipp</t>
+          <t>G. Rodriguez</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4902</v>
+        <v>0.4952</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3608</v>
+        <v>0.3642</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1294</v>
+        <v>0.131</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0496</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.365</v>
+        <v>1.348</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.125</v>
+        <v>1.429</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.235</v>
+        <v>0.306</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.6</v>
+        <v>0.6271</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.3544</v>
+        <v>0.3937</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>85 of 159</t>
+          <t>79 of 161</t>
         </is>
       </c>
     </row>
@@ -1289,45 +1289,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N. Eovaldi</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>21.3</v>
+        <v>26</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4561</v>
+        <v>0.4627</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3596</v>
+        <v>0.3735</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0965</v>
+        <v>0.0892</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.0288</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.376</v>
+        <v>1.334</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.359</v>
+        <v>1.308</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.29</v>
+        <v>0.309</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5818</v>
+        <v>0.6102</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3418</v>
+        <v>0.4125</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88 of 159</t>
+          <t>76 of 161</t>
         </is>
       </c>
     </row>
@@ -1337,45 +1337,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>K. Freeland</t>
+          <t>N. Eovaldi</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>24.7</v>
+        <v>21.3</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4485</v>
+        <v>0.4561</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3536</v>
+        <v>0.3596</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.095</v>
+        <v>0.0965</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.0556</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.379</v>
+        <v>1.376</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.257</v>
+        <v>1.359</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.274</v>
+        <v>0.29</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5636</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3291</v>
+        <v>0.3563</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92 of 159</t>
+          <t>85 of 161</t>
         </is>
       </c>
     </row>
@@ -1385,45 +1385,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>B. Singer</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>30</v>
+        <v>32.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4509</v>
+        <v>0.447</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3758</v>
+        <v>0.3453</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0752</v>
+        <v>0.1017</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.0317</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.243</v>
+        <v>1.391</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.3</v>
+        <v>1.102</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.315</v>
+        <v>0.245</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.5273</v>
+        <v>0.5593</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3481</v>
+        <v>0.3187</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>87 of 159</t>
+          <t>95 of 161</t>
         </is>
       </c>
     </row>
@@ -1464,14 +1464,14 @@
         <v>0.435</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.5091</v>
+        <v>0.5254</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.3418</v>
+        <v>0.3438</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89 of 159</t>
+          <t>90 of 161</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>D. Peterson</t>
         </is>
@@ -1496,13 +1496,13 @@
       <c r="F21" s="4" t="n">
         <v>0.3739</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G21" s="5" t="n">
         <v>0.0721</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>0.0171</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="6" t="n">
         <v>1.24</v>
       </c>
       <c r="J21" s="7" t="n">
@@ -1512,14 +1512,14 @@
         <v>0.305</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.4909</v>
+        <v>0.5085</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.3291</v>
+        <v>0.3312</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>93 of 159</t>
+          <t>92 of 161</t>
         </is>
       </c>
     </row>
@@ -1560,14 +1560,14 @@
         <v>0.364</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4727</v>
+        <v>0.4915</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.3228</v>
+        <v>0.325</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>94 of 159</t>
+          <t>94 of 161</t>
         </is>
       </c>
     </row>
@@ -1608,14 +1608,14 @@
         <v>0.366</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4727</v>
+        <v>0.4915</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.2595</v>
+        <v>0.2687</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>103 of 159</t>
+          <t>101 of 161</t>
         </is>
       </c>
     </row>
@@ -1656,14 +1656,14 @@
         <v>0.261</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4364</v>
+        <v>0.4576</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.3038</v>
+        <v>0.3063</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>97 of 159</t>
+          <t>97 of 161</t>
         </is>
       </c>
     </row>
@@ -1673,45 +1673,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Z. Matthews</t>
+          <t>S. Lugo</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>24</v>
+        <v>34.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4633</v>
+        <v>0.4432</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3807</v>
+        <v>0.3815</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0617</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0377</v>
+        <v>0.0073</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.451</v>
+        <v>1.348</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.708</v>
+        <v>1.212</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.373</v>
+        <v>0.284</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.4182</v>
+        <v>0.4237</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.2089</v>
+        <v>0.2562</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>113 of 159</t>
+          <t>103 of 161</t>
         </is>
       </c>
     </row>
@@ -1721,45 +1721,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>G. Holmes</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>26.7</v>
+        <v>24</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4274</v>
+        <v>0.4633</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3656</v>
+        <v>0.3807</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0618</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0283</v>
+        <v>0.0377</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.395</v>
+        <v>1.451</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.312</v>
+        <v>1.708</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.303</v>
+        <v>0.373</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.4</v>
+        <v>0.4237</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.2532</v>
+        <v>0.2125</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>104 of 159</t>
+          <t>111 of 161</t>
         </is>
       </c>
     </row>
@@ -1800,14 +1800,14 @@
         <v>0.395</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.3818</v>
+        <v>0.4068</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.2468</v>
+        <v>0.25</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>105 of 159</t>
+          <t>104 of 161</t>
         </is>
       </c>
     </row>
@@ -1821,41 +1821,41 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4726</v>
+        <v>0.4779</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3562</v>
+        <v>0.3717</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.1164</v>
+        <v>0.1062</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0167</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.493</v>
+        <v>1.461</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>2.125</v>
+        <v>1.865</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.423</v>
+        <v>0.368</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.3455</v>
+        <v>0.4068</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1646</v>
+        <v>0.2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>122 of 159</t>
+          <t>114 of 161</t>
         </is>
       </c>
     </row>
@@ -1896,14 +1896,14 @@
         <v>0.316</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.3273</v>
+        <v>0.3559</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1835</v>
+        <v>0.1812</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>115 of 159</t>
+          <t>116 of 161</t>
         </is>
       </c>
     </row>
@@ -1944,14 +1944,14 @@
         <v>0.291</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.3091</v>
+        <v>0.339</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1709</v>
+        <v>0.175</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>120 of 159</t>
+          <t>119 of 161</t>
         </is>
       </c>
     </row>
@@ -1961,45 +1961,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>L. Avila</t>
+          <t>G. Jump</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>13.3</v>
+        <v>29.3</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4765</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.3996</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0769</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0308</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.535</v>
+        <v>1.522</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.575</v>
+        <v>1.705</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.3</v>
+        <v>0.358</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.3091</v>
+        <v>0.322</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.1392</v>
+        <v>0.15</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>125 of 159</t>
+          <t>122 of 161</t>
         </is>
       </c>
     </row>
@@ -2009,45 +2009,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>27.7</v>
+        <v>13.3</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4632</v>
+        <v>0.4444</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3725</v>
+        <v>0.3981</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0907</v>
+        <v>0.0463</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0367</v>
+        <v>0.1</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.548</v>
+        <v>1.136</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.337</v>
+        <v>1.05</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.275</v>
+        <v>0.267</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2909</v>
+        <v>0.3051</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.1329</v>
+        <v>0.15</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>126 of 159</t>
+          <t>123 of 161</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>E. Fedde</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2067,35 +2067,35 @@
         <v>13.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.443</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3904</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0526</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0167</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.136</v>
+        <v>1.535</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.05</v>
+        <v>1.575</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.2727</v>
+        <v>0.3051</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1456</v>
+        <v>0.1375</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>123 of 159</t>
+          <t>126 of 161</t>
         </is>
       </c>
     </row>
@@ -2105,45 +2105,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>R. Vasquez</t>
+          <t>G. Marquez</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>13.7</v>
+        <v>5.3</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.4333</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3584</v>
+        <v>0.3889</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0444</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.08</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.563</v>
+        <v>1.414</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.585</v>
+        <v>1.875</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.2727</v>
+        <v>0.2881</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1139</v>
+        <v>0.1375</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>130 of 159</t>
+          <t>125 of 161</t>
         </is>
       </c>
     </row>
@@ -2153,45 +2153,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>A. Alvarez</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>16</v>
+        <v>27.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.4632</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3756</v>
+        <v>0.3725</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0907</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.461</v>
+        <v>1.548</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.188</v>
+        <v>1.337</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.25</v>
+        <v>0.275</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.2545</v>
+        <v>0.2881</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.1266</v>
+        <v>0.1313</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>128 of 159</t>
+          <t>127 of 161</t>
         </is>
       </c>
     </row>
@@ -2201,41 +2201,47 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>M. Englert</t>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5</v>
+        <v>13.7</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.451</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3059</v>
+        <v>0.4078</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.2118</v>
+        <v>0.0431</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.1304</v>
+        <v>0.0312</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.589</v>
+        <v>1.578</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.8</v>
+        <v>1.756</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.333</v>
+        <v>0.325</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.2364</v>
-      </c>
-      <c r="M36" s="8" t="n"/>
-      <c r="N36" s="2" t="n"/>
+        <v>0.2712</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>133 of 161</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2243,45 +2249,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>G. Marquez</t>
+          <t>L. Roupp</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>5.3</v>
+        <v>32.3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.4472</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3889</v>
+        <v>0.3935</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0537</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.08</v>
+        <v>0.0233</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>1.414</v>
+        <v>1.581</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.875</v>
+        <v>1.268</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.4</v>
+        <v>0.238</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.2364</v>
+        <v>0.2542</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.1203</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>129 of 159</t>
+          <t>137 of 161</t>
         </is>
       </c>
     </row>
@@ -2291,45 +2297,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>B. Sproat</t>
+          <t>W. Buehler</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>13.7</v>
+        <v>25.3</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.451</v>
+        <v>0.4371</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3943</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.0428</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0187</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>1.578</v>
+        <v>1.462</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.756</v>
+        <v>1.382</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.325</v>
+        <v>0.284</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.2182</v>
+        <v>0.2542</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.1076</v>
+        <v>0.125</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>132 of 159</t>
+          <t>129 of 161</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2345,7 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Q. Mathews</t>
+          <t>M. Englert</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2349,16 +2355,16 @@
         <v>5</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3696</v>
+        <v>0.3059</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0.1196</v>
+        <v>0.2118</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0</v>
+        <v>0.1304</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>1.589</v>
@@ -2367,10 +2373,10 @@
         <v>1.8</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.2182</v>
+        <v>0.2373</v>
       </c>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="2" t="n"/>
@@ -2379,47 +2385,47 @@
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>W. Buehler</t>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>A. Alvarez</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>25.3</v>
+        <v>21.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4371</v>
+        <v>0.4158</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3943</v>
-      </c>
-      <c r="G40" s="13" t="n">
-        <v>0.0428</v>
+        <v>0.3746</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>0.0412</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0187</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>1.462</v>
+        <v>0.0118</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>1.411</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.382</v>
+        <v>1.015</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.284</v>
+        <v>0.206</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.2</v>
+        <v>0.2373</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.1076</v>
+        <v>0.1187</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>131 of 159</t>
+          <t>130 of 161</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2433,7 @@
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>R. Lopez</t>
         </is>
@@ -2444,13 +2450,13 @@
       <c r="F41" s="4" t="n">
         <v>0.3931</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="10" t="n">
         <v>0.0405</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>0.0435</v>
       </c>
-      <c r="I41" s="14" t="n">
+      <c r="I41" s="11" t="n">
         <v>1.261</v>
       </c>
       <c r="J41" s="7" t="n">
@@ -2460,14 +2466,14 @@
         <v>0.429</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.1818</v>
+        <v>0.2203</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.1013</v>
+        <v>0.1125</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>134 of 159</t>
+          <t>131 of 161</t>
         </is>
       </c>
     </row>
@@ -2477,47 +2483,41 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>S. Cecconi</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4891</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3696</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.1196</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.596</v>
+        <v>1.589</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>0.0759</v>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>140 of 159</t>
-        </is>
-      </c>
+        <v>0.2203</v>
+      </c>
+      <c r="M42" s="8" t="n"/>
+      <c r="N42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2525,45 +2525,45 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>M. Perez</t>
+          <t>K. Rocker</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.4269</v>
+        <v>0.43</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.3926</v>
+        <v>0.3931</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.0344</v>
+        <v>0.0369</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.0104</v>
+        <v>0.0348</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.42</v>
+        <v>1.419</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.197</v>
+        <v>0.306</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.1636</v>
+        <v>0.2034</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.0886</v>
+        <v>0.1062</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>138 of 159</t>
+          <t>134 of 161</t>
         </is>
       </c>
     </row>
@@ -2573,45 +2573,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>M. Perez</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>17.3</v>
+        <v>25</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4572</v>
+        <v>0.4269</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.3926</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0344</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0361</v>
+        <v>0.0104</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.637</v>
+        <v>1.42</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.904</v>
+        <v>1</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.346</v>
+        <v>0.197</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.1636</v>
+        <v>0.1864</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.0696</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>142 of 159</t>
+          <t>138 of 161</t>
         </is>
       </c>
     </row>
@@ -2652,14 +2652,14 @@
         <v>0.233</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.1455</v>
+        <v>0.1695</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.0823</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>139 of 159</t>
+          <t>139 of 161</t>
         </is>
       </c>
     </row>
@@ -2669,45 +2669,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>M. Mikolas</t>
+          <t>S. Cecconi</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4643</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3512</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.1131</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0682</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.59</v>
+        <v>1.596</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>1.867</v>
+        <v>2.16</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.351</v>
+        <v>0.367</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.1273</v>
+        <v>0.1695</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.0759</v>
+        <v>0.075</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>141 of 159</t>
+          <t>142 of 161</t>
         </is>
       </c>
     </row>
@@ -2717,45 +2717,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>M. Lorenzen</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4491</v>
+        <v>0.4572</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.3862</v>
+        <v>0.3882</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.0629</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0513</v>
+        <v>0.0361</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.708</v>
+        <v>1.637</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>2.533</v>
+        <v>1.904</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.448</v>
+        <v>0.346</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.1091</v>
+        <v>0.1525</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0443</v>
+        <v>0.0688</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>147 of 159</t>
+          <t>144 of 161</t>
         </is>
       </c>
     </row>
@@ -2765,45 +2765,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>R. Johnson</t>
+          <t>C. Holmes</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>21.7</v>
+        <v>10.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4181</v>
+        <v>0.411</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.4257</v>
+        <v>0.3836</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>-0.0076</v>
+        <v>0.0274</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0256</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.705</v>
+        <v>1.499</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.662</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.279</v>
+        <v>0.194</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1525</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.038</v>
+        <v>0.0813</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>148 of 159</t>
+          <t>141 of 161</t>
         </is>
       </c>
     </row>
@@ -2813,45 +2813,45 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>M. Mikolas</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.4598</v>
+        <v>0.3827</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.375</v>
+        <v>0.3704</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.0848</v>
+        <v>0.0123</v>
       </c>
       <c r="H49" s="4" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.715</v>
+        <v>1.59</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>1.171</v>
+        <v>1.867</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.158</v>
+        <v>0.351</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1356</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.038</v>
+        <v>0.075</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>149 of 159</t>
+          <t>143 of 161</t>
         </is>
       </c>
     </row>
@@ -2861,45 +2861,45 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>R. Blanco</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>19.3</v>
+        <v>21.7</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.4861</v>
+        <v>0.4181</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.3622</v>
+        <v>0.4257</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.1238</v>
+        <v>-0.0076</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.0779</v>
+        <v>0.051</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.725</v>
+        <v>1.705</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1.345</v>
+        <v>1.662</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.209</v>
+        <v>0.279</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>0.0727</v>
+        <v>0.1017</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.0316</v>
+        <v>0.0375</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>150 of 159</t>
+          <t>150 of 161</t>
         </is>
       </c>
     </row>
@@ -2909,45 +2909,45 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>M. Keller</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>12.3</v>
+        <v>15</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4491</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.3862</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0629</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0513</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.494</v>
+        <v>1.708</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>1.784</v>
+        <v>2.533</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.351</v>
+        <v>0.448</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.0727</v>
+        <v>0.1017</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.0316</v>
+        <v>0.0437</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>151 of 159</t>
+          <t>149 of 161</t>
         </is>
       </c>
     </row>
@@ -2957,45 +2957,45 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>K. Drake</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>16.7</v>
+        <v>12.3</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4091</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.4182</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0345</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1.413</v>
+        <v>1.494</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>1.56</v>
+        <v>1.784</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>0.333</v>
+        <v>0.351</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>0.0545</v>
+        <v>0.0847</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0.0253</v>
+        <v>0.0312</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>153 of 159</t>
+          <t>153 of 161</t>
         </is>
       </c>
     </row>
@@ -3005,45 +3005,45 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Z. Littell</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>10.7</v>
+        <v>13.7</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.4294</v>
+        <v>0.4598</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.3824</v>
+        <v>0.375</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.0471</v>
+        <v>0.0848</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.04</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>1.792</v>
+        <v>1.715</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>1.781</v>
+        <v>1.171</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.286</v>
+        <v>0.158</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>0.0364</v>
+        <v>0.0847</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>0.0127</v>
+        <v>0.0375</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>154 of 159</t>
+          <t>151 of 161</t>
         </is>
       </c>
     </row>
@@ -3053,45 +3053,45 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>M. Barnett</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.4861</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.4299</v>
+        <v>0.3622</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>-0.0327</v>
+        <v>0.1238</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.0984</v>
+        <v>0.0779</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>1.695</v>
+        <v>1.725</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>1.575</v>
+        <v>1.345</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>0.229</v>
+        <v>0.209</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>0.0182</v>
+        <v>0.0678</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>0.0127</v>
+        <v>0.0312</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>155 of 159</t>
+          <t>152 of 161</t>
         </is>
       </c>
     </row>
@@ -3101,45 +3101,45 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>C. Mlodzinski</t>
+          <t>K. Drake</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>5.3</v>
+        <v>16.7</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.4</v>
+        <v>0.4167</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.4</v>
+        <v>0.4263</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.0411</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>1.855</v>
+        <v>1.413</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.478</v>
+        <v>0.333</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0.0182</v>
+        <v>0.0678</v>
       </c>
       <c r="M55" s="8" t="n">
-        <v>0.0063</v>
+        <v>0.025</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>157 of 159</t>
+          <t>155 of 161</t>
         </is>
       </c>
     </row>
@@ -3149,47 +3149,41 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>S. Arrighetti</t>
+          <t>C. Bassitt</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.4144</v>
+        <v>0.3855</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.4685</v>
+        <v>0.3976</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>-0.0541</v>
+        <v>-0.012</v>
       </c>
       <c r="H56" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>1.778</v>
+        <v>1.589</v>
       </c>
       <c r="J56" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>0.2</v>
+        <v>0.312</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>158 of 159</t>
-        </is>
-      </c>
+        <v>0.0508</v>
+      </c>
+      <c r="M56" s="8" t="n"/>
+      <c r="N56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3197,113 +3191,305 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
+          <t>Z. Littell</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="M57" s="8" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>156 of 161</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>M. Barnett</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>-0.0327</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="L58" s="8" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="M58" s="8" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>157 of 161</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>C. Mlodzinski</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="M59" s="8" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>159 of 161</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>S. Arrighetti</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>-0.0541</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="14" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>160 of 161</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
           <t>J. Springs</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D61" s="2" t="n">
         <v>10.3</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E61" s="4" t="n">
         <v>0.401</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F61" s="4" t="n">
         <v>0.4213</v>
       </c>
-      <c r="G57" s="13" t="n">
+      <c r="G61" s="13" t="n">
         <v>-0.0203</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <v>0.0408</v>
       </c>
-      <c r="I57" s="14" t="n">
+      <c r="I61" s="14" t="n">
         <v>1.892</v>
       </c>
-      <c r="J57" s="7" t="n">
+      <c r="J61" s="7" t="n">
         <v>2.032</v>
       </c>
-      <c r="K57" s="7" t="n">
+      <c r="K61" s="7" t="n">
         <v>0.333</v>
       </c>
-      <c r="L57" s="8" t="n">
+      <c r="L61" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M57" s="8" t="n">
+      <c r="M61" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>159 of 159</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="15" t="inlineStr">
-        <is>
-          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>161 of 161</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -606,7 +606,7 @@
         <v>0.182</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9831</v>
+        <v>0.9833</v>
       </c>
       <c r="M2" s="8" t="n"/>
       <c r="N2" s="2" t="n"/>
@@ -648,14 +648,14 @@
         <v>0.263</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.9153</v>
+        <v>0.9167</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.6875</v>
+        <v>0.675</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>34 of 161</t>
+          <t>37 of 161</t>
         </is>
       </c>
     </row>
@@ -696,14 +696,14 @@
         <v>0.32</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8814</v>
+        <v>0.8833</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.7375</v>
+        <v>0.7312</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28 of 161</t>
+          <t>29 of 161</t>
         </is>
       </c>
     </row>
@@ -744,14 +744,14 @@
         <v>0.5</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8667</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>0.7125</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30 of 161</t>
+          <t>31 of 161</t>
         </is>
       </c>
     </row>
@@ -792,14 +792,14 @@
         <v>0.388</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.8305</v>
+        <v>0.8333</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>0.6562</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39 of 161</t>
+          <t>40 of 161</t>
         </is>
       </c>
     </row>
@@ -840,14 +840,14 @@
         <v>0.23</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.7966</v>
+        <v>0.8</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.6062</v>
+        <v>0.6125</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45 of 161</t>
+          <t>46 of 161</t>
         </is>
       </c>
     </row>
@@ -857,45 +857,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>A. Kay</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>26.7</v>
+        <v>23.7</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4686</v>
+        <v>0.4759</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3551</v>
+        <v>0.3229</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1135</v>
+        <v>0.153</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.027</v>
+        <v>0.051</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.252</v>
+        <v>1.256</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.238</v>
+        <v>1.268</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.286</v>
+        <v>0.294</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7833</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.5875</v>
+        <v>0.5563</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47 of 161</t>
+          <t>54 of 161</t>
         </is>
       </c>
     </row>
@@ -905,41 +905,41 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>T. Phillips</t>
+          <t>A. Kay</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>23.7</v>
+        <v>32</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4759</v>
+        <v>0.4677</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3229</v>
+        <v>0.3548</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1129</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0305</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.256</v>
+        <v>1.252</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.268</v>
+        <v>1.25</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.294</v>
+        <v>0.297</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7667</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.5625</v>
+        <v>0.575</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -984,14 +984,14 @@
         <v>0.242</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.7627</v>
+        <v>0.7667</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>0.55</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54 of 161</t>
+          <t>55 of 161</t>
         </is>
       </c>
     </row>
@@ -1032,14 +1032,14 @@
         <v>0.302</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.7288</v>
+        <v>0.7333</v>
       </c>
       <c r="M11" s="8" t="n">
         <v>0.5563</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52 of 161</t>
+          <t>53 of 161</t>
         </is>
       </c>
     </row>
@@ -1080,14 +1080,14 @@
         <v>0.308</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.7288</v>
+        <v>0.7333</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>0.5375</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>56 of 161</t>
+          <t>57 of 161</t>
         </is>
       </c>
     </row>
@@ -1128,10 +1128,10 @@
         <v>0.333</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.678</v>
+        <v>0.6833</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.4313</v>
+        <v>0.425</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1176,14 +1176,14 @@
         <v>0.31</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.661</v>
+        <v>0.6667</v>
       </c>
       <c r="M14" s="8" t="n">
         <v>0.5125</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59 of 161</t>
+          <t>60 of 161</t>
         </is>
       </c>
     </row>
@@ -1224,10 +1224,10 @@
         <v>0.333</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.6441</v>
+        <v>0.65</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3937</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         <v>0.306</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.6271</v>
+        <v>0.6333</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.3937</v>
+        <v>0.3875</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         <v>0.309</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.6102</v>
+        <v>0.6167</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.4125</v>
+        <v>0.4062</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1368,14 +1368,14 @@
         <v>0.29</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5833</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3563</v>
+        <v>0.3438</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85 of 161</t>
+          <t>87 of 161</t>
         </is>
       </c>
     </row>
@@ -1416,14 +1416,14 @@
         <v>0.245</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.5593</v>
+        <v>0.55</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3187</v>
+        <v>0.3</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>95 of 161</t>
+          <t>97 of 161</t>
         </is>
       </c>
     </row>
@@ -1464,14 +1464,14 @@
         <v>0.435</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.5254</v>
+        <v>0.5333</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.3438</v>
+        <v>0.35</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90 of 161</t>
+          <t>86 of 161</t>
         </is>
       </c>
     </row>
@@ -1512,14 +1512,14 @@
         <v>0.305</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.5085</v>
+        <v>0.5167</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>0.3312</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>92 of 161</t>
+          <t>91 of 161</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>S. Drohan</t>
         </is>
@@ -1544,13 +1544,13 @@
       <c r="F22" s="4" t="n">
         <v>0.3853</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="5" t="n">
         <v>0.0709</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>0.027</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="6" t="n">
         <v>1.211</v>
       </c>
       <c r="J22" s="7" t="n">
@@ -1560,14 +1560,14 @@
         <v>0.364</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4915</v>
+        <v>0.5</v>
       </c>
       <c r="M22" s="8" t="n">
         <v>0.325</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>94 of 161</t>
+          <t>93 of 161</t>
         </is>
       </c>
     </row>
@@ -1608,14 +1608,14 @@
         <v>0.366</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4915</v>
+        <v>0.4833</v>
       </c>
       <c r="M23" s="8" t="n">
         <v>0.2687</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>101 of 161</t>
+          <t>102 of 161</t>
         </is>
       </c>
     </row>
@@ -1656,14 +1656,14 @@
         <v>0.261</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4576</v>
+        <v>0.4667</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>0.3063</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>97 of 161</t>
+          <t>96 of 161</t>
         </is>
       </c>
     </row>
@@ -1704,14 +1704,14 @@
         <v>0.284</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.4237</v>
+        <v>0.45</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.2562</v>
+        <v>0.2687</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>103 of 161</t>
+          <t>101 of 161</t>
         </is>
       </c>
     </row>
@@ -1721,45 +1721,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Z. Matthews</t>
+          <t>P. Sandoval</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24</v>
+        <v>25.7</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4633</v>
+        <v>0.445</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3807</v>
+        <v>0.3839</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0611</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0377</v>
+        <v>0.0261</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.451</v>
+        <v>1.387</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.708</v>
+        <v>1.753</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.373</v>
+        <v>0.395</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.4237</v>
+        <v>0.4333</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.2125</v>
+        <v>0.2625</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>111 of 161</t>
+          <t>103 of 161</t>
         </is>
       </c>
     </row>
@@ -1769,45 +1769,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>P. Sandoval</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>25.7</v>
+        <v>24</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.445</v>
+        <v>0.4633</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3839</v>
+        <v>0.3807</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0611</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0261</v>
+        <v>0.0377</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.387</v>
+        <v>1.451</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.753</v>
+        <v>1.708</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.395</v>
+        <v>0.373</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.4068</v>
+        <v>0.4167</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2125</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>104 of 161</t>
+          <t>111 of 161</t>
         </is>
       </c>
     </row>
@@ -1848,10 +1848,10 @@
         <v>0.368</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.4068</v>
+        <v>0.4</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1938</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1865,45 +1865,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>A. Nola</t>
+          <t>Z. Thornton</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4495</v>
+        <v>0.4197</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3989</v>
+        <v>0.3705</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0492</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0288</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.463</v>
+        <v>1.44</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.515</v>
+        <v>1.214</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.316</v>
+        <v>0.291</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.3559</v>
+        <v>0.35</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>0.1812</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>116 of 161</t>
+          <t>117 of 161</t>
         </is>
       </c>
     </row>
@@ -1913,45 +1913,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Z. Thornton</t>
+          <t>G. Jump</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>28</v>
+        <v>29.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4197</v>
+        <v>0.4765</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3705</v>
+        <v>0.3996</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.0769</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.0308</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.44</v>
+        <v>1.522</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.214</v>
+        <v>1.705</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.291</v>
+        <v>0.358</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.339</v>
+        <v>0.3333</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.175</v>
+        <v>0.1562</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>119 of 161</t>
+          <t>120 of 161</t>
         </is>
       </c>
     </row>
@@ -1961,45 +1961,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>G. Jump</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>29.3</v>
+        <v>13.3</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4765</v>
+        <v>0.4444</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3996</v>
+        <v>0.3981</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0769</v>
+        <v>0.0463</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0308</v>
+        <v>0.1</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.522</v>
+        <v>1.136</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.705</v>
+        <v>1.05</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.358</v>
+        <v>0.267</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.322</v>
+        <v>0.3167</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.15</v>
+        <v>0.1562</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>122 of 161</t>
+          <t>121 of 161</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>E. Fedde</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2019,35 +2019,35 @@
         <v>13.3</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.443</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3904</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0526</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0167</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.136</v>
+        <v>1.535</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.05</v>
+        <v>1.575</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.3051</v>
+        <v>0.3167</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.15</v>
+        <v>0.1437</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>123 of 161</t>
+          <t>124 of 161</t>
         </is>
       </c>
     </row>
@@ -2057,45 +2057,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>L. Avila</t>
+          <t>G. Marquez</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>13.3</v>
+        <v>5.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4333</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.3889</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0444</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.08</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.535</v>
+        <v>1.414</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.575</v>
+        <v>1.875</v>
       </c>
       <c r="K33" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L33" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L33" s="8" t="n">
-        <v>0.3051</v>
-      </c>
       <c r="M33" s="8" t="n">
-        <v>0.1375</v>
+        <v>0.1437</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>126 of 161</t>
+          <t>123 of 161</t>
         </is>
       </c>
     </row>
@@ -2105,38 +2105,38 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>G. Marquez</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5.3</v>
+        <v>27.7</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.4632</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3889</v>
+        <v>0.3725</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0907</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.08</v>
+        <v>0.0367</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.414</v>
+        <v>1.548</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.875</v>
+        <v>1.337</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.4</v>
+        <v>0.275</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.2881</v>
+        <v>0.3</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>0.1375</v>
@@ -2153,45 +2153,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>27.7</v>
+        <v>13.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4632</v>
+        <v>0.4162</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3725</v>
+        <v>0.3584</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.0907</v>
+        <v>0.0578</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0367</v>
+        <v>0.0217</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.548</v>
+        <v>1.563</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.337</v>
+        <v>0.585</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.275</v>
+        <v>0.1</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.2881</v>
+        <v>0.2833</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.1313</v>
+        <v>0.1125</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>127 of 161</t>
+          <t>132 of 161</t>
         </is>
       </c>
     </row>
@@ -2201,45 +2201,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>B. Sproat</t>
+          <t>W. Buehler</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>13.7</v>
+        <v>25.3</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.451</v>
+        <v>0.4371</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3943</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.0428</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0187</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.578</v>
+        <v>1.462</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.756</v>
+        <v>1.382</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.325</v>
+        <v>0.284</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.2712</v>
+        <v>0.2667</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.1062</v>
+        <v>0.1313</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>133 of 161</t>
+          <t>127 of 161</t>
         </is>
       </c>
     </row>
@@ -2249,45 +2249,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>L. Roupp</t>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>32.3</v>
+        <v>13.7</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4472</v>
+        <v>0.451</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3935</v>
+        <v>0.4078</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.0537</v>
+        <v>0.0431</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0233</v>
+        <v>0.0312</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>1.581</v>
+        <v>1.578</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.268</v>
+        <v>1.756</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.238</v>
+        <v>0.325</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.2542</v>
+        <v>0.2667</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1062</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>137 of 161</t>
+          <t>133 of 161</t>
         </is>
       </c>
     </row>
@@ -2297,45 +2297,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>W. Buehler</t>
+          <t>L. Roupp</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>25.3</v>
+        <v>32.3</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4371</v>
+        <v>0.4472</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3943</v>
+        <v>0.3935</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0.0428</v>
+        <v>0.0537</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0187</v>
+        <v>0.0233</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>1.462</v>
+        <v>1.581</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.382</v>
+        <v>1.268</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.284</v>
+        <v>0.238</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.2542</v>
+        <v>0.25</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.125</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>129 of 161</t>
+          <t>137 of 161</t>
         </is>
       </c>
     </row>
@@ -2345,41 +2345,47 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>M. Englert</t>
+          <t>A. Alvarez</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>5</v>
+        <v>21.7</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4158</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3059</v>
+        <v>0.3746</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0.2118</v>
+        <v>0.0412</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.1304</v>
+        <v>0.0118</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>1.589</v>
+        <v>1.411</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.8</v>
+        <v>1.015</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.333</v>
+        <v>0.206</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.2373</v>
-      </c>
-      <c r="M39" s="8" t="n"/>
-      <c r="N39" s="2" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>128 of 161</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2387,47 +2393,41 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>A. Alvarez</t>
+          <t>M. Englert</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>21.7</v>
+        <v>5</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4158</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3746</v>
+        <v>0.3059</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0.0412</v>
+        <v>0.2118</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0118</v>
+        <v>0.1304</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>1.411</v>
+        <v>1.589</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.015</v>
+        <v>1.8</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.206</v>
+        <v>0.333</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.2373</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>0.1187</v>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>130 of 161</t>
-        </is>
-      </c>
+        <v>0.2333</v>
+      </c>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2466,14 +2466,14 @@
         <v>0.429</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.2203</v>
+        <v>0.2333</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.1125</v>
+        <v>0.1187</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>131 of 161</t>
+          <t>130 of 161</t>
         </is>
       </c>
     </row>
@@ -2481,43 +2481,49 @@
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>Q. Mathews</t>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>A. Nola</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.4444</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3696</v>
-      </c>
-      <c r="G42" s="13" t="n">
-        <v>0.1196</v>
+        <v>0.4074</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>0.037</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>1.589</v>
+        <v>0.0614</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>1.365</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.8</v>
+        <v>1.481</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.2203</v>
-      </c>
-      <c r="M42" s="8" t="n"/>
-      <c r="N42" s="2" t="n"/>
+        <v>0.2167</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>131 of 161</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2525,47 +2531,41 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>K. Rocker</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="2" t="n">
-        <v>26</v>
-      </c>
       <c r="E43" s="4" t="n">
-        <v>0.43</v>
+        <v>0.4891</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.3696</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.0369</v>
+        <v>0.1196</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.0348</v>
+        <v>0</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.419</v>
+        <v>1.589</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.306</v>
+        <v>0.375</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.2034</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>0.1062</v>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>134 of 161</t>
-        </is>
-      </c>
+        <v>0.2167</v>
+      </c>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2573,45 +2573,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>M. Perez</t>
+          <t>K. Rocker</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4269</v>
+        <v>0.43</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3926</v>
+        <v>0.3931</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.0344</v>
+        <v>0.0369</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0104</v>
+        <v>0.0348</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.42</v>
+        <v>1.419</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.197</v>
+        <v>0.306</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.1864</v>
+        <v>0.2</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1062</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>138 of 161</t>
+          <t>134 of 161</t>
         </is>
       </c>
     </row>
@@ -2621,45 +2621,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>T. Sugano</t>
+          <t>M. Perez</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>29.3</v>
+        <v>25</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4086</v>
+        <v>0.4269</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3777</v>
+        <v>0.3926</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.0309</v>
+        <v>0.0344</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0696</v>
+        <v>0.0104</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.321</v>
+        <v>1.42</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>1.057</v>
+        <v>1</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.233</v>
+        <v>0.197</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.1695</v>
+        <v>0.1833</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>139 of 161</t>
+          <t>138 of 161</t>
         </is>
       </c>
     </row>
@@ -2669,45 +2669,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>S. Cecconi</t>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4086</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3777</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.0309</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.0696</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.596</v>
+        <v>1.321</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>2.16</v>
+        <v>1.057</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.367</v>
+        <v>0.233</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.1695</v>
+        <v>0.1667</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.075</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>142 of 161</t>
+          <t>139 of 161</t>
         </is>
       </c>
     </row>
@@ -2717,45 +2717,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>S. Cecconi</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>17.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4572</v>
+        <v>0.4643</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.3512</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.1131</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0361</v>
+        <v>0.0682</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.637</v>
+        <v>1.596</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.904</v>
+        <v>2.16</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.346</v>
+        <v>0.367</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.1525</v>
+        <v>0.1667</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0688</v>
+        <v>0.075</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>144 of 161</t>
+          <t>142 of 161</t>
         </is>
       </c>
     </row>
@@ -2765,45 +2765,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>C. Holmes</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>10.7</v>
+        <v>17.3</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.411</v>
+        <v>0.4572</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.3836</v>
+        <v>0.3882</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.0274</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.0361</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.499</v>
+        <v>1.637</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.904</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.194</v>
+        <v>0.346</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.1525</v>
+        <v>0.15</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0813</v>
+        <v>0.0688</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>141 of 161</t>
+          <t>145 of 161</t>
         </is>
       </c>
     </row>
@@ -2813,45 +2813,45 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>M. Mikolas</t>
+          <t>C. Holmes</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>15</v>
+        <v>10.7</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.411</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3836</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.0274</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0256</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.59</v>
+        <v>1.499</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>1.867</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.351</v>
+        <v>0.194</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.1356</v>
+        <v>0.15</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.075</v>
+        <v>0.0813</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>143 of 161</t>
+          <t>141 of 161</t>
         </is>
       </c>
     </row>
@@ -2861,45 +2861,45 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>R. Johnson</t>
+          <t>M. Mikolas</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>21.7</v>
+        <v>15</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.4181</v>
+        <v>0.3827</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.4257</v>
+        <v>0.3704</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>-0.0076</v>
+        <v>0.0123</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.051</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.705</v>
+        <v>1.59</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1.662</v>
+        <v>1.867</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.279</v>
+        <v>0.351</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>0.1017</v>
+        <v>0.1333</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.075</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>150 of 161</t>
+          <t>143 of 161</t>
         </is>
       </c>
     </row>
@@ -2909,45 +2909,45 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>M. Lorenzen</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>15</v>
+        <v>21.7</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.4491</v>
+        <v>0.4181</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.3862</v>
+        <v>0.4257</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.0629</v>
+        <v>-0.0076</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.0513</v>
+        <v>0.051</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.708</v>
+        <v>1.705</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>2.533</v>
+        <v>1.662</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.448</v>
+        <v>0.279</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.1017</v>
+        <v>0.1</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.0437</v>
+        <v>0.0375</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>149 of 161</t>
+          <t>150 of 161</t>
         </is>
       </c>
     </row>
@@ -2957,45 +2957,45 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>M. Keller</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>12.3</v>
+        <v>13.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4598</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.375</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0848</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1.494</v>
+        <v>1.715</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>1.784</v>
+        <v>1.171</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>0.351</v>
+        <v>0.158</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>0.0847</v>
+        <v>0.1</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0.0312</v>
+        <v>0.0437</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>153 of 161</t>
+          <t>149 of 161</t>
         </is>
       </c>
     </row>
@@ -3005,38 +3005,38 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>13.7</v>
+        <v>19.3</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.4598</v>
+        <v>0.4861</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.375</v>
+        <v>0.3622</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.0848</v>
+        <v>0.1238</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0779</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>1.715</v>
+        <v>1.725</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>1.171</v>
+        <v>1.345</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.158</v>
+        <v>0.209</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>0.0847</v>
+        <v>0.0833</v>
       </c>
       <c r="M53" s="8" t="n">
         <v>0.0375</v>
@@ -3053,45 +3053,45 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>R. Blanco</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.4861</v>
+        <v>0.4091</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.3622</v>
+        <v>0.4182</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.1238</v>
+        <v>-0.0091</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.0779</v>
+        <v>0.0345</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>1.725</v>
+        <v>1.494</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>1.345</v>
+        <v>1.784</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>0.209</v>
+        <v>0.351</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>0.0678</v>
+        <v>0.0833</v>
       </c>
       <c r="M54" s="8" t="n">
         <v>0.0312</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>152 of 161</t>
+          <t>153 of 161</t>
         </is>
       </c>
     </row>
@@ -3132,14 +3132,14 @@
         <v>0.333</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0.0678</v>
+        <v>0.0667</v>
       </c>
       <c r="M55" s="8" t="n">
         <v>0.025</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>155 of 161</t>
+          <t>154 of 161</t>
         </is>
       </c>
     </row>
@@ -3149,41 +3149,47 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>C. Bassitt</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>5.3</v>
+        <v>18.7</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.3855</v>
+        <v>0.4477</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.3976</v>
+        <v>0.3917</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>-0.012</v>
+        <v>0.056</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>1.589</v>
+        <v>1.778</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>1.5</v>
+        <v>2.411</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>0.312</v>
+        <v>0.403</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>0.0508</v>
-      </c>
-      <c r="M56" s="8" t="n"/>
-      <c r="N56" s="2" t="n"/>
+        <v>0.05</v>
+      </c>
+      <c r="M56" s="8" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>155 of 161</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3191,47 +3197,41 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>Z. Littell</t>
+          <t>C. Bassitt</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>10.7</v>
+        <v>5.3</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.4294</v>
+        <v>0.3855</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.3824</v>
+        <v>0.3976</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.0471</v>
+        <v>-0.012</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>1.792</v>
+        <v>1.589</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>1.781</v>
+        <v>1.5</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.286</v>
+        <v>0.312</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="M57" s="8" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>156 of 161</t>
-        </is>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="M57" s="8" t="n"/>
+      <c r="N57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3239,45 +3239,45 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>M. Barnett</t>
+          <t>Z. Littell</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>13.3</v>
+        <v>10.7</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.3972</v>
+        <v>0.4294</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.4299</v>
+        <v>0.3824</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>-0.0327</v>
+        <v>0.0471</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>0.0984</v>
+        <v>0.04</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>1.695</v>
+        <v>1.792</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>1.575</v>
+        <v>1.781</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>0.229</v>
+        <v>0.286</v>
       </c>
       <c r="L58" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0333</v>
       </c>
       <c r="M58" s="8" t="n">
         <v>0.0125</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>157 of 161</t>
+          <t>156 of 161</t>
         </is>
       </c>
     </row>
@@ -3287,45 +3287,45 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>C. Mlodzinski</t>
+          <t>M. Barnett</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>5.3</v>
+        <v>13.3</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3972</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.4</v>
+        <v>0.4299</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0</v>
+        <v>-0.0327</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.0984</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>1.855</v>
+        <v>1.695</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>3</v>
+        <v>1.575</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.478</v>
+        <v>0.229</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0167</v>
       </c>
       <c r="M59" s="8" t="n">
-        <v>0.0063</v>
+        <v>0.0125</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>159 of 161</t>
+          <t>157 of 161</t>
         </is>
       </c>
     </row>
@@ -3335,45 +3335,45 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>S. Arrighetti</t>
+          <t>C. Mlodzinski</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.4144</v>
+        <v>0.4</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.4685</v>
+        <v>0.4</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>-0.0541</v>
+        <v>0</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
       <c r="I60" s="14" t="n">
-        <v>1.778</v>
+        <v>1.855</v>
       </c>
       <c r="J60" s="7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>0.2</v>
+        <v>0.478</v>
       </c>
       <c r="L60" s="8" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="M60" s="8" t="n">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>160 of 161</t>
+          <t>159 of 161</t>
         </is>
       </c>
     </row>
@@ -3383,35 +3383,35 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>J. Springs</t>
+          <t>S. Arrighetti</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>10.3</v>
+        <v>6</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.401</v>
+        <v>0.4144</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>0.4213</v>
+        <v>0.4685</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>-0.0203</v>
+        <v>-0.0541</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>1.892</v>
+        <v>1.778</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>2.032</v>
+        <v>1.5</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="L61" s="8" t="n">
         <v>0</v>
@@ -3421,75 +3421,123 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
+          <t>160 of 161</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>J. Springs</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="I62" s="14" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>2.032</v>
+      </c>
+      <c r="K62" s="7" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
           <t>161 of 161</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -606,7 +606,7 @@
         <v>0.182</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9833</v>
+        <v>1</v>
       </c>
       <c r="M2" s="8" t="n"/>
       <c r="N2" s="2" t="n"/>
@@ -648,14 +648,14 @@
         <v>0.263</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.9167</v>
+        <v>0.8833</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.675</v>
+        <v>0.6852</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>37 of 161</t>
+          <t>36 of 163</t>
         </is>
       </c>
     </row>
@@ -699,11 +699,11 @@
         <v>0.8833</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.7312</v>
+        <v>0.7222</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29 of 161</t>
+          <t>29 of 163</t>
         </is>
       </c>
     </row>
@@ -713,45 +713,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N. Schultz</t>
+          <t>A. Kay</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7.3</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4767</v>
+        <v>0.4689</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3488</v>
+        <v>0.3397</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1279</v>
+        <v>0.1292</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0265</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.166</v>
+        <v>1.194</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.455</v>
+        <v>1.25</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.317</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>0.8667</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.7125</v>
+        <v>0.6914</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31 of 161</t>
+          <t>35 of 163</t>
         </is>
       </c>
     </row>
@@ -761,45 +761,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>M. Liberatore</t>
+          <t>N. Schultz</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>25.3</v>
+        <v>7.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4824</v>
+        <v>0.4767</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3607</v>
+        <v>0.3488</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1218</v>
+        <v>0.1279</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0283</v>
+        <v>0.0244</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.146</v>
+        <v>1.166</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.461</v>
+        <v>2.455</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.388</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.8333</v>
+        <v>0.85</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.6562</v>
+        <v>0.7037</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40 of 161</t>
+          <t>32 of 163</t>
         </is>
       </c>
     </row>
@@ -809,45 +809,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>C. Rea</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23</v>
+        <v>23.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4759</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3534</v>
+        <v>0.3229</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1178</v>
+        <v>0.153</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0444</v>
+        <v>0.051</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.211</v>
+        <v>1.256</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1</v>
+        <v>1.268</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.23</v>
+        <v>0.294</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.6125</v>
+        <v>0.5802</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46 of 161</t>
+          <t>50 of 163</t>
         </is>
       </c>
     </row>
@@ -857,45 +857,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>T. Phillips</t>
+          <t>M. Liberatore</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>23.7</v>
+        <v>25.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4759</v>
+        <v>0.4824</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3229</v>
+        <v>0.3607</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1218</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0283</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.256</v>
+        <v>1.146</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.268</v>
+        <v>1.461</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.294</v>
+        <v>0.388</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.7833</v>
+        <v>0.8</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.5563</v>
+        <v>0.6481</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54 of 161</t>
+          <t>40 of 163</t>
         </is>
       </c>
     </row>
@@ -905,45 +905,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>A. Kay</t>
+          <t>C. Rea</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4677</v>
+        <v>0.4713</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3548</v>
+        <v>0.3487</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1129</v>
+        <v>0.1226</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0305</v>
+        <v>0.0455</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.252</v>
+        <v>1.26</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.297</v>
+        <v>0.222</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7667</v>
+        <v>0.7833</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.575</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51 of 161</t>
+          <t>51 of 163</t>
         </is>
       </c>
     </row>
@@ -987,11 +987,11 @@
         <v>0.7667</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.55</v>
+        <v>0.5679</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55 of 161</t>
+          <t>52 of 163</t>
         </is>
       </c>
     </row>
@@ -1005,41 +1005,41 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4511</v>
+        <v>0.4597</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3489</v>
+        <v>0.3472</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1021</v>
+        <v>0.1125</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0224</v>
+        <v>0.0263</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.242</v>
+        <v>1.253</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.242</v>
+        <v>1.444</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.302</v>
+        <v>0.35</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.7333</v>
+        <v>0.75</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.5563</v>
+        <v>0.5926</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53 of 161</t>
+          <t>48 of 163</t>
         </is>
       </c>
     </row>
@@ -1083,11 +1083,11 @@
         <v>0.7333</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.5375</v>
+        <v>0.5556</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57 of 161</t>
+          <t>54 of 163</t>
         </is>
       </c>
     </row>
@@ -1097,45 +1097,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>J. Assad</t>
+          <t>C. Bradford</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10</v>
+        <v>15.3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4884</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3116</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1767</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0161</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.327</v>
+        <v>1.279</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.4</v>
+        <v>1.435</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.333</v>
+        <v>0.362</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6833</v>
+        <v>0.7167</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.425</v>
+        <v>0.5185</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73 of 161</t>
+          <t>60 of 163</t>
         </is>
       </c>
     </row>
@@ -1145,45 +1145,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>C. Quantrill</t>
+          <t>J. Assad</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>20.3</v>
+        <v>10</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4574</v>
+        <v>0.4678</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3596</v>
+        <v>0.3684</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0978</v>
+        <v>0.0994</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0244</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.216</v>
+        <v>1.327</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.328</v>
+        <v>1.4</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.31</v>
+        <v>0.333</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>0.6667</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.5125</v>
+        <v>0.4506</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60 of 161</t>
+          <t>71 of 163</t>
         </is>
       </c>
     </row>
@@ -1224,14 +1224,14 @@
         <v>0.333</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.65</v>
+        <v>0.6333</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.3937</v>
+        <v>0.4198</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78 of 161</t>
+          <t>75 of 163</t>
         </is>
       </c>
     </row>
@@ -1272,14 +1272,14 @@
         <v>0.306</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.6333</v>
+        <v>0.6167</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.3875</v>
+        <v>0.4136</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79 of 161</t>
+          <t>76 of 163</t>
         </is>
       </c>
     </row>
@@ -1289,45 +1289,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>D. Kremer</t>
+          <t>C. Quantrill</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>26</v>
+        <v>16.3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4627</v>
+        <v>0.4569</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3735</v>
+        <v>0.375</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0892</v>
+        <v>0.0819</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.0156</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.334</v>
+        <v>1.106</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.308</v>
+        <v>0.918</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.309</v>
+        <v>0.22</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.6167</v>
+        <v>0.6</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.4062</v>
+        <v>0.4383</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76 of 161</t>
+          <t>73 of 163</t>
         </is>
       </c>
     </row>
@@ -1337,45 +1337,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>N. Eovaldi</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>21.3</v>
+        <v>9</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4561</v>
+        <v>0.4558</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3596</v>
+        <v>0.381</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0965</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.0278</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.376</v>
+        <v>1.209</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.359</v>
+        <v>1.556</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.29</v>
+        <v>0.435</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5833</v>
+        <v>0.5667</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3438</v>
+        <v>0.3827</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>87 of 161</t>
+          <t>83 of 163</t>
         </is>
       </c>
     </row>
@@ -1385,45 +1385,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>K. Freeland</t>
+          <t>P. Sandoval</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>32.7</v>
+        <v>29.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.447</v>
+        <v>0.4527</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3453</v>
+        <v>0.3783</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.1017</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0317</v>
+        <v>0.0216</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.391</v>
+        <v>1.37</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.102</v>
+        <v>1.921</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.245</v>
+        <v>0.429</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>0.55</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3</v>
+        <v>0.3704</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>97 of 161</t>
+          <t>85 of 163</t>
         </is>
       </c>
     </row>
@@ -1433,45 +1433,45 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>C. Povich</t>
+          <t>N. Eovaldi</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9</v>
+        <v>21.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.4561</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.381</v>
+        <v>0.3596</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0965</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.0556</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1.209</v>
+        <v>1.376</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.556</v>
+        <v>1.359</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.435</v>
+        <v>0.29</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.5333</v>
+        <v>0.55</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.35</v>
+        <v>0.3642</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86 of 161</t>
+          <t>87 of 163</t>
         </is>
       </c>
     </row>
@@ -1481,45 +1481,45 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>D. Peterson</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>28.7</v>
+        <v>32.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4459</v>
+        <v>0.447</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3739</v>
+        <v>0.3453</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0721</v>
+        <v>0.1017</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0171</v>
+        <v>0.0317</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1.24</v>
+        <v>1.391</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.256</v>
+        <v>1.102</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.305</v>
+        <v>0.245</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.5167</v>
+        <v>0.5333</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.3312</v>
+        <v>0.3457</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>91 of 161</t>
+          <t>91 of 163</t>
         </is>
       </c>
     </row>
@@ -1529,45 +1529,45 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>S. Drohan</t>
+          <t>D. Peterson</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>28.3</v>
+        <v>28.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4563</v>
+        <v>0.4459</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3853</v>
+        <v>0.3739</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0709</v>
+        <v>0.0721</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.027</v>
+        <v>0.0171</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>1.211</v>
+        <v>1.24</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.341</v>
+        <v>1.256</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.364</v>
+        <v>0.305</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5333</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.325</v>
+        <v>0.3642</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93 of 161</t>
+          <t>88 of 163</t>
         </is>
       </c>
     </row>
@@ -1577,45 +1577,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>J. Perkins</t>
+          <t>S. Drohan</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>24</v>
+        <v>28.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4455</v>
+        <v>0.4563</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.3853</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0767</v>
+        <v>0.0709</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.027</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.416</v>
+        <v>1.211</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.708</v>
+        <v>1.341</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4833</v>
+        <v>0.5167</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.2687</v>
+        <v>0.3519</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>102 of 161</t>
+          <t>90 of 163</t>
         </is>
       </c>
     </row>
@@ -1625,45 +1625,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>H. Dobbins</t>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>17.3</v>
+        <v>24</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4508</v>
+        <v>0.4455</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3826</v>
+        <v>0.3688</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0682</v>
+        <v>0.0767</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.029</v>
+        <v>0.0556</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.302</v>
+        <v>1.416</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.154</v>
+        <v>1.708</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.261</v>
+        <v>0.366</v>
       </c>
       <c r="L24" s="8" t="n">
         <v>0.4667</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.3063</v>
+        <v>0.3148</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>96 of 161</t>
+          <t>94 of 163</t>
         </is>
       </c>
     </row>
@@ -1673,45 +1673,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>S. Lugo</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>34.7</v>
+        <v>27.3</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4432</v>
+        <v>0.4431</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3815</v>
+        <v>0.3791</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.0617</v>
+        <v>0.064</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0073</v>
+        <v>0.0364</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.348</v>
+        <v>1.305</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.212</v>
+        <v>1.244</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.45</v>
+        <v>0.4667</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.2687</v>
+        <v>0.2963</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>101 of 161</t>
+          <t>98 of 163</t>
         </is>
       </c>
     </row>
@@ -1721,45 +1721,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>P. Sandoval</t>
+          <t>H. Dobbins</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>25.7</v>
+        <v>22.3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.445</v>
+        <v>0.454</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3839</v>
+        <v>0.3955</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0611</v>
+        <v>0.0585</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0261</v>
+        <v>0.0333</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.387</v>
+        <v>1.365</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.753</v>
+        <v>1.164</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.395</v>
+        <v>0.236</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.4333</v>
+        <v>0.45</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.2625</v>
+        <v>0.2654</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>103 of 161</t>
+          <t>103 of 163</t>
         </is>
       </c>
     </row>
@@ -1800,14 +1800,14 @@
         <v>0.373</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.4167</v>
+        <v>0.4</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.2125</v>
+        <v>0.2284</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>111 of 161</t>
+          <t>108 of 163</t>
         </is>
       </c>
     </row>
@@ -1817,45 +1817,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>R. Stock</t>
+          <t>S. Lugo</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12.3</v>
+        <v>28.7</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4779</v>
+        <v>0.4398</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3717</v>
+        <v>0.3843</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.1062</v>
+        <v>0.0556</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.461</v>
+        <v>1.341</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.865</v>
+        <v>1.256</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.368</v>
+        <v>0.294</v>
       </c>
       <c r="L28" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.1938</v>
+        <v>0.2407</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>114 of 161</t>
+          <t>107 of 163</t>
         </is>
       </c>
     </row>
@@ -1865,45 +1865,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Z. Thornton</t>
+          <t>R. Stock</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>28</v>
+        <v>12.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4197</v>
+        <v>0.4779</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3705</v>
+        <v>0.3717</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.1062</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.0167</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.44</v>
+        <v>1.461</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.214</v>
+        <v>1.865</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.291</v>
+        <v>0.368</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.35</v>
+        <v>0.3833</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.1812</v>
+        <v>0.2099</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>117 of 161</t>
+          <t>112 of 163</t>
         </is>
       </c>
     </row>
@@ -1913,45 +1913,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>G. Jump</t>
+          <t>Z. Thornton</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>29.3</v>
+        <v>28</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4765</v>
+        <v>0.4197</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3996</v>
+        <v>0.3705</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0769</v>
+        <v>0.0492</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0308</v>
+        <v>0.0288</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.522</v>
+        <v>1.44</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.705</v>
+        <v>1.214</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.358</v>
+        <v>0.291</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.3667</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.1562</v>
+        <v>0.2037</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>120 of 161</t>
+          <t>113 of 163</t>
         </is>
       </c>
     </row>
@@ -1995,11 +1995,11 @@
         <v>0.3167</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.1562</v>
+        <v>0.1667</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>121 of 161</t>
+          <t>120 of 163</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
         <v>0.3167</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.1437</v>
+        <v>0.142</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>124 of 161</t>
+          <t>124 of 163</t>
         </is>
       </c>
     </row>
@@ -2091,11 +2091,11 @@
         <v>0.3</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1437</v>
+        <v>0.1543</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>123 of 161</t>
+          <t>121 of 163</t>
         </is>
       </c>
     </row>
@@ -2139,11 +2139,11 @@
         <v>0.3</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1375</v>
+        <v>0.1358</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>125 of 161</t>
+          <t>125 of 163</t>
         </is>
       </c>
     </row>
@@ -2187,11 +2187,11 @@
         <v>0.2833</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.1125</v>
+        <v>0.1173</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>132 of 161</t>
+          <t>132 of 163</t>
         </is>
       </c>
     </row>
@@ -2235,11 +2235,11 @@
         <v>0.2667</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.1313</v>
+        <v>0.1358</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>127 of 161</t>
+          <t>126 of 163</t>
         </is>
       </c>
     </row>
@@ -2249,45 +2249,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>B. Sproat</t>
+          <t>L. Roupp</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>13.7</v>
+        <v>25.3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.451</v>
+        <v>0.459</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3888</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.0703</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0286</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>1.578</v>
+        <v>1.564</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.756</v>
+        <v>1.421</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.325</v>
+        <v>0.277</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>0.2667</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.1062</v>
+        <v>0.1111</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>133 of 161</t>
+          <t>133 of 163</t>
         </is>
       </c>
     </row>
@@ -2297,45 +2297,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>L. Roupp</t>
+          <t>A. Alvarez</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>32.3</v>
+        <v>21.7</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4472</v>
+        <v>0.4158</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3935</v>
+        <v>0.3746</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0.0537</v>
+        <v>0.0412</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0233</v>
+        <v>0.0118</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>1.581</v>
+        <v>1.411</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.268</v>
+        <v>1.015</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.238</v>
+        <v>0.206</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1296</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>137 of 161</t>
+          <t>127 of 163</t>
         </is>
       </c>
     </row>
@@ -2345,45 +2345,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>A. Alvarez</t>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>21.7</v>
+        <v>13.7</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4158</v>
+        <v>0.451</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3746</v>
+        <v>0.4078</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0.0412</v>
+        <v>0.0431</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0118</v>
+        <v>0.0312</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>1.411</v>
+        <v>1.578</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.015</v>
+        <v>1.756</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.206</v>
+        <v>0.325</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.125</v>
+        <v>0.1049</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>128 of 161</t>
+          <t>135 of 163</t>
         </is>
       </c>
     </row>
@@ -2393,41 +2393,47 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>M. Englert</t>
+          <t>R. Lopez</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4335</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3059</v>
+        <v>0.3931</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0.2118</v>
+        <v>0.0405</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.1304</v>
+        <v>0.0435</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>1.589</v>
+        <v>1.261</v>
       </c>
       <c r="J40" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>0.2333</v>
       </c>
-      <c r="M40" s="8" t="n"/>
-      <c r="N40" s="2" t="n"/>
+      <c r="M40" s="8" t="n">
+        <v>0.1235</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>130 of 163</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2435,47 +2441,41 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>R. Lopez</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.4891</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.3696</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.1196</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0435</v>
+        <v>0</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>1.261</v>
+        <v>1.589</v>
       </c>
       <c r="J41" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>0.2333</v>
       </c>
-      <c r="M41" s="8" t="n">
-        <v>0.1187</v>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>130 of 161</t>
-        </is>
-      </c>
+      <c r="M41" s="8" t="n"/>
+      <c r="N41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2517,11 +2517,11 @@
         <v>0.2167</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.1125</v>
+        <v>0.1111</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>131 of 161</t>
+          <t>134 of 163</t>
         </is>
       </c>
     </row>
@@ -2531,41 +2531,47 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Q. Mathews</t>
+          <t>K. Rocker</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.43</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.3696</v>
+        <v>0.3931</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.1196</v>
+        <v>0.0369</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0</v>
+        <v>0.0348</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.589</v>
+        <v>1.419</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.375</v>
+        <v>0.306</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.2167</v>
-      </c>
-      <c r="M43" s="8" t="n"/>
-      <c r="N43" s="2" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>136 of 163</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2573,45 +2579,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>K. Rocker</t>
+          <t>S. Cecconi</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>26</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.43</v>
+        <v>0.4643</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.3512</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.0369</v>
+        <v>0.1131</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0348</v>
+        <v>0.0682</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.419</v>
+        <v>1.596</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.306</v>
+        <v>0.367</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1833</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.1062</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>134 of 161</t>
+          <t>142 of 163</t>
         </is>
       </c>
     </row>
@@ -2655,11 +2661,11 @@
         <v>0.1833</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0988</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>138 of 161</t>
+          <t>138 of 163</t>
         </is>
       </c>
     </row>
@@ -2703,11 +2709,11 @@
         <v>0.1667</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0926</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>139 of 161</t>
+          <t>139 of 163</t>
         </is>
       </c>
     </row>
@@ -2717,45 +2723,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>S. Cecconi</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4656</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3688</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.0969</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.0602</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.596</v>
+        <v>1.622</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>2.16</v>
+        <v>1.373</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.367</v>
+        <v>0.236</v>
       </c>
       <c r="L47" s="8" t="n">
         <v>0.1667</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.075</v>
+        <v>0.0741</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>142 of 161</t>
+          <t>145 of 163</t>
         </is>
       </c>
     </row>
@@ -2765,45 +2771,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>G. Jump</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>17.3</v>
+        <v>25.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4572</v>
+        <v>0.4564</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.4094</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0361</v>
+        <v>0.0354</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.637</v>
+        <v>1.636</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.904</v>
+        <v>1.714</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.346</v>
+        <v>0.333</v>
       </c>
       <c r="L48" s="8" t="n">
         <v>0.15</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0688</v>
+        <v>0.0679</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>145 of 161</t>
+          <t>146 of 163</t>
         </is>
       </c>
     </row>
@@ -2847,11 +2853,11 @@
         <v>0.15</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.0813</v>
+        <v>0.0864</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>141 of 161</t>
+          <t>141 of 163</t>
         </is>
       </c>
     </row>
@@ -2895,11 +2901,11 @@
         <v>0.1333</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.075</v>
+        <v>0.0679</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>143 of 161</t>
+          <t>147 of 163</t>
         </is>
       </c>
     </row>
@@ -2909,45 +2915,45 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>R. Johnson</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>21.7</v>
+        <v>17.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.4181</v>
+        <v>0.4572</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.4257</v>
+        <v>0.3882</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>-0.0076</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0361</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.705</v>
+        <v>1.637</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>1.662</v>
+        <v>1.904</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.279</v>
+        <v>0.346</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.1</v>
+        <v>0.1333</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0617</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>150 of 161</t>
+          <t>149 of 163</t>
         </is>
       </c>
     </row>
@@ -2957,45 +2963,45 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>13.7</v>
+        <v>27</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.4598</v>
+        <v>0.42</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.375</v>
+        <v>0.4179</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.0848</v>
+        <v>0.0021</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0588</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1.715</v>
+        <v>1.695</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>1.171</v>
+        <v>1.593</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>0.158</v>
+        <v>0.27</v>
       </c>
       <c r="L52" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0.0437</v>
+        <v>0.0432</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>149 of 161</t>
+          <t>151 of 163</t>
         </is>
       </c>
     </row>
@@ -3039,11 +3045,11 @@
         <v>0.0833</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.037</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>151 of 161</t>
+          <t>153 of 163</t>
         </is>
       </c>
     </row>
@@ -3087,11 +3093,11 @@
         <v>0.0833</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>0.0312</v>
+        <v>0.0309</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>153 of 161</t>
+          <t>155 of 163</t>
         </is>
       </c>
     </row>
@@ -3135,11 +3141,11 @@
         <v>0.0667</v>
       </c>
       <c r="M55" s="8" t="n">
-        <v>0.025</v>
+        <v>0.0247</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>154 of 161</t>
+          <t>156 of 163</t>
         </is>
       </c>
     </row>
@@ -3183,11 +3189,11 @@
         <v>0.05</v>
       </c>
       <c r="M56" s="8" t="n">
-        <v>0.0187</v>
+        <v>0.0185</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>155 of 161</t>
+          <t>157 of 163</t>
         </is>
       </c>
     </row>
@@ -3273,11 +3279,11 @@
         <v>0.0333</v>
       </c>
       <c r="M58" s="8" t="n">
-        <v>0.0125</v>
+        <v>0.0123</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>156 of 161</t>
+          <t>158 of 163</t>
         </is>
       </c>
     </row>
@@ -3321,11 +3327,11 @@
         <v>0.0167</v>
       </c>
       <c r="M59" s="8" t="n">
-        <v>0.0125</v>
+        <v>0.0123</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>157 of 161</t>
+          <t>159 of 163</t>
         </is>
       </c>
     </row>
@@ -3369,11 +3375,11 @@
         <v>0.0167</v>
       </c>
       <c r="M60" s="8" t="n">
-        <v>0.0063</v>
+        <v>0.0062</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>159 of 161</t>
+          <t>161 of 163</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3427,7 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>160 of 161</t>
+          <t>162 of 163</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3475,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>161 of 161</t>
+          <t>163 of 163</t>
         </is>
       </c>
     </row>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -575,41 +575,47 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>A. Houser</t>
+          <t>T. Yesavage</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>18.7</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.5143</v>
+        <v>0.5149</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3143</v>
+        <v>0.3498</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.2</v>
+        <v>0.165</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0</v>
+        <v>0.0429</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0.9</v>
+        <v>1.198</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>0.5</v>
+        <v>1.071</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.182</v>
+        <v>0.263</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="8" t="n"/>
-      <c r="N2" s="2" t="n"/>
+        <v>0.9107</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>0.6832</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>37 of 162</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -617,45 +623,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>T. Yesavage</t>
+          <t>J. Lopez</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>18.7</v>
+        <v>32.7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.5149</v>
+        <v>0.4971</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3498</v>
+        <v>0.3652</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.165</v>
+        <v>0.1319</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0429</v>
+        <v>0.0317</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.198</v>
+        <v>1.163</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.071</v>
+        <v>1.102</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.263</v>
+        <v>0.278</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.8833</v>
+        <v>0.9107</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.6852</v>
+        <v>0.7329</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>36 of 163</t>
+          <t>28 of 162</t>
         </is>
       </c>
     </row>
@@ -696,14 +702,14 @@
         <v>0.32</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8833</v>
+        <v>0.8929</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.7222</v>
+        <v>0.7205</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29 of 163</t>
+          <t>29 of 162</t>
         </is>
       </c>
     </row>
@@ -713,45 +719,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>A. Kay</t>
+          <t>T. Bibee</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28</v>
+        <v>37.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4689</v>
+        <v>0.4885</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3397</v>
+        <v>0.3363</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1292</v>
+        <v>0.1522</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0265</v>
+        <v>0.0342</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.194</v>
+        <v>1.237</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.25</v>
+        <v>1.152</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.317</v>
+        <v>0.284</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.875</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.6914</v>
+        <v>0.6211</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35 of 163</t>
+          <t>45 of 162</t>
         </is>
       </c>
     </row>
@@ -761,45 +767,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N. Schultz</t>
+          <t>A. Kay</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7.3</v>
+        <v>28</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4767</v>
+        <v>0.4689</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3488</v>
+        <v>0.3397</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1279</v>
+        <v>0.1292</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0265</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.166</v>
+        <v>1.194</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>2.455</v>
+        <v>1.25</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.5</v>
+        <v>0.317</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.85</v>
+        <v>0.875</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.7037</v>
+        <v>0.6894</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32 of 163</t>
+          <t>36 of 162</t>
         </is>
       </c>
     </row>
@@ -809,45 +815,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>T. Phillips</t>
+          <t>N. Schultz</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23.7</v>
+        <v>7.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4759</v>
+        <v>0.4767</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3229</v>
+        <v>0.3488</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1279</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0244</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.256</v>
+        <v>1.166</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.268</v>
+        <v>2.455</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.294</v>
+        <v>0.5</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.8</v>
+        <v>0.8571</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5802</v>
+        <v>0.7081</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50 of 163</t>
+          <t>31 of 162</t>
         </is>
       </c>
     </row>
@@ -857,45 +863,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>M. Liberatore</t>
+          <t>C. Rea</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>25.3</v>
+        <v>17</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4824</v>
+        <v>0.4713</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3607</v>
+        <v>0.3487</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1218</v>
+        <v>0.1226</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0283</v>
+        <v>0.0455</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.146</v>
+        <v>1.26</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.461</v>
+        <v>1</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.388</v>
+        <v>0.222</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.8</v>
+        <v>0.8214</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.6481</v>
+        <v>0.5776</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40 of 163</t>
+          <t>50 of 162</t>
         </is>
       </c>
     </row>
@@ -905,45 +911,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>C. Rea</t>
+          <t>H. Greene</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4749</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3487</v>
+        <v>0.3398</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1226</v>
+        <v>0.1351</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0455</v>
+        <v>0.0411</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.26</v>
+        <v>1.263</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1</v>
+        <v>1.327</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.222</v>
+        <v>0.308</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7833</v>
+        <v>0.7857</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51 of 163</t>
+          <t>53 of 162</t>
         </is>
       </c>
     </row>
@@ -953,45 +959,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>E. Lauer</t>
+          <t>J. Bennett</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>21.7</v>
+        <v>27</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4866</v>
+        <v>0.4597</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3548</v>
+        <v>0.3472</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1317</v>
+        <v>0.1125</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0444</v>
+        <v>0.0263</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.26</v>
+        <v>1.253</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.108</v>
+        <v>1.444</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.242</v>
+        <v>0.35</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.7667</v>
+        <v>0.75</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.5679</v>
+        <v>0.5839</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52 of 163</t>
+          <t>48 of 162</t>
         </is>
       </c>
     </row>
@@ -1001,45 +1007,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>J. Bennett</t>
+          <t>C. Bradford</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>27</v>
+        <v>15.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4597</v>
+        <v>0.4884</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3472</v>
+        <v>0.3116</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1125</v>
+        <v>0.1767</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.0161</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.253</v>
+        <v>1.279</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.444</v>
+        <v>1.435</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.35</v>
+        <v>0.362</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>0.75</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.5926</v>
+        <v>0.528</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48 of 163</t>
+          <t>58 of 162</t>
         </is>
       </c>
     </row>
@@ -1049,45 +1055,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>H. Greene</t>
+          <t>J. Assad</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>17.3</v>
+        <v>10</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4749</v>
+        <v>0.4678</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3398</v>
+        <v>0.3684</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1351</v>
+        <v>0.0994</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0244</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.263</v>
+        <v>1.327</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.327</v>
+        <v>1.4</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.308</v>
+        <v>0.333</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.7333</v>
+        <v>0.6786</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.5556</v>
+        <v>0.4534</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54 of 163</t>
+          <t>68 of 162</t>
         </is>
       </c>
     </row>
@@ -1097,45 +1103,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>C. Bradford</t>
+          <t>G. Rodriguez</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>15.3</v>
+        <v>24</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4884</v>
+        <v>0.5023</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3116</v>
+        <v>0.3607</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1767</v>
+        <v>0.1416</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.05</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.279</v>
+        <v>1.344</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.435</v>
+        <v>1.333</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.362</v>
+        <v>0.286</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.7167</v>
+        <v>0.6607</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.5185</v>
+        <v>0.4224</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60 of 163</t>
+          <t>76 of 162</t>
         </is>
       </c>
     </row>
@@ -1145,45 +1151,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>J. Assad</t>
+          <t>E. Sheehan</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4643</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3661</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.0982</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0833</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.327</v>
+        <v>1.345</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.4</v>
+        <v>1.615</v>
       </c>
       <c r="K14" s="7" t="n">
         <v>0.333</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6667</v>
+        <v>0.6429</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.4506</v>
+        <v>0.4161</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71 of 163</t>
+          <t>77 of 162</t>
         </is>
       </c>
     </row>
@@ -1193,45 +1199,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>E. Sheehan</t>
+          <t>N. Eovaldi</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>13</v>
+        <v>21.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4561</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3661</v>
+        <v>0.3596</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0982</v>
+        <v>0.0965</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0556</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.345</v>
+        <v>1.376</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.615</v>
+        <v>1.359</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.333</v>
+        <v>0.29</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.6333</v>
+        <v>0.5893</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.4198</v>
+        <v>0.3727</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>75 of 163</t>
+          <t>83 of 162</t>
         </is>
       </c>
     </row>
@@ -1241,45 +1247,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>G. Rodriguez</t>
+          <t>G. Hughes</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>28</v>
+        <v>23.3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4952</v>
+        <v>0.4641</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3642</v>
+        <v>0.3692</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.131</v>
+        <v>0.0949</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0496</v>
+        <v>0.0297</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.348</v>
+        <v>1.335</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.429</v>
+        <v>1.543</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.306</v>
+        <v>0.352</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.6167</v>
+        <v>0.5893</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.4136</v>
+        <v>0.4472</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76 of 163</t>
+          <t>69 of 162</t>
         </is>
       </c>
     </row>
@@ -1289,45 +1295,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>C. Quantrill</t>
+          <t>J. Junk</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>16.3</v>
+        <v>27.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4569</v>
+        <v>0.466</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.375</v>
+        <v>0.3513</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0819</v>
+        <v>0.1148</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0156</v>
+        <v>0.0263</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.106</v>
+        <v>1.388</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.918</v>
+        <v>1.482</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.22</v>
+        <v>0.345</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.6</v>
+        <v>0.5536</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.4383</v>
+        <v>0.3478</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73 of 163</t>
+          <t>88 of 162</t>
         </is>
       </c>
     </row>
@@ -1337,45 +1343,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>C. Povich</t>
+          <t>B. Singer</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.4486</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.381</v>
+        <v>0.3711</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0776</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.024</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.209</v>
+        <v>1.379</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.556</v>
+        <v>1.552</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.435</v>
+        <v>0.348</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5667</v>
+        <v>0.5536</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3827</v>
+        <v>0.3665</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>83 of 163</t>
+          <t>86 of 162</t>
         </is>
       </c>
     </row>
@@ -1385,45 +1391,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>P. Sandoval</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>29.7</v>
+        <v>32.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4527</v>
+        <v>0.447</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3783</v>
+        <v>0.3453</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.1017</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.0317</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.37</v>
+        <v>1.391</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.921</v>
+        <v>1.102</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.429</v>
+        <v>0.245</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.55</v>
+        <v>0.5357</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3704</v>
+        <v>0.3416</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>85 of 163</t>
+          <t>90 of 162</t>
         </is>
       </c>
     </row>
@@ -1433,45 +1439,45 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>N. Eovaldi</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>21.3</v>
+        <v>9</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4561</v>
+        <v>0.4558</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3596</v>
+        <v>0.381</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0965</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.0278</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1.376</v>
+        <v>1.209</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.359</v>
+        <v>1.556</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.29</v>
+        <v>0.435</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.55</v>
+        <v>0.5179</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.3642</v>
+        <v>0.3789</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87 of 163</t>
+          <t>82 of 162</t>
         </is>
       </c>
     </row>
@@ -1479,47 +1485,47 @@
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>K. Freeland</t>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>H. Wesneski</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>32.7</v>
+        <v>22.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.447</v>
+        <v>0.4322</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3453</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0.1017</v>
+        <v>0.3596</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>0.0726</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0317</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1.391</v>
+        <v>0.0215</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>1.275</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.102</v>
+        <v>1.324</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.245</v>
+        <v>0.318</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.5333</v>
+        <v>0.5</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.3457</v>
+        <v>0.3727</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>91 of 163</t>
+          <t>84 of 162</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1533,7 @@
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>D. Peterson</t>
         </is>
@@ -1544,13 +1550,13 @@
       <c r="F22" s="4" t="n">
         <v>0.3739</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="10" t="n">
         <v>0.0721</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>0.0171</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="11" t="n">
         <v>1.24</v>
       </c>
       <c r="J22" s="7" t="n">
@@ -1560,14 +1566,14 @@
         <v>0.305</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.5333</v>
+        <v>0.4821</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.3642</v>
+        <v>0.3665</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88 of 163</t>
+          <t>85 of 162</t>
         </is>
       </c>
     </row>
@@ -1577,45 +1583,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>S. Drohan</t>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>28.3</v>
+        <v>24</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4563</v>
+        <v>0.4455</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3853</v>
+        <v>0.3688</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0709</v>
+        <v>0.0767</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.027</v>
+        <v>0.0556</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.211</v>
+        <v>1.416</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.341</v>
+        <v>1.708</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.5167</v>
+        <v>0.4464</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.3519</v>
+        <v>0.2981</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90 of 163</t>
+          <t>94 of 162</t>
         </is>
       </c>
     </row>
@@ -1625,45 +1631,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>J. Perkins</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>24</v>
+        <v>27.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4455</v>
+        <v>0.4431</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.3791</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0767</v>
+        <v>0.064</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.0364</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.416</v>
+        <v>1.305</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.708</v>
+        <v>1.244</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.366</v>
+        <v>0.288</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4667</v>
+        <v>0.4107</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.3148</v>
+        <v>0.2919</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94 of 163</t>
+          <t>96 of 162</t>
         </is>
       </c>
     </row>
@@ -1673,45 +1679,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>D. Kremer</t>
+          <t>C. Prielipp</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>27.3</v>
+        <v>21</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4431</v>
+        <v>0.4827</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3791</v>
+        <v>0.3671</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.064</v>
+        <v>0.1156</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0364</v>
+        <v>0.046</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.305</v>
+        <v>1.436</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.244</v>
+        <v>1.429</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.288</v>
+        <v>0.306</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.4667</v>
+        <v>0.4107</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.2963</v>
+        <v>0.2547</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>98 of 163</t>
+          <t>104 of 162</t>
         </is>
       </c>
     </row>
@@ -1752,14 +1758,14 @@
         <v>0.236</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.45</v>
+        <v>0.3929</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.2654</v>
+        <v>0.2547</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>103 of 163</t>
+          <t>103 of 162</t>
         </is>
       </c>
     </row>
@@ -1800,14 +1806,14 @@
         <v>0.373</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.2284</v>
+        <v>0.2236</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>108 of 163</t>
+          <t>108 of 162</t>
         </is>
       </c>
     </row>
@@ -1817,45 +1823,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>S. Lugo</t>
+          <t>R. Stock</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>28.7</v>
+        <v>12.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4398</v>
+        <v>0.4779</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3843</v>
+        <v>0.3717</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0556</v>
+        <v>0.1062</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0167</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.341</v>
+        <v>1.461</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.256</v>
+        <v>1.865</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.294</v>
+        <v>0.368</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3571</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.2407</v>
+        <v>0.205</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>107 of 163</t>
+          <t>112 of 162</t>
         </is>
       </c>
     </row>
@@ -1865,47 +1871,41 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>R. Stock</t>
+          <t>K. Emanuel</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>12.3</v>
+        <v>5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4779</v>
+        <v>0.4839</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3717</v>
+        <v>0.3763</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.1062</v>
+        <v>0.1075</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0167</v>
+        <v>0</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.461</v>
+        <v>1.489</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.865</v>
+        <v>1.6</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.368</v>
+        <v>0.333</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.3833</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>0.2099</v>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>112 of 163</t>
-        </is>
-      </c>
+        <v>0.3393</v>
+      </c>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1913,45 +1913,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Z. Thornton</t>
+          <t>S. Lugo</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4197</v>
+        <v>0.4398</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3705</v>
+        <v>0.3843</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.0556</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.44</v>
+        <v>1.341</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.214</v>
+        <v>1.256</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.291</v>
+        <v>0.294</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.3667</v>
+        <v>0.3214</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.2037</v>
+        <v>0.2298</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>113 of 163</t>
+          <t>107 of 162</t>
         </is>
       </c>
     </row>
@@ -1961,45 +1961,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>E. Fedde</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>13.3</v>
+        <v>9</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4973</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.4</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0973</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0256</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.136</v>
+        <v>1.498</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.05</v>
+        <v>1.556</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.267</v>
+        <v>0.318</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.3167</v>
+        <v>0.3036</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.1667</v>
+        <v>0.1553</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>120 of 163</t>
+          <t>123 of 162</t>
         </is>
       </c>
     </row>
@@ -2009,45 +2009,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>L. Avila</t>
+          <t>P. Sandoval</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>13.3</v>
+        <v>24.7</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4466</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.3943</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0523</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0172</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.535</v>
+        <v>1.41</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.575</v>
+        <v>1.905</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.3</v>
+        <v>0.413</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.3167</v>
+        <v>0.2857</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.142</v>
+        <v>0.205</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>124 of 163</t>
+          <t>111 of 162</t>
         </is>
       </c>
     </row>
@@ -2057,45 +2057,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>G. Marquez</t>
+          <t>Z. Thornton</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.4197</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3889</v>
+        <v>0.3705</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0492</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.08</v>
+        <v>0.0288</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.414</v>
+        <v>1.44</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.875</v>
+        <v>1.214</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.4</v>
+        <v>0.291</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.3</v>
+        <v>0.2679</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1543</v>
+        <v>0.1863</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>121 of 163</t>
+          <t>117 of 162</t>
         </is>
       </c>
     </row>
@@ -2105,45 +2105,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>B. Tidwell</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>27.7</v>
+        <v>15</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4632</v>
+        <v>0.444</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3725</v>
+        <v>0.388</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.0907</v>
+        <v>0.056</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0367</v>
+        <v>0.0169</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.548</v>
+        <v>1.502</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.337</v>
+        <v>1.333</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.275</v>
+        <v>0.293</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.3</v>
+        <v>0.2679</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1358</v>
+        <v>0.1366</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>125 of 163</t>
+          <t>126 of 162</t>
         </is>
       </c>
     </row>
@@ -2153,45 +2153,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>R. Vasquez</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.4444</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3584</v>
+        <v>0.3981</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0463</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.1</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.563</v>
+        <v>1.136</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.585</v>
+        <v>1.05</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.1</v>
+        <v>0.267</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.2833</v>
+        <v>0.25</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.1173</v>
+        <v>0.1491</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>132 of 163</t>
+          <t>124 of 162</t>
         </is>
       </c>
     </row>
@@ -2201,45 +2201,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>W. Buehler</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>25.3</v>
+        <v>13.3</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.4371</v>
+        <v>0.443</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3943</v>
+        <v>0.3904</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.0428</v>
+        <v>0.0526</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0187</v>
+        <v>0.0167</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.462</v>
+        <v>1.535</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.382</v>
+        <v>1.575</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.284</v>
+        <v>0.3</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.2667</v>
+        <v>0.25</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.1358</v>
+        <v>0.118</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>126 of 163</t>
+          <t>128 of 162</t>
         </is>
       </c>
     </row>
@@ -2249,45 +2249,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>L. Roupp</t>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>25.3</v>
+        <v>13.7</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.459</v>
+        <v>0.4162</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3888</v>
+        <v>0.3584</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.0703</v>
+        <v>0.0578</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0286</v>
+        <v>0.0217</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>1.564</v>
+        <v>1.563</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.421</v>
+        <v>0.585</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.277</v>
+        <v>0.1</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.2667</v>
+        <v>0.2321</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.1111</v>
+        <v>0.1056</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>133 of 163</t>
+          <t>132 of 162</t>
         </is>
       </c>
     </row>
@@ -2297,45 +2297,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>A. Alvarez</t>
+          <t>G. Marquez</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>21.7</v>
+        <v>5.3</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4158</v>
+        <v>0.4333</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3746</v>
+        <v>0.3889</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0.0412</v>
+        <v>0.0444</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0118</v>
+        <v>0.08</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>1.411</v>
+        <v>1.414</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.015</v>
+        <v>1.875</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.206</v>
+        <v>0.4</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2143</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.1296</v>
+        <v>0.1304</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>127 of 163</t>
+          <t>127 of 162</t>
         </is>
       </c>
     </row>
@@ -2345,45 +2345,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>B. Sproat</t>
+          <t>L. Roupp</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>13.7</v>
+        <v>25.3</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.451</v>
+        <v>0.459</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3888</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0.0431</v>
+        <v>0.0703</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0286</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>1.578</v>
+        <v>1.564</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.756</v>
+        <v>1.421</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.325</v>
+        <v>0.277</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2143</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.1049</v>
+        <v>0.0994</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>135 of 163</t>
+          <t>134 of 162</t>
         </is>
       </c>
     </row>
@@ -2391,47 +2391,47 @@
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>R. Lopez</t>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>10</v>
+        <v>13.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.451</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3931</v>
-      </c>
-      <c r="G40" s="10" t="n">
-        <v>0.0405</v>
+        <v>0.4078</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>0.0431</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0435</v>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>1.261</v>
+        <v>0.0312</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>1.578</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.8</v>
+        <v>1.756</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.429</v>
+        <v>0.325</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.2333</v>
+        <v>0.1964</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.1235</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>130 of 163</t>
+          <t>135 of 162</t>
         </is>
       </c>
     </row>
@@ -2439,89 +2439,95 @@
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Q. Mathews</t>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>A. Alvarez</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>5</v>
+        <v>21.7</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4891</v>
+        <v>0.4158</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3696</v>
-      </c>
-      <c r="G41" s="10" t="n">
-        <v>0.1196</v>
+        <v>0.3746</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.0412</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>1.589</v>
+        <v>0.0118</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>1.411</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>1.8</v>
+        <v>1.015</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.375</v>
+        <v>0.206</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.2333</v>
-      </c>
-      <c r="M41" s="8" t="n"/>
-      <c r="N41" s="2" t="n"/>
+        <v>0.1786</v>
+      </c>
+      <c r="M41" s="8" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>129 of 162</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>A. Nola</t>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>R. Lopez</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4335</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.4074</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>0.037</v>
+        <v>0.3931</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0.0405</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0614</v>
-      </c>
-      <c r="I42" s="11" t="n">
-        <v>1.365</v>
+        <v>0.0435</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>1.261</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.481</v>
+        <v>1.8</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.2167</v>
+        <v>0.1607</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.1111</v>
+        <v>0.1056</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>134 of 163</t>
+          <t>131 of 162</t>
         </is>
       </c>
     </row>
@@ -2562,14 +2568,14 @@
         <v>0.306</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1429</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.1049</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>136 of 163</t>
+          <t>138 of 162</t>
         </is>
       </c>
     </row>
@@ -2610,14 +2616,14 @@
         <v>0.367</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.1833</v>
+        <v>0.1429</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0745</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>142 of 163</t>
+          <t>140 of 162</t>
         </is>
       </c>
     </row>
@@ -2627,45 +2633,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>M. Perez</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>25</v>
+        <v>19.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4269</v>
+        <v>0.4656</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3926</v>
+        <v>0.3688</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.0344</v>
+        <v>0.0969</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0104</v>
+        <v>0.0602</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.42</v>
+        <v>1.622</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>1</v>
+        <v>1.373</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.197</v>
+        <v>0.236</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.1833</v>
+        <v>0.125</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.0988</v>
+        <v>0.0621</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>138 of 163</t>
+          <t>145 of 162</t>
         </is>
       </c>
     </row>
@@ -2675,45 +2681,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>T. Sugano</t>
+          <t>C. Holmes</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>29.3</v>
+        <v>10.7</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4086</v>
+        <v>0.411</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.3777</v>
+        <v>0.3836</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.0309</v>
+        <v>0.0274</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0696</v>
+        <v>0.0256</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.321</v>
+        <v>1.499</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>1.057</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.233</v>
+        <v>0.194</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.1667</v>
+        <v>0.125</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.0926</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>139 of 163</t>
+          <t>139 of 162</t>
         </is>
       </c>
     </row>
@@ -2723,45 +2729,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>19.7</v>
+        <v>30.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4656</v>
+        <v>0.452</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.3838</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.0969</v>
+        <v>0.0682</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0602</v>
+        <v>0.0323</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.622</v>
+        <v>1.623</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.373</v>
+        <v>1.435</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.236</v>
+        <v>0.284</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.1667</v>
+        <v>0.1071</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0741</v>
+        <v>0.0559</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>145 of 163</t>
+          <t>146 of 162</t>
         </is>
       </c>
     </row>
@@ -2771,45 +2777,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>G. Jump</t>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>25.7</v>
+        <v>28</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4564</v>
+        <v>0.4084</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.4094</v>
+        <v>0.3898</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.047</v>
+        <v>0.0186</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0354</v>
+        <v>0.0696</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.636</v>
+        <v>1.359</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.714</v>
+        <v>1.179</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.333</v>
+        <v>0.247</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.15</v>
+        <v>0.1071</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0679</v>
+        <v>0.0559</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>146 of 163</t>
+          <t>147 of 162</t>
         </is>
       </c>
     </row>
@@ -2819,45 +2825,45 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>C. Holmes</t>
+          <t>M. Mikolas</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10.7</v>
+        <v>15</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.411</v>
+        <v>0.3827</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.3836</v>
+        <v>0.3704</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.0274</v>
+        <v>0.0123</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.499</v>
+        <v>1.59</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.867</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.194</v>
+        <v>0.351</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.15</v>
+        <v>0.0893</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.0864</v>
+        <v>0.0497</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>141 of 163</t>
+          <t>149 of 162</t>
         </is>
       </c>
     </row>
@@ -2867,45 +2873,45 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>M. Mikolas</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4572</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3882</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0361</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.59</v>
+        <v>1.637</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1.867</v>
+        <v>1.904</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.351</v>
+        <v>0.346</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>0.1333</v>
+        <v>0.0893</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.0679</v>
+        <v>0.0435</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>147 of 163</t>
+          <t>151 of 162</t>
         </is>
       </c>
     </row>
@@ -2915,45 +2921,45 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>C. Mlodzinski</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>17.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.4572</v>
+        <v>0.4148</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.3693</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0455</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.0361</v>
+        <v>0.0426</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.637</v>
+        <v>1.684</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>1.904</v>
+        <v>3</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.346</v>
+        <v>0.514</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.1333</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.0617</v>
+        <v>0.0311</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>149 of 163</t>
+          <t>153 of 162</t>
         </is>
       </c>
     </row>
@@ -2994,14 +3000,14 @@
         <v>0.27</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>0.1</v>
+        <v>0.0536</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0.0432</v>
+        <v>0.0248</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>151 of 163</t>
+          <t>154 of 162</t>
         </is>
       </c>
     </row>
@@ -3011,45 +3017,45 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>R. Blanco</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.4861</v>
+        <v>0.4091</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.3622</v>
+        <v>0.4182</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.1238</v>
+        <v>-0.0091</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.0779</v>
+        <v>0.0345</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>1.725</v>
+        <v>1.494</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>1.345</v>
+        <v>1.784</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.209</v>
+        <v>0.351</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>0.0833</v>
+        <v>0.0536</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>0.037</v>
+        <v>0.0186</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>153 of 163</t>
+          <t>157 of 162</t>
         </is>
       </c>
     </row>
@@ -3059,45 +3065,45 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>M. Keller</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>12.3</v>
+        <v>19.3</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4861</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.3622</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.1238</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0779</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>1.494</v>
+        <v>1.725</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>1.784</v>
+        <v>1.345</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>0.351</v>
+        <v>0.209</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>0.0833</v>
+        <v>0.0357</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>0.0309</v>
+        <v>0.0186</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>155 of 163</t>
+          <t>156 of 162</t>
         </is>
       </c>
     </row>
@@ -3138,14 +3144,14 @@
         <v>0.333</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0.0667</v>
+        <v>0.0357</v>
       </c>
       <c r="M55" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.0124</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>156 of 163</t>
+          <t>159 of 162</t>
         </is>
       </c>
     </row>
@@ -3186,14 +3192,14 @@
         <v>0.403</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>0.05</v>
+        <v>0.0179</v>
       </c>
       <c r="M56" s="8" t="n">
-        <v>0.0185</v>
+        <v>0.0062</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>157 of 163</t>
+          <t>160 of 162</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3240,7 @@
         <v>0.312</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0.05</v>
+        <v>0.0179</v>
       </c>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="2" t="n"/>
@@ -3245,305 +3251,113 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Z. Littell</t>
+          <t>J. Springs</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.4294</v>
+        <v>0.401</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.3824</v>
+        <v>0.4213</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>0.0471</v>
+        <v>-0.0203</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>0.04</v>
+        <v>0.0408</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>1.792</v>
+        <v>1.892</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>1.781</v>
+        <v>2.032</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="L58" s="8" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
       <c r="M58" s="8" t="n">
-        <v>0.0123</v>
+        <v>0</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>158 of 163</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>M. Barnett</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>0.3972</v>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>0.4299</v>
-      </c>
-      <c r="G59" s="13" t="n">
-        <v>-0.0327</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>0.0984</v>
-      </c>
-      <c r="I59" s="14" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="J59" s="7" t="n">
-        <v>1.575</v>
-      </c>
-      <c r="K59" s="7" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="L59" s="8" t="n">
-        <v>0.0167</v>
-      </c>
-      <c r="M59" s="8" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>159 of 163</t>
+          <t>161 of 162</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>C. Mlodzinski</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>0.0333</v>
-      </c>
-      <c r="I60" s="14" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="J60" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" s="7" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="L60" s="8" t="n">
-        <v>0.0167</v>
-      </c>
-      <c r="M60" s="8" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>161 of 163</t>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>S. Arrighetti</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>0.4144</v>
-      </c>
-      <c r="F61" s="4" t="n">
-        <v>0.4685</v>
-      </c>
-      <c r="G61" s="13" t="n">
-        <v>-0.0541</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="14" t="n">
-        <v>1.778</v>
-      </c>
-      <c r="J61" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K61" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>162 of 163</t>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t>J. Springs</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>0.4213</v>
-      </c>
-      <c r="G62" s="13" t="n">
-        <v>-0.0203</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="I62" s="14" t="n">
-        <v>1.892</v>
-      </c>
-      <c r="J62" s="7" t="n">
-        <v>2.032</v>
-      </c>
-      <c r="K62" s="7" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="L62" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>163 of 163</t>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -575,45 +575,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>T. Yesavage</t>
+          <t>J. Lopez</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>18.7</v>
+        <v>28.3</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.5149</v>
+        <v>0.4933</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3498</v>
+        <v>0.3632</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.165</v>
+        <v>0.13</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.0429</v>
+        <v>0.037</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1.198</v>
+        <v>1.183</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1.071</v>
+        <v>1.129</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.263</v>
+        <v>0.29</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9107</v>
+        <v>0.9298</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.6832</v>
+        <v>0.7329</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>37 of 162</t>
+          <t>28 of 162</t>
         </is>
       </c>
     </row>
@@ -623,45 +623,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>J. Lopez</t>
+          <t>A. Kay</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32.7</v>
+        <v>28</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.4971</v>
+        <v>0.4689</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3652</v>
+        <v>0.3397</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1319</v>
+        <v>0.1292</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0317</v>
+        <v>0.0265</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.163</v>
+        <v>1.194</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.102</v>
+        <v>1.25</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.278</v>
+        <v>0.317</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.9107</v>
+        <v>0.9123</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.7329</v>
+        <v>0.7019</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>28 of 162</t>
+          <t>35 of 162</t>
         </is>
       </c>
     </row>
@@ -671,45 +671,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>R. Gasser</t>
+          <t>N. Schultz</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>27</v>
+        <v>7.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.4763</v>
+        <v>0.4767</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.346</v>
+        <v>0.3488</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1303</v>
+        <v>0.1279</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.0244</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.087</v>
+        <v>1.166</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1.185</v>
+        <v>2.455</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8929</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>0.7205</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29 of 162</t>
+          <t>30 of 162</t>
         </is>
       </c>
     </row>
@@ -750,14 +750,14 @@
         <v>0.284</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.875</v>
+        <v>0.8772</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.6211</v>
+        <v>0.6273</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45 of 162</t>
+          <t>44 of 162</t>
         </is>
       </c>
     </row>
@@ -767,45 +767,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>A. Kay</t>
+          <t>R. Gasser</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4689</v>
+        <v>0.4718</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3397</v>
+        <v>0.3442</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1292</v>
+        <v>0.1276</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0265</v>
+        <v>0.022</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.194</v>
+        <v>1.129</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.25</v>
+        <v>1.318</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.317</v>
+        <v>0.344</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.875</v>
+        <v>0.8772</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.6894</v>
+        <v>0.7143</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36 of 162</t>
+          <t>32 of 162</t>
         </is>
       </c>
     </row>
@@ -815,45 +815,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>N. Schultz</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7.3</v>
+        <v>23.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4767</v>
+        <v>0.4759</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3488</v>
+        <v>0.3229</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1279</v>
+        <v>0.153</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.051</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.166</v>
+        <v>1.256</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>2.455</v>
+        <v>1.268</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.5</v>
+        <v>0.294</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.8571</v>
+        <v>0.8246</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.7081</v>
+        <v>0.5839</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31 of 162</t>
+          <t>50 of 162</t>
         </is>
       </c>
     </row>
@@ -894,14 +894,14 @@
         <v>0.222</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.8214</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>0.5776</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50 of 162</t>
+          <t>51 of 162</t>
         </is>
       </c>
     </row>
@@ -911,45 +911,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>H. Greene</t>
+          <t>J. Bennett</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>17.3</v>
+        <v>27</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4749</v>
+        <v>0.4597</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3398</v>
+        <v>0.3472</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1351</v>
+        <v>0.1125</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0263</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.263</v>
+        <v>1.253</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.327</v>
+        <v>1.444</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.308</v>
+        <v>0.35</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7857</v>
+        <v>0.7719</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53 of 162</t>
+          <t>47 of 162</t>
         </is>
       </c>
     </row>
@@ -959,45 +959,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>J. Bennett</t>
+          <t>C. Bradford</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>27</v>
+        <v>15.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4597</v>
+        <v>0.4884</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3472</v>
+        <v>0.3116</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1125</v>
+        <v>0.1767</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.0161</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.253</v>
+        <v>1.279</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.444</v>
+        <v>1.435</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.35</v>
+        <v>0.362</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.75</v>
+        <v>0.7544</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.5839</v>
+        <v>0.5404</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48 of 162</t>
+          <t>58 of 162</t>
         </is>
       </c>
     </row>
@@ -1007,45 +1007,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>C. Bradford</t>
+          <t>N. Eovaldi</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>15.3</v>
+        <v>17.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4884</v>
+        <v>0.4601</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3116</v>
+        <v>0.3536</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1767</v>
+        <v>0.1065</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.0282</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.279</v>
+        <v>1.178</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.435</v>
+        <v>1.212</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.362</v>
+        <v>0.3</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.75</v>
+        <v>0.7368</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.528</v>
+        <v>0.5776</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58 of 162</t>
+          <t>52 of 162</t>
         </is>
       </c>
     </row>
@@ -1086,14 +1086,14 @@
         <v>0.333</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6786</v>
+        <v>0.6842</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.4534</v>
+        <v>0.4596</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68 of 162</t>
+          <t>66 of 162</t>
         </is>
       </c>
     </row>
@@ -1134,14 +1134,14 @@
         <v>0.286</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6607</v>
+        <v>0.6491</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.4224</v>
+        <v>0.4286</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76 of 162</t>
+          <t>74 of 162</t>
         </is>
       </c>
     </row>
@@ -1182,14 +1182,14 @@
         <v>0.333</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6429</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.4161</v>
+        <v>0.4224</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77 of 162</t>
+          <t>75 of 162</t>
         </is>
       </c>
     </row>
@@ -1199,45 +1199,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>N. Eovaldi</t>
+          <t>G. Hughes</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4561</v>
+        <v>0.4641</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3596</v>
+        <v>0.3692</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0965</v>
+        <v>0.0949</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.0297</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.376</v>
+        <v>1.335</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.359</v>
+        <v>1.543</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.29</v>
+        <v>0.352</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.5893</v>
+        <v>0.614</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.3727</v>
+        <v>0.4472</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>83 of 162</t>
+          <t>68 of 162</t>
         </is>
       </c>
     </row>
@@ -1247,38 +1247,38 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>G. Hughes</t>
+          <t>T. Yesavage</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>23.3</v>
+        <v>12.7</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4641</v>
+        <v>0.4717</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3692</v>
+        <v>0.3821</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0949</v>
+        <v>0.0896</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.0417</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.335</v>
+        <v>1.307</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.543</v>
+        <v>1.026</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.352</v>
+        <v>0.214</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5893</v>
+        <v>0.5789</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>0.4472</v>
@@ -1295,45 +1295,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>J. Junk</t>
+          <t>G. Klassen</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>27.7</v>
+        <v>17</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.466</v>
+        <v>0.4575</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3513</v>
+        <v>0.3765</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1148</v>
+        <v>0.081</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.0147</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.388</v>
+        <v>1.376</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.482</v>
+        <v>1.059</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.345</v>
+        <v>0.205</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5536</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3478</v>
+        <v>0.3665</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88 of 162</t>
+          <t>81 of 162</t>
         </is>
       </c>
     </row>
@@ -1343,41 +1343,41 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>B. Singer</t>
+          <t>Z. Thornton</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4486</v>
+        <v>0.4468</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3711</v>
+        <v>0.357</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0776</v>
+        <v>0.0898</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.024</v>
+        <v>0.0397</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.379</v>
+        <v>1.386</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.552</v>
+        <v>1.242</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.348</v>
+        <v>0.297</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5536</v>
+        <v>0.5263</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3665</v>
+        <v>0.3416</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1391,45 +1391,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>K. Freeland</t>
+          <t>B. Singer</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>32.7</v>
+        <v>29</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.447</v>
+        <v>0.4486</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3453</v>
+        <v>0.3711</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.1017</v>
+        <v>0.0776</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.0317</v>
+        <v>0.024</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.391</v>
+        <v>1.379</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.102</v>
+        <v>1.552</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.245</v>
+        <v>0.348</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.5357</v>
+        <v>0.5263</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3416</v>
+        <v>0.3602</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>90 of 162</t>
+          <t>82 of 162</t>
         </is>
       </c>
     </row>
@@ -1439,45 +1439,45 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>C. Povich</t>
+          <t>J. Junk</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9</v>
+        <v>27.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.466</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.381</v>
+        <v>0.3513</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.1148</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.0263</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1.209</v>
+        <v>1.388</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.556</v>
+        <v>1.482</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.435</v>
+        <v>0.345</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.5179</v>
+        <v>0.5088</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.3789</v>
+        <v>0.3354</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82 of 162</t>
+          <t>88 of 162</t>
         </is>
       </c>
     </row>
@@ -1485,47 +1485,47 @@
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>H. Wesneski</t>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>22.7</v>
+        <v>32.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4322</v>
+        <v>0.447</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3596</v>
-      </c>
-      <c r="G21" s="10" t="n">
-        <v>0.0726</v>
+        <v>0.3453</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.1017</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>1.275</v>
+        <v>0.0317</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1.391</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.324</v>
+        <v>1.102</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.318</v>
+        <v>0.245</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.5</v>
+        <v>0.4912</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.3727</v>
+        <v>0.3292</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>84 of 162</t>
+          <t>90 of 162</t>
         </is>
       </c>
     </row>
@@ -1535,45 +1535,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>D. Peterson</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>28.7</v>
+        <v>9</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4459</v>
+        <v>0.4558</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3739</v>
+        <v>0.381</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.0721</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0171</v>
+        <v>0.0278</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.24</v>
+        <v>1.209</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.256</v>
+        <v>1.556</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.305</v>
+        <v>0.435</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4821</v>
+        <v>0.4912</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.3665</v>
+        <v>0.3602</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>85 of 162</t>
+          <t>83 of 162</t>
         </is>
       </c>
     </row>
@@ -1583,45 +1583,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>J. Perkins</t>
+          <t>H. Greene</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>24</v>
+        <v>11.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4455</v>
+        <v>0.4386</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.3567</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0767</v>
+        <v>0.0819</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.0192</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.416</v>
+        <v>1.404</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.708</v>
+        <v>1.676</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.366</v>
+        <v>0.35</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4464</v>
+        <v>0.4737</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.2981</v>
+        <v>0.323</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94 of 162</t>
+          <t>91 of 162</t>
         </is>
       </c>
     </row>
@@ -1631,45 +1631,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>D. Kremer</t>
+          <t>H. Wesneski</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>27.3</v>
+        <v>22.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4431</v>
+        <v>0.4322</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3791</v>
+        <v>0.3596</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.064</v>
+        <v>0.0726</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0364</v>
+        <v>0.0215</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.305</v>
+        <v>1.275</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.244</v>
+        <v>1.324</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.288</v>
+        <v>0.318</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4107</v>
+        <v>0.4737</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.2919</v>
+        <v>0.3416</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>96 of 162</t>
+          <t>87 of 162</t>
         </is>
       </c>
     </row>
@@ -1679,45 +1679,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>C. Prielipp</t>
+          <t>D. Peterson</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>21</v>
+        <v>28.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4827</v>
+        <v>0.4459</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3671</v>
+        <v>0.3739</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.1156</v>
+        <v>0.0721</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.046</v>
+        <v>0.0171</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.436</v>
+        <v>1.24</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.429</v>
+        <v>1.256</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.306</v>
+        <v>0.305</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.4107</v>
+        <v>0.4561</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.2547</v>
+        <v>0.3354</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>104 of 162</t>
+          <t>89 of 162</t>
         </is>
       </c>
     </row>
@@ -1727,45 +1727,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>H. Dobbins</t>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>22.3</v>
+        <v>24</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.454</v>
+        <v>0.4455</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3955</v>
+        <v>0.3688</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0585</v>
+        <v>0.0767</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.0556</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.365</v>
+        <v>1.416</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.164</v>
+        <v>1.708</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.236</v>
+        <v>0.366</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.3929</v>
+        <v>0.4035</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.2547</v>
+        <v>0.2857</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>103 of 162</t>
+          <t>95 of 162</t>
         </is>
       </c>
     </row>
@@ -1775,45 +1775,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Z. Matthews</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>24</v>
+        <v>27.3</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4633</v>
+        <v>0.4431</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3807</v>
+        <v>0.3791</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0377</v>
+        <v>0.0364</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.451</v>
+        <v>1.305</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.708</v>
+        <v>1.244</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.373</v>
+        <v>0.288</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.375</v>
+        <v>0.4035</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.2236</v>
+        <v>0.2733</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>108 of 162</t>
+          <t>99 of 162</t>
         </is>
       </c>
     </row>
@@ -1823,45 +1823,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>R. Stock</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12.3</v>
+        <v>26.7</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4779</v>
+        <v>0.4502</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3717</v>
+        <v>0.3891</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.1062</v>
+        <v>0.0611</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0367</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.461</v>
+        <v>1.366</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.865</v>
+        <v>1.312</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.368</v>
+        <v>0.292</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.3571</v>
+        <v>0.386</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.205</v>
+        <v>0.2547</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>112 of 162</t>
+          <t>102 of 162</t>
         </is>
       </c>
     </row>
@@ -1871,41 +1871,47 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>K. Emanuel</t>
+          <t>H. Dobbins</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>5</v>
+        <v>22.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4839</v>
+        <v>0.454</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3763</v>
+        <v>0.3955</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.1075</v>
+        <v>0.0585</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.489</v>
+        <v>1.365</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.6</v>
+        <v>1.164</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.333</v>
+        <v>0.236</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.3393</v>
-      </c>
-      <c r="M29" s="8" t="n"/>
-      <c r="N29" s="2" t="n"/>
+        <v>0.3684</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>105 of 162</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1913,45 +1919,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>S. Lugo</t>
+          <t>C. Prielipp</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>28.7</v>
+        <v>21</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4398</v>
+        <v>0.4827</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3843</v>
+        <v>0.3671</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0556</v>
+        <v>0.1156</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.341</v>
+        <v>1.436</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.256</v>
+        <v>1.429</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.294</v>
+        <v>0.306</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.3214</v>
+        <v>0.3684</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.2298</v>
+        <v>0.2422</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>107 of 162</t>
+          <t>106 of 162</t>
         </is>
       </c>
     </row>
@@ -1961,45 +1967,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Q. Mathews</t>
+          <t>R. Stock</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>9</v>
+        <v>12.3</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4973</v>
+        <v>0.4779</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3717</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.0973</v>
+        <v>0.1062</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.0167</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.498</v>
+        <v>1.461</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.556</v>
+        <v>1.865</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.318</v>
+        <v>0.368</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.3036</v>
+        <v>0.3509</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.1553</v>
+        <v>0.205</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>123 of 162</t>
+          <t>113 of 162</t>
         </is>
       </c>
     </row>
@@ -2009,47 +2015,41 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>P. Sandoval</t>
+          <t>K. Emanuel</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="2" t="n">
-        <v>24.7</v>
-      </c>
       <c r="E32" s="4" t="n">
-        <v>0.4466</v>
+        <v>0.4839</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3943</v>
+        <v>0.3763</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.0523</v>
+        <v>0.1075</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0172</v>
+        <v>0</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.41</v>
+        <v>1.489</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.905</v>
+        <v>1.6</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.413</v>
+        <v>0.333</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>111 of 162</t>
-        </is>
-      </c>
+        <v>0.3333</v>
+      </c>
+      <c r="M32" s="8" t="n"/>
+      <c r="N32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2057,45 +2057,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Z. Thornton</t>
+          <t>S. Lugo</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4197</v>
+        <v>0.4398</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3705</v>
+        <v>0.3843</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0492</v>
+        <v>0.0556</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0288</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.44</v>
+        <v>1.341</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.214</v>
+        <v>1.256</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.291</v>
+        <v>0.294</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.2679</v>
+        <v>0.2982</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1863</v>
+        <v>0.2112</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>117 of 162</t>
+          <t>112 of 162</t>
         </is>
       </c>
     </row>
@@ -2105,45 +2105,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>B. Tidwell</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.444</v>
+        <v>0.4973</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.388</v>
+        <v>0.4</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.056</v>
+        <v>0.0973</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0169</v>
+        <v>0.0256</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.502</v>
+        <v>1.498</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.333</v>
+        <v>1.556</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.293</v>
+        <v>0.318</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.2679</v>
+        <v>0.2982</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.1366</v>
+        <v>0.1615</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>126 of 162</t>
+          <t>123 of 162</t>
         </is>
       </c>
     </row>
@@ -2153,45 +2153,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>E. Fedde</t>
+          <t>P. Sandoval</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>13.3</v>
+        <v>24.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4466</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3943</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0523</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0172</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.136</v>
+        <v>1.41</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.05</v>
+        <v>1.905</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.267</v>
+        <v>0.413</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2632</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.1491</v>
+        <v>0.1801</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>124 of 162</t>
+          <t>118 of 162</t>
         </is>
       </c>
     </row>
@@ -2201,45 +2201,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>L. Avila</t>
+          <t>B. Tidwell</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.388</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.056</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0169</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.535</v>
+        <v>1.502</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.575</v>
+        <v>1.333</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.3</v>
+        <v>0.293</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2632</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.118</v>
+        <v>0.1429</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>128 of 162</t>
+          <t>126 of 162</t>
         </is>
       </c>
     </row>
@@ -2249,45 +2249,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>R. Vasquez</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.4444</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3584</v>
+        <v>0.3981</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0463</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.1</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>1.563</v>
+        <v>1.136</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>0.585</v>
+        <v>1.05</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.1</v>
+        <v>0.267</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.2321</v>
+        <v>0.2456</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.1056</v>
+        <v>0.1491</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>132 of 162</t>
+          <t>124 of 162</t>
         </is>
       </c>
     </row>
@@ -2297,45 +2297,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>G. Marquez</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5.3</v>
+        <v>13.3</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.443</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3889</v>
+        <v>0.3904</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0526</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.08</v>
+        <v>0.0167</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>1.414</v>
+        <v>1.535</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.875</v>
+        <v>1.575</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.2143</v>
+        <v>0.2456</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.1304</v>
+        <v>0.1118</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>127 of 162</t>
+          <t>130 of 162</t>
         </is>
       </c>
     </row>
@@ -2345,45 +2345,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>L. Roupp</t>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>25.3</v>
+        <v>13.7</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.459</v>
+        <v>0.4162</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3888</v>
+        <v>0.3584</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0.0703</v>
+        <v>0.0578</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0286</v>
+        <v>0.0217</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>1.564</v>
+        <v>1.563</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.421</v>
+        <v>0.585</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.277</v>
+        <v>0.1</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.2143</v>
+        <v>0.2281</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.0994</v>
+        <v>0.1056</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>134 of 162</t>
+          <t>132 of 162</t>
         </is>
       </c>
     </row>
@@ -2391,47 +2391,47 @@
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>B. Sproat</t>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>L. Roupp</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>13.7</v>
+        <v>25.3</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.451</v>
+        <v>0.459</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.4078</v>
-      </c>
-      <c r="G40" s="13" t="n">
-        <v>0.0431</v>
+        <v>0.3888</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>0.0703</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0312</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>1.578</v>
+        <v>0.0286</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>1.564</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.756</v>
+        <v>1.421</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.325</v>
+        <v>0.277</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.1964</v>
+        <v>0.2105</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0994</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>135 of 162</t>
+          <t>133 of 162</t>
         </is>
       </c>
     </row>
@@ -2472,14 +2472,14 @@
         <v>0.206</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.1786</v>
+        <v>0.193</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.1118</v>
+        <v>0.1304</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>129 of 162</t>
+          <t>127 of 162</t>
         </is>
       </c>
     </row>
@@ -2489,45 +2489,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>R. Lopez</t>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>10</v>
+        <v>13.7</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.451</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.4078</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.0405</v>
+        <v>0.0431</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0435</v>
+        <v>0.0312</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.261</v>
+        <v>1.578</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.8</v>
+        <v>1.756</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.429</v>
+        <v>0.325</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.1607</v>
+        <v>0.193</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.1056</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>131 of 162</t>
+          <t>135 of 162</t>
         </is>
       </c>
     </row>
@@ -2537,45 +2537,45 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>K. Rocker</t>
+          <t>R. Lopez</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.43</v>
+        <v>0.4335</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>0.3931</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.0369</v>
+        <v>0.0405</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.0348</v>
+        <v>0.0435</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.419</v>
+        <v>1.261</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.306</v>
+        <v>0.429</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.1429</v>
+        <v>0.1754</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1242</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>138 of 162</t>
+          <t>129 of 162</t>
         </is>
       </c>
     </row>
@@ -2585,45 +2585,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>S. Cecconi</t>
+          <t>K. Rocker</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>26</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.43</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3931</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.0369</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.0348</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.596</v>
+        <v>1.419</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>2.16</v>
+        <v>1.5</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.367</v>
+        <v>0.306</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.1429</v>
+        <v>0.1404</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.0745</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>140 of 162</t>
+          <t>136 of 162</t>
         </is>
       </c>
     </row>
@@ -2633,45 +2633,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>S. Cecconi</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>19.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4656</v>
+        <v>0.4643</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.3512</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.0969</v>
+        <v>0.1131</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0602</v>
+        <v>0.0682</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.622</v>
+        <v>1.596</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>1.373</v>
+        <v>2.16</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.236</v>
+        <v>0.367</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.125</v>
+        <v>0.1404</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.0621</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>145 of 162</t>
+          <t>138 of 162</t>
         </is>
       </c>
     </row>
@@ -2681,45 +2681,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>C. Holmes</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>10.7</v>
+        <v>19.7</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.411</v>
+        <v>0.4656</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.3836</v>
+        <v>0.3688</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.0274</v>
+        <v>0.0969</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.0602</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.499</v>
+        <v>1.622</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.373</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.194</v>
+        <v>0.236</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.125</v>
+        <v>0.1228</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0621</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>139 of 162</t>
+          <t>145 of 162</t>
         </is>
       </c>
     </row>
@@ -2729,45 +2729,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>C. Holmes</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>30.7</v>
+        <v>10.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.452</v>
+        <v>0.411</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.3838</v>
+        <v>0.3836</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.0682</v>
+        <v>0.0274</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0323</v>
+        <v>0.0256</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.623</v>
+        <v>1.499</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.435</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.284</v>
+        <v>0.194</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.1071</v>
+        <v>0.1228</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0559</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>146 of 162</t>
+          <t>139 of 162</t>
         </is>
       </c>
     </row>
@@ -2777,38 +2777,38 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>T. Sugano</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>28</v>
+        <v>30.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4084</v>
+        <v>0.452</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.3898</v>
+        <v>0.3838</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.0186</v>
+        <v>0.0682</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0696</v>
+        <v>0.0323</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.359</v>
+        <v>1.623</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.179</v>
+        <v>1.435</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.247</v>
+        <v>0.284</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.1071</v>
+        <v>0.1053</v>
       </c>
       <c r="M48" s="8" t="n">
         <v>0.0559</v>
@@ -2825,38 +2825,38 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>M. Mikolas</t>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4084</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3898</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.0186</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.59</v>
+        <v>1.359</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>1.867</v>
+        <v>1.179</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.351</v>
+        <v>0.247</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.0893</v>
+        <v>0.1053</v>
       </c>
       <c r="M49" s="8" t="n">
         <v>0.0497</v>
@@ -2873,38 +2873,38 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>M. Mikolas</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>17.3</v>
+        <v>15</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.4572</v>
+        <v>0.3827</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.3882</v>
+        <v>0.3704</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0123</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.0361</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.637</v>
+        <v>1.59</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1.904</v>
+        <v>1.867</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.346</v>
+        <v>0.351</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>0.0893</v>
+        <v>0.0877</v>
       </c>
       <c r="M50" s="8" t="n">
         <v>0.0435</v>
@@ -2921,45 +2921,45 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>C. Mlodzinski</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>21.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.4148</v>
+        <v>0.4323</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.3693</v>
+        <v>0.3932</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.0455</v>
+        <v>0.0391</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.0426</v>
+        <v>0.0377</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.684</v>
+        <v>1.659</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>3</v>
+        <v>2.062</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.514</v>
+        <v>0.366</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0877</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.0311</v>
+        <v>0.0373</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>153 of 162</t>
+          <t>152 of 162</t>
         </is>
       </c>
     </row>
@@ -2969,45 +2969,45 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>R. Johnson</t>
+          <t>C. Mlodzinski</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>27</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.42</v>
+        <v>0.4148</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.4179</v>
+        <v>0.3693</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.0021</v>
+        <v>0.0455</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.0588</v>
+        <v>0.0426</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1.695</v>
+        <v>1.684</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>1.593</v>
+        <v>3</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>0.27</v>
+        <v>0.514</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>0.0536</v>
+        <v>0.0702</v>
       </c>
       <c r="M52" s="8" t="n">
         <v>0.0248</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>154 of 162</t>
+          <t>155 of 162</t>
         </is>
       </c>
     </row>
@@ -3048,14 +3048,14 @@
         <v>0.351</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>0.0536</v>
+        <v>0.0526</v>
       </c>
       <c r="M53" s="8" t="n">
         <v>0.0186</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>157 of 162</t>
+          <t>156 of 162</t>
         </is>
       </c>
     </row>
@@ -3065,45 +3065,45 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>R. Blanco</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>19.3</v>
+        <v>22</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.4861</v>
+        <v>0.4209</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.3622</v>
+        <v>0.4107</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.1238</v>
+        <v>0.0102</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.0779</v>
+        <v>0.0606</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>1.725</v>
+        <v>1.717</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>1.345</v>
+        <v>1.727</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>0.209</v>
+        <v>0.302</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>0.0357</v>
+        <v>0.0526</v>
       </c>
       <c r="M54" s="8" t="n">
         <v>0.0186</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>156 of 162</t>
+          <t>157 of 162</t>
         </is>
       </c>
     </row>
@@ -3113,45 +3113,45 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>K. Drake</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>16.7</v>
+        <v>19.3</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4861</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.3622</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.1238</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0779</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>1.413</v>
+        <v>1.725</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>1.56</v>
+        <v>1.345</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.333</v>
+        <v>0.209</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0.0357</v>
+        <v>0.0351</v>
       </c>
       <c r="M55" s="8" t="n">
         <v>0.0124</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>159 of 162</t>
+          <t>158 of 162</t>
         </is>
       </c>
     </row>
@@ -3161,45 +3161,45 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>M. Lorenzen</t>
+          <t>K. Drake</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>18.7</v>
+        <v>16.7</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.4477</v>
+        <v>0.4167</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.3917</v>
+        <v>0.4263</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.056</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>0.0515</v>
+        <v>0.0411</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>1.778</v>
+        <v>1.413</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>2.411</v>
+        <v>1.56</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>0.403</v>
+        <v>0.333</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>0.0179</v>
+        <v>0.0351</v>
       </c>
       <c r="M56" s="8" t="n">
-        <v>0.0062</v>
+        <v>0.0124</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>160 of 162</t>
+          <t>159 of 162</t>
         </is>
       </c>
     </row>
@@ -3209,41 +3209,47 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>C. Bassitt</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>5.3</v>
+        <v>18.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.3855</v>
+        <v>0.4477</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.3976</v>
+        <v>0.3917</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>-0.012</v>
+        <v>0.056</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>1.589</v>
+        <v>1.778</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>1.5</v>
+        <v>2.411</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.312</v>
+        <v>0.403</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0.0179</v>
-      </c>
-      <c r="M57" s="8" t="n"/>
-      <c r="N57" s="2" t="n"/>
+        <v>0.0175</v>
+      </c>
+      <c r="M57" s="8" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>160 of 162</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3251,113 +3257,155 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
+          <t>C. Bassitt</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <v>1.589</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="L58" s="8" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="M58" s="8" t="n"/>
+      <c r="N58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
           <t>J. Springs</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D59" s="2" t="n">
         <v>10.3</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E59" s="4" t="n">
         <v>0.401</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F59" s="4" t="n">
         <v>0.4213</v>
       </c>
-      <c r="G58" s="13" t="n">
+      <c r="G59" s="13" t="n">
         <v>-0.0203</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>0.0408</v>
       </c>
-      <c r="I58" s="14" t="n">
+      <c r="I59" s="14" t="n">
         <v>1.892</v>
       </c>
-      <c r="J58" s="7" t="n">
+      <c r="J59" s="7" t="n">
         <v>2.032</v>
       </c>
-      <c r="K58" s="7" t="n">
+      <c r="K59" s="7" t="n">
         <v>0.333</v>
       </c>
-      <c r="L58" s="8" t="n">
+      <c r="L59" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M58" s="8" t="n">
+      <c r="M59" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>161 of 162</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -606,14 +606,14 @@
         <v>0.29</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.9298</v>
+        <v>0.931</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.7329</v>
+        <v>0.7284</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>28 of 162</t>
+          <t>30 of 163</t>
         </is>
       </c>
     </row>
@@ -654,14 +654,14 @@
         <v>0.317</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.9123</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.7019</v>
+        <v>0.6852</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>35 of 162</t>
+          <t>38 of 163</t>
         </is>
       </c>
     </row>
@@ -702,14 +702,14 @@
         <v>0.5</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8966</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.7205</v>
+        <v>0.7099</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30 of 162</t>
+          <t>32 of 163</t>
         </is>
       </c>
     </row>
@@ -719,45 +719,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>T. Bibee</t>
+          <t>R. Gasser</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>37.3</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4885</v>
+        <v>0.4718</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3363</v>
+        <v>0.3442</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1522</v>
+        <v>0.1276</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.0342</v>
+        <v>0.022</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.237</v>
+        <v>1.129</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.152</v>
+        <v>1.318</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.284</v>
+        <v>0.344</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8772</v>
+        <v>0.8793</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.6273</v>
+        <v>0.7037</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44 of 162</t>
+          <t>34 of 163</t>
         </is>
       </c>
     </row>
@@ -767,45 +767,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>R. Gasser</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>22</v>
+        <v>23.7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4718</v>
+        <v>0.4759</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3442</v>
+        <v>0.3229</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.1276</v>
+        <v>0.153</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.022</v>
+        <v>0.051</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.129</v>
+        <v>1.256</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.318</v>
+        <v>1.268</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.344</v>
+        <v>0.294</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.8772</v>
+        <v>0.8621</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.7143</v>
+        <v>0.5988</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32 of 162</t>
+          <t>48 of 163</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>T. Phillips</t>
+          <t>J. Junk</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -825,35 +825,35 @@
         <v>23.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4759</v>
+        <v>0.4629</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3229</v>
+        <v>0.3457</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1171</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0105</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.256</v>
+        <v>1.259</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.268</v>
+        <v>1.394</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.294</v>
+        <v>0.356</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.8246</v>
+        <v>0.8448</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5839</v>
+        <v>0.5926</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50 of 162</t>
+          <t>50 of 163</t>
         </is>
       </c>
     </row>
@@ -894,14 +894,14 @@
         <v>0.222</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8276</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.5776</v>
+        <v>0.5802</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51 of 162</t>
+          <t>53 of 163</t>
         </is>
       </c>
     </row>
@@ -942,14 +942,14 @@
         <v>0.35</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7719</v>
+        <v>0.7931</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.6049</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47 of 162</t>
+          <t>47 of 163</t>
         </is>
       </c>
     </row>
@@ -990,14 +990,14 @@
         <v>0.362</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.7544</v>
+        <v>0.7759</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.5404</v>
+        <v>0.5494</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58 of 162</t>
+          <t>59 of 163</t>
         </is>
       </c>
     </row>
@@ -1007,45 +1007,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N. Eovaldi</t>
+          <t>T. Bibee</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>17.3</v>
+        <v>31.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4601</v>
+        <v>0.4979</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3536</v>
+        <v>0.3305</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1065</v>
+        <v>0.1674</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.0282</v>
+        <v>0.041</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.178</v>
+        <v>1.281</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.212</v>
+        <v>1.149</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.3</v>
+        <v>0.274</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.7368</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.5776</v>
+        <v>0.5432</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52 of 162</t>
+          <t>60 of 163</t>
         </is>
       </c>
     </row>
@@ -1055,45 +1055,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>J. Assad</t>
+          <t>N. Eovaldi</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10</v>
+        <v>17.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4601</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3536</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.1065</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0282</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.327</v>
+        <v>1.178</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.4</v>
+        <v>1.212</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.6842</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.4596</v>
+        <v>0.5679</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66 of 162</t>
+          <t>55 of 163</t>
         </is>
       </c>
     </row>
@@ -1103,45 +1103,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>G. Rodriguez</t>
+          <t>J. Assad</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5023</v>
+        <v>0.4678</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3607</v>
+        <v>0.3684</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1416</v>
+        <v>0.0994</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0244</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.344</v>
+        <v>1.327</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6491</v>
+        <v>0.6552</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.4286</v>
+        <v>0.463</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74 of 162</t>
+          <t>67 of 163</t>
         </is>
       </c>
     </row>
@@ -1151,45 +1151,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>E. Sheehan</t>
+          <t>G. Hughes</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13</v>
+        <v>23.3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4641</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3661</v>
+        <v>0.3692</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0982</v>
+        <v>0.0949</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0833</v>
+        <v>0.0297</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.345</v>
+        <v>1.335</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.615</v>
+        <v>1.543</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.333</v>
+        <v>0.352</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6379</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.4224</v>
+        <v>0.4383</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75 of 162</t>
+          <t>72 of 163</t>
         </is>
       </c>
     </row>
@@ -1199,45 +1199,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>G. Hughes</t>
+          <t>T. Yesavage</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>23.3</v>
+        <v>12.7</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4641</v>
+        <v>0.4717</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3692</v>
+        <v>0.3821</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0949</v>
+        <v>0.0896</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.0417</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.335</v>
+        <v>1.307</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.543</v>
+        <v>1.026</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.352</v>
+        <v>0.214</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.614</v>
+        <v>0.6207</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.4472</v>
+        <v>0.4815</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68 of 162</t>
+          <t>65 of 163</t>
         </is>
       </c>
     </row>
@@ -1247,45 +1247,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>T. Yesavage</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12.7</v>
+        <v>30.3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4717</v>
+        <v>0.4531</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3821</v>
+        <v>0.346</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0896</v>
+        <v>0.1071</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0333</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.307</v>
+        <v>1.341</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.026</v>
+        <v>1.121</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.214</v>
+        <v>0.25</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.5789</v>
+        <v>0.6034</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.4472</v>
+        <v>0.4259</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69 of 162</t>
+          <t>74 of 163</t>
         </is>
       </c>
     </row>
@@ -1295,45 +1295,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>G. Klassen</t>
+          <t>G. Rodriguez</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4575</v>
+        <v>0.5023</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3765</v>
+        <v>0.3607</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.081</v>
+        <v>0.1416</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0147</v>
+        <v>0.05</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.376</v>
+        <v>1.344</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.059</v>
+        <v>1.333</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.205</v>
+        <v>0.286</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.3665</v>
+        <v>0.4198</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81 of 162</t>
+          <t>75 of 163</t>
         </is>
       </c>
     </row>
@@ -1343,45 +1343,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Z. Thornton</t>
+          <t>G. Klassen</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4468</v>
+        <v>0.4575</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.357</v>
+        <v>0.3765</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0898</v>
+        <v>0.081</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0397</v>
+        <v>0.0147</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.386</v>
+        <v>1.376</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.242</v>
+        <v>1.059</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.297</v>
+        <v>0.205</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5263</v>
+        <v>0.5172</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3416</v>
+        <v>0.3704</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>86 of 162</t>
+          <t>79 of 163</t>
         </is>
       </c>
     </row>
@@ -1422,14 +1422,14 @@
         <v>0.348</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.5263</v>
+        <v>0.5</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3602</v>
+        <v>0.3642</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>82 of 162</t>
+          <t>80 of 163</t>
         </is>
       </c>
     </row>
@@ -1439,45 +1439,45 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>J. Junk</t>
+          <t>Z. Thornton</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>6</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>27.7</v>
+        <v>33</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.466</v>
+        <v>0.4468</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3513</v>
+        <v>0.357</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.1148</v>
+        <v>0.0898</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.0397</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1.388</v>
+        <v>1.386</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.482</v>
+        <v>1.242</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.345</v>
+        <v>0.297</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.5088</v>
+        <v>0.4828</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.3354</v>
+        <v>0.3333</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88 of 162</t>
+          <t>88 of 163</t>
         </is>
       </c>
     </row>
@@ -1487,45 +1487,45 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>K. Freeland</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>32.7</v>
+        <v>9</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.447</v>
+        <v>0.4558</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3453</v>
+        <v>0.381</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.1017</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0317</v>
+        <v>0.0278</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1.391</v>
+        <v>1.209</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.102</v>
+        <v>1.556</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.245</v>
+        <v>0.435</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.4912</v>
+        <v>0.4828</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.3292</v>
+        <v>0.3704</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>90 of 162</t>
+          <t>78 of 163</t>
         </is>
       </c>
     </row>
@@ -1535,45 +1535,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>C. Povich</t>
+          <t>H. Greene</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.4386</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.381</v>
+        <v>0.3567</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0278</v>
+        <v>0.0192</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.209</v>
+        <v>1.404</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.556</v>
+        <v>1.676</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.435</v>
+        <v>0.35</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4912</v>
+        <v>0.4655</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.3602</v>
+        <v>0.321</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>83 of 162</t>
+          <t>90 of 163</t>
         </is>
       </c>
     </row>
@@ -1583,45 +1583,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>H. Greene</t>
+          <t>H. Wesneski</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>11.3</v>
+        <v>22.7</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4386</v>
+        <v>0.4322</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3567</v>
+        <v>0.3596</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0819</v>
+        <v>0.0726</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.0215</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.404</v>
+        <v>1.275</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.676</v>
+        <v>1.324</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.35</v>
+        <v>0.318</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4737</v>
+        <v>0.4655</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.323</v>
+        <v>0.358</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91 of 162</t>
+          <t>82 of 163</t>
         </is>
       </c>
     </row>
@@ -1631,45 +1631,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>H. Wesneski</t>
+          <t>D. Peterson</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>22.7</v>
+        <v>28.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4322</v>
+        <v>0.4459</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3596</v>
+        <v>0.3739</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0726</v>
+        <v>0.0721</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0215</v>
+        <v>0.0171</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.324</v>
+        <v>1.256</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.318</v>
+        <v>0.305</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4737</v>
+        <v>0.4483</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.3416</v>
+        <v>0.3519</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>87 of 162</t>
+          <t>83 of 163</t>
         </is>
       </c>
     </row>
@@ -1679,45 +1679,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>D. Peterson</t>
+          <t>C. Bassitt</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>28.7</v>
+        <v>11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4459</v>
+        <v>0.44</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3739</v>
+        <v>0.3714</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.0721</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0171</v>
+        <v>0.0227</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.24</v>
+        <v>1.324</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.256</v>
+        <v>1.545</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.305</v>
+        <v>0.4</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.4561</v>
+        <v>0.4138</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.3354</v>
+        <v>0.3148</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>89 of 162</t>
+          <t>91 of 163</t>
         </is>
       </c>
     </row>
@@ -1727,45 +1727,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>J. Perkins</t>
+          <t>D. Kremer</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24</v>
+        <v>27.3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4455</v>
+        <v>0.4431</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.3791</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0.0767</v>
+        <v>0.064</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.0364</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>1.416</v>
+        <v>1.305</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.708</v>
+        <v>1.244</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.366</v>
+        <v>0.288</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.4035</v>
+        <v>0.3966</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.2857</v>
+        <v>0.2778</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95 of 162</t>
+          <t>99 of 163</t>
         </is>
       </c>
     </row>
@@ -1775,45 +1775,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>D. Kremer</t>
+          <t>E. Sheehan</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>27.3</v>
+        <v>7.7</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4431</v>
+        <v>0.4643</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3791</v>
+        <v>0.3786</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.064</v>
+        <v>0.0857</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.0364</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.305</v>
+        <v>1.415</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.244</v>
+        <v>1.565</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.288</v>
+        <v>0.273</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.4035</v>
+        <v>0.3966</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.2733</v>
+        <v>0.284</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>99 of 162</t>
+          <t>97 of 163</t>
         </is>
       </c>
     </row>
@@ -1823,45 +1823,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Z. Matthews</t>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>26.7</v>
+        <v>24</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4502</v>
+        <v>0.4455</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3891</v>
+        <v>0.3688</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0611</v>
+        <v>0.0767</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0367</v>
+        <v>0.0556</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.366</v>
+        <v>1.416</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.312</v>
+        <v>1.708</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.292</v>
+        <v>0.366</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.386</v>
+        <v>0.3793</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.2547</v>
+        <v>0.2778</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>102 of 162</t>
+          <t>98 of 163</t>
         </is>
       </c>
     </row>
@@ -1871,45 +1871,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>H. Dobbins</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>22.3</v>
+        <v>26.7</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.454</v>
+        <v>0.4502</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3955</v>
+        <v>0.3891</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0585</v>
+        <v>0.0611</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.0367</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.365</v>
+        <v>1.366</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.164</v>
+        <v>1.312</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.236</v>
+        <v>0.292</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.3684</v>
+        <v>0.3793</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.2422</v>
+        <v>0.2654</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>105 of 162</t>
+          <t>102 of 163</t>
         </is>
       </c>
     </row>
@@ -1919,45 +1919,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>C. Prielipp</t>
+          <t>H. Dobbins</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>21</v>
+        <v>22.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4827</v>
+        <v>0.454</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3671</v>
+        <v>0.3955</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.1156</v>
+        <v>0.0585</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.046</v>
+        <v>0.0333</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.436</v>
+        <v>1.365</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.429</v>
+        <v>1.164</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.306</v>
+        <v>0.236</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.3684</v>
+        <v>0.3621</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.2422</v>
+        <v>0.2531</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>106 of 162</t>
+          <t>105 of 163</t>
         </is>
       </c>
     </row>
@@ -1971,41 +1971,41 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>12.3</v>
+        <v>16.7</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4779</v>
+        <v>0.482</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3717</v>
+        <v>0.377</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.1062</v>
+        <v>0.1049</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0128</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.461</v>
+        <v>1.421</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.865</v>
+        <v>1.68</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.368</v>
+        <v>0.34</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.3509</v>
+        <v>0.3621</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.205</v>
+        <v>0.2593</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>113 of 162</t>
+          <t>104 of 163</t>
         </is>
       </c>
     </row>
@@ -2015,41 +2015,47 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>K. Emanuel</t>
+          <t>C. Prielipp</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4839</v>
+        <v>0.4827</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3763</v>
+        <v>0.3671</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.1075</v>
+        <v>0.1156</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.489</v>
+        <v>1.436</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.6</v>
+        <v>1.429</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.333</v>
+        <v>0.306</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="M32" s="8" t="n"/>
-      <c r="N32" s="2" t="n"/>
+        <v>0.3448</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>110 of 163</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2057,45 +2063,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>S. Lugo</t>
+          <t>A. Smith-Shawver</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>28.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4398</v>
+        <v>0.4532</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3843</v>
+        <v>0.3741</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0556</v>
+        <v>0.0791</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.341</v>
+        <v>1.462</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.256</v>
+        <v>1.615</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.294</v>
+        <v>0.346</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.2982</v>
+        <v>0.3276</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.2112</v>
+        <v>0.1975</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>112 of 162</t>
+          <t>116 of 163</t>
         </is>
       </c>
     </row>
@@ -2105,47 +2111,41 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Q. Mathews</t>
+          <t>K. Emanuel</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4973</v>
+        <v>0.4839</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3763</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.0973</v>
+        <v>0.1075</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0256</v>
+        <v>0</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.498</v>
+        <v>1.489</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.556</v>
+        <v>1.6</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.318</v>
+        <v>0.333</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.2982</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>0.1615</v>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>123 of 162</t>
-        </is>
-      </c>
+        <v>0.3103</v>
+      </c>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2153,45 +2153,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>P. Sandoval</t>
+          <t>A. Alvarez</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>24.7</v>
+        <v>17.3</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4466</v>
+        <v>0.4208</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3943</v>
+        <v>0.3665</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.0523</v>
+        <v>0.0543</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0172</v>
+        <v>0.0154</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.41</v>
+        <v>1.313</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.905</v>
+        <v>0.75</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.413</v>
+        <v>0.146</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.2632</v>
+        <v>0.2931</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.1801</v>
+        <v>0.216</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>118 of 162</t>
+          <t>113 of 163</t>
         </is>
       </c>
     </row>
@@ -2201,45 +2201,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>B. Tidwell</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.444</v>
+        <v>0.4973</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.388</v>
+        <v>0.4</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.056</v>
+        <v>0.0973</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0169</v>
+        <v>0.0256</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.502</v>
+        <v>1.498</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.333</v>
+        <v>1.556</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.293</v>
+        <v>0.318</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.2632</v>
+        <v>0.2759</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.1429</v>
+        <v>0.1728</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>126 of 162</t>
+          <t>122 of 163</t>
         </is>
       </c>
     </row>
@@ -2249,45 +2249,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>E. Fedde</t>
+          <t>P. Sandoval</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>13.3</v>
+        <v>24.7</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4444</v>
+        <v>0.4466</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.3943</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0523</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0172</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>1.136</v>
+        <v>1.41</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.05</v>
+        <v>1.905</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.267</v>
+        <v>0.413</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.2456</v>
+        <v>0.2586</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.1491</v>
+        <v>0.1975</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>124 of 162</t>
+          <t>115 of 163</t>
         </is>
       </c>
     </row>
@@ -2297,45 +2297,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>L. Avila</t>
+          <t>B. Tidwell</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.3904</v>
+        <v>0.388</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.056</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0167</v>
+        <v>0.0169</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>1.535</v>
+        <v>1.502</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.575</v>
+        <v>1.333</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.3</v>
+        <v>0.293</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.2456</v>
+        <v>0.2586</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.1118</v>
+        <v>0.1605</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>130 of 162</t>
+          <t>126 of 163</t>
         </is>
       </c>
     </row>
@@ -2345,45 +2345,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>R. Vasquez</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.443</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3584</v>
+        <v>0.3904</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.0526</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.0167</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>1.563</v>
+        <v>1.535</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>0.585</v>
+        <v>1.575</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.2281</v>
+        <v>0.2414</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.1056</v>
+        <v>0.1296</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>132 of 162</t>
+          <t>128 of 163</t>
         </is>
       </c>
     </row>
@@ -2393,45 +2393,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>L. Roupp</t>
+          <t>S. Lugo</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>25.3</v>
+        <v>34.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.459</v>
+        <v>0.4307</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3888</v>
+        <v>0.3833</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0.0703</v>
+        <v>0.0474</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0286</v>
+        <v>0.0071</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>1.564</v>
+        <v>1.284</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.421</v>
+        <v>1.298</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.277</v>
+        <v>0.315</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.2105</v>
+        <v>0.2414</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.0994</v>
+        <v>0.1605</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>133 of 162</t>
+          <t>125 of 163</t>
         </is>
       </c>
     </row>
@@ -2439,47 +2439,47 @@
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>A. Alvarez</t>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>21.7</v>
+        <v>13.7</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4158</v>
+        <v>0.4162</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3746</v>
-      </c>
-      <c r="G41" s="13" t="n">
-        <v>0.0412</v>
+        <v>0.3584</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>0.0578</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>1.411</v>
+        <v>0.0217</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>1.563</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>1.015</v>
+        <v>0.585</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.206</v>
+        <v>0.1</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.193</v>
+        <v>0.2069</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.1304</v>
+        <v>0.1173</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>127 of 162</t>
+          <t>131 of 163</t>
         </is>
       </c>
     </row>
@@ -2489,45 +2489,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>B. Sproat</t>
+          <t>L. Roupp</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>13.7</v>
+        <v>25.3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.451</v>
+        <v>0.459</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3888</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.0431</v>
+        <v>0.0703</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0286</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.578</v>
+        <v>1.564</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.756</v>
+        <v>1.421</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.325</v>
+        <v>0.277</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.193</v>
+        <v>0.1897</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.1111</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>135 of 162</t>
+          <t>132 of 163</t>
         </is>
       </c>
     </row>
@@ -2568,14 +2568,14 @@
         <v>0.429</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.1754</v>
+        <v>0.1724</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.1242</v>
+        <v>0.1235</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>129 of 162</t>
+          <t>129 of 163</t>
         </is>
       </c>
     </row>
@@ -2585,45 +2585,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>K. Rocker</t>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>26</v>
+        <v>13.7</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.43</v>
+        <v>0.451</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.4078</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.0369</v>
+        <v>0.0431</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0348</v>
+        <v>0.0312</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.419</v>
+        <v>1.578</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.5</v>
+        <v>1.756</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.306</v>
+        <v>0.325</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.1404</v>
+        <v>0.1724</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.1049</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>136 of 162</t>
+          <t>133 of 163</t>
         </is>
       </c>
     </row>
@@ -2633,45 +2633,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>S. Cecconi</t>
+          <t>K. Rocker</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>31</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4297</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3896</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.0402</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.0365</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.596</v>
+        <v>1.41</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>2.16</v>
+        <v>1.484</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.367</v>
+        <v>0.303</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.1404</v>
+        <v>0.1552</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.1173</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>138 of 162</t>
+          <t>130 of 163</t>
         </is>
       </c>
     </row>
@@ -2681,45 +2681,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>S. Cecconi</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>19.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4656</v>
+        <v>0.4643</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.3512</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.0969</v>
+        <v>0.1131</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0602</v>
+        <v>0.0682</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.622</v>
+        <v>1.596</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>1.373</v>
+        <v>2.16</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.236</v>
+        <v>0.367</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.1228</v>
+        <v>0.1379</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.0621</v>
+        <v>0.0864</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>145 of 162</t>
+          <t>137 of 163</t>
         </is>
       </c>
     </row>
@@ -2729,45 +2729,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>C. Holmes</t>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>10.7</v>
+        <v>28</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.411</v>
+        <v>0.4084</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.3836</v>
+        <v>0.3898</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.0274</v>
+        <v>0.0186</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.0696</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.499</v>
+        <v>1.359</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.179</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.194</v>
+        <v>0.247</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.1228</v>
+        <v>0.1207</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0679</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>139 of 162</t>
+          <t>143 of 163</t>
         </is>
       </c>
     </row>
@@ -2777,45 +2777,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>30.7</v>
+        <v>19.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.452</v>
+        <v>0.4656</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.3838</v>
+        <v>0.3688</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.0682</v>
+        <v>0.0969</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0323</v>
+        <v>0.0602</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.623</v>
+        <v>1.622</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.435</v>
+        <v>1.373</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.284</v>
+        <v>0.236</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.1053</v>
+        <v>0.1207</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0559</v>
+        <v>0.0617</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>147 of 162</t>
+          <t>146 of 163</t>
         </is>
       </c>
     </row>
@@ -2825,45 +2825,45 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>T. Sugano</t>
+          <t>M. Mikolas</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.4084</v>
+        <v>0.3827</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.3898</v>
+        <v>0.3704</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.0186</v>
+        <v>0.0123</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.0696</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.359</v>
+        <v>1.59</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>1.179</v>
+        <v>1.867</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.247</v>
+        <v>0.351</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.1053</v>
+        <v>0.1034</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.0497</v>
+        <v>0.0617</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>149 of 162</t>
+          <t>145 of 163</t>
         </is>
       </c>
     </row>
@@ -2873,45 +2873,45 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>M. Mikolas</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>15</v>
+        <v>21.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4323</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3932</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.0391</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0377</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.59</v>
+        <v>1.659</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1.867</v>
+        <v>2.062</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.351</v>
+        <v>0.366</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>0.0877</v>
+        <v>0.1034</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.0432</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>151 of 162</t>
+          <t>151 of 163</t>
         </is>
       </c>
     </row>
@@ -2921,45 +2921,45 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>21.3</v>
+        <v>26</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.4323</v>
+        <v>0.4407</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.3932</v>
+        <v>0.3995</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.0391</v>
+        <v>0.0412</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.0377</v>
+        <v>0.0196</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.659</v>
+        <v>1.665</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>2.062</v>
+        <v>1.346</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.366</v>
+        <v>0.258</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.0877</v>
+        <v>0.0862</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.0373</v>
+        <v>0.037</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>152 of 162</t>
+          <t>152 of 163</t>
         </is>
       </c>
     </row>
@@ -2969,45 +2969,45 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>C. Mlodzinski</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.4148</v>
+        <v>0.4091</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.3693</v>
+        <v>0.4156</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.0455</v>
+        <v>-0.0065</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.0426</v>
+        <v>0.1111</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1.684</v>
+        <v>1.34</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>3</v>
+        <v>1.071</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>0.514</v>
+        <v>0.217</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>0.0702</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0.0248</v>
+        <v>0.0432</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>155 of 162</t>
+          <t>150 of 163</t>
         </is>
       </c>
     </row>
@@ -3017,45 +3017,45 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>M. Keller</t>
+          <t>C. Mlodzinski</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>12.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4148</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.3693</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>-0.0091</v>
+        <v>0.0455</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0426</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>1.494</v>
+        <v>1.684</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>1.784</v>
+        <v>3</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.351</v>
+        <v>0.514</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>0.0526</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0309</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>156 of 162</t>
+          <t>155 of 163</t>
         </is>
       </c>
     </row>
@@ -3065,45 +3065,45 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>R. Johnson</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>22</v>
+        <v>12.3</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.4209</v>
+        <v>0.4091</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.4107</v>
+        <v>0.4182</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.0102</v>
+        <v>-0.0091</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.0606</v>
+        <v>0.0345</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>1.717</v>
+        <v>1.494</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>1.727</v>
+        <v>1.784</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>0.302</v>
+        <v>0.351</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>0.0526</v>
+        <v>0.0517</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>0.0186</v>
+        <v>0.0309</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>157 of 162</t>
+          <t>154 of 163</t>
         </is>
       </c>
     </row>
@@ -3113,45 +3113,45 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>R. Blanco</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>19.3</v>
+        <v>22</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.4861</v>
+        <v>0.4209</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.3622</v>
+        <v>0.4107</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0.1238</v>
+        <v>0.0102</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>0.0779</v>
+        <v>0.0606</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>1.725</v>
+        <v>1.717</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>1.345</v>
+        <v>1.727</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.209</v>
+        <v>0.302</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0517</v>
       </c>
       <c r="M55" s="8" t="n">
-        <v>0.0124</v>
+        <v>0.0247</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>158 of 162</t>
+          <t>157 of 163</t>
         </is>
       </c>
     </row>
@@ -3161,45 +3161,45 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>K. Drake</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>16.7</v>
+        <v>18.7</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.4167</v>
+        <v>0.4477</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.4263</v>
+        <v>0.3917</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.056</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>0.0411</v>
+        <v>0.0515</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>1.413</v>
+        <v>1.778</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>1.56</v>
+        <v>2.411</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>0.333</v>
+        <v>0.403</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.0345</v>
       </c>
       <c r="M56" s="8" t="n">
-        <v>0.0124</v>
+        <v>0.0123</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>159 of 162</t>
+          <t>159 of 163</t>
         </is>
       </c>
     </row>
@@ -3209,45 +3209,45 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>M. Lorenzen</t>
+          <t>K. Drake</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>18.7</v>
+        <v>16.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.4477</v>
+        <v>0.4167</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.3917</v>
+        <v>0.4263</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.056</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>0.0515</v>
+        <v>0.0411</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>1.778</v>
+        <v>1.413</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>2.411</v>
+        <v>1.56</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.403</v>
+        <v>0.333</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0.0175</v>
+        <v>0.0345</v>
       </c>
       <c r="M57" s="8" t="n">
-        <v>0.0062</v>
+        <v>0.0247</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>160 of 162</t>
+          <t>156 of 163</t>
         </is>
       </c>
     </row>
@@ -3257,41 +3257,47 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>C. Bassitt</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>5.3</v>
+        <v>14.7</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.3855</v>
+        <v>0.4538</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.3976</v>
+        <v>0.3739</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>-0.012</v>
+        <v>0.0798</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>1.589</v>
+        <v>1.814</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>1.5</v>
+        <v>1.432</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>0.312</v>
+        <v>0.243</v>
       </c>
       <c r="L58" s="8" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="M58" s="8" t="n"/>
-      <c r="N58" s="2" t="n"/>
+        <v>0.0172</v>
+      </c>
+      <c r="M58" s="8" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>161 of 163</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -3299,113 +3305,161 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>J. Springs</t>
+          <t>C. Holmes</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>10.3</v>
+        <v>16</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.401</v>
+        <v>0.3911</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.4213</v>
+        <v>0.4089</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>-0.0203</v>
+        <v>-0.0178</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>0.0408</v>
+        <v>0.0167</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>1.892</v>
+        <v>1.536</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>2.032</v>
+        <v>1.125</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.333</v>
+        <v>0.245</v>
       </c>
       <c r="L59" s="8" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="M59" s="8" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>160 of 163</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>J. Springs</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="I60" s="14" t="n">
+        <v>2.027</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L60" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M59" s="8" t="n">
+      <c r="M60" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>161 of 162</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="15" t="inlineStr">
-        <is>
-          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>163 of 163</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>

--- a/output/cmd_free_agents.xlsx
+++ b/output/cmd_free_agents.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -575,45 +575,45 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>J. Lopez</t>
+          <t>A. Kay</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>28.3</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.4933</v>
+        <v>0.4716</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.3632</v>
+        <v>0.3405</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.13</v>
+        <v>0.1311</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.037</v>
+        <v>0.0219</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1.183</v>
+        <v>1.146</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>1.129</v>
+        <v>1.206</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>0.29</v>
+        <v>0.313</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.931</v>
+        <v>0.9423</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.7284</v>
+        <v>0.7438</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>30 of 163</t>
+          <t>30 of 161</t>
         </is>
       </c>
     </row>
@@ -623,45 +623,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>A. Kay</t>
+          <t>T. Phillips</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>28</v>
+        <v>19.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.4689</v>
+        <v>0.486</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3397</v>
+        <v>0.3147</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1292</v>
+        <v>0.1713</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0265</v>
+        <v>0.0506</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1.194</v>
+        <v>1.2</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>1.25</v>
+        <v>1.241</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.317</v>
+        <v>0.302</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9423</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.6852</v>
+        <v>0.6937</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>38 of 163</t>
+          <t>37 of 161</t>
         </is>
       </c>
     </row>
@@ -671,45 +671,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>N. Schultz</t>
+          <t>J. Junk</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7.3</v>
+        <v>23.7</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.4767</v>
+        <v>0.4629</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.3488</v>
+        <v>0.3457</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1279</v>
+        <v>0.1171</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0105</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1.166</v>
+        <v>1.259</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>2.455</v>
+        <v>1.394</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>0.5</v>
+        <v>0.356</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.8966</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.7099</v>
+        <v>0.6125</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32 of 163</t>
+          <t>46 of 161</t>
         </is>
       </c>
     </row>
@@ -719,45 +719,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>R. Gasser</t>
+          <t>C. Rea</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.4718</v>
+        <v>0.4713</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.3442</v>
+        <v>0.3487</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1276</v>
+        <v>0.1226</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.022</v>
+        <v>0.0455</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1.129</v>
+        <v>1.26</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.318</v>
+        <v>1</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.344</v>
+        <v>0.222</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.8793</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.7037</v>
+        <v>0.6</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34 of 163</t>
+          <t>48 of 161</t>
         </is>
       </c>
     </row>
@@ -767,45 +767,45 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>T. Phillips</t>
+          <t>J. Bennett</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>23.7</v>
+        <v>27</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4759</v>
+        <v>0.4597</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3229</v>
+        <v>0.3472</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.153</v>
+        <v>0.1125</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.051</v>
+        <v>0.0263</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1.256</v>
+        <v>1.253</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.268</v>
+        <v>1.444</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.294</v>
+        <v>0.35</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.8621</v>
+        <v>0.8462</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.5988</v>
+        <v>0.6125</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48 of 163</t>
+          <t>45 of 161</t>
         </is>
       </c>
     </row>
@@ -815,45 +815,45 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>J. Junk</t>
+          <t>G. Rodriguez</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23.7</v>
+        <v>31</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4629</v>
+        <v>0.5122</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3457</v>
+        <v>0.3452</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.1171</v>
+        <v>0.167</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0105</v>
+        <v>0.0397</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1.259</v>
+        <v>1.298</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>1.394</v>
+        <v>1.258</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.356</v>
+        <v>0.284</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.8448</v>
+        <v>0.7885</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.5926</v>
+        <v>0.5437</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50 of 163</t>
+          <t>58 of 161</t>
         </is>
       </c>
     </row>
@@ -863,45 +863,45 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>C. Rea</t>
+          <t>N. Eovaldi</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4713</v>
+        <v>0.4601</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3487</v>
+        <v>0.3536</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.1226</v>
+        <v>0.1065</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0455</v>
+        <v>0.0282</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1.26</v>
+        <v>1.178</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1</v>
+        <v>1.212</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.222</v>
+        <v>0.3</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.8276</v>
+        <v>0.7885</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.5802</v>
+        <v>0.5687</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53 of 163</t>
+          <t>55 of 161</t>
         </is>
       </c>
     </row>
@@ -911,45 +911,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>J. Bennett</t>
+          <t>J. Assad</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4597</v>
+        <v>0.4678</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3472</v>
+        <v>0.3684</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1125</v>
+        <v>0.0994</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.0244</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1.253</v>
+        <v>1.327</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.444</v>
+        <v>1.4</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.7931</v>
+        <v>0.7115</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.6049</v>
+        <v>0.4688</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47 of 163</t>
+          <t>67 of 161</t>
         </is>
       </c>
     </row>
@@ -959,45 +959,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>C. Bradford</t>
+          <t>G. Hughes</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>15.3</v>
+        <v>23.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4884</v>
+        <v>0.4641</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3116</v>
+        <v>0.3692</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1767</v>
+        <v>0.0949</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.0297</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1.279</v>
+        <v>1.335</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.435</v>
+        <v>1.543</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.362</v>
+        <v>0.352</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.7759</v>
+        <v>0.6923</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.5494</v>
+        <v>0.4375</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59 of 163</t>
+          <t>72 of 161</t>
         </is>
       </c>
     </row>
@@ -1007,45 +1007,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>T. Bibee</t>
+          <t>T. Yesavage</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>31.3</v>
+        <v>12.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4979</v>
+        <v>0.4717</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3305</v>
+        <v>0.3821</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1674</v>
+        <v>0.0896</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.041</v>
+        <v>0.0417</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1.281</v>
+        <v>1.307</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.149</v>
+        <v>1.026</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.274</v>
+        <v>0.214</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.6731</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.5432</v>
+        <v>0.4875</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60 of 163</t>
+          <t>64 of 161</t>
         </is>
       </c>
     </row>
@@ -1055,45 +1055,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>N. Eovaldi</t>
+          <t>K. Freeland</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>17.3</v>
+        <v>30.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4601</v>
+        <v>0.4531</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3536</v>
+        <v>0.346</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1065</v>
+        <v>0.1071</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0282</v>
+        <v>0.0333</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1.178</v>
+        <v>1.341</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.212</v>
+        <v>1.121</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.6538</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.5679</v>
+        <v>0.425</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55 of 163</t>
+          <t>75 of 161</t>
         </is>
       </c>
     </row>
@@ -1103,45 +1103,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>J. Assad</t>
+          <t>D. Peterson</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4678</v>
+        <v>0.4517</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3684</v>
+        <v>0.3693</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0994</v>
+        <v>0.0824</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0244</v>
+        <v>0.0215</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1.327</v>
+        <v>1.275</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1.4</v>
+        <v>1.455</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.333</v>
+        <v>0.349</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0.6552</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.463</v>
+        <v>0.4313</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67 of 163</t>
+          <t>74 of 161</t>
         </is>
       </c>
     </row>
@@ -1151,45 +1151,45 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>G. Hughes</t>
+          <t>B. Singer</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>23.3</v>
+        <v>35</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4641</v>
+        <v>0.4504</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3692</v>
+        <v>0.3687</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0949</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.027</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1.335</v>
+        <v>1.376</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.543</v>
+        <v>1.457</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.352</v>
+        <v>0.327</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0.6379</v>
+        <v>0.5577</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.4383</v>
+        <v>0.3563</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72 of 163</t>
+          <t>79 of 161</t>
         </is>
       </c>
     </row>
@@ -1199,45 +1199,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>T. Yesavage</t>
+          <t>H. Greene</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12.7</v>
+        <v>11.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4717</v>
+        <v>0.4386</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3821</v>
+        <v>0.3567</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0896</v>
+        <v>0.0819</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0192</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1.307</v>
+        <v>1.404</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1.026</v>
+        <v>1.676</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.214</v>
+        <v>0.35</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.6207</v>
+        <v>0.5385</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.4815</v>
+        <v>0.3125</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>65 of 163</t>
+          <t>89 of 161</t>
         </is>
       </c>
     </row>
@@ -1247,45 +1247,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>K. Freeland</t>
+          <t>G. Klassen</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>30.3</v>
+        <v>17</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4531</v>
+        <v>0.4575</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.346</v>
+        <v>0.3765</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1071</v>
+        <v>0.081</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.0147</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1.341</v>
+        <v>1.376</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>1.121</v>
+        <v>1.059</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.25</v>
+        <v>0.205</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.6034</v>
+        <v>0.5385</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.4259</v>
+        <v>0.35</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74 of 163</t>
+          <t>81 of 161</t>
         </is>
       </c>
     </row>
@@ -1295,45 +1295,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>G. Rodriguez</t>
+          <t>Z. Thornton</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5023</v>
+        <v>0.4461</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3607</v>
+        <v>0.3584</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1416</v>
+        <v>0.0877</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0472</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1.344</v>
+        <v>1.404</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>1.333</v>
+        <v>1.37</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.286</v>
+        <v>0.324</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5192</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.4198</v>
+        <v>0.3063</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75 of 163</t>
+          <t>92 of 161</t>
         </is>
       </c>
     </row>
@@ -1343,45 +1343,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>G. Klassen</t>
+          <t>E. Sheehan</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>17</v>
+        <v>7.7</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4575</v>
+        <v>0.4643</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3765</v>
+        <v>0.3786</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.081</v>
+        <v>0.0857</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0147</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1.376</v>
+        <v>1.415</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.059</v>
+        <v>1.565</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.205</v>
+        <v>0.273</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.5172</v>
+        <v>0.4808</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.3704</v>
+        <v>0.275</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79 of 163</t>
+          <t>99 of 161</t>
         </is>
       </c>
     </row>
@@ -1391,45 +1391,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>B. Singer</t>
+          <t>C. Povich</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4486</v>
+        <v>0.4558</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3711</v>
+        <v>0.381</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0776</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.024</v>
+        <v>0.0278</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1.379</v>
+        <v>1.209</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.552</v>
+        <v>1.556</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.348</v>
+        <v>0.435</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.5</v>
+        <v>0.4808</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.3642</v>
+        <v>0.3563</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80 of 163</t>
+          <t>80 of 161</t>
         </is>
       </c>
     </row>
@@ -1437,47 +1437,47 @@
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Z. Thornton</t>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>H. Wesneski</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>33</v>
+        <v>22.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4468</v>
+        <v>0.4322</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0.0898</v>
+        <v>0.3596</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0.0726</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0397</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>1.386</v>
+        <v>0.0215</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>1.275</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.242</v>
+        <v>1.324</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.297</v>
+        <v>0.318</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.4828</v>
+        <v>0.4615</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.3438</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88 of 163</t>
+          <t>83 of 161</t>
         </is>
       </c>
     </row>
@@ -1485,47 +1485,47 @@
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>C. Povich</t>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>R. Stock</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9</v>
+        <v>16.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4558</v>
+        <v>0.482</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.377</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>0.1049</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.0278</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1.209</v>
+        <v>0.0128</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>1.421</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.556</v>
+        <v>1.68</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.435</v>
+        <v>0.34</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.4828</v>
+        <v>0.4615</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.3704</v>
+        <v>0.2625</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>78 of 163</t>
+          <t>103 of 161</t>
         </is>
       </c>
     </row>
@@ -1535,45 +1535,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>H. Greene</t>
+          <t>C. Prielipp</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11.3</v>
+        <v>21</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4386</v>
+        <v>0.4827</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3567</v>
+        <v>0.3671</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>0.0819</v>
+        <v>0.1156</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.046</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>1.404</v>
+        <v>1.436</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.676</v>
+        <v>1.429</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.35</v>
+        <v>0.306</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.4655</v>
+        <v>0.4231</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.321</v>
+        <v>0.2375</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>90 of 163</t>
+          <t>107 of 161</t>
         </is>
       </c>
     </row>
@@ -1583,45 +1583,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>H. Wesneski</t>
+          <t>C. Bassitt</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>22.7</v>
+        <v>11</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4322</v>
+        <v>0.44</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.3596</v>
+        <v>0.3714</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.0726</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0215</v>
+        <v>0.0227</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>1.275</v>
+        <v>1.324</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.324</v>
+        <v>1.545</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.318</v>
+        <v>0.4</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.4655</v>
+        <v>0.4231</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.358</v>
+        <v>0.3125</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82 of 163</t>
+          <t>90 of 161</t>
         </is>
       </c>
     </row>
@@ -1631,47 +1631,41 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>D. Peterson</t>
+          <t>R. Lopez</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>28.7</v>
+        <v>5.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4459</v>
+        <v>0.4432</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3739</v>
+        <v>0.375</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.0721</v>
+        <v>0.0682</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0171</v>
+        <v>0</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>1.24</v>
+        <v>0.905</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.256</v>
+        <v>1.059</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.305</v>
+        <v>0.312</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4483</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>0.3519</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>83 of 163</t>
-        </is>
-      </c>
+        <v>0.4038</v>
+      </c>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1679,45 +1673,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>C. Bassitt</t>
+          <t>J. Perkins</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.44</v>
+        <v>0.4479</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3714</v>
+        <v>0.3659</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0227</v>
+        <v>0.0575</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>1.324</v>
+        <v>1.454</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.545</v>
+        <v>1.842</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.4138</v>
+        <v>0.4038</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.3148</v>
+        <v>0.225</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>91 of 163</t>
+          <t>109 of 161</t>
         </is>
       </c>
     </row>
@@ -1758,14 +1752,14 @@
         <v>0.288</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.3966</v>
+        <v>0.3846</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.2778</v>
+        <v>0.2812</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99 of 163</t>
+          <t>97 of 161</t>
         </is>
       </c>
     </row>
@@ -1775,45 +1769,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>E. Sheehan</t>
+          <t>A. Smith-Shawver</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4532</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3786</v>
+        <v>0.3741</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.0791</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.08110000000000001</v>
+        <v>0</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>1.415</v>
+        <v>1.462</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1.565</v>
+        <v>1.615</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.273</v>
+        <v>0.346</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.3966</v>
+        <v>0.3846</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.284</v>
+        <v>0.2125</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>97 of 163</t>
+          <t>113 of 161</t>
         </is>
       </c>
     </row>
@@ -1823,45 +1817,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>J. Perkins</t>
+          <t>Z. Matthews</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>24</v>
+        <v>26.7</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4455</v>
+        <v>0.4502</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.3891</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>0.0767</v>
+        <v>0.0611</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0556</v>
+        <v>0.0367</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>1.416</v>
+        <v>1.366</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.708</v>
+        <v>1.312</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.366</v>
+        <v>0.292</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.3793</v>
+        <v>0.3654</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.2778</v>
+        <v>0.275</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>98 of 163</t>
+          <t>98 of 161</t>
         </is>
       </c>
     </row>
@@ -1871,45 +1865,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Z. Matthews</t>
+          <t>H. Dobbins</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>26.7</v>
+        <v>22.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4502</v>
+        <v>0.454</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3891</v>
+        <v>0.3955</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.0611</v>
+        <v>0.0585</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0367</v>
+        <v>0.0333</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>1.366</v>
+        <v>1.365</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1.312</v>
+        <v>1.164</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.292</v>
+        <v>0.236</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.3793</v>
+        <v>0.3462</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.2654</v>
+        <v>0.2625</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>102 of 163</t>
+          <t>102 of 161</t>
         </is>
       </c>
     </row>
@@ -1919,45 +1913,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>H. Dobbins</t>
+          <t>A. Painter</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>22.3</v>
+        <v>20.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.454</v>
+        <v>0.4526</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3955</v>
+        <v>0.3823</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.0585</v>
+        <v>0.0703</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0333</v>
+        <v>0.0357</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>1.365</v>
+        <v>1.475</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1.164</v>
+        <v>1.18</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.236</v>
+        <v>0.208</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.3621</v>
+        <v>0.3462</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.2531</v>
+        <v>0.2</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>105 of 163</t>
+          <t>115 of 161</t>
         </is>
       </c>
     </row>
@@ -1967,47 +1961,41 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>R. Stock</t>
+          <t>K. Emanuel</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>16.7</v>
+        <v>5</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.482</v>
+        <v>0.4839</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.377</v>
+        <v>0.3763</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.1049</v>
+        <v>0.1075</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>1.421</v>
+        <v>1.489</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.34</v>
+        <v>0.333</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.3621</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>0.2593</v>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>104 of 163</t>
-        </is>
-      </c>
+        <v>0.3269</v>
+      </c>
+      <c r="M31" s="8" t="n"/>
+      <c r="N31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2015,45 +2003,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>C. Prielipp</t>
+          <t>P. Sandoval</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>21</v>
+        <v>24.7</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4827</v>
+        <v>0.4466</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3671</v>
+        <v>0.3943</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.1156</v>
+        <v>0.0523</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.046</v>
+        <v>0.0172</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>1.436</v>
+        <v>1.41</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.429</v>
+        <v>1.905</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.306</v>
+        <v>0.413</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.3448</v>
+        <v>0.2885</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.2284</v>
+        <v>0.2188</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>110 of 163</t>
+          <t>110 of 161</t>
         </is>
       </c>
     </row>
@@ -2063,45 +2051,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>A. Smith-Shawver</t>
+          <t>Q. Mathews</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.4532</v>
+        <v>0.4973</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.3741</v>
+        <v>0.4</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.0791</v>
+        <v>0.0973</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>1.462</v>
+        <v>1.498</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.615</v>
+        <v>1.556</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.346</v>
+        <v>0.318</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.3276</v>
+        <v>0.2885</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.1975</v>
+        <v>0.1688</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>116 of 163</t>
+          <t>121 of 161</t>
         </is>
       </c>
     </row>
@@ -2111,41 +2099,47 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>K. Emanuel</t>
+          <t>S. Lugo</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5</v>
+        <v>34.7</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4839</v>
+        <v>0.4307</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3763</v>
+        <v>0.3833</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.1075</v>
+        <v>0.0474</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
+        <v>0.0071</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>1.489</v>
+        <v>1.284</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>1.6</v>
+        <v>1.298</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>0.333</v>
+        <v>0.315</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>0.3103</v>
-      </c>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="2" t="n"/>
+        <v>0.2692</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>119 of 161</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2153,45 +2147,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>A. Alvarez</t>
+          <t>B. Tidwell</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>17.3</v>
+        <v>15</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.444</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3665</v>
+        <v>0.388</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0.0543</v>
+        <v>0.056</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.0154</v>
+        <v>0.0169</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>1.313</v>
+        <v>1.502</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.75</v>
+        <v>1.333</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.146</v>
+        <v>0.293</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.2931</v>
+        <v>0.2692</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.216</v>
+        <v>0.1562</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>113 of 163</t>
+          <t>124 of 161</t>
         </is>
       </c>
     </row>
@@ -2201,45 +2195,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Q. Mathews</t>
+          <t>R. Vasquez</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>9</v>
+        <v>13.7</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.4973</v>
+        <v>0.4162</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3584</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0.0973</v>
+        <v>0.0578</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.0217</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>1.498</v>
+        <v>1.563</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>1.556</v>
+        <v>0.585</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.318</v>
+        <v>0.1</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.2759</v>
+        <v>0.2308</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.1728</v>
+        <v>0.1187</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>122 of 163</t>
+          <t>128 of 161</t>
         </is>
       </c>
     </row>
@@ -2249,45 +2243,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>P. Sandoval</t>
+          <t>S. Cecconi</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>24.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4466</v>
+        <v>0.4643</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.3943</v>
+        <v>0.3512</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0.0523</v>
+        <v>0.1131</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0172</v>
+        <v>0.0682</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>1.41</v>
+        <v>1.596</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>1.905</v>
+        <v>2.16</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.413</v>
+        <v>0.367</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.2586</v>
+        <v>0.1923</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.1975</v>
+        <v>0.1062</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>115 of 163</t>
+          <t>130 of 161</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2289,47 @@
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>B. Tidwell</t>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>K. Rocker</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.444</v>
+        <v>0.4184</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="G38" s="10" t="n">
-        <v>0.056</v>
+        <v>0.3995</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0.0189</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0169</v>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>1.502</v>
+        <v>0.0431</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>1.47</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>1.333</v>
+        <v>1.72</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.293</v>
+        <v>0.342</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.2586</v>
+        <v>0.1731</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.1605</v>
+        <v>0.1</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>126 of 163</t>
+          <t>133 of 161</t>
         </is>
       </c>
     </row>
@@ -2343,47 +2337,47 @@
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>L. Avila</t>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>J. Wrobleski</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>13.3</v>
+        <v>19.7</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.443</v>
+        <v>0.4986</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3904</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.3471</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0.1515</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.0167</v>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>1.535</v>
+        <v>0.1236</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>1.606</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>1.575</v>
+        <v>1.576</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.3</v>
+        <v>0.255</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.2414</v>
+        <v>0.1731</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.1296</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>128 of 163</t>
+          <t>135 of 161</t>
         </is>
       </c>
     </row>
@@ -2391,47 +2385,47 @@
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>S. Lugo</t>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>T. Sugano</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>34.7</v>
+        <v>28</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.4307</v>
+        <v>0.4084</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3833</v>
-      </c>
-      <c r="G40" s="10" t="n">
-        <v>0.0474</v>
+        <v>0.3898</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>0.0186</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0071</v>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>1.284</v>
+        <v>0.0696</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>1.359</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>1.298</v>
+        <v>1.179</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.315</v>
+        <v>0.247</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.2414</v>
+        <v>0.1538</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.1605</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>125 of 163</t>
+          <t>134 of 161</t>
         </is>
       </c>
     </row>
@@ -2439,47 +2433,47 @@
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>R. Vasquez</t>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>J. Irvin</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>13.7</v>
+        <v>19.7</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.4656</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3584</v>
-      </c>
-      <c r="G41" s="10" t="n">
-        <v>0.0578</v>
+        <v>0.3688</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.0969</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.0217</v>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>1.563</v>
+        <v>0.0602</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>1.622</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>0.585</v>
+        <v>1.373</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.1</v>
+        <v>0.236</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>0.2069</v>
+        <v>0.1538</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.1173</v>
+        <v>0.0688</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>131 of 163</t>
+          <t>143 of 161</t>
         </is>
       </c>
     </row>
@@ -2489,45 +2483,45 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>L. Roupp</t>
+          <t>M. Mikolas</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>25.3</v>
+        <v>15</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.459</v>
+        <v>0.3827</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3888</v>
+        <v>0.3704</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.0703</v>
+        <v>0.0123</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0286</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.564</v>
+        <v>1.59</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>1.421</v>
+        <v>1.867</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>0.277</v>
+        <v>0.351</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>0.1897</v>
+        <v>0.1346</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.1111</v>
+        <v>0.075</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>132 of 163</t>
+          <t>141 of 161</t>
         </is>
       </c>
     </row>
@@ -2537,45 +2531,45 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>R. Lopez</t>
+          <t>C. Whisenhunt</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>10</v>
+        <v>21.3</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.4335</v>
+        <v>0.4323</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.3931</v>
+        <v>0.3932</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.0405</v>
+        <v>0.0391</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.0435</v>
+        <v>0.0377</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1.261</v>
+        <v>1.659</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1.8</v>
+        <v>2.062</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.429</v>
+        <v>0.366</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>0.1724</v>
+        <v>0.1346</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.1235</v>
+        <v>0.0563</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>129 of 163</t>
+          <t>146 of 161</t>
         </is>
       </c>
     </row>
@@ -2585,45 +2579,45 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>B. Sproat</t>
+          <t>M. Bratt</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>13.7</v>
+        <v>26</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.451</v>
+        <v>0.4407</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.4078</v>
+        <v>0.3995</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.0431</v>
+        <v>0.0412</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.0312</v>
+        <v>0.0196</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1.578</v>
+        <v>1.665</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1.756</v>
+        <v>1.346</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>0.325</v>
+        <v>0.258</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>0.1724</v>
+        <v>0.1154</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.1049</v>
+        <v>0.0437</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>133 of 163</t>
+          <t>149 of 161</t>
         </is>
       </c>
     </row>
@@ -2633,45 +2627,45 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>K. Rocker</t>
+          <t>K. Drake</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>31</v>
+        <v>11.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4297</v>
+        <v>0.4254</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3896</v>
+        <v>0.4167</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.0402</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.0365</v>
+        <v>0.0577</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>1.41</v>
+        <v>1.506</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>1.484</v>
+        <v>1.714</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.303</v>
+        <v>0.351</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>0.1552</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.1173</v>
+        <v>0.0563</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>130 of 163</t>
+          <t>145 of 161</t>
         </is>
       </c>
     </row>
@@ -2681,45 +2675,45 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>S. Cecconi</t>
+          <t>C. Mlodzinski</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4643</v>
+        <v>0.4148</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.3512</v>
+        <v>0.3693</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.1131</v>
+        <v>0.0455</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0682</v>
+        <v>0.0426</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.596</v>
+        <v>1.684</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>0.367</v>
+        <v>0.514</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>0.1379</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.0864</v>
+        <v>0.0375</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>137 of 163</t>
+          <t>152 of 161</t>
         </is>
       </c>
     </row>
@@ -2729,45 +2723,45 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>T. Sugano</t>
+          <t>R. Johnson</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>5</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.4084</v>
+        <v>0.4209</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.3898</v>
+        <v>0.4107</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.0186</v>
+        <v>0.0102</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.0696</v>
+        <v>0.0606</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>1.359</v>
+        <v>1.717</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1.179</v>
+        <v>1.727</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.247</v>
+        <v>0.302</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>0.1207</v>
+        <v>0.0769</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.0679</v>
+        <v>0.0312</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>143 of 163</t>
+          <t>154 of 161</t>
         </is>
       </c>
     </row>
@@ -2777,45 +2771,45 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>J. Irvin</t>
+          <t>B. Sproat</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>19.7</v>
+        <v>9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.4656</v>
+        <v>0.4241</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.3688</v>
+        <v>0.4177</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.0969</v>
+        <v>0.0063</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0602</v>
+        <v>0.0233</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>1.622</v>
+        <v>1.427</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>1.373</v>
+        <v>1.778</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0.236</v>
+        <v>0.357</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.1207</v>
+        <v>0.0769</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0617</v>
+        <v>0.05</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>146 of 163</t>
+          <t>148 of 161</t>
         </is>
       </c>
     </row>
@@ -2825,45 +2819,45 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>M. Mikolas</t>
+          <t>R. Blanco</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.3827</v>
+        <v>0.4538</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3739</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.0798</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>1.59</v>
+        <v>1.814</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>1.867</v>
+        <v>1.432</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.351</v>
+        <v>0.243</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.1034</v>
+        <v>0.0577</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.0617</v>
+        <v>0.0187</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>145 of 163</t>
+          <t>157 of 161</t>
         </is>
       </c>
     </row>
@@ -2873,45 +2867,45 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>C. Whisenhunt</t>
+          <t>E. Fedde</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>21.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.4323</v>
+        <v>0.4091</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.3932</v>
+        <v>0.4156</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.0391</v>
+        <v>-0.0065</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.0377</v>
+        <v>0.1111</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>1.659</v>
+        <v>1.34</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>2.062</v>
+        <v>1.071</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>0.366</v>
+        <v>0.217</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>0.1034</v>
+        <v>0.0577</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.0432</v>
+        <v>0.0437</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>151 of 163</t>
+          <t>150 of 161</t>
         </is>
       </c>
     </row>
@@ -2921,45 +2915,45 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>M. Bratt</t>
+          <t>M. Keller</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>26</v>
+        <v>12.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.4407</v>
+        <v>0.4091</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.3995</v>
+        <v>0.4182</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.0412</v>
+        <v>-0.0091</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.0196</v>
+        <v>0.0345</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1.665</v>
+        <v>1.494</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>1.346</v>
+        <v>1.784</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.258</v>
+        <v>0.351</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0.0862</v>
+        <v>0.0385</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.037</v>
+        <v>0.0312</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>152 of 163</t>
+          <t>153 of 161</t>
         </is>
       </c>
     </row>
@@ -2969,45 +2963,45 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>E. Fedde</t>
+          <t>M. Lorenzen</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>15</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.4337</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.4156</v>
+        <v>0.4036</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>-0.0065</v>
+        <v>0.0301</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.0385</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1.34</v>
+        <v>1.886</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>1.071</v>
+        <v>2.467</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>0.217</v>
+        <v>0.393</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0385</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0.0432</v>
+        <v>0.0125</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>150 of 163</t>
+          <t>158 of 161</t>
         </is>
       </c>
     </row>
@@ -3017,45 +3011,45 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>C. Mlodzinski</t>
+          <t>L. Avila</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.4148</v>
+        <v>0.3904</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.3693</v>
+        <v>0.4452</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.0455</v>
+        <v>-0.0548</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.0426</v>
+        <v>0.0278</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>1.684</v>
+        <v>2.005</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>3</v>
+        <v>2.143</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.514</v>
+        <v>0.292</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>0.0309</v>
+        <v>0</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>155 of 163</t>
+          <t>160 of 161</t>
         </is>
       </c>
     </row>
@@ -3065,401 +3059,113 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>M. Keller</t>
+          <t>J. Springs</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.4091</v>
+        <v>0.3842</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.4182</v>
+        <v>0.4286</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>-0.0091</v>
+        <v>-0.0443</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0364</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>1.494</v>
+        <v>2.027</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>1.784</v>
+        <v>2</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>0.351</v>
+        <v>0.268</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>0.0517</v>
+        <v>0</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>0.0309</v>
+        <v>0</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>154 of 163</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>R. Johnson</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>0.4209</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>0.4107</v>
-      </c>
-      <c r="G55" s="13" t="n">
-        <v>0.0102</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>0.0606</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>1.717</v>
-      </c>
-      <c r="J55" s="7" t="n">
-        <v>1.727</v>
-      </c>
-      <c r="K55" s="7" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="L55" s="8" t="n">
-        <v>0.0517</v>
-      </c>
-      <c r="M55" s="8" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>157 of 163</t>
+          <t>161 of 161</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>M. Lorenzen</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>0.4477</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>0.3917</v>
-      </c>
-      <c r="G56" s="13" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>1.778</v>
-      </c>
-      <c r="J56" s="7" t="n">
-        <v>2.411</v>
-      </c>
-      <c r="K56" s="7" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="L56" s="8" t="n">
-        <v>0.0345</v>
-      </c>
-      <c r="M56" s="8" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>159 of 163</t>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>K. Drake</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>0.4263</v>
-      </c>
-      <c r="G57" s="13" t="n">
-        <v>-0.009599999999999999</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>0.0411</v>
-      </c>
-      <c r="I57" s="14" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="J57" s="7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="K57" s="7" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="L57" s="8" t="n">
-        <v>0.0345</v>
-      </c>
-      <c r="M57" s="8" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>156 of 163</t>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>R. Blanco</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>0.4538</v>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>0.3739</v>
-      </c>
-      <c r="G58" s="13" t="n">
-        <v>0.0798</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>1.814</v>
-      </c>
-      <c r="J58" s="7" t="n">
-        <v>1.432</v>
-      </c>
-      <c r="K58" s="7" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="L58" s="8" t="n">
-        <v>0.0172</v>
-      </c>
-      <c r="M58" s="8" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>161 of 163</t>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>C. Holmes</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>0.3911</v>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>0.4089</v>
-      </c>
-      <c r="G59" s="13" t="n">
-        <v>-0.0178</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>0.0167</v>
-      </c>
-      <c r="I59" s="14" t="n">
-        <v>1.536</v>
-      </c>
-      <c r="J59" s="7" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="K59" s="7" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="L59" s="8" t="n">
-        <v>0.0172</v>
-      </c>
-      <c r="M59" s="8" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>160 of 163</t>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>J. Springs</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>0.3842</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>0.4286</v>
-      </c>
-      <c r="G60" s="13" t="n">
-        <v>-0.0443</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>0.0364</v>
-      </c>
-      <c r="I60" s="14" t="n">
-        <v>2.027</v>
-      </c>
-      <c r="J60" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K60" s="7" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="L60" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>163 of 163</t>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Column key: m_whip = Model WHIP, rl_whip = Actual (real) WHIP, rel_score = Score (Relative), abs_score = Score (Absolute), abs_rank = Rank (Absolute). Renamed for column width, same formulas as always.</t>
+          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Stoplight shading (Pitcher, CMD%, m_whip) reflects rel_score: MIN of each pitcher's percentile rank on CMD% (higher=better) and m_whip (lower=better) within this free-agent-only pool -- a pitcher must be strong on BOTH to score green. Green = top third, yellow = middle third, red = bottom third, by rel_score rank position.</t>
+          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>abs_score uses the same min-of-two-percentiles formula but computed against the league-wide qualifying pool (all qualifying rostered pitchers across all 12 teams, plus free agents; 2+ starts and 5+ IP in the trailing 30-day window). abs_rank shows literal rank position within that league-wide pool.</t>
+          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>'Starts' are restricted to genuine starting pitchers: first-listed in the box score AND a season-wide average of 4.0+ IP when first-listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>Pure% and Ball% are each that pitch type's share of total pitches thrown (balls + pure strikes + in-play pitches), not batters faced. CMD% = Pure% - Ball%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>K%, BB%, HR% (m_whip inputs) are correctly denominated by batters faced (BF) -- separate, correct usage from Pure%/Ball%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>BABIP approximated as (H-HR)/(BF-BB-K-HR); HBP and sac flies aren't broken out in the source gamelogs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t>m_whip = 1.290 - 2.208*K% + 4.402*BB% + 3.766*HR%, cross-validated regression, CV R^2 = 0.58. rl_whip is real (H+BB)/IP over the same window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>Free agent status computed as of the roster snapshot date plus any subsequent add/drop/trade transactions in the file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>FA leaderboard inclusion floor is 1+ start (and 5+ IP) in the trailing 30-day window -- single-start genuine starters are included here. The league-wide absolute pool behind abs_score/abs_rank still requires 2+ starts, so a 1-start pitcher can appear here with a rel_score but a blank abs_score/abs_rank.</t>
         </is>
